--- a/artfynd/A 30047-2025 artfynd.xlsx
+++ b/artfynd/A 30047-2025 artfynd.xlsx
@@ -11720,32 +11720,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128423089</v>
+        <v>128423193</v>
       </c>
       <c r="B111" t="n">
-        <v>91325</v>
+        <v>88761</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11755,10 +11755,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>635295</v>
+        <v>634638</v>
       </c>
       <c r="R111" t="n">
-        <v>7087129</v>
+        <v>7087656</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11817,10 +11817,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128423116</v>
+        <v>128423626</v>
       </c>
       <c r="B112" t="n">
-        <v>57673</v>
+        <v>88761</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11828,21 +11828,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11852,10 +11852,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>635330</v>
+        <v>634705</v>
       </c>
       <c r="R112" t="n">
-        <v>7087114</v>
+        <v>7087668</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11890,11 +11890,6 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
@@ -11907,12 +11902,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -12128,32 +12123,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128423193</v>
+        <v>128423089</v>
       </c>
       <c r="B115" t="n">
-        <v>88761</v>
+        <v>91325</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12163,10 +12158,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>634638</v>
+        <v>635295</v>
       </c>
       <c r="R115" t="n">
-        <v>7087656</v>
+        <v>7087129</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12225,10 +12220,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128423626</v>
+        <v>128423136</v>
       </c>
       <c r="B116" t="n">
-        <v>88761</v>
+        <v>80135</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12236,21 +12231,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12260,10 +12255,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>634705</v>
+        <v>635422</v>
       </c>
       <c r="R116" t="n">
-        <v>7087668</v>
+        <v>7087149</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12310,22 +12305,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128423136</v>
+        <v>128410776</v>
       </c>
       <c r="B117" t="n">
-        <v>80135</v>
+        <v>79032</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12333,34 +12328,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>635422</v>
+        <v>634709</v>
       </c>
       <c r="R117" t="n">
-        <v>7087149</v>
+        <v>7087670</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12390,9 +12385,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12407,39 +12412,39 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128410776</v>
+        <v>128423195</v>
       </c>
       <c r="B118" t="n">
-        <v>79032</v>
+        <v>80170</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -12450,14 +12455,14 @@
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>634709</v>
+        <v>635228</v>
       </c>
       <c r="R118" t="n">
-        <v>7087670</v>
+        <v>7087058</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12487,19 +12492,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>14:41</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>14:41</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12514,39 +12509,39 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128423195</v>
+        <v>128423154</v>
       </c>
       <c r="B119" t="n">
-        <v>80170</v>
+        <v>79032</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -12561,10 +12556,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>635228</v>
+        <v>635479</v>
       </c>
       <c r="R119" t="n">
-        <v>7087058</v>
+        <v>7087148</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12623,10 +12618,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128423154</v>
+        <v>128423116</v>
       </c>
       <c r="B120" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12634,21 +12629,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12658,10 +12653,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>635479</v>
+        <v>635330</v>
       </c>
       <c r="R120" t="n">
-        <v>7087148</v>
+        <v>7087114</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12694,6 +12689,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14323,32 +14323,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128423578</v>
+        <v>128423096</v>
       </c>
       <c r="B137" t="n">
-        <v>91325</v>
+        <v>91360</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14358,10 +14358,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>635327</v>
+        <v>635249</v>
       </c>
       <c r="R137" t="n">
-        <v>7087158</v>
+        <v>7087032</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14408,19 +14408,19 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128423096</v>
+        <v>128423098</v>
       </c>
       <c r="B138" t="n">
         <v>91360</v>
@@ -14455,10 +14455,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>635249</v>
+        <v>635186</v>
       </c>
       <c r="R138" t="n">
-        <v>7087032</v>
+        <v>7087317</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14517,10 +14517,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128423098</v>
+        <v>128423157</v>
       </c>
       <c r="B139" t="n">
-        <v>91360</v>
+        <v>79032</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14528,21 +14528,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14552,10 +14552,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>635186</v>
+        <v>635204</v>
       </c>
       <c r="R139" t="n">
-        <v>7087317</v>
+        <v>7087134</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14614,32 +14614,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128423167</v>
+        <v>128423139</v>
       </c>
       <c r="B140" t="n">
-        <v>79032</v>
+        <v>80171</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14649,10 +14649,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>634719</v>
+        <v>635237</v>
       </c>
       <c r="R140" t="n">
-        <v>7087623</v>
+        <v>7087043</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14711,10 +14711,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128423128</v>
+        <v>128423194</v>
       </c>
       <c r="B141" t="n">
-        <v>80163</v>
+        <v>80170</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14722,21 +14722,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6461</v>
+        <v>6463</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14746,10 +14746,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>634915</v>
+        <v>635234</v>
       </c>
       <c r="R141" t="n">
-        <v>7087322</v>
+        <v>7087032</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14808,10 +14808,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128423607</v>
+        <v>128404427</v>
       </c>
       <c r="B142" t="n">
-        <v>80135</v>
+        <v>79032</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14819,34 +14819,39 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>635459</v>
+        <v>635552</v>
       </c>
       <c r="R142" t="n">
-        <v>7087231</v>
+        <v>7087334</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14876,9 +14881,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -14893,22 +14908,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128423157</v>
+        <v>128423602</v>
       </c>
       <c r="B143" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14916,21 +14931,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14940,10 +14955,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>635204</v>
+        <v>635210</v>
       </c>
       <c r="R143" t="n">
-        <v>7087134</v>
+        <v>7087158</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14978,6 +14993,11 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD143" t="b">
         <v>0</v>
       </c>
@@ -14990,22 +15010,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128423187</v>
+        <v>128413141</v>
       </c>
       <c r="B144" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15013,34 +15033,42 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>635591</v>
+        <v>634574</v>
       </c>
       <c r="R144" t="n">
-        <v>7087249</v>
+        <v>7087273</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15070,9 +15098,24 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15087,44 +15130,44 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128423177</v>
+        <v>128423578</v>
       </c>
       <c r="B145" t="n">
-        <v>79032</v>
+        <v>91325</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15134,10 +15177,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>635285</v>
+        <v>635327</v>
       </c>
       <c r="R145" t="n">
-        <v>7087169</v>
+        <v>7087158</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15184,44 +15227,44 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128423139</v>
+        <v>128423167</v>
       </c>
       <c r="B146" t="n">
-        <v>80171</v>
+        <v>79032</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15231,10 +15274,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>635237</v>
+        <v>634719</v>
       </c>
       <c r="R146" t="n">
-        <v>7087043</v>
+        <v>7087623</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15293,10 +15336,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128423194</v>
+        <v>128423128</v>
       </c>
       <c r="B147" t="n">
-        <v>80170</v>
+        <v>80163</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15304,21 +15347,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6463</v>
+        <v>6461</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15328,10 +15371,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>635234</v>
+        <v>634915</v>
       </c>
       <c r="R147" t="n">
-        <v>7087032</v>
+        <v>7087322</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15390,10 +15433,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128404427</v>
+        <v>128423607</v>
       </c>
       <c r="B148" t="n">
-        <v>79032</v>
+        <v>80135</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15401,39 +15444,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>635552</v>
+        <v>635459</v>
       </c>
       <c r="R148" t="n">
-        <v>7087334</v>
+        <v>7087231</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15463,19 +15501,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>10:33</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15490,22 +15518,22 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128423602</v>
+        <v>128423187</v>
       </c>
       <c r="B149" t="n">
-        <v>57673</v>
+        <v>79032</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15513,21 +15541,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15537,10 +15565,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>635210</v>
+        <v>635591</v>
       </c>
       <c r="R149" t="n">
-        <v>7087158</v>
+        <v>7087249</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15575,11 +15603,6 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
@@ -15592,22 +15615,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128413141</v>
+        <v>128423177</v>
       </c>
       <c r="B150" t="n">
-        <v>57673</v>
+        <v>79032</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15615,42 +15638,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>634574</v>
+        <v>635285</v>
       </c>
       <c r="R150" t="n">
-        <v>7087273</v>
+        <v>7087169</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15680,24 +15695,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15712,12 +15712,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
@@ -16753,10 +16753,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128423113</v>
+        <v>128423101</v>
       </c>
       <c r="B161" t="n">
-        <v>80136</v>
+        <v>57833</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16764,21 +16764,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16788,10 +16788,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>635240</v>
+        <v>634716</v>
       </c>
       <c r="R161" t="n">
-        <v>7087040</v>
+        <v>7087613</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16850,32 +16850,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128423090</v>
+        <v>128423191</v>
       </c>
       <c r="B162" t="n">
-        <v>91325</v>
+        <v>88761</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16885,10 +16885,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>635155</v>
+        <v>634676</v>
       </c>
       <c r="R162" t="n">
-        <v>7087185</v>
+        <v>7087233</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17044,10 +17044,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128423191</v>
+        <v>128423113</v>
       </c>
       <c r="B164" t="n">
-        <v>88761</v>
+        <v>80136</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17055,21 +17055,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>510</v>
+        <v>2081</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17079,10 +17079,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>634676</v>
+        <v>635240</v>
       </c>
       <c r="R164" t="n">
-        <v>7087233</v>
+        <v>7087040</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17141,32 +17141,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128423185</v>
+        <v>128423090</v>
       </c>
       <c r="B165" t="n">
-        <v>79032</v>
+        <v>91325</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17176,10 +17176,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>635559</v>
+        <v>635155</v>
       </c>
       <c r="R165" t="n">
-        <v>7087269</v>
+        <v>7087185</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17238,32 +17238,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128423126</v>
+        <v>128423185</v>
       </c>
       <c r="B166" t="n">
-        <v>79056</v>
+        <v>79032</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17273,10 +17273,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>635212</v>
+        <v>635559</v>
       </c>
       <c r="R166" t="n">
-        <v>7087212</v>
+        <v>7087269</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17335,32 +17335,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128423101</v>
+        <v>128423126</v>
       </c>
       <c r="B167" t="n">
-        <v>57833</v>
+        <v>79056</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>103021</v>
+        <v>6434</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17370,10 +17370,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>634716</v>
+        <v>635212</v>
       </c>
       <c r="R167" t="n">
-        <v>7087613</v>
+        <v>7087212</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17432,32 +17432,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128423576</v>
+        <v>128423614</v>
       </c>
       <c r="B168" t="n">
-        <v>91325</v>
+        <v>91374</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17467,10 +17467,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>634705</v>
+        <v>634673</v>
       </c>
       <c r="R168" t="n">
-        <v>7087668</v>
+        <v>7087631</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17529,10 +17529,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128423181</v>
+        <v>128423147</v>
       </c>
       <c r="B169" t="n">
-        <v>79032</v>
+        <v>91374</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17540,21 +17540,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17564,10 +17564,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>635471</v>
+        <v>634571</v>
       </c>
       <c r="R169" t="n">
-        <v>7087243</v>
+        <v>7087288</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17626,10 +17626,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128423614</v>
+        <v>128412855</v>
       </c>
       <c r="B170" t="n">
-        <v>91374</v>
+        <v>91656</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17637,34 +17637,34 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>634673</v>
+        <v>634574</v>
       </c>
       <c r="R170" t="n">
-        <v>7087631</v>
+        <v>7087273</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17694,9 +17694,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -17711,22 +17721,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128423147</v>
+        <v>128404367</v>
       </c>
       <c r="B171" t="n">
-        <v>91374</v>
+        <v>79032</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17734,34 +17744,41 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>634571</v>
+        <v>635556</v>
       </c>
       <c r="R171" t="n">
-        <v>7087288</v>
+        <v>7087281</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17791,39 +17808,50 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AD171" t="b">
         <v>0</v>
       </c>
       <c r="AE171" t="b">
         <v>0</v>
       </c>
+      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128412855</v>
+        <v>128423161</v>
       </c>
       <c r="B172" t="n">
-        <v>91656</v>
+        <v>79032</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17831,34 +17859,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>634574</v>
+        <v>634702</v>
       </c>
       <c r="R172" t="n">
-        <v>7087273</v>
+        <v>7087248</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17888,19 +17916,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>16:03</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -17915,19 +17933,19 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128404367</v>
+        <v>128423181</v>
       </c>
       <c r="B173" t="n">
         <v>79032</v>
@@ -17956,23 +17974,16 @@
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>635556</v>
+        <v>635471</v>
       </c>
       <c r="R173" t="n">
-        <v>7087281</v>
+        <v>7087243</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18002,72 +18013,61 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AD173" t="b">
         <v>0</v>
       </c>
       <c r="AE173" t="b">
         <v>0</v>
       </c>
-      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128423161</v>
+        <v>128423576</v>
       </c>
       <c r="B174" t="n">
-        <v>79032</v>
+        <v>91325</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18077,10 +18077,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>634702</v>
+        <v>634705</v>
       </c>
       <c r="R174" t="n">
-        <v>7087248</v>
+        <v>7087668</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18127,12 +18127,12 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
@@ -19954,10 +19954,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128423590</v>
+        <v>128423588</v>
       </c>
       <c r="B193" t="n">
-        <v>92642</v>
+        <v>57833</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19965,21 +19965,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4361</v>
+        <v>103021</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19989,10 +19989,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>635182</v>
+        <v>634560</v>
       </c>
       <c r="R193" t="n">
-        <v>7087227</v>
+        <v>7087311</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20051,10 +20051,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128423596</v>
+        <v>128423590</v>
       </c>
       <c r="B194" t="n">
-        <v>57670</v>
+        <v>92642</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20062,21 +20062,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>100049</v>
+        <v>4361</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20086,10 +20086,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>634648</v>
+        <v>635182</v>
       </c>
       <c r="R194" t="n">
-        <v>7087590</v>
+        <v>7087227</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20148,10 +20148,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128423172</v>
+        <v>128423596</v>
       </c>
       <c r="B195" t="n">
-        <v>79032</v>
+        <v>57670</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20159,21 +20159,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20183,10 +20183,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>635010</v>
+        <v>634648</v>
       </c>
       <c r="R195" t="n">
-        <v>7087362</v>
+        <v>7087590</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20233,44 +20233,44 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>128423138</v>
+        <v>128423172</v>
       </c>
       <c r="B196" t="n">
-        <v>80171</v>
+        <v>79032</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20280,10 +20280,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>635160</v>
+        <v>635010</v>
       </c>
       <c r="R196" t="n">
-        <v>7087012</v>
+        <v>7087362</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20342,32 +20342,32 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>128423168</v>
+        <v>128423138</v>
       </c>
       <c r="B197" t="n">
-        <v>79032</v>
+        <v>80171</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20377,10 +20377,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>634865</v>
+        <v>635160</v>
       </c>
       <c r="R197" t="n">
-        <v>7087586</v>
+        <v>7087012</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20439,32 +20439,32 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>128423109</v>
+        <v>128423168</v>
       </c>
       <c r="B198" t="n">
-        <v>80164</v>
+        <v>79032</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -20474,10 +20474,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>635407</v>
+        <v>634865</v>
       </c>
       <c r="R198" t="n">
-        <v>7087128</v>
+        <v>7087586</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20536,32 +20536,32 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>128423160</v>
+        <v>128423109</v>
       </c>
       <c r="B199" t="n">
-        <v>79032</v>
+        <v>80164</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -20571,10 +20571,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>634916</v>
+        <v>635407</v>
       </c>
       <c r="R199" t="n">
-        <v>7087311</v>
+        <v>7087128</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20633,10 +20633,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>128423135</v>
+        <v>128423160</v>
       </c>
       <c r="B200" t="n">
-        <v>80135</v>
+        <v>79032</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20644,21 +20644,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20668,10 +20668,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>635412</v>
+        <v>634916</v>
       </c>
       <c r="R200" t="n">
-        <v>7087118</v>
+        <v>7087311</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20730,10 +20730,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>128423118</v>
+        <v>128423135</v>
       </c>
       <c r="B201" t="n">
-        <v>57673</v>
+        <v>80135</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20741,21 +20741,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20765,10 +20765,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>634924</v>
+        <v>635412</v>
       </c>
       <c r="R201" t="n">
-        <v>7087288</v>
+        <v>7087118</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20803,11 +20803,6 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD201" t="b">
         <v>0</v>
       </c>
@@ -20816,21 +20811,6 @@
       </c>
       <c r="AG201" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ201" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK201" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO201" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
@@ -20847,10 +20827,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>128423588</v>
+        <v>128423118</v>
       </c>
       <c r="B202" t="n">
-        <v>57833</v>
+        <v>57673</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20858,21 +20838,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -20882,10 +20862,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>634560</v>
+        <v>634924</v>
       </c>
       <c r="R202" t="n">
-        <v>7087311</v>
+        <v>7087288</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20920,6 +20900,11 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD202" t="b">
         <v>0</v>
       </c>
@@ -20928,48 +20913,63 @@
       </c>
       <c r="AG202" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO202" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>128423132</v>
+        <v>128423580</v>
       </c>
       <c r="B203" t="n">
-        <v>80135</v>
+        <v>91325</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -20979,10 +20979,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>635159</v>
+        <v>635478</v>
       </c>
       <c r="R203" t="n">
-        <v>7087014</v>
+        <v>7087280</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21029,57 +21029,57 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>128406204</v>
+        <v>128423579</v>
       </c>
       <c r="B204" t="n">
-        <v>80135</v>
+        <v>91325</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>635335</v>
+        <v>635424</v>
       </c>
       <c r="R204" t="n">
-        <v>7087214</v>
+        <v>7087198</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21109,19 +21109,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z204" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>11:43</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -21136,22 +21126,22 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>128423156</v>
+        <v>128423151</v>
       </c>
       <c r="B205" t="n">
-        <v>79032</v>
+        <v>91378</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -21159,21 +21149,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -21183,10 +21173,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>635300</v>
+        <v>634546</v>
       </c>
       <c r="R205" t="n">
-        <v>7087123</v>
+        <v>7087320</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21245,32 +21235,32 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>128423580</v>
+        <v>128423132</v>
       </c>
       <c r="B206" t="n">
-        <v>91325</v>
+        <v>80135</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -21280,10 +21270,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>635478</v>
+        <v>635159</v>
       </c>
       <c r="R206" t="n">
-        <v>7087280</v>
+        <v>7087014</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21330,57 +21320,57 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>128423579</v>
+        <v>128406204</v>
       </c>
       <c r="B207" t="n">
-        <v>91325</v>
+        <v>80135</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>635424</v>
+        <v>635335</v>
       </c>
       <c r="R207" t="n">
-        <v>7087198</v>
+        <v>7087214</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21410,9 +21400,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -21427,22 +21427,22 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>128423151</v>
+        <v>128423156</v>
       </c>
       <c r="B208" t="n">
-        <v>91378</v>
+        <v>79032</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -21450,21 +21450,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -21474,10 +21474,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>634546</v>
+        <v>635300</v>
       </c>
       <c r="R208" t="n">
-        <v>7087320</v>
+        <v>7087123</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21638,7 +21638,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128423171</v>
+        <v>128423188</v>
       </c>
       <c r="B210" t="n">
         <v>79032</v>
@@ -21673,10 +21673,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>634973</v>
+        <v>635610</v>
       </c>
       <c r="R210" t="n">
-        <v>7087410</v>
+        <v>7087261</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21735,32 +21735,32 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>128423595</v>
+        <v>128423170</v>
       </c>
       <c r="B211" t="n">
-        <v>80164</v>
+        <v>79032</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -21770,10 +21770,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>635632</v>
+        <v>634897</v>
       </c>
       <c r="R211" t="n">
-        <v>7087270</v>
+        <v>7087496</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21820,61 +21820,57 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>128423199</v>
+        <v>128423595</v>
       </c>
       <c r="B212" t="n">
-        <v>57673</v>
+        <v>80164</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
-      <c r="K212" t="inlineStr"/>
-      <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr"/>
-      <c r="N212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>635298</v>
+        <v>635632</v>
       </c>
       <c r="R212" t="n">
-        <v>7087096</v>
+        <v>7087270</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21909,11 +21905,6 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD212" t="b">
         <v>0</v>
       </c>
@@ -21926,19 +21917,19 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>128423121</v>
+        <v>128423199</v>
       </c>
       <c r="B213" t="n">
         <v>57673</v>
@@ -21967,16 +21958,20 @@
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>635167</v>
+        <v>635298</v>
       </c>
       <c r="R213" t="n">
-        <v>7087269</v>
+        <v>7087096</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22040,10 +22035,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>128423188</v>
+        <v>128423121</v>
       </c>
       <c r="B214" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -22051,21 +22046,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -22075,10 +22070,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>635610</v>
+        <v>635167</v>
       </c>
       <c r="R214" t="n">
-        <v>7087261</v>
+        <v>7087269</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22111,6 +22106,11 @@
       <c r="AA214" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -22137,7 +22137,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>128423170</v>
+        <v>128423171</v>
       </c>
       <c r="B215" t="n">
         <v>79032</v>
@@ -22172,10 +22172,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>634897</v>
+        <v>634973</v>
       </c>
       <c r="R215" t="n">
-        <v>7087496</v>
+        <v>7087410</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22234,32 +22234,32 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>128423094</v>
+        <v>128423601</v>
       </c>
       <c r="B216" t="n">
-        <v>91325</v>
+        <v>91656</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -22269,10 +22269,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>635358</v>
+        <v>634475</v>
       </c>
       <c r="R216" t="n">
-        <v>7087128</v>
+        <v>7087365</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22319,44 +22319,44 @@
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>128423574</v>
+        <v>128423183</v>
       </c>
       <c r="B217" t="n">
-        <v>91325</v>
+        <v>79032</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -22366,10 +22366,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>634571</v>
+        <v>635482</v>
       </c>
       <c r="R217" t="n">
-        <v>7087253</v>
+        <v>7087300</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22416,22 +22416,22 @@
       <c r="AT217" t="inlineStr"/>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>128423601</v>
+        <v>128423130</v>
       </c>
       <c r="B218" t="n">
-        <v>91656</v>
+        <v>80135</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -22439,21 +22439,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -22463,10 +22463,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>634475</v>
+        <v>635267</v>
       </c>
       <c r="R218" t="n">
-        <v>7087365</v>
+        <v>7087054</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -22510,47 +22510,62 @@
       <c r="AG218" t="b">
         <v>0</v>
       </c>
+      <c r="AJ218" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK218" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO218" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>128423183</v>
+        <v>128423094</v>
       </c>
       <c r="B219" t="n">
-        <v>79032</v>
+        <v>91325</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -22560,10 +22575,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>635482</v>
+        <v>635358</v>
       </c>
       <c r="R219" t="n">
-        <v>7087300</v>
+        <v>7087128</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22622,32 +22637,32 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>128423130</v>
+        <v>128423574</v>
       </c>
       <c r="B220" t="n">
-        <v>80135</v>
+        <v>91325</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -22657,10 +22672,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>635267</v>
+        <v>634571</v>
       </c>
       <c r="R220" t="n">
-        <v>7087054</v>
+        <v>7087253</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22704,30 +22719,15 @@
       <c r="AG220" t="b">
         <v>0</v>
       </c>
-      <c r="AJ220" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK220" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO220" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
@@ -26096,10 +26096,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>128428569</v>
+        <v>128428583</v>
       </c>
       <c r="B255" t="n">
-        <v>91378</v>
+        <v>82873</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -26107,21 +26107,21 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -26131,10 +26131,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>635359</v>
+        <v>634880</v>
       </c>
       <c r="R255" t="n">
-        <v>7087150</v>
+        <v>7087375</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26193,10 +26193,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>128428583</v>
+        <v>128428569</v>
       </c>
       <c r="B256" t="n">
-        <v>82873</v>
+        <v>91378</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -26204,21 +26204,21 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -26228,10 +26228,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>634880</v>
+        <v>635359</v>
       </c>
       <c r="R256" t="n">
-        <v>7087375</v>
+        <v>7087150</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -27370,10 +27370,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>128428567</v>
+        <v>128428565</v>
       </c>
       <c r="B268" t="n">
-        <v>75139</v>
+        <v>58043</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -27381,34 +27381,46 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6439</v>
+        <v>103015</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I268" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr"/>
+      <c r="L268" t="inlineStr"/>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>635532</v>
+        <v>635275</v>
       </c>
       <c r="R268" t="n">
-        <v>7087324</v>
+        <v>7087098</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -27467,32 +27479,32 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>128428561</v>
+        <v>128428541</v>
       </c>
       <c r="B269" t="n">
-        <v>80171</v>
+        <v>57833</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -27502,10 +27514,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>634879</v>
+        <v>635537</v>
       </c>
       <c r="R269" t="n">
-        <v>7087368</v>
+        <v>7087207</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -27564,32 +27576,32 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>128428541</v>
+        <v>128428567</v>
       </c>
       <c r="B270" t="n">
-        <v>57833</v>
+        <v>75139</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>103021</v>
+        <v>6439</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
@@ -27599,10 +27611,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>635537</v>
+        <v>635532</v>
       </c>
       <c r="R270" t="n">
-        <v>7087207</v>
+        <v>7087324</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -27661,10 +27673,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>128428565</v>
+        <v>128428561</v>
       </c>
       <c r="B271" t="n">
-        <v>58043</v>
+        <v>80171</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -27672,46 +27684,34 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>103015</v>
+        <v>6464</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I271" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K271" t="inlineStr"/>
-      <c r="L271" t="inlineStr"/>
-      <c r="M271" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N271" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>635275</v>
+        <v>634879</v>
       </c>
       <c r="R271" t="n">
-        <v>7087098</v>
+        <v>7087368</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -28158,45 +28158,53 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>128428562</v>
+        <v>128428550</v>
       </c>
       <c r="B276" t="n">
-        <v>80171</v>
+        <v>57670</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr"/>
       <c r="P276" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>635398</v>
+        <v>634487</v>
       </c>
       <c r="R276" t="n">
-        <v>7087183</v>
+        <v>7087401</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -28255,7 +28263,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>128428550</v>
+        <v>128428552</v>
       </c>
       <c r="B277" t="n">
         <v>57670</v>
@@ -28298,10 +28306,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>634487</v>
+        <v>635170</v>
       </c>
       <c r="R277" t="n">
-        <v>7087401</v>
+        <v>7087231</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -28360,53 +28368,45 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>128428552</v>
+        <v>128428562</v>
       </c>
       <c r="B278" t="n">
-        <v>57670</v>
+        <v>80171</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>635170</v>
+        <v>635398</v>
       </c>
       <c r="R278" t="n">
-        <v>7087231</v>
+        <v>7087183</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -28659,10 +28659,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>128428535</v>
+        <v>128428574</v>
       </c>
       <c r="B281" t="n">
-        <v>57673</v>
+        <v>79032</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -28670,42 +28670,34 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>635058</v>
+        <v>635129</v>
       </c>
       <c r="R281" t="n">
-        <v>7087271</v>
+        <v>7087323</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -28738,11 +28730,6 @@
       <c r="AA281" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC281" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD281" t="b">
@@ -28769,7 +28756,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>128428536</v>
+        <v>128428535</v>
       </c>
       <c r="B282" t="n">
         <v>57673</v>
@@ -28812,10 +28799,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>634669</v>
+        <v>635058</v>
       </c>
       <c r="R282" t="n">
-        <v>7087314</v>
+        <v>7087271</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -28879,10 +28866,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>128428574</v>
+        <v>128428536</v>
       </c>
       <c r="B283" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -28890,34 +28877,42 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
+      <c r="K283" t="inlineStr"/>
+      <c r="L283" t="inlineStr"/>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr"/>
       <c r="P283" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>635129</v>
+        <v>634669</v>
       </c>
       <c r="R283" t="n">
-        <v>7087323</v>
+        <v>7087314</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -28950,6 +28945,11 @@
       <c r="AA283" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC283" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD283" t="b">

--- a/artfynd/A 30047-2025 artfynd.xlsx
+++ b/artfynd/A 30047-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY285"/>
+  <dimension ref="A1:AY286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7596,32 +7596,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128423192</v>
+        <v>128423573</v>
       </c>
       <c r="B69" t="n">
-        <v>88853</v>
+        <v>91417</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7631,10 +7631,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>634595</v>
+        <v>634599</v>
       </c>
       <c r="R69" t="n">
-        <v>7087268</v>
+        <v>7087225</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7681,19 +7681,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128423623</v>
+        <v>128423192</v>
       </c>
       <c r="B70" t="n">
         <v>88853</v>
@@ -7728,10 +7728,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>634583</v>
+        <v>634595</v>
       </c>
       <c r="R70" t="n">
-        <v>7087261</v>
+        <v>7087268</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7778,22 +7778,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128423180</v>
+        <v>128423623</v>
       </c>
       <c r="B71" t="n">
-        <v>79083</v>
+        <v>88853</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7801,21 +7801,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7825,10 +7825,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>635376</v>
+        <v>634583</v>
       </c>
       <c r="R71" t="n">
-        <v>7087128</v>
+        <v>7087261</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7875,19 +7875,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128423178</v>
+        <v>128423180</v>
       </c>
       <c r="B72" t="n">
         <v>79083</v>
@@ -7922,10 +7922,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>635318</v>
+        <v>635376</v>
       </c>
       <c r="R72" t="n">
-        <v>7087158</v>
+        <v>7087128</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7984,7 +7984,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128423179</v>
+        <v>128423178</v>
       </c>
       <c r="B73" t="n">
         <v>79083</v>
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>635348</v>
+        <v>635318</v>
       </c>
       <c r="R73" t="n">
-        <v>7087138</v>
+        <v>7087158</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8081,32 +8081,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128423573</v>
+        <v>128423179</v>
       </c>
       <c r="B74" t="n">
-        <v>91417</v>
+        <v>79083</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8116,10 +8116,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>634599</v>
+        <v>635348</v>
       </c>
       <c r="R74" t="n">
-        <v>7087225</v>
+        <v>7087138</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8166,44 +8166,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128423142</v>
+        <v>128423621</v>
       </c>
       <c r="B75" t="n">
-        <v>80224</v>
+        <v>82942</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8213,10 +8213,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>635234</v>
+        <v>634525</v>
       </c>
       <c r="R75" t="n">
-        <v>7087170</v>
+        <v>7087295</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8263,44 +8263,44 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128423159</v>
+        <v>128423142</v>
       </c>
       <c r="B76" t="n">
-        <v>79083</v>
+        <v>80224</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8310,10 +8310,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>635080</v>
+        <v>635234</v>
       </c>
       <c r="R76" t="n">
-        <v>7087206</v>
+        <v>7087170</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8372,32 +8372,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128423140</v>
+        <v>128423159</v>
       </c>
       <c r="B77" t="n">
-        <v>80224</v>
+        <v>79083</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8407,10 +8407,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>635608</v>
+        <v>635080</v>
       </c>
       <c r="R77" t="n">
-        <v>7087280</v>
+        <v>7087206</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8469,32 +8469,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128423165</v>
+        <v>128423140</v>
       </c>
       <c r="B78" t="n">
-        <v>79083</v>
+        <v>80224</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8504,10 +8504,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>634654</v>
+        <v>635608</v>
       </c>
       <c r="R78" t="n">
-        <v>7087545</v>
+        <v>7087280</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8566,32 +8566,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128423591</v>
+        <v>128423165</v>
       </c>
       <c r="B79" t="n">
-        <v>80217</v>
+        <v>79083</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8601,10 +8601,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>635451</v>
+        <v>634654</v>
       </c>
       <c r="R79" t="n">
-        <v>7087225</v>
+        <v>7087545</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8651,22 +8651,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128411934</v>
+        <v>128423591</v>
       </c>
       <c r="B80" t="n">
-        <v>91417</v>
+        <v>80217</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8674,34 +8674,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>634525</v>
+        <v>635451</v>
       </c>
       <c r="R80" t="n">
-        <v>7087336</v>
+        <v>7087225</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8731,19 +8731,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8758,57 +8748,57 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128423621</v>
+        <v>128411934</v>
       </c>
       <c r="B81" t="n">
-        <v>82942</v>
+        <v>91417</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
         <v>634525</v>
       </c>
       <c r="R81" t="n">
-        <v>7087295</v>
+        <v>7087336</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8838,9 +8828,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8855,12 +8855,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -10730,10 +10730,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128423622</v>
+        <v>128423119</v>
       </c>
       <c r="B101" t="n">
-        <v>88853</v>
+        <v>57685</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10741,21 +10741,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10765,10 +10765,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>634642</v>
+        <v>634914</v>
       </c>
       <c r="R101" t="n">
-        <v>7087251</v>
+        <v>7087316</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10803,6 +10803,11 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
@@ -10815,19 +10820,19 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128423625</v>
+        <v>128423622</v>
       </c>
       <c r="B102" t="n">
         <v>88853</v>
@@ -10862,10 +10867,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>634494</v>
+        <v>634642</v>
       </c>
       <c r="R102" t="n">
-        <v>7087408</v>
+        <v>7087251</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10924,10 +10929,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128423148</v>
+        <v>128423625</v>
       </c>
       <c r="B103" t="n">
-        <v>91466</v>
+        <v>88853</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10935,21 +10940,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1204</v>
+        <v>510</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10959,10 +10964,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>634924</v>
+        <v>634494</v>
       </c>
       <c r="R103" t="n">
-        <v>7087448</v>
+        <v>7087408</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11009,22 +11014,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128405478</v>
+        <v>128423148</v>
       </c>
       <c r="B104" t="n">
-        <v>79083</v>
+        <v>91466</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11032,39 +11037,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>635443</v>
+        <v>634924</v>
       </c>
       <c r="R104" t="n">
-        <v>7087145</v>
+        <v>7087448</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11094,19 +11094,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>11:18</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11121,19 +11111,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128423176</v>
+        <v>128405478</v>
       </c>
       <c r="B105" t="n">
         <v>79083</v>
@@ -11162,16 +11152,21 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>635233</v>
+        <v>635443</v>
       </c>
       <c r="R105" t="n">
-        <v>7087199</v>
+        <v>7087145</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11201,9 +11196,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11218,44 +11223,44 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128423593</v>
+        <v>128423176</v>
       </c>
       <c r="B106" t="n">
-        <v>80217</v>
+        <v>79083</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11265,10 +11270,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>635471</v>
+        <v>635233</v>
       </c>
       <c r="R106" t="n">
-        <v>7087281</v>
+        <v>7087199</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11315,19 +11320,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128423110</v>
+        <v>128423593</v>
       </c>
       <c r="B107" t="n">
         <v>80217</v>
@@ -11362,10 +11367,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>635475</v>
+        <v>635471</v>
       </c>
       <c r="R107" t="n">
-        <v>7087242</v>
+        <v>7087281</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11412,22 +11417,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128423629</v>
+        <v>128423110</v>
       </c>
       <c r="B108" t="n">
-        <v>80223</v>
+        <v>80217</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11435,21 +11440,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11459,10 +11464,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>635454</v>
+        <v>635475</v>
       </c>
       <c r="R108" t="n">
-        <v>7087257</v>
+        <v>7087242</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11509,44 +11514,44 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128423617</v>
+        <v>128423629</v>
       </c>
       <c r="B109" t="n">
-        <v>91470</v>
+        <v>80223</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11556,10 +11561,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>634507</v>
+        <v>635454</v>
       </c>
       <c r="R109" t="n">
-        <v>7087328</v>
+        <v>7087257</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11618,10 +11623,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128423119</v>
+        <v>128423617</v>
       </c>
       <c r="B110" t="n">
-        <v>57685</v>
+        <v>91470</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11629,21 +11634,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11653,10 +11658,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>634914</v>
+        <v>634507</v>
       </c>
       <c r="R110" t="n">
-        <v>7087316</v>
+        <v>7087328</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11691,11 +11696,6 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
@@ -11708,12 +11708,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
@@ -11914,10 +11914,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128423136</v>
+        <v>128423116</v>
       </c>
       <c r="B113" t="n">
-        <v>80188</v>
+        <v>57685</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11925,21 +11925,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11949,10 +11949,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>635422</v>
+        <v>635330</v>
       </c>
       <c r="R113" t="n">
-        <v>7087149</v>
+        <v>7087114</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11985,6 +11985,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12011,10 +12016,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128410776</v>
+        <v>128423085</v>
       </c>
       <c r="B114" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12022,34 +12027,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>634709</v>
+        <v>635508</v>
       </c>
       <c r="R114" t="n">
-        <v>7087670</v>
+        <v>7087292</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12079,19 +12084,14 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>14:41</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>14:41</t>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12106,22 +12106,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128423195</v>
+        <v>128409304</v>
       </c>
       <c r="B115" t="n">
-        <v>80223</v>
+        <v>56876</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12129,34 +12129,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6463</v>
+        <v>100138</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>635228</v>
+        <v>634947</v>
       </c>
       <c r="R115" t="n">
-        <v>7087058</v>
+        <v>7087432</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12186,9 +12186,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12203,22 +12213,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128423154</v>
+        <v>128423136</v>
       </c>
       <c r="B116" t="n">
-        <v>79083</v>
+        <v>80188</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12226,21 +12236,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12250,10 +12260,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>635479</v>
+        <v>635422</v>
       </c>
       <c r="R116" t="n">
-        <v>7087148</v>
+        <v>7087149</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12312,45 +12322,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128423089</v>
+        <v>128410776</v>
       </c>
       <c r="B117" t="n">
-        <v>91417</v>
+        <v>79083</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>635295</v>
+        <v>634709</v>
       </c>
       <c r="R117" t="n">
-        <v>7087129</v>
+        <v>7087670</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12380,9 +12390,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12397,44 +12417,44 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128423116</v>
+        <v>128423195</v>
       </c>
       <c r="B118" t="n">
-        <v>57685</v>
+        <v>80223</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12444,10 +12464,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>635330</v>
+        <v>635228</v>
       </c>
       <c r="R118" t="n">
-        <v>7087114</v>
+        <v>7087058</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12480,11 +12500,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12511,10 +12526,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128423085</v>
+        <v>128423154</v>
       </c>
       <c r="B119" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12522,21 +12537,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12546,10 +12561,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>635508</v>
+        <v>635479</v>
       </c>
       <c r="R119" t="n">
-        <v>7087292</v>
+        <v>7087148</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12582,11 +12597,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12613,10 +12623,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128409304</v>
+        <v>128423089</v>
       </c>
       <c r="B120" t="n">
-        <v>56876</v>
+        <v>91417</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12624,34 +12634,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>634947</v>
+        <v>635295</v>
       </c>
       <c r="R120" t="n">
-        <v>7087432</v>
+        <v>7087129</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12681,19 +12691,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>13:34</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12708,12 +12708,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -16753,10 +16753,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128423572</v>
+        <v>128423101</v>
       </c>
       <c r="B161" t="n">
-        <v>96823</v>
+        <v>57845</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16764,21 +16764,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16788,10 +16788,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>634574</v>
+        <v>634716</v>
       </c>
       <c r="R161" t="n">
-        <v>7087286</v>
+        <v>7087613</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16838,22 +16838,22 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128423191</v>
+        <v>128423572</v>
       </c>
       <c r="B162" t="n">
-        <v>88853</v>
+        <v>96823</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16861,21 +16861,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>510</v>
+        <v>53</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16885,10 +16885,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>634676</v>
+        <v>634574</v>
       </c>
       <c r="R162" t="n">
-        <v>7087233</v>
+        <v>7087286</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16935,22 +16935,22 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128423113</v>
+        <v>128423191</v>
       </c>
       <c r="B163" t="n">
-        <v>80189</v>
+        <v>88853</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16958,21 +16958,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>2081</v>
+        <v>510</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16982,10 +16982,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>635240</v>
+        <v>634676</v>
       </c>
       <c r="R163" t="n">
-        <v>7087040</v>
+        <v>7087233</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17044,10 +17044,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128423185</v>
+        <v>128423113</v>
       </c>
       <c r="B164" t="n">
-        <v>79083</v>
+        <v>80189</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17055,21 +17055,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17079,10 +17079,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>635559</v>
+        <v>635240</v>
       </c>
       <c r="R164" t="n">
-        <v>7087269</v>
+        <v>7087040</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17141,32 +17141,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128423126</v>
+        <v>128423185</v>
       </c>
       <c r="B165" t="n">
-        <v>79107</v>
+        <v>79083</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17176,10 +17176,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>635212</v>
+        <v>635559</v>
       </c>
       <c r="R165" t="n">
-        <v>7087212</v>
+        <v>7087269</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17238,32 +17238,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128423101</v>
+        <v>128423126</v>
       </c>
       <c r="B166" t="n">
-        <v>57845</v>
+        <v>79107</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>103021</v>
+        <v>6434</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17273,10 +17273,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>634716</v>
+        <v>635212</v>
       </c>
       <c r="R166" t="n">
-        <v>7087613</v>
+        <v>7087212</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17432,10 +17432,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128404367</v>
+        <v>128412855</v>
       </c>
       <c r="B168" t="n">
-        <v>79083</v>
+        <v>91748</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17443,41 +17443,34 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>635556</v>
+        <v>634574</v>
       </c>
       <c r="R168" t="n">
-        <v>7087281</v>
+        <v>7087273</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17509,7 +17502,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -17519,7 +17512,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17528,7 +17521,6 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -17547,10 +17539,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128423161</v>
+        <v>128423614</v>
       </c>
       <c r="B169" t="n">
-        <v>79083</v>
+        <v>91466</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17558,21 +17550,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17582,10 +17574,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>634702</v>
+        <v>634673</v>
       </c>
       <c r="R169" t="n">
-        <v>7087248</v>
+        <v>7087631</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17632,22 +17624,22 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128423181</v>
+        <v>128423147</v>
       </c>
       <c r="B170" t="n">
-        <v>79083</v>
+        <v>91466</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17655,21 +17647,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17679,10 +17671,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>635471</v>
+        <v>634571</v>
       </c>
       <c r="R170" t="n">
-        <v>7087243</v>
+        <v>7087288</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17741,45 +17733,45 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128412855</v>
+        <v>128423576</v>
       </c>
       <c r="B171" t="n">
-        <v>91748</v>
+        <v>91417</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>634574</v>
+        <v>634705</v>
       </c>
       <c r="R171" t="n">
-        <v>7087273</v>
+        <v>7087668</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17809,19 +17801,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>16:03</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -17836,22 +17818,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128423614</v>
+        <v>128423603</v>
       </c>
       <c r="B172" t="n">
-        <v>91466</v>
+        <v>57685</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17859,34 +17841,38 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>634673</v>
+        <v>635240</v>
       </c>
       <c r="R172" t="n">
-        <v>7087631</v>
+        <v>7087224</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17919,6 +17905,11 @@
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -17945,10 +17936,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128423147</v>
+        <v>128404367</v>
       </c>
       <c r="B173" t="n">
-        <v>91466</v>
+        <v>79083</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17956,34 +17947,41 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>634571</v>
+        <v>635556</v>
       </c>
       <c r="R173" t="n">
-        <v>7087288</v>
+        <v>7087281</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18013,61 +18011,72 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AD173" t="b">
         <v>0</v>
       </c>
       <c r="AE173" t="b">
         <v>0</v>
       </c>
+      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128423576</v>
+        <v>128423161</v>
       </c>
       <c r="B174" t="n">
-        <v>91417</v>
+        <v>79083</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18077,10 +18086,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>634705</v>
+        <v>634702</v>
       </c>
       <c r="R174" t="n">
-        <v>7087668</v>
+        <v>7087248</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18127,22 +18136,22 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128423603</v>
+        <v>128423181</v>
       </c>
       <c r="B175" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18150,38 +18159,34 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>635240</v>
+        <v>635471</v>
       </c>
       <c r="R175" t="n">
-        <v>7087224</v>
+        <v>7087243</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18216,11 +18221,6 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD175" t="b">
         <v>0</v>
       </c>
@@ -18233,12 +18233,12 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
@@ -19270,32 +19270,32 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128423088</v>
+        <v>128423604</v>
       </c>
       <c r="B186" t="n">
-        <v>96823</v>
+        <v>95803</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>53</v>
+        <v>2809</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19305,10 +19305,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>634571</v>
+        <v>634948</v>
       </c>
       <c r="R186" t="n">
-        <v>7087288</v>
+        <v>7087579</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19355,22 +19355,22 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128423190</v>
+        <v>128423137</v>
       </c>
       <c r="B187" t="n">
-        <v>88853</v>
+        <v>80188</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19378,21 +19378,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19402,10 +19402,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>634804</v>
+        <v>635683</v>
       </c>
       <c r="R187" t="n">
-        <v>7087321</v>
+        <v>7087267</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19464,32 +19464,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128423604</v>
+        <v>128423186</v>
       </c>
       <c r="B188" t="n">
-        <v>95803</v>
+        <v>79083</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19499,10 +19499,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>634948</v>
+        <v>635555</v>
       </c>
       <c r="R188" t="n">
-        <v>7087579</v>
+        <v>7087248</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19549,44 +19549,44 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128423137</v>
+        <v>128423129</v>
       </c>
       <c r="B189" t="n">
-        <v>80188</v>
+        <v>80216</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19596,10 +19596,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>635683</v>
+        <v>635614</v>
       </c>
       <c r="R189" t="n">
-        <v>7087267</v>
+        <v>7087262</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19658,10 +19658,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128423186</v>
+        <v>128423088</v>
       </c>
       <c r="B190" t="n">
-        <v>79083</v>
+        <v>96823</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19669,21 +19669,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19693,10 +19693,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>635555</v>
+        <v>634571</v>
       </c>
       <c r="R190" t="n">
-        <v>7087248</v>
+        <v>7087288</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19755,32 +19755,32 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128423129</v>
+        <v>128423190</v>
       </c>
       <c r="B191" t="n">
-        <v>80216</v>
+        <v>88853</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6461</v>
+        <v>510</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19790,10 +19790,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>635614</v>
+        <v>634804</v>
       </c>
       <c r="R191" t="n">
-        <v>7087262</v>
+        <v>7087321</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19954,10 +19954,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128423590</v>
+        <v>128423118</v>
       </c>
       <c r="B193" t="n">
-        <v>92734</v>
+        <v>57685</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19965,21 +19965,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19989,10 +19989,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>635182</v>
+        <v>634924</v>
       </c>
       <c r="R193" t="n">
-        <v>7087227</v>
+        <v>7087288</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20027,6 +20027,11 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD193" t="b">
         <v>0</v>
       </c>
@@ -20035,26 +20040,41 @@
       </c>
       <c r="AG193" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO193" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128423172</v>
+        <v>128423588</v>
       </c>
       <c r="B194" t="n">
-        <v>79083</v>
+        <v>57845</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20062,21 +20082,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20086,10 +20106,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>635010</v>
+        <v>634560</v>
       </c>
       <c r="R194" t="n">
-        <v>7087362</v>
+        <v>7087311</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20136,44 +20156,44 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128423138</v>
+        <v>128423590</v>
       </c>
       <c r="B195" t="n">
-        <v>80224</v>
+        <v>92734</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6464</v>
+        <v>4361</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20183,10 +20203,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>635160</v>
+        <v>635182</v>
       </c>
       <c r="R195" t="n">
-        <v>7087012</v>
+        <v>7087227</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20233,19 +20253,19 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>128423168</v>
+        <v>128423172</v>
       </c>
       <c r="B196" t="n">
         <v>79083</v>
@@ -20280,10 +20300,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>634865</v>
+        <v>635010</v>
       </c>
       <c r="R196" t="n">
-        <v>7087586</v>
+        <v>7087362</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20342,10 +20362,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>128423109</v>
+        <v>128423138</v>
       </c>
       <c r="B197" t="n">
-        <v>80217</v>
+        <v>80224</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20353,21 +20373,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20377,10 +20397,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>635407</v>
+        <v>635160</v>
       </c>
       <c r="R197" t="n">
-        <v>7087128</v>
+        <v>7087012</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20439,7 +20459,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>128423160</v>
+        <v>128423168</v>
       </c>
       <c r="B198" t="n">
         <v>79083</v>
@@ -20474,10 +20494,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>634916</v>
+        <v>634865</v>
       </c>
       <c r="R198" t="n">
-        <v>7087311</v>
+        <v>7087586</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20536,32 +20556,32 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>128423135</v>
+        <v>128423109</v>
       </c>
       <c r="B199" t="n">
-        <v>80188</v>
+        <v>80217</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -20571,10 +20591,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>635412</v>
+        <v>635407</v>
       </c>
       <c r="R199" t="n">
-        <v>7087118</v>
+        <v>7087128</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20633,10 +20653,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>128423596</v>
+        <v>128423160</v>
       </c>
       <c r="B200" t="n">
-        <v>57682</v>
+        <v>79083</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20644,21 +20664,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20668,10 +20688,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>634648</v>
+        <v>634916</v>
       </c>
       <c r="R200" t="n">
-        <v>7087590</v>
+        <v>7087311</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20718,22 +20738,22 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>128423118</v>
+        <v>128423135</v>
       </c>
       <c r="B201" t="n">
-        <v>57685</v>
+        <v>80188</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20741,21 +20761,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20765,10 +20785,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>634924</v>
+        <v>635412</v>
       </c>
       <c r="R201" t="n">
-        <v>7087288</v>
+        <v>7087118</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20803,11 +20823,6 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD201" t="b">
         <v>0</v>
       </c>
@@ -20816,21 +20831,6 @@
       </c>
       <c r="AG201" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ201" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK201" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO201" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
@@ -20847,10 +20847,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>128423588</v>
+        <v>128423596</v>
       </c>
       <c r="B202" t="n">
-        <v>57845</v>
+        <v>57682</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20858,21 +20858,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -20882,10 +20882,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>634560</v>
+        <v>634648</v>
       </c>
       <c r="R202" t="n">
-        <v>7087311</v>
+        <v>7087590</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22734,10 +22734,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>128405308</v>
+        <v>128423087</v>
       </c>
       <c r="B221" t="n">
-        <v>80188</v>
+        <v>79115</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -22745,34 +22745,34 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>635477</v>
+        <v>634647</v>
       </c>
       <c r="R221" t="n">
-        <v>7087164</v>
+        <v>7087542</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22802,19 +22802,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z221" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA221" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB221" t="inlineStr">
-        <is>
-          <t>11:11</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -22829,22 +22819,22 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>128423173</v>
+        <v>128423613</v>
       </c>
       <c r="B222" t="n">
-        <v>79083</v>
+        <v>91466</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -22852,21 +22842,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -22876,10 +22866,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>635138</v>
+        <v>634599</v>
       </c>
       <c r="R222" t="n">
-        <v>7087339</v>
+        <v>7087225</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -22926,19 +22916,19 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>128423134</v>
+        <v>128405308</v>
       </c>
       <c r="B223" t="n">
         <v>80188</v>
@@ -22969,14 +22959,14 @@
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>635231</v>
+        <v>635477</v>
       </c>
       <c r="R223" t="n">
-        <v>7087059</v>
+        <v>7087164</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23006,9 +22996,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA223" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -23023,19 +23023,19 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>128407951</v>
+        <v>128423173</v>
       </c>
       <c r="B224" t="n">
         <v>79083</v>
@@ -23066,14 +23066,14 @@
       <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>635217</v>
+        <v>635138</v>
       </c>
       <c r="R224" t="n">
-        <v>7087316</v>
+        <v>7087339</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23103,19 +23103,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z224" t="inlineStr">
-        <is>
-          <t>12:49</t>
-        </is>
-      </c>
       <c r="AA224" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB224" t="inlineStr">
-        <is>
-          <t>12:49</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -23130,22 +23120,22 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>128423087</v>
+        <v>128423134</v>
       </c>
       <c r="B225" t="n">
-        <v>79115</v>
+        <v>80188</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23153,21 +23143,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23177,10 +23167,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>634647</v>
+        <v>635231</v>
       </c>
       <c r="R225" t="n">
-        <v>7087542</v>
+        <v>7087059</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23239,10 +23229,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>128423613</v>
+        <v>128407951</v>
       </c>
       <c r="B226" t="n">
-        <v>91466</v>
+        <v>79083</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23250,34 +23240,34 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>634599</v>
+        <v>635217</v>
       </c>
       <c r="R226" t="n">
-        <v>7087225</v>
+        <v>7087316</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23307,9 +23297,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
       <c r="AA226" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -23324,12 +23324,12 @@
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
@@ -23724,32 +23724,32 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>128428595</v>
+        <v>128428563</v>
       </c>
       <c r="B231" t="n">
-        <v>75163</v>
+        <v>57789</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>308</v>
+        <v>103031</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -23759,10 +23759,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>634678</v>
+        <v>635011</v>
       </c>
       <c r="R231" t="n">
-        <v>7087320</v>
+        <v>7087362</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -23821,32 +23821,32 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>128428547</v>
+        <v>128428595</v>
       </c>
       <c r="B232" t="n">
-        <v>80217</v>
+        <v>75163</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6462</v>
+        <v>308</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -23856,10 +23856,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>635305</v>
+        <v>634678</v>
       </c>
       <c r="R232" t="n">
-        <v>7087219</v>
+        <v>7087320</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -23918,10 +23918,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>128428563</v>
+        <v>128428547</v>
       </c>
       <c r="B233" t="n">
-        <v>57789</v>
+        <v>80217</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -23929,21 +23929,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>103031</v>
+        <v>6462</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -23953,10 +23953,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>635011</v>
+        <v>635305</v>
       </c>
       <c r="R233" t="n">
-        <v>7087362</v>
+        <v>7087219</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24517,10 +24517,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>128428568</v>
+        <v>128428537</v>
       </c>
       <c r="B239" t="n">
-        <v>91466</v>
+        <v>57685</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -24528,34 +24528,42 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>634725</v>
+        <v>635466</v>
       </c>
       <c r="R239" t="n">
-        <v>7087631</v>
+        <v>7087249</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24588,6 +24596,11 @@
       <c r="AA239" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC239" t="inlineStr">
+        <is>
+          <t>Ca 3 m upp på liggande granlåga. Runt bohål, omkr 45 mm i diameter.</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -24614,10 +24627,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>128428554</v>
+        <v>128428568</v>
       </c>
       <c r="B240" t="n">
-        <v>80189</v>
+        <v>91466</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -24625,21 +24638,21 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -24649,10 +24662,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>635037</v>
+        <v>634725</v>
       </c>
       <c r="R240" t="n">
-        <v>7087279</v>
+        <v>7087631</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24711,10 +24724,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>128428571</v>
+        <v>128428554</v>
       </c>
       <c r="B241" t="n">
-        <v>79083</v>
+        <v>80189</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24722,21 +24735,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -24746,10 +24759,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>635190</v>
+        <v>635037</v>
       </c>
       <c r="R241" t="n">
-        <v>7087142</v>
+        <v>7087279</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -24808,10 +24821,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>128428537</v>
+        <v>128428571</v>
       </c>
       <c r="B242" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -24819,42 +24832,34 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
-      <c r="K242" t="inlineStr"/>
-      <c r="L242" t="inlineStr"/>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>635466</v>
+        <v>635190</v>
       </c>
       <c r="R242" t="n">
-        <v>7087249</v>
+        <v>7087142</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24887,11 +24892,6 @@
       <c r="AA242" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC242" t="inlineStr">
-        <is>
-          <t>Ca 3 m upp på liggande granlåga. Runt bohål, omkr 45 mm i diameter.</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -25015,32 +25015,32 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>128428577</v>
+        <v>128428533</v>
       </c>
       <c r="B244" t="n">
-        <v>79083</v>
+        <v>92149</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -25050,10 +25050,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>635291</v>
+        <v>634621</v>
       </c>
       <c r="R244" t="n">
-        <v>7087126</v>
+        <v>7087294</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25112,32 +25112,32 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>128428533</v>
+        <v>128428577</v>
       </c>
       <c r="B245" t="n">
-        <v>92149</v>
+        <v>79083</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -25147,10 +25147,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>634621</v>
+        <v>635291</v>
       </c>
       <c r="R245" t="n">
-        <v>7087294</v>
+        <v>7087126</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25306,45 +25306,53 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>128428557</v>
+        <v>128428551</v>
       </c>
       <c r="B247" t="n">
-        <v>79107</v>
+        <v>57682</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>635151</v>
+        <v>634768</v>
       </c>
       <c r="R247" t="n">
-        <v>7087221</v>
+        <v>7087607</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25403,10 +25411,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>128428564</v>
+        <v>128428557</v>
       </c>
       <c r="B248" t="n">
-        <v>80092</v>
+        <v>79107</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -25414,21 +25422,21 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6456</v>
+        <v>6434</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -25438,10 +25446,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>635518</v>
+        <v>635151</v>
       </c>
       <c r="R248" t="n">
-        <v>7087188</v>
+        <v>7087221</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25476,18 +25484,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC248" t="inlineStr">
-        <is>
-          <t>På aspbark</t>
-        </is>
-      </c>
       <c r="AD248" t="b">
         <v>0</v>
       </c>
       <c r="AE248" t="b">
         <v>0</v>
       </c>
-      <c r="AF248" t="inlineStr"/>
       <c r="AG248" t="b">
         <v>0</v>
       </c>
@@ -25506,53 +25508,45 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>128428551</v>
+        <v>128428564</v>
       </c>
       <c r="B249" t="n">
-        <v>57682</v>
+        <v>80092</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
-      <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr"/>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>634768</v>
+        <v>635518</v>
       </c>
       <c r="R249" t="n">
-        <v>7087607</v>
+        <v>7087188</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25587,12 +25581,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t>På aspbark</t>
+        </is>
+      </c>
       <c r="AD249" t="b">
         <v>0</v>
       </c>
       <c r="AE249" t="b">
         <v>0</v>
       </c>
+      <c r="AF249" t="inlineStr"/>
       <c r="AG249" t="b">
         <v>0</v>
       </c>
@@ -25805,10 +25805,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>128428581</v>
+        <v>128428559</v>
       </c>
       <c r="B252" t="n">
-        <v>82942</v>
+        <v>80188</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -25816,21 +25816,21 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -25840,10 +25840,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>635622</v>
+        <v>635416</v>
       </c>
       <c r="R252" t="n">
-        <v>7087310</v>
+        <v>7087178</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -25902,32 +25902,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>128428559</v>
+        <v>128428529</v>
       </c>
       <c r="B253" t="n">
-        <v>80188</v>
+        <v>91417</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -25937,10 +25937,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>635416</v>
+        <v>634593</v>
       </c>
       <c r="R253" t="n">
-        <v>7087178</v>
+        <v>7087306</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -25999,32 +25999,32 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128428529</v>
+        <v>128428581</v>
       </c>
       <c r="B254" t="n">
-        <v>91417</v>
+        <v>82942</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -26034,10 +26034,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>634593</v>
+        <v>635622</v>
       </c>
       <c r="R254" t="n">
-        <v>7087306</v>
+        <v>7087310</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -27370,32 +27370,32 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>128428567</v>
+        <v>128428541</v>
       </c>
       <c r="B268" t="n">
-        <v>75154</v>
+        <v>57845</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6439</v>
+        <v>103021</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -27405,10 +27405,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>635532</v>
+        <v>635537</v>
       </c>
       <c r="R268" t="n">
-        <v>7087324</v>
+        <v>7087207</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -27467,10 +27467,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>128428561</v>
+        <v>128428565</v>
       </c>
       <c r="B269" t="n">
-        <v>80224</v>
+        <v>58055</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -27478,34 +27478,46 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6464</v>
+        <v>103015</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I269" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr"/>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>634879</v>
+        <v>635275</v>
       </c>
       <c r="R269" t="n">
-        <v>7087368</v>
+        <v>7087098</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -27564,32 +27576,32 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>128428541</v>
+        <v>128428567</v>
       </c>
       <c r="B270" t="n">
-        <v>57845</v>
+        <v>75154</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>103021</v>
+        <v>6439</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
@@ -27599,10 +27611,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>635537</v>
+        <v>635532</v>
       </c>
       <c r="R270" t="n">
-        <v>7087207</v>
+        <v>7087324</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -27661,10 +27673,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>128428565</v>
+        <v>128428561</v>
       </c>
       <c r="B271" t="n">
-        <v>58055</v>
+        <v>80224</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -27672,46 +27684,34 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>103015</v>
+        <v>6464</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I271" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K271" t="inlineStr"/>
-      <c r="L271" t="inlineStr"/>
-      <c r="M271" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N271" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>635275</v>
+        <v>634879</v>
       </c>
       <c r="R271" t="n">
-        <v>7087098</v>
+        <v>7087368</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -28255,7 +28255,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>128428550</v>
+        <v>128428552</v>
       </c>
       <c r="B277" t="n">
         <v>57682</v>
@@ -28298,10 +28298,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>634487</v>
+        <v>635170</v>
       </c>
       <c r="R277" t="n">
-        <v>7087401</v>
+        <v>7087231</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -28360,7 +28360,7 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>128428552</v>
+        <v>128428550</v>
       </c>
       <c r="B278" t="n">
         <v>57682</v>
@@ -28403,10 +28403,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>635170</v>
+        <v>634487</v>
       </c>
       <c r="R278" t="n">
-        <v>7087231</v>
+        <v>7087401</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -28465,10 +28465,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>128428580</v>
+        <v>128428582</v>
       </c>
       <c r="B279" t="n">
-        <v>79083</v>
+        <v>82942</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -28476,21 +28476,21 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
@@ -28500,10 +28500,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>634932</v>
+        <v>635259</v>
       </c>
       <c r="R279" t="n">
-        <v>7087436</v>
+        <v>7087140</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -28562,10 +28562,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>128428582</v>
+        <v>128428580</v>
       </c>
       <c r="B280" t="n">
-        <v>82942</v>
+        <v>79083</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -28573,21 +28573,21 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -28597,10 +28597,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>635259</v>
+        <v>634932</v>
       </c>
       <c r="R280" t="n">
-        <v>7087140</v>
+        <v>7087436</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -29168,6 +29168,103 @@
       </c>
       <c r="AY285" t="inlineStr"/>
     </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>128651017</v>
+      </c>
+      <c r="B286" t="n">
+        <v>96919</v>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>1841</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Vedflikmossa</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Lophozia guttulata</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr"/>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q286" t="n">
+        <v>634897</v>
+      </c>
+      <c r="R286" t="n">
+        <v>7087591</v>
+      </c>
+      <c r="S286" t="n">
+        <v>10</v>
+      </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V286" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W286" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y286" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD286" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE286" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG286" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT286" t="inlineStr"/>
+      <c r="AW286" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX286" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY286" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30047-2025 artfynd.xlsx
+++ b/artfynd/A 30047-2025 artfynd.xlsx
@@ -7596,32 +7596,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128423573</v>
+        <v>128423192</v>
       </c>
       <c r="B69" t="n">
-        <v>91417</v>
+        <v>88853</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7631,10 +7631,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>634599</v>
+        <v>634595</v>
       </c>
       <c r="R69" t="n">
-        <v>7087225</v>
+        <v>7087268</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7681,19 +7681,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128423192</v>
+        <v>128423623</v>
       </c>
       <c r="B70" t="n">
         <v>88853</v>
@@ -7728,10 +7728,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>634595</v>
+        <v>634583</v>
       </c>
       <c r="R70" t="n">
-        <v>7087268</v>
+        <v>7087261</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7778,22 +7778,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128423623</v>
+        <v>128423180</v>
       </c>
       <c r="B71" t="n">
-        <v>88853</v>
+        <v>79083</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7801,21 +7801,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7825,10 +7825,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>634583</v>
+        <v>635376</v>
       </c>
       <c r="R71" t="n">
-        <v>7087261</v>
+        <v>7087128</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7875,19 +7875,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128423180</v>
+        <v>128423178</v>
       </c>
       <c r="B72" t="n">
         <v>79083</v>
@@ -7922,10 +7922,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>635376</v>
+        <v>635318</v>
       </c>
       <c r="R72" t="n">
-        <v>7087128</v>
+        <v>7087158</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7984,7 +7984,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128423178</v>
+        <v>128423179</v>
       </c>
       <c r="B73" t="n">
         <v>79083</v>
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>635318</v>
+        <v>635348</v>
       </c>
       <c r="R73" t="n">
-        <v>7087158</v>
+        <v>7087138</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8081,32 +8081,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128423179</v>
+        <v>128423573</v>
       </c>
       <c r="B74" t="n">
-        <v>79083</v>
+        <v>91417</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8116,10 +8116,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>635348</v>
+        <v>634599</v>
       </c>
       <c r="R74" t="n">
-        <v>7087138</v>
+        <v>7087225</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8166,12 +8166,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -15724,32 +15724,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128409243</v>
+        <v>128409160</v>
       </c>
       <c r="B151" t="n">
-        <v>91466</v>
+        <v>91417</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15759,10 +15759,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>634946</v>
+        <v>634944</v>
       </c>
       <c r="R151" t="n">
-        <v>7087431</v>
+        <v>7087430</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15794,7 +15794,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -15804,7 +15804,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15831,7 +15831,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128409160</v>
+        <v>128423093</v>
       </c>
       <c r="B152" t="n">
         <v>91417</v>
@@ -15862,14 +15862,14 @@
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>634944</v>
+        <v>634938</v>
       </c>
       <c r="R152" t="n">
-        <v>7087430</v>
+        <v>7087435</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15899,19 +15899,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -15926,44 +15916,44 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128423093</v>
+        <v>128423200</v>
       </c>
       <c r="B153" t="n">
-        <v>91417</v>
+        <v>57685</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15973,10 +15963,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>634938</v>
+        <v>635225</v>
       </c>
       <c r="R153" t="n">
-        <v>7087435</v>
+        <v>7087115</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16009,6 +15999,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16035,59 +16030,45 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128409844</v>
+        <v>128411777</v>
       </c>
       <c r="B154" t="n">
-        <v>57789</v>
+        <v>88853</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>103031</v>
+        <v>510</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>634713</v>
+        <v>634505</v>
       </c>
       <c r="R154" t="n">
-        <v>7087635</v>
+        <v>7087326</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16119,7 +16100,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -16129,7 +16110,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16144,22 +16125,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128411777</v>
+        <v>128409243</v>
       </c>
       <c r="B155" t="n">
-        <v>88853</v>
+        <v>91466</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16167,21 +16148,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>510</v>
+        <v>1204</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16191,10 +16172,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>634505</v>
+        <v>634946</v>
       </c>
       <c r="R155" t="n">
-        <v>7087326</v>
+        <v>7087431</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16226,7 +16207,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -16236,7 +16217,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16554,32 +16535,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128423200</v>
+        <v>128423122</v>
       </c>
       <c r="B159" t="n">
-        <v>57685</v>
+        <v>97448</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16589,10 +16570,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>635225</v>
+        <v>634926</v>
       </c>
       <c r="R159" t="n">
-        <v>7087115</v>
+        <v>7087302</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16625,11 +16606,6 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16656,10 +16632,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128423122</v>
+        <v>128409844</v>
       </c>
       <c r="B160" t="n">
-        <v>97448</v>
+        <v>57789</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16667,34 +16643,48 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>221945</v>
+        <v>103031</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>634926</v>
+        <v>634713</v>
       </c>
       <c r="R160" t="n">
-        <v>7087302</v>
+        <v>7087635</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16724,9 +16714,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16746,7 +16746,7 @@
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
@@ -17432,10 +17432,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128412855</v>
+        <v>128404367</v>
       </c>
       <c r="B168" t="n">
-        <v>91748</v>
+        <v>79083</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17443,34 +17443,41 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>634574</v>
+        <v>635556</v>
       </c>
       <c r="R168" t="n">
-        <v>7087273</v>
+        <v>7087281</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17502,7 +17509,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -17512,7 +17519,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17521,6 +17528,7 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -17539,10 +17547,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128423614</v>
+        <v>128423161</v>
       </c>
       <c r="B169" t="n">
-        <v>91466</v>
+        <v>79083</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17550,21 +17558,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17574,10 +17582,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>634673</v>
+        <v>634702</v>
       </c>
       <c r="R169" t="n">
-        <v>7087631</v>
+        <v>7087248</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17624,22 +17632,22 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128423147</v>
+        <v>128423181</v>
       </c>
       <c r="B170" t="n">
-        <v>91466</v>
+        <v>79083</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17647,21 +17655,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17671,10 +17679,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>634571</v>
+        <v>635471</v>
       </c>
       <c r="R170" t="n">
-        <v>7087288</v>
+        <v>7087243</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17733,45 +17741,45 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128423576</v>
+        <v>128412855</v>
       </c>
       <c r="B171" t="n">
-        <v>91417</v>
+        <v>91748</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>634705</v>
+        <v>634574</v>
       </c>
       <c r="R171" t="n">
-        <v>7087668</v>
+        <v>7087273</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17801,9 +17809,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -17818,22 +17836,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128423603</v>
+        <v>128423614</v>
       </c>
       <c r="B172" t="n">
-        <v>57685</v>
+        <v>91466</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17841,38 +17859,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>635240</v>
+        <v>634673</v>
       </c>
       <c r="R172" t="n">
-        <v>7087224</v>
+        <v>7087631</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17905,11 +17919,6 @@
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -17936,10 +17945,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128404367</v>
+        <v>128423147</v>
       </c>
       <c r="B173" t="n">
-        <v>79083</v>
+        <v>91466</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17947,41 +17956,34 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>635556</v>
+        <v>634571</v>
       </c>
       <c r="R173" t="n">
-        <v>7087281</v>
+        <v>7087288</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18011,72 +18013,61 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AD173" t="b">
         <v>0</v>
       </c>
       <c r="AE173" t="b">
         <v>0</v>
       </c>
-      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128423161</v>
+        <v>128423576</v>
       </c>
       <c r="B174" t="n">
-        <v>79083</v>
+        <v>91417</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18086,10 +18077,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>634702</v>
+        <v>634705</v>
       </c>
       <c r="R174" t="n">
-        <v>7087248</v>
+        <v>7087668</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18136,22 +18127,22 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128423181</v>
+        <v>128423603</v>
       </c>
       <c r="B175" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18159,34 +18150,38 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>635471</v>
+        <v>635240</v>
       </c>
       <c r="R175" t="n">
-        <v>7087243</v>
+        <v>7087224</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18221,6 +18216,11 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD175" t="b">
         <v>0</v>
       </c>
@@ -18233,12 +18233,12 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
@@ -23724,10 +23724,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>128428563</v>
+        <v>128428547</v>
       </c>
       <c r="B231" t="n">
-        <v>57789</v>
+        <v>80217</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -23735,21 +23735,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>103031</v>
+        <v>6462</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -23759,10 +23759,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>635011</v>
+        <v>635305</v>
       </c>
       <c r="R231" t="n">
-        <v>7087362</v>
+        <v>7087219</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -23821,32 +23821,32 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>128428595</v>
+        <v>128428563</v>
       </c>
       <c r="B232" t="n">
-        <v>75163</v>
+        <v>57789</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>308</v>
+        <v>103031</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -23856,10 +23856,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>634678</v>
+        <v>635011</v>
       </c>
       <c r="R232" t="n">
-        <v>7087320</v>
+        <v>7087362</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -23918,32 +23918,32 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>128428547</v>
+        <v>128428595</v>
       </c>
       <c r="B233" t="n">
-        <v>80217</v>
+        <v>75163</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6462</v>
+        <v>308</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -23953,10 +23953,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>635305</v>
+        <v>634678</v>
       </c>
       <c r="R233" t="n">
-        <v>7087219</v>
+        <v>7087320</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24015,49 +24015,45 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>128428540</v>
+        <v>128428530</v>
       </c>
       <c r="B234" t="n">
-        <v>57845</v>
+        <v>91417</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I234" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>634887</v>
+        <v>634478</v>
       </c>
       <c r="R234" t="n">
-        <v>7087502</v>
+        <v>7087363</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24116,45 +24112,53 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>128428530</v>
+        <v>128428556</v>
       </c>
       <c r="B235" t="n">
-        <v>91417</v>
+        <v>57685</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>634478</v>
+        <v>634718</v>
       </c>
       <c r="R235" t="n">
-        <v>7087363</v>
+        <v>7087671</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24187,6 +24191,11 @@
       <c r="AA235" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t>Ringhack på högstubbe av gran. Sannolikt flera decennier gammalt. Tecken på långsiktigt nyttjande av området.</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -24213,10 +24222,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>128428556</v>
+        <v>128428540</v>
       </c>
       <c r="B236" t="n">
-        <v>57685</v>
+        <v>57845</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24224,42 +24233,38 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr"/>
-      <c r="K236" t="inlineStr"/>
-      <c r="L236" t="inlineStr"/>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N236" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P236" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>634718</v>
+        <v>634887</v>
       </c>
       <c r="R236" t="n">
-        <v>7087671</v>
+        <v>7087502</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24292,11 +24297,6 @@
       <c r="AA236" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC236" t="inlineStr">
-        <is>
-          <t>Ringhack på högstubbe av gran. Sannolikt flera decennier gammalt. Tecken på långsiktigt nyttjande av området.</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -25306,53 +25306,45 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>128428551</v>
+        <v>128428557</v>
       </c>
       <c r="B247" t="n">
-        <v>57682</v>
+        <v>79107</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
-      <c r="K247" t="inlineStr"/>
-      <c r="L247" t="inlineStr"/>
-      <c r="M247" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>634768</v>
+        <v>635151</v>
       </c>
       <c r="R247" t="n">
-        <v>7087607</v>
+        <v>7087221</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25411,10 +25403,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>128428557</v>
+        <v>128428564</v>
       </c>
       <c r="B248" t="n">
-        <v>79107</v>
+        <v>80092</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -25422,21 +25414,21 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6434</v>
+        <v>6456</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -25446,10 +25438,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>635151</v>
+        <v>635518</v>
       </c>
       <c r="R248" t="n">
-        <v>7087221</v>
+        <v>7087188</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25484,12 +25476,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>På aspbark</t>
+        </is>
+      </c>
       <c r="AD248" t="b">
         <v>0</v>
       </c>
       <c r="AE248" t="b">
         <v>0</v>
       </c>
+      <c r="AF248" t="inlineStr"/>
       <c r="AG248" t="b">
         <v>0</v>
       </c>
@@ -25508,45 +25506,53 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>128428564</v>
+        <v>128428551</v>
       </c>
       <c r="B249" t="n">
-        <v>80092</v>
+        <v>57682</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>635518</v>
+        <v>634768</v>
       </c>
       <c r="R249" t="n">
-        <v>7087188</v>
+        <v>7087607</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25581,18 +25587,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC249" t="inlineStr">
-        <is>
-          <t>På aspbark</t>
-        </is>
-      </c>
       <c r="AD249" t="b">
         <v>0</v>
       </c>
       <c r="AE249" t="b">
         <v>0</v>
       </c>
-      <c r="AF249" t="inlineStr"/>
       <c r="AG249" t="b">
         <v>0</v>
       </c>
@@ -26096,32 +26096,32 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>128428569</v>
+        <v>128428566</v>
       </c>
       <c r="B255" t="n">
-        <v>91470</v>
+        <v>58055</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -26131,10 +26131,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>635359</v>
+        <v>634515</v>
       </c>
       <c r="R255" t="n">
-        <v>7087150</v>
+        <v>7087381</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26193,32 +26193,32 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>128428566</v>
+        <v>128428583</v>
       </c>
       <c r="B256" t="n">
-        <v>58055</v>
+        <v>82942</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>103015</v>
+        <v>1312</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -26228,10 +26228,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>634515</v>
+        <v>634880</v>
       </c>
       <c r="R256" t="n">
-        <v>7087381</v>
+        <v>7087375</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26290,10 +26290,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128428583</v>
+        <v>128428569</v>
       </c>
       <c r="B257" t="n">
-        <v>82942</v>
+        <v>91470</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -26301,21 +26301,21 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -26325,10 +26325,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>634880</v>
+        <v>635359</v>
       </c>
       <c r="R257" t="n">
-        <v>7087375</v>
+        <v>7087150</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -26387,10 +26387,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128428579</v>
+        <v>128428543</v>
       </c>
       <c r="B258" t="n">
-        <v>79083</v>
+        <v>57845</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -26398,21 +26398,21 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -26422,10 +26422,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>634645</v>
+        <v>635352</v>
       </c>
       <c r="R258" t="n">
-        <v>7087310</v>
+        <v>7087202</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -26484,32 +26484,32 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>128428549</v>
+        <v>128428579</v>
       </c>
       <c r="B259" t="n">
-        <v>80217</v>
+        <v>79083</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -26519,10 +26519,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>635412</v>
+        <v>634645</v>
       </c>
       <c r="R259" t="n">
-        <v>7087169</v>
+        <v>7087310</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -26581,32 +26581,32 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>128428543</v>
+        <v>128428549</v>
       </c>
       <c r="B260" t="n">
-        <v>57845</v>
+        <v>80217</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -26616,10 +26616,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>635352</v>
+        <v>635412</v>
       </c>
       <c r="R260" t="n">
-        <v>7087202</v>
+        <v>7087169</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -27370,32 +27370,32 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>128428541</v>
+        <v>128428567</v>
       </c>
       <c r="B268" t="n">
-        <v>57845</v>
+        <v>75154</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>103021</v>
+        <v>6439</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -27405,10 +27405,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>635537</v>
+        <v>635532</v>
       </c>
       <c r="R268" t="n">
-        <v>7087207</v>
+        <v>7087324</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -27467,10 +27467,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>128428565</v>
+        <v>128428561</v>
       </c>
       <c r="B269" t="n">
-        <v>58055</v>
+        <v>80224</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -27478,46 +27478,34 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>103015</v>
+        <v>6464</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I269" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K269" t="inlineStr"/>
-      <c r="L269" t="inlineStr"/>
-      <c r="M269" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N269" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>635275</v>
+        <v>634879</v>
       </c>
       <c r="R269" t="n">
-        <v>7087098</v>
+        <v>7087368</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -27576,32 +27564,32 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>128428567</v>
+        <v>128428541</v>
       </c>
       <c r="B270" t="n">
-        <v>75154</v>
+        <v>57845</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>6439</v>
+        <v>103021</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
@@ -27611,10 +27599,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>635532</v>
+        <v>635537</v>
       </c>
       <c r="R270" t="n">
-        <v>7087324</v>
+        <v>7087207</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -27673,10 +27661,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>128428561</v>
+        <v>128428565</v>
       </c>
       <c r="B271" t="n">
-        <v>80224</v>
+        <v>58055</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -27684,34 +27672,46 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>6464</v>
+        <v>103015</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I271" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr"/>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>634879</v>
+        <v>635275</v>
       </c>
       <c r="R271" t="n">
-        <v>7087368</v>
+        <v>7087098</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -27770,32 +27770,32 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>128428593</v>
+        <v>128428585</v>
       </c>
       <c r="B272" t="n">
-        <v>80223</v>
+        <v>82942</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
@@ -27805,10 +27805,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>635390</v>
+        <v>634615</v>
       </c>
       <c r="R272" t="n">
-        <v>7087179</v>
+        <v>7087516</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -27867,10 +27867,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>128428544</v>
+        <v>128428593</v>
       </c>
       <c r="B273" t="n">
-        <v>80217</v>
+        <v>80223</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -27878,21 +27878,21 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
@@ -27902,10 +27902,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>635039</v>
+        <v>635390</v>
       </c>
       <c r="R273" t="n">
-        <v>7087283</v>
+        <v>7087179</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -27964,32 +27964,32 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>128428572</v>
+        <v>128428544</v>
       </c>
       <c r="B274" t="n">
-        <v>79083</v>
+        <v>80217</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -27999,10 +27999,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>634969</v>
+        <v>635039</v>
       </c>
       <c r="R274" t="n">
-        <v>7087325</v>
+        <v>7087283</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28061,10 +28061,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>128428585</v>
+        <v>128428572</v>
       </c>
       <c r="B275" t="n">
-        <v>82942</v>
+        <v>79083</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -28072,21 +28072,21 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -28096,10 +28096,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>634615</v>
+        <v>634969</v>
       </c>
       <c r="R275" t="n">
-        <v>7087516</v>
+        <v>7087325</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -28979,7 +28979,7 @@
         <v>128492196</v>
       </c>
       <c r="B284" t="n">
-        <v>95815</v>
+        <v>95821</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>128492197</v>
       </c>
       <c r="B285" t="n">
-        <v>95803</v>
+        <v>95809</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>128651017</v>
       </c>
       <c r="B286" t="n">
-        <v>96919</v>
+        <v>96924</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>

--- a/artfynd/A 30047-2025 artfynd.xlsx
+++ b/artfynd/A 30047-2025 artfynd.xlsx
@@ -8178,32 +8178,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128423621</v>
+        <v>128423612</v>
       </c>
       <c r="B75" t="n">
-        <v>82946</v>
+        <v>58059</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1312</v>
+        <v>103015</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8213,10 +8213,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>634525</v>
+        <v>634913</v>
       </c>
       <c r="R75" t="n">
-        <v>7087295</v>
+        <v>7087585</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8275,45 +8275,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128411934</v>
+        <v>128423621</v>
       </c>
       <c r="B76" t="n">
-        <v>91429</v>
+        <v>82946</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
         <v>634525</v>
       </c>
       <c r="R76" t="n">
-        <v>7087336</v>
+        <v>7087295</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8343,19 +8343,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8370,57 +8360,57 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128423159</v>
+        <v>128411934</v>
       </c>
       <c r="B77" t="n">
-        <v>79087</v>
+        <v>91429</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>635080</v>
+        <v>634525</v>
       </c>
       <c r="R77" t="n">
-        <v>7087206</v>
+        <v>7087336</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8450,9 +8440,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8467,44 +8467,44 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128423142</v>
+        <v>128423159</v>
       </c>
       <c r="B78" t="n">
-        <v>80228</v>
+        <v>79087</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8514,10 +8514,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>635234</v>
+        <v>635080</v>
       </c>
       <c r="R78" t="n">
-        <v>7087170</v>
+        <v>7087206</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8576,7 +8576,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128423140</v>
+        <v>128423142</v>
       </c>
       <c r="B79" t="n">
         <v>80228</v>
@@ -8611,10 +8611,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>635608</v>
+        <v>635234</v>
       </c>
       <c r="R79" t="n">
-        <v>7087280</v>
+        <v>7087170</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8673,32 +8673,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128423165</v>
+        <v>128423140</v>
       </c>
       <c r="B80" t="n">
-        <v>79087</v>
+        <v>80228</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8708,10 +8708,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>634654</v>
+        <v>635608</v>
       </c>
       <c r="R80" t="n">
-        <v>7087545</v>
+        <v>7087280</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8770,32 +8770,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128423591</v>
+        <v>128423165</v>
       </c>
       <c r="B81" t="n">
-        <v>80221</v>
+        <v>79087</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>635451</v>
+        <v>634654</v>
       </c>
       <c r="R81" t="n">
-        <v>7087225</v>
+        <v>7087545</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8855,44 +8855,44 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128423597</v>
+        <v>128423591</v>
       </c>
       <c r="B82" t="n">
-        <v>57686</v>
+        <v>80221</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8902,10 +8902,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>634913</v>
+        <v>635451</v>
       </c>
       <c r="R82" t="n">
-        <v>7087585</v>
+        <v>7087225</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8964,27 +8964,27 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128423612</v>
+        <v>128423597</v>
       </c>
       <c r="B83" t="n">
-        <v>58059</v>
+        <v>57686</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -9061,32 +9061,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128423575</v>
+        <v>128423618</v>
       </c>
       <c r="B84" t="n">
-        <v>91429</v>
+        <v>91482</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9096,10 +9096,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>634574</v>
+        <v>634676</v>
       </c>
       <c r="R84" t="n">
-        <v>7087286</v>
+        <v>7087616</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9158,32 +9158,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128423618</v>
+        <v>128423575</v>
       </c>
       <c r="B85" t="n">
-        <v>91482</v>
+        <v>91429</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9193,10 +9193,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>634676</v>
+        <v>634574</v>
       </c>
       <c r="R85" t="n">
-        <v>7087616</v>
+        <v>7087286</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10827,10 +10827,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128423176</v>
+        <v>128423148</v>
       </c>
       <c r="B102" t="n">
-        <v>79087</v>
+        <v>91478</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10838,21 +10838,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10862,10 +10862,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>635233</v>
+        <v>634924</v>
       </c>
       <c r="R102" t="n">
-        <v>7087199</v>
+        <v>7087448</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10924,10 +10924,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128405478</v>
+        <v>128423622</v>
       </c>
       <c r="B103" t="n">
-        <v>79087</v>
+        <v>88865</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10935,39 +10935,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>635443</v>
+        <v>634642</v>
       </c>
       <c r="R103" t="n">
-        <v>7087145</v>
+        <v>7087251</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10997,19 +10992,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>11:18</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11024,22 +11009,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128423148</v>
+        <v>128423625</v>
       </c>
       <c r="B104" t="n">
-        <v>91478</v>
+        <v>88865</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11047,21 +11032,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1204</v>
+        <v>510</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11071,10 +11056,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>634924</v>
+        <v>634494</v>
       </c>
       <c r="R104" t="n">
-        <v>7087448</v>
+        <v>7087408</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11121,22 +11106,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128423622</v>
+        <v>128423176</v>
       </c>
       <c r="B105" t="n">
-        <v>88865</v>
+        <v>79087</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11144,21 +11129,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11168,10 +11153,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>634642</v>
+        <v>635233</v>
       </c>
       <c r="R105" t="n">
-        <v>7087251</v>
+        <v>7087199</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11218,22 +11203,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128423625</v>
+        <v>128405478</v>
       </c>
       <c r="B106" t="n">
-        <v>88865</v>
+        <v>79087</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11241,34 +11226,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>634494</v>
+        <v>635443</v>
       </c>
       <c r="R106" t="n">
-        <v>7087408</v>
+        <v>7087145</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11298,9 +11288,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11315,12 +11315,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -17432,10 +17432,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128423181</v>
+        <v>128423614</v>
       </c>
       <c r="B168" t="n">
-        <v>79087</v>
+        <v>91478</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17443,21 +17443,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17467,10 +17467,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>635471</v>
+        <v>634673</v>
       </c>
       <c r="R168" t="n">
-        <v>7087243</v>
+        <v>7087631</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17517,44 +17517,44 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128423576</v>
+        <v>128423147</v>
       </c>
       <c r="B169" t="n">
-        <v>91429</v>
+        <v>91478</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17564,10 +17564,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>634705</v>
+        <v>634571</v>
       </c>
       <c r="R169" t="n">
-        <v>7087668</v>
+        <v>7087288</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17614,22 +17614,22 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128404367</v>
+        <v>128412855</v>
       </c>
       <c r="B170" t="n">
-        <v>79087</v>
+        <v>91760</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17637,41 +17637,34 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>635556</v>
+        <v>634574</v>
       </c>
       <c r="R170" t="n">
-        <v>7087281</v>
+        <v>7087273</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17703,7 +17696,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -17713,7 +17706,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -17722,7 +17715,6 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
-      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -17741,7 +17733,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128423161</v>
+        <v>128423181</v>
       </c>
       <c r="B171" t="n">
         <v>79087</v>
@@ -17776,10 +17768,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>634702</v>
+        <v>635471</v>
       </c>
       <c r="R171" t="n">
-        <v>7087248</v>
+        <v>7087243</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17838,32 +17830,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128423614</v>
+        <v>128423576</v>
       </c>
       <c r="B172" t="n">
-        <v>91478</v>
+        <v>91429</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17873,10 +17865,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>634673</v>
+        <v>634705</v>
       </c>
       <c r="R172" t="n">
-        <v>7087631</v>
+        <v>7087668</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17935,10 +17927,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128423147</v>
+        <v>128404367</v>
       </c>
       <c r="B173" t="n">
-        <v>91478</v>
+        <v>79087</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17946,34 +17938,41 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>634571</v>
+        <v>635556</v>
       </c>
       <c r="R173" t="n">
-        <v>7087288</v>
+        <v>7087281</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18003,39 +18002,50 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AD173" t="b">
         <v>0</v>
       </c>
       <c r="AE173" t="b">
         <v>0</v>
       </c>
+      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128412855</v>
+        <v>128423161</v>
       </c>
       <c r="B174" t="n">
-        <v>91760</v>
+        <v>79087</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18043,34 +18053,34 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>634574</v>
+        <v>634702</v>
       </c>
       <c r="R174" t="n">
-        <v>7087273</v>
+        <v>7087248</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18100,19 +18110,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB174" t="inlineStr">
-        <is>
-          <t>16:03</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18127,12 +18127,12 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
@@ -18245,10 +18245,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128411794</v>
+        <v>128423598</v>
       </c>
       <c r="B176" t="n">
-        <v>57849</v>
+        <v>80193</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18256,42 +18256,34 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>634505</v>
+        <v>635632</v>
       </c>
       <c r="R176" t="n">
-        <v>7087326</v>
+        <v>7087270</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18321,19 +18313,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z176" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB176" t="inlineStr">
-        <is>
-          <t>15:28</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18348,44 +18330,44 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128423592</v>
+        <v>128423149</v>
       </c>
       <c r="B177" t="n">
-        <v>80221</v>
+        <v>91478</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18395,10 +18377,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>635454</v>
+        <v>634942</v>
       </c>
       <c r="R177" t="n">
-        <v>7087257</v>
+        <v>7087434</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18445,44 +18427,44 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128423598</v>
+        <v>128423111</v>
       </c>
       <c r="B178" t="n">
-        <v>80193</v>
+        <v>91475</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>2081</v>
+        <v>1205</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18492,10 +18474,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>635632</v>
+        <v>635441</v>
       </c>
       <c r="R178" t="n">
-        <v>7087270</v>
+        <v>7087163</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18542,44 +18524,44 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128423149</v>
+        <v>128423599</v>
       </c>
       <c r="B179" t="n">
-        <v>91478</v>
+        <v>91918</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18589,10 +18571,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>634942</v>
+        <v>635464</v>
       </c>
       <c r="R179" t="n">
-        <v>7087434</v>
+        <v>7087275</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18639,44 +18621,44 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128423111</v>
+        <v>128423150</v>
       </c>
       <c r="B180" t="n">
-        <v>91475</v>
+        <v>91482</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1205</v>
+        <v>5432</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18686,10 +18668,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>635441</v>
+        <v>634998</v>
       </c>
       <c r="R180" t="n">
-        <v>7087163</v>
+        <v>7087278</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18748,45 +18730,53 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128423599</v>
+        <v>128411527</v>
       </c>
       <c r="B181" t="n">
-        <v>91918</v>
+        <v>57689</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>635464</v>
+        <v>634480</v>
       </c>
       <c r="R181" t="n">
-        <v>7087275</v>
+        <v>7087349</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18816,9 +18806,24 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -18833,22 +18838,22 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128423150</v>
+        <v>128423120</v>
       </c>
       <c r="B182" t="n">
-        <v>91482</v>
+        <v>57689</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18856,34 +18861,38 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>634998</v>
+        <v>635205</v>
       </c>
       <c r="R182" t="n">
-        <v>7087278</v>
+        <v>7087342</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18916,6 +18925,11 @@
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -18942,7 +18956,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128411527</v>
+        <v>128423115</v>
       </c>
       <c r="B183" t="n">
         <v>57689</v>
@@ -18971,24 +18985,16 @@
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>634480</v>
+        <v>635461</v>
       </c>
       <c r="R183" t="n">
-        <v>7087349</v>
+        <v>7087189</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19018,24 +19024,14 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z183" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AB183" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19050,61 +19046,57 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128423120</v>
+        <v>128423592</v>
       </c>
       <c r="B184" t="n">
-        <v>57689</v>
+        <v>80221</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>635205</v>
+        <v>635454</v>
       </c>
       <c r="R184" t="n">
-        <v>7087342</v>
+        <v>7087257</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19139,11 +19131,6 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD184" t="b">
         <v>0</v>
       </c>
@@ -19156,22 +19143,22 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128423115</v>
+        <v>128411794</v>
       </c>
       <c r="B185" t="n">
-        <v>57689</v>
+        <v>57849</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19179,34 +19166,42 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>635461</v>
+        <v>634505</v>
       </c>
       <c r="R185" t="n">
-        <v>7087189</v>
+        <v>7087326</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19236,14 +19231,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19258,12 +19258,12 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
@@ -19954,10 +19954,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128423590</v>
+        <v>128423172</v>
       </c>
       <c r="B193" t="n">
-        <v>92746</v>
+        <v>79087</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19965,21 +19965,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19989,10 +19989,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>635182</v>
+        <v>635010</v>
       </c>
       <c r="R193" t="n">
-        <v>7087227</v>
+        <v>7087362</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20039,44 +20039,44 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128423172</v>
+        <v>128423138</v>
       </c>
       <c r="B194" t="n">
-        <v>79087</v>
+        <v>80228</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20086,10 +20086,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>635010</v>
+        <v>635160</v>
       </c>
       <c r="R194" t="n">
-        <v>7087362</v>
+        <v>7087012</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20148,32 +20148,32 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128423138</v>
+        <v>128423168</v>
       </c>
       <c r="B195" t="n">
-        <v>80228</v>
+        <v>79087</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20183,10 +20183,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>635160</v>
+        <v>634865</v>
       </c>
       <c r="R195" t="n">
-        <v>7087012</v>
+        <v>7087586</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20245,32 +20245,32 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>128423168</v>
+        <v>128423109</v>
       </c>
       <c r="B196" t="n">
-        <v>79087</v>
+        <v>80221</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20280,10 +20280,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>634865</v>
+        <v>635407</v>
       </c>
       <c r="R196" t="n">
-        <v>7087586</v>
+        <v>7087128</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20342,32 +20342,32 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>128423109</v>
+        <v>128423135</v>
       </c>
       <c r="B197" t="n">
-        <v>80221</v>
+        <v>80192</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20377,10 +20377,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>635407</v>
+        <v>635412</v>
       </c>
       <c r="R197" t="n">
-        <v>7087128</v>
+        <v>7087118</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20439,10 +20439,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>128423135</v>
+        <v>128423118</v>
       </c>
       <c r="B198" t="n">
-        <v>80192</v>
+        <v>57689</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20450,21 +20450,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -20474,10 +20474,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>635412</v>
+        <v>634924</v>
       </c>
       <c r="R198" t="n">
-        <v>7087118</v>
+        <v>7087288</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20512,6 +20512,11 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD198" t="b">
         <v>0</v>
       </c>
@@ -20520,6 +20525,21 @@
       </c>
       <c r="AG198" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ198" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK198" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO198" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
@@ -20536,10 +20556,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>128423160</v>
+        <v>128423590</v>
       </c>
       <c r="B199" t="n">
-        <v>79087</v>
+        <v>92746</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20547,21 +20567,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -20571,10 +20591,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>634916</v>
+        <v>635182</v>
       </c>
       <c r="R199" t="n">
-        <v>7087311</v>
+        <v>7087227</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20621,22 +20641,22 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>128423596</v>
+        <v>128423160</v>
       </c>
       <c r="B200" t="n">
-        <v>57686</v>
+        <v>79087</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20644,21 +20664,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20668,10 +20688,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>634648</v>
+        <v>634916</v>
       </c>
       <c r="R200" t="n">
-        <v>7087590</v>
+        <v>7087311</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20718,22 +20738,22 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>128423118</v>
+        <v>128423596</v>
       </c>
       <c r="B201" t="n">
-        <v>57689</v>
+        <v>57686</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20741,16 +20761,16 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -20765,10 +20785,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>634924</v>
+        <v>634648</v>
       </c>
       <c r="R201" t="n">
-        <v>7087288</v>
+        <v>7087590</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20803,11 +20823,6 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD201" t="b">
         <v>0</v>
       </c>
@@ -20816,31 +20831,16 @@
       </c>
       <c r="AG201" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ201" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK201" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO201" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
@@ -22331,32 +22331,32 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>128423094</v>
+        <v>128423130</v>
       </c>
       <c r="B217" t="n">
-        <v>91429</v>
+        <v>80192</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -22366,10 +22366,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>635358</v>
+        <v>635267</v>
       </c>
       <c r="R217" t="n">
-        <v>7087128</v>
+        <v>7087054</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22412,6 +22412,21 @@
       </c>
       <c r="AG217" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ217" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK217" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO217" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT217" t="inlineStr"/>
       <c r="AW217" t="inlineStr">
@@ -22428,7 +22443,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>128423574</v>
+        <v>128423094</v>
       </c>
       <c r="B218" t="n">
         <v>91429</v>
@@ -22463,10 +22478,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>634571</v>
+        <v>635358</v>
       </c>
       <c r="R218" t="n">
-        <v>7087253</v>
+        <v>7087128</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -22513,44 +22528,44 @@
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>128423183</v>
+        <v>128423574</v>
       </c>
       <c r="B219" t="n">
-        <v>79087</v>
+        <v>91429</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -22560,10 +22575,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>635482</v>
+        <v>634571</v>
       </c>
       <c r="R219" t="n">
-        <v>7087300</v>
+        <v>7087253</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22610,22 +22625,22 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>128423130</v>
+        <v>128423183</v>
       </c>
       <c r="B220" t="n">
-        <v>80192</v>
+        <v>79087</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -22633,21 +22648,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -22657,10 +22672,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>635267</v>
+        <v>635482</v>
       </c>
       <c r="R220" t="n">
-        <v>7087054</v>
+        <v>7087300</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22703,21 +22718,6 @@
       </c>
       <c r="AG220" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ220" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK220" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO220" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
@@ -23724,32 +23724,32 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>128428563</v>
+        <v>128428595</v>
       </c>
       <c r="B231" t="n">
-        <v>57793</v>
+        <v>75167</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>103031</v>
+        <v>308</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -23759,10 +23759,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>635011</v>
+        <v>634678</v>
       </c>
       <c r="R231" t="n">
-        <v>7087362</v>
+        <v>7087320</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -23821,32 +23821,32 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>128428595</v>
+        <v>128428547</v>
       </c>
       <c r="B232" t="n">
-        <v>75167</v>
+        <v>80221</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>308</v>
+        <v>6462</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -23856,10 +23856,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>634678</v>
+        <v>635305</v>
       </c>
       <c r="R232" t="n">
-        <v>7087320</v>
+        <v>7087219</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -23918,10 +23918,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>128428547</v>
+        <v>128428563</v>
       </c>
       <c r="B233" t="n">
-        <v>80221</v>
+        <v>57793</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -23929,21 +23929,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6462</v>
+        <v>103031</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -23953,10 +23953,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>635305</v>
+        <v>635011</v>
       </c>
       <c r="R233" t="n">
-        <v>7087219</v>
+        <v>7087362</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -25611,32 +25611,32 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>128428559</v>
+        <v>128428529</v>
       </c>
       <c r="B250" t="n">
-        <v>80192</v>
+        <v>91429</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -25646,10 +25646,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>635416</v>
+        <v>634593</v>
       </c>
       <c r="R250" t="n">
-        <v>7087178</v>
+        <v>7087306</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -25708,32 +25708,32 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>128428529</v>
+        <v>128428559</v>
       </c>
       <c r="B251" t="n">
-        <v>91429</v>
+        <v>80192</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -25743,10 +25743,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>634593</v>
+        <v>635416</v>
       </c>
       <c r="R251" t="n">
-        <v>7087306</v>
+        <v>7087178</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -26096,32 +26096,32 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>128428566</v>
+        <v>128428583</v>
       </c>
       <c r="B255" t="n">
-        <v>58059</v>
+        <v>82946</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>103015</v>
+        <v>1312</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -26131,10 +26131,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>634515</v>
+        <v>634880</v>
       </c>
       <c r="R255" t="n">
-        <v>7087381</v>
+        <v>7087375</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26193,10 +26193,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>128428583</v>
+        <v>128428569</v>
       </c>
       <c r="B256" t="n">
-        <v>82946</v>
+        <v>91482</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -26204,21 +26204,21 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -26228,10 +26228,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>634880</v>
+        <v>635359</v>
       </c>
       <c r="R256" t="n">
-        <v>7087375</v>
+        <v>7087150</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26290,32 +26290,32 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128428569</v>
+        <v>128428566</v>
       </c>
       <c r="B257" t="n">
-        <v>91482</v>
+        <v>58059</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -26325,10 +26325,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>635359</v>
+        <v>634515</v>
       </c>
       <c r="R257" t="n">
-        <v>7087150</v>
+        <v>7087381</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -26678,10 +26678,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128428532</v>
+        <v>128428558</v>
       </c>
       <c r="B261" t="n">
-        <v>91464</v>
+        <v>80192</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -26689,21 +26689,21 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -26713,10 +26713,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>634476</v>
+        <v>635306</v>
       </c>
       <c r="R261" t="n">
-        <v>7087366</v>
+        <v>7087221</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26775,10 +26775,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128428558</v>
+        <v>128428532</v>
       </c>
       <c r="B262" t="n">
-        <v>80192</v>
+        <v>91464</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -26786,21 +26786,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -26810,10 +26810,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>635306</v>
+        <v>634476</v>
       </c>
       <c r="R262" t="n">
-        <v>7087221</v>
+        <v>7087366</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>

--- a/artfynd/A 30047-2025 artfynd.xlsx
+++ b/artfynd/A 30047-2025 artfynd.xlsx
@@ -6800,10 +6800,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128423582</v>
+        <v>128408718</v>
       </c>
       <c r="B61" t="n">
-        <v>91746</v>
+        <v>91484</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6811,34 +6811,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>73</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>635466</v>
+        <v>635017</v>
       </c>
       <c r="R61" t="n">
-        <v>7087277</v>
+        <v>7087370</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6868,9 +6868,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6885,44 +6895,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128423112</v>
+        <v>128423091</v>
       </c>
       <c r="B62" t="n">
-        <v>91414</v>
+        <v>91431</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>112</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6932,10 +6942,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>634544</v>
+        <v>634922</v>
       </c>
       <c r="R62" t="n">
-        <v>7087320</v>
+        <v>7087295</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6994,10 +7004,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128408718</v>
+        <v>128408152</v>
       </c>
       <c r="B63" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7029,10 +7039,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>635017</v>
+        <v>635231</v>
       </c>
       <c r="R63" t="n">
-        <v>7087370</v>
+        <v>7087279</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7064,7 +7074,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7074,7 +7084,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7101,32 +7111,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128423091</v>
+        <v>128423582</v>
       </c>
       <c r="B64" t="n">
-        <v>91429</v>
+        <v>91748</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>73</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7136,10 +7146,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>634922</v>
+        <v>635466</v>
       </c>
       <c r="R64" t="n">
-        <v>7087295</v>
+        <v>7087277</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7186,22 +7196,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128423158</v>
+        <v>128423112</v>
       </c>
       <c r="B65" t="n">
-        <v>79087</v>
+        <v>91416</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7209,21 +7219,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7233,10 +7243,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>635124</v>
+        <v>634544</v>
       </c>
       <c r="R65" t="n">
-        <v>7087198</v>
+        <v>7087320</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7295,10 +7305,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128408152</v>
+        <v>128423158</v>
       </c>
       <c r="B66" t="n">
-        <v>91482</v>
+        <v>79089</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7306,34 +7316,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>635231</v>
+        <v>635124</v>
       </c>
       <c r="R66" t="n">
-        <v>7087279</v>
+        <v>7087198</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7363,19 +7373,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>12:54</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7390,12 +7390,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7405,7 +7405,7 @@
         <v>128423605</v>
       </c>
       <c r="B67" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>128423608</v>
       </c>
       <c r="B68" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7596,32 +7596,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128423192</v>
+        <v>128423573</v>
       </c>
       <c r="B69" t="n">
-        <v>88865</v>
+        <v>91431</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7631,10 +7631,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>634595</v>
+        <v>634599</v>
       </c>
       <c r="R69" t="n">
-        <v>7087268</v>
+        <v>7087225</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7681,22 +7681,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128423623</v>
+        <v>128423192</v>
       </c>
       <c r="B70" t="n">
-        <v>88865</v>
+        <v>88867</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7728,10 +7728,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>634583</v>
+        <v>634595</v>
       </c>
       <c r="R70" t="n">
-        <v>7087261</v>
+        <v>7087268</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7778,44 +7778,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128423573</v>
+        <v>128423623</v>
       </c>
       <c r="B71" t="n">
-        <v>91429</v>
+        <v>88867</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7825,10 +7825,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>634599</v>
+        <v>634583</v>
       </c>
       <c r="R71" t="n">
-        <v>7087225</v>
+        <v>7087261</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7887,10 +7887,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128423179</v>
+        <v>128423180</v>
       </c>
       <c r="B72" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7922,10 +7922,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>635348</v>
+        <v>635376</v>
       </c>
       <c r="R72" t="n">
-        <v>7087138</v>
+        <v>7087128</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7987,7 +7987,7 @@
         <v>128423178</v>
       </c>
       <c r="B73" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8081,10 +8081,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128423180</v>
+        <v>128423179</v>
       </c>
       <c r="B74" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8116,10 +8116,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>635376</v>
+        <v>635348</v>
       </c>
       <c r="R74" t="n">
-        <v>7087128</v>
+        <v>7087138</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8178,32 +8178,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128423612</v>
+        <v>128423621</v>
       </c>
       <c r="B75" t="n">
-        <v>58059</v>
+        <v>82948</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103015</v>
+        <v>1312</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8213,10 +8213,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>634913</v>
+        <v>634525</v>
       </c>
       <c r="R75" t="n">
-        <v>7087585</v>
+        <v>7087295</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8275,10 +8275,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128423621</v>
+        <v>128423597</v>
       </c>
       <c r="B76" t="n">
-        <v>82946</v>
+        <v>57686</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8286,21 +8286,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8310,10 +8310,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>634525</v>
+        <v>634913</v>
       </c>
       <c r="R76" t="n">
-        <v>7087295</v>
+        <v>7087585</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8372,10 +8372,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128411934</v>
+        <v>128423142</v>
       </c>
       <c r="B77" t="n">
-        <v>91429</v>
+        <v>80230</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8383,34 +8383,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>6464</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>634525</v>
+        <v>635234</v>
       </c>
       <c r="R77" t="n">
-        <v>7087336</v>
+        <v>7087170</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8440,19 +8440,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8467,12 +8457,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8482,7 +8472,7 @@
         <v>128423159</v>
       </c>
       <c r="B78" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8576,10 +8566,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128423142</v>
+        <v>128423140</v>
       </c>
       <c r="B79" t="n">
-        <v>80228</v>
+        <v>80230</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8611,10 +8601,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>635234</v>
+        <v>635608</v>
       </c>
       <c r="R79" t="n">
-        <v>7087170</v>
+        <v>7087280</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8673,32 +8663,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128423140</v>
+        <v>128423165</v>
       </c>
       <c r="B80" t="n">
-        <v>80228</v>
+        <v>79089</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8708,10 +8698,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>635608</v>
+        <v>634654</v>
       </c>
       <c r="R80" t="n">
-        <v>7087280</v>
+        <v>7087545</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8770,32 +8760,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128423165</v>
+        <v>128423591</v>
       </c>
       <c r="B81" t="n">
-        <v>79087</v>
+        <v>80223</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8805,10 +8795,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>634654</v>
+        <v>635451</v>
       </c>
       <c r="R81" t="n">
-        <v>7087545</v>
+        <v>7087225</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8855,22 +8845,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128423591</v>
+        <v>128411934</v>
       </c>
       <c r="B82" t="n">
-        <v>80221</v>
+        <v>91431</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8878,34 +8868,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>635451</v>
+        <v>634525</v>
       </c>
       <c r="R82" t="n">
-        <v>7087225</v>
+        <v>7087336</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8935,9 +8925,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8952,39 +8952,39 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128423597</v>
+        <v>128423612</v>
       </c>
       <c r="B83" t="n">
-        <v>57686</v>
+        <v>58059</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -9061,32 +9061,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128423618</v>
+        <v>128423106</v>
       </c>
       <c r="B84" t="n">
-        <v>91482</v>
+        <v>80223</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9096,10 +9096,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>634676</v>
+        <v>634926</v>
       </c>
       <c r="R84" t="n">
-        <v>7087616</v>
+        <v>7087292</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9146,44 +9146,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128423575</v>
+        <v>128423166</v>
       </c>
       <c r="B85" t="n">
-        <v>91429</v>
+        <v>79089</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9193,10 +9193,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>634574</v>
+        <v>634652</v>
       </c>
       <c r="R85" t="n">
-        <v>7087286</v>
+        <v>7087690</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9243,44 +9243,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128423106</v>
+        <v>128423606</v>
       </c>
       <c r="B86" t="n">
-        <v>80221</v>
+        <v>80194</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9290,10 +9290,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>634926</v>
+        <v>635122</v>
       </c>
       <c r="R86" t="n">
-        <v>7087292</v>
+        <v>7087242</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9340,22 +9340,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128423166</v>
+        <v>128423618</v>
       </c>
       <c r="B87" t="n">
-        <v>79087</v>
+        <v>91484</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9363,21 +9363,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9387,10 +9387,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>634652</v>
+        <v>634676</v>
       </c>
       <c r="R87" t="n">
-        <v>7087690</v>
+        <v>7087616</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9437,44 +9437,44 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128423606</v>
+        <v>128423575</v>
       </c>
       <c r="B88" t="n">
-        <v>80192</v>
+        <v>91431</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9484,10 +9484,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>635122</v>
+        <v>634574</v>
       </c>
       <c r="R88" t="n">
-        <v>7087242</v>
+        <v>7087286</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9546,32 +9546,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128423099</v>
+        <v>128423624</v>
       </c>
       <c r="B89" t="n">
-        <v>92161</v>
+        <v>88867</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3298</v>
+        <v>510</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9581,10 +9581,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>634570</v>
+        <v>634461</v>
       </c>
       <c r="R89" t="n">
-        <v>7087303</v>
+        <v>7087363</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9631,22 +9631,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128423624</v>
+        <v>128423615</v>
       </c>
       <c r="B90" t="n">
-        <v>88865</v>
+        <v>91480</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9654,21 +9654,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>510</v>
+        <v>1204</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9678,10 +9678,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>634461</v>
+        <v>634897</v>
       </c>
       <c r="R90" t="n">
-        <v>7087363</v>
+        <v>7087591</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9740,10 +9740,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128423615</v>
+        <v>128423097</v>
       </c>
       <c r="B91" t="n">
-        <v>91478</v>
+        <v>91466</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9751,21 +9751,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9775,10 +9775,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>634897</v>
+        <v>635320</v>
       </c>
       <c r="R91" t="n">
-        <v>7087591</v>
+        <v>7087069</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9825,44 +9825,44 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128423097</v>
+        <v>128423099</v>
       </c>
       <c r="B92" t="n">
-        <v>91464</v>
+        <v>92163</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9872,10 +9872,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>635320</v>
+        <v>634570</v>
       </c>
       <c r="R92" t="n">
-        <v>7087069</v>
+        <v>7087303</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9934,45 +9934,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128423092</v>
+        <v>128404903</v>
       </c>
       <c r="B93" t="n">
-        <v>91429</v>
+        <v>91484</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>634661</v>
+        <v>635552</v>
       </c>
       <c r="R93" t="n">
-        <v>7087688</v>
+        <v>7087334</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10002,9 +10002,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10019,57 +10029,57 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128404903</v>
+        <v>128423092</v>
       </c>
       <c r="B94" t="n">
-        <v>91482</v>
+        <v>91431</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>635552</v>
+        <v>634661</v>
       </c>
       <c r="R94" t="n">
-        <v>7087334</v>
+        <v>7087688</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10099,19 +10109,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10126,12 +10126,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10141,7 +10141,7 @@
         <v>128409643</v>
       </c>
       <c r="B95" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>128423628</v>
       </c>
       <c r="B96" t="n">
-        <v>80227</v>
+        <v>80229</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>128423127</v>
       </c>
       <c r="B97" t="n">
-        <v>79111</v>
+        <v>79113</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>128423189</v>
       </c>
       <c r="B98" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>128423155</v>
       </c>
       <c r="B99" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>128423175</v>
       </c>
       <c r="B100" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10730,10 +10730,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128423617</v>
+        <v>128423625</v>
       </c>
       <c r="B101" t="n">
-        <v>91482</v>
+        <v>88867</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10741,21 +10741,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10765,10 +10765,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>634507</v>
+        <v>634494</v>
       </c>
       <c r="R101" t="n">
-        <v>7087328</v>
+        <v>7087408</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10827,10 +10827,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128423148</v>
+        <v>128423617</v>
       </c>
       <c r="B102" t="n">
-        <v>91478</v>
+        <v>91484</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10838,21 +10838,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10862,10 +10862,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>634924</v>
+        <v>634507</v>
       </c>
       <c r="R102" t="n">
-        <v>7087448</v>
+        <v>7087328</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10912,22 +10912,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128423622</v>
+        <v>128423148</v>
       </c>
       <c r="B103" t="n">
-        <v>88865</v>
+        <v>91480</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10935,21 +10935,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>510</v>
+        <v>1204</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10959,10 +10959,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>634642</v>
+        <v>634924</v>
       </c>
       <c r="R103" t="n">
-        <v>7087251</v>
+        <v>7087448</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11009,22 +11009,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128423625</v>
+        <v>128423622</v>
       </c>
       <c r="B104" t="n">
-        <v>88865</v>
+        <v>88867</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11056,10 +11056,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>634494</v>
+        <v>634642</v>
       </c>
       <c r="R104" t="n">
-        <v>7087408</v>
+        <v>7087251</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11118,10 +11118,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128423176</v>
+        <v>128405478</v>
       </c>
       <c r="B105" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11147,16 +11147,21 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>635233</v>
+        <v>635443</v>
       </c>
       <c r="R105" t="n">
-        <v>7087199</v>
+        <v>7087145</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11186,9 +11191,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11203,22 +11218,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128405478</v>
+        <v>128423176</v>
       </c>
       <c r="B106" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11244,21 +11259,16 @@
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>635443</v>
+        <v>635233</v>
       </c>
       <c r="R106" t="n">
-        <v>7087145</v>
+        <v>7087199</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11288,19 +11298,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>11:18</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11315,12 +11315,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -11330,7 +11330,7 @@
         <v>128423593</v>
       </c>
       <c r="B107" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11427,7 +11427,7 @@
         <v>128423110</v>
       </c>
       <c r="B108" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         <v>128423629</v>
       </c>
       <c r="B109" t="n">
-        <v>80227</v>
+        <v>80229</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11720,32 +11720,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128423193</v>
+        <v>128423089</v>
       </c>
       <c r="B111" t="n">
-        <v>88865</v>
+        <v>91431</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11755,10 +11755,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>634638</v>
+        <v>635295</v>
       </c>
       <c r="R111" t="n">
-        <v>7087656</v>
+        <v>7087129</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11817,10 +11817,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128423626</v>
+        <v>128423193</v>
       </c>
       <c r="B112" t="n">
-        <v>88865</v>
+        <v>88867</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11852,10 +11852,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>634705</v>
+        <v>634638</v>
       </c>
       <c r="R112" t="n">
-        <v>7087668</v>
+        <v>7087656</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11902,22 +11902,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128423116</v>
+        <v>128423626</v>
       </c>
       <c r="B113" t="n">
-        <v>57689</v>
+        <v>88867</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11925,21 +11925,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11949,10 +11949,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>635330</v>
+        <v>634705</v>
       </c>
       <c r="R113" t="n">
-        <v>7087114</v>
+        <v>7087668</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11987,11 +11987,6 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
@@ -12004,22 +11999,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128423085</v>
+        <v>128410776</v>
       </c>
       <c r="B114" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12027,34 +12022,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>635508</v>
+        <v>634709</v>
       </c>
       <c r="R114" t="n">
-        <v>7087292</v>
+        <v>7087670</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12084,14 +12079,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12106,44 +12106,44 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128423089</v>
+        <v>128423136</v>
       </c>
       <c r="B115" t="n">
-        <v>91429</v>
+        <v>80194</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12153,10 +12153,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>635295</v>
+        <v>635422</v>
       </c>
       <c r="R115" t="n">
-        <v>7087129</v>
+        <v>7087149</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12215,27 +12215,27 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128423154</v>
+        <v>128423195</v>
       </c>
       <c r="B116" t="n">
-        <v>79087</v>
+        <v>80229</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12250,10 +12250,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>635479</v>
+        <v>635228</v>
       </c>
       <c r="R116" t="n">
-        <v>7087148</v>
+        <v>7087058</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12312,10 +12312,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128423136</v>
+        <v>128423154</v>
       </c>
       <c r="B117" t="n">
-        <v>80192</v>
+        <v>79089</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12323,21 +12323,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12347,10 +12347,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>635422</v>
+        <v>635479</v>
       </c>
       <c r="R117" t="n">
-        <v>7087149</v>
+        <v>7087148</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12409,10 +12409,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128410776</v>
+        <v>128423116</v>
       </c>
       <c r="B118" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12420,34 +12420,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>634709</v>
+        <v>635330</v>
       </c>
       <c r="R118" t="n">
-        <v>7087670</v>
+        <v>7087114</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12477,19 +12477,14 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>14:41</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>14:41</t>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12504,44 +12499,44 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128423195</v>
+        <v>128423085</v>
       </c>
       <c r="B119" t="n">
-        <v>80227</v>
+        <v>57689</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12551,10 +12546,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>635228</v>
+        <v>635508</v>
       </c>
       <c r="R119" t="n">
-        <v>7087058</v>
+        <v>7087292</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12587,6 +12582,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12720,32 +12720,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128423585</v>
+        <v>128423153</v>
       </c>
       <c r="B121" t="n">
-        <v>92161</v>
+        <v>91484</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12755,10 +12755,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>634942</v>
+        <v>634880</v>
       </c>
       <c r="R121" t="n">
-        <v>7087590</v>
+        <v>7087564</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12805,44 +12805,44 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128423620</v>
+        <v>128423577</v>
       </c>
       <c r="B122" t="n">
-        <v>79087</v>
+        <v>91431</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12852,10 +12852,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>634756</v>
+        <v>635153</v>
       </c>
       <c r="R122" t="n">
-        <v>7087642</v>
+        <v>7087180</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12914,32 +12914,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128423577</v>
+        <v>128423616</v>
       </c>
       <c r="B123" t="n">
-        <v>91429</v>
+        <v>91484</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12949,10 +12949,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>635153</v>
+        <v>634993</v>
       </c>
       <c r="R123" t="n">
-        <v>7087180</v>
+        <v>7087294</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13011,10 +13011,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128423616</v>
+        <v>128423619</v>
       </c>
       <c r="B124" t="n">
-        <v>91482</v>
+        <v>79089</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13022,21 +13022,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13046,10 +13046,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>634993</v>
+        <v>635513</v>
       </c>
       <c r="R124" t="n">
-        <v>7087294</v>
+        <v>7087316</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13084,12 +13084,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13108,10 +13114,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128423153</v>
+        <v>128423620</v>
       </c>
       <c r="B125" t="n">
-        <v>91482</v>
+        <v>79089</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13119,21 +13125,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13143,10 +13149,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>634880</v>
+        <v>634756</v>
       </c>
       <c r="R125" t="n">
-        <v>7087564</v>
+        <v>7087642</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13193,22 +13199,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128408809</v>
+        <v>128423585</v>
       </c>
       <c r="B126" t="n">
-        <v>80221</v>
+        <v>92163</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13216,34 +13222,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>635017</v>
+        <v>634942</v>
       </c>
       <c r="R126" t="n">
-        <v>7087370</v>
+        <v>7087590</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13273,19 +13279,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>13:18</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13300,57 +13296,57 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128423131</v>
+        <v>128408809</v>
       </c>
       <c r="B127" t="n">
-        <v>80192</v>
+        <v>80223</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>635236</v>
+        <v>635017</v>
       </c>
       <c r="R127" t="n">
-        <v>7087039</v>
+        <v>7087370</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13380,9 +13376,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13397,22 +13403,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128423619</v>
+        <v>128423131</v>
       </c>
       <c r="B128" t="n">
-        <v>79087</v>
+        <v>80194</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13420,21 +13426,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13444,10 +13450,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>635513</v>
+        <v>635236</v>
       </c>
       <c r="R128" t="n">
-        <v>7087316</v>
+        <v>7087039</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13482,30 +13488,24 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -13515,7 +13515,7 @@
         <v>128423594</v>
       </c>
       <c r="B129" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>128423108</v>
       </c>
       <c r="B130" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>128423163</v>
       </c>
       <c r="B131" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>128423174</v>
       </c>
       <c r="B132" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>128423105</v>
       </c>
       <c r="B133" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14000,7 +14000,7 @@
         <v>128423184</v>
       </c>
       <c r="B134" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14094,10 +14094,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128413206</v>
+        <v>128423117</v>
       </c>
       <c r="B135" t="n">
-        <v>57686</v>
+        <v>57689</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14105,16 +14105,16 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -14123,21 +14123,16 @@
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>634574</v>
+        <v>635201</v>
       </c>
       <c r="R135" t="n">
-        <v>7087273</v>
+        <v>7087140</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14167,19 +14162,14 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>16:13</t>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14190,26 +14180,41 @@
       </c>
       <c r="AG135" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128423117</v>
+        <v>128413206</v>
       </c>
       <c r="B136" t="n">
-        <v>57689</v>
+        <v>57686</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14217,16 +14222,16 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -14235,16 +14240,21 @@
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>635201</v>
+        <v>634574</v>
       </c>
       <c r="R136" t="n">
-        <v>7087140</v>
+        <v>7087273</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14274,14 +14284,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14292,41 +14307,26 @@
       </c>
       <c r="AG136" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ136" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK136" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO136" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128423096</v>
+        <v>128423602</v>
       </c>
       <c r="B137" t="n">
-        <v>91464</v>
+        <v>57689</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14334,21 +14334,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14358,10 +14358,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>635249</v>
+        <v>635210</v>
       </c>
       <c r="R137" t="n">
-        <v>7087032</v>
+        <v>7087158</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14396,6 +14396,11 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD137" t="b">
         <v>0</v>
       </c>
@@ -14408,44 +14413,44 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128423098</v>
+        <v>128423578</v>
       </c>
       <c r="B138" t="n">
-        <v>91464</v>
+        <v>91431</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14455,10 +14460,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>635186</v>
+        <v>635327</v>
       </c>
       <c r="R138" t="n">
-        <v>7087317</v>
+        <v>7087158</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14505,22 +14510,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128423177</v>
+        <v>128423096</v>
       </c>
       <c r="B139" t="n">
-        <v>79087</v>
+        <v>91466</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14528,21 +14533,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14552,10 +14557,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>635285</v>
+        <v>635249</v>
       </c>
       <c r="R139" t="n">
-        <v>7087169</v>
+        <v>7087032</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14614,32 +14619,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128423578</v>
+        <v>128423098</v>
       </c>
       <c r="B140" t="n">
-        <v>91429</v>
+        <v>91466</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14649,10 +14654,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>635327</v>
+        <v>635186</v>
       </c>
       <c r="R140" t="n">
-        <v>7087158</v>
+        <v>7087317</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14699,22 +14704,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128423167</v>
+        <v>128404427</v>
       </c>
       <c r="B141" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14740,16 +14745,21 @@
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>634719</v>
+        <v>635552</v>
       </c>
       <c r="R141" t="n">
-        <v>7087623</v>
+        <v>7087334</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14779,9 +14789,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14796,44 +14816,44 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128423128</v>
+        <v>128423167</v>
       </c>
       <c r="B142" t="n">
-        <v>80220</v>
+        <v>79089</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14843,10 +14863,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>634915</v>
+        <v>634719</v>
       </c>
       <c r="R142" t="n">
-        <v>7087322</v>
+        <v>7087623</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14905,32 +14925,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128423607</v>
+        <v>128423128</v>
       </c>
       <c r="B143" t="n">
-        <v>80192</v>
+        <v>80222</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14940,10 +14960,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>635459</v>
+        <v>634915</v>
       </c>
       <c r="R143" t="n">
-        <v>7087231</v>
+        <v>7087322</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14990,22 +15010,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128423157</v>
+        <v>128423607</v>
       </c>
       <c r="B144" t="n">
-        <v>79087</v>
+        <v>80194</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15013,21 +15033,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15037,10 +15057,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>635204</v>
+        <v>635459</v>
       </c>
       <c r="R144" t="n">
-        <v>7087134</v>
+        <v>7087231</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15087,22 +15107,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128423187</v>
+        <v>128423157</v>
       </c>
       <c r="B145" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15134,10 +15154,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>635591</v>
+        <v>635204</v>
       </c>
       <c r="R145" t="n">
-        <v>7087249</v>
+        <v>7087134</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15196,32 +15216,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128423139</v>
+        <v>128423187</v>
       </c>
       <c r="B146" t="n">
-        <v>80228</v>
+        <v>79089</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15231,10 +15251,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>635237</v>
+        <v>635591</v>
       </c>
       <c r="R146" t="n">
-        <v>7087043</v>
+        <v>7087249</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15293,27 +15313,27 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128423194</v>
+        <v>128423177</v>
       </c>
       <c r="B147" t="n">
-        <v>80227</v>
+        <v>79089</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -15328,10 +15348,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>635234</v>
+        <v>635285</v>
       </c>
       <c r="R147" t="n">
-        <v>7087032</v>
+        <v>7087169</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15390,50 +15410,45 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128404427</v>
+        <v>128423139</v>
       </c>
       <c r="B148" t="n">
-        <v>79087</v>
+        <v>80230</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>635552</v>
+        <v>635237</v>
       </c>
       <c r="R148" t="n">
-        <v>7087334</v>
+        <v>7087043</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15463,19 +15478,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>10:33</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15490,44 +15495,44 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128423602</v>
+        <v>128423194</v>
       </c>
       <c r="B149" t="n">
-        <v>57689</v>
+        <v>80229</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15537,10 +15542,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>635210</v>
+        <v>635234</v>
       </c>
       <c r="R149" t="n">
-        <v>7087158</v>
+        <v>7087032</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15575,11 +15580,6 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
@@ -15592,12 +15592,12 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
@@ -15724,45 +15724,45 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128423093</v>
+        <v>128411777</v>
       </c>
       <c r="B151" t="n">
-        <v>91429</v>
+        <v>88867</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>634938</v>
+        <v>634505</v>
       </c>
       <c r="R151" t="n">
-        <v>7087435</v>
+        <v>7087326</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15792,9 +15792,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15809,22 +15819,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128423162</v>
+        <v>128409243</v>
       </c>
       <c r="B152" t="n">
-        <v>79087</v>
+        <v>91480</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15832,34 +15842,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>634580</v>
+        <v>634946</v>
       </c>
       <c r="R152" t="n">
-        <v>7087268</v>
+        <v>7087431</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15889,9 +15899,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -15906,44 +15926,44 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128423107</v>
+        <v>128423162</v>
       </c>
       <c r="B153" t="n">
-        <v>80221</v>
+        <v>79089</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15953,10 +15973,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>634931</v>
+        <v>634580</v>
       </c>
       <c r="R153" t="n">
-        <v>7087432</v>
+        <v>7087268</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16015,10 +16035,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128423141</v>
+        <v>128423107</v>
       </c>
       <c r="B154" t="n">
-        <v>80228</v>
+        <v>80223</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16026,21 +16046,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16050,10 +16070,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>635232</v>
+        <v>634931</v>
       </c>
       <c r="R154" t="n">
-        <v>7087062</v>
+        <v>7087432</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16112,32 +16132,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128423200</v>
+        <v>128423141</v>
       </c>
       <c r="B155" t="n">
-        <v>57689</v>
+        <v>80230</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16147,10 +16167,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>635225</v>
+        <v>635232</v>
       </c>
       <c r="R155" t="n">
-        <v>7087115</v>
+        <v>7087062</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16183,11 +16203,6 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16214,27 +16229,27 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128409844</v>
+        <v>128423200</v>
       </c>
       <c r="B156" t="n">
-        <v>57793</v>
+        <v>57689</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -16242,31 +16257,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>634713</v>
+        <v>635225</v>
       </c>
       <c r="R156" t="n">
-        <v>7087635</v>
+        <v>7087115</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16296,19 +16297,14 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>13:54</t>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16328,17 +16324,17 @@
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128423122</v>
+        <v>128409160</v>
       </c>
       <c r="B157" t="n">
-        <v>97460</v>
+        <v>91431</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16346,34 +16342,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>634926</v>
+        <v>634944</v>
       </c>
       <c r="R157" t="n">
-        <v>7087302</v>
+        <v>7087430</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16403,9 +16399,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16420,57 +16426,57 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128411777</v>
+        <v>128423093</v>
       </c>
       <c r="B158" t="n">
-        <v>88865</v>
+        <v>91431</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>634505</v>
+        <v>634938</v>
       </c>
       <c r="R158" t="n">
-        <v>7087326</v>
+        <v>7087435</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16500,19 +16506,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>15:28</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16527,57 +16523,71 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128409243</v>
+        <v>128409844</v>
       </c>
       <c r="B159" t="n">
-        <v>91478</v>
+        <v>57793</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1204</v>
+        <v>103031</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>634946</v>
+        <v>634713</v>
       </c>
       <c r="R159" t="n">
-        <v>7087431</v>
+        <v>7087635</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16609,7 +16619,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -16619,7 +16629,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16634,22 +16644,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128409160</v>
+        <v>128423122</v>
       </c>
       <c r="B160" t="n">
-        <v>91429</v>
+        <v>97462</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16657,34 +16667,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>634944</v>
+        <v>634926</v>
       </c>
       <c r="R160" t="n">
-        <v>7087430</v>
+        <v>7087302</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16714,19 +16724,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16741,44 +16741,44 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128423126</v>
+        <v>128423113</v>
       </c>
       <c r="B161" t="n">
-        <v>79111</v>
+        <v>80195</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6434</v>
+        <v>2081</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16788,10 +16788,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>635212</v>
+        <v>635240</v>
       </c>
       <c r="R161" t="n">
-        <v>7087212</v>
+        <v>7087040</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16850,10 +16850,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128423101</v>
+        <v>128423185</v>
       </c>
       <c r="B162" t="n">
-        <v>57849</v>
+        <v>79089</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16861,21 +16861,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16885,10 +16885,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>634716</v>
+        <v>635559</v>
       </c>
       <c r="R162" t="n">
-        <v>7087613</v>
+        <v>7087269</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16947,32 +16947,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128423113</v>
+        <v>128423126</v>
       </c>
       <c r="B163" t="n">
-        <v>80193</v>
+        <v>79113</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>2081</v>
+        <v>6434</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16982,10 +16982,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>635240</v>
+        <v>635212</v>
       </c>
       <c r="R163" t="n">
-        <v>7087040</v>
+        <v>7087212</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17044,10 +17044,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128423572</v>
+        <v>128423101</v>
       </c>
       <c r="B164" t="n">
-        <v>96835</v>
+        <v>57849</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17055,21 +17055,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17079,10 +17079,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>634574</v>
+        <v>634716</v>
       </c>
       <c r="R164" t="n">
-        <v>7087286</v>
+        <v>7087613</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17129,44 +17129,44 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128423191</v>
+        <v>128423090</v>
       </c>
       <c r="B165" t="n">
-        <v>88865</v>
+        <v>91431</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17176,10 +17176,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>634676</v>
+        <v>635155</v>
       </c>
       <c r="R165" t="n">
-        <v>7087233</v>
+        <v>7087185</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17238,32 +17238,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128423090</v>
+        <v>128423572</v>
       </c>
       <c r="B166" t="n">
-        <v>91429</v>
+        <v>96837</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17273,10 +17273,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>635155</v>
+        <v>634574</v>
       </c>
       <c r="R166" t="n">
-        <v>7087185</v>
+        <v>7087286</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17323,22 +17323,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128423185</v>
+        <v>128423191</v>
       </c>
       <c r="B167" t="n">
-        <v>79087</v>
+        <v>88867</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17346,21 +17346,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17370,10 +17370,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>635559</v>
+        <v>634676</v>
       </c>
       <c r="R167" t="n">
-        <v>7087269</v>
+        <v>7087233</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17432,32 +17432,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128423614</v>
+        <v>128423576</v>
       </c>
       <c r="B168" t="n">
-        <v>91478</v>
+        <v>91431</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17467,10 +17467,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>634673</v>
+        <v>634705</v>
       </c>
       <c r="R168" t="n">
-        <v>7087631</v>
+        <v>7087668</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17532,7 +17532,7 @@
         <v>128423147</v>
       </c>
       <c r="B169" t="n">
-        <v>91478</v>
+        <v>91480</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>128412855</v>
       </c>
       <c r="B170" t="n">
-        <v>91760</v>
+        <v>91762</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17733,10 +17733,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128423181</v>
+        <v>128404367</v>
       </c>
       <c r="B171" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17762,16 +17762,23 @@
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>635471</v>
+        <v>635556</v>
       </c>
       <c r="R171" t="n">
-        <v>7087243</v>
+        <v>7087281</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17801,61 +17808,72 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AD171" t="b">
         <v>0</v>
       </c>
       <c r="AE171" t="b">
         <v>0</v>
       </c>
+      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128423576</v>
+        <v>128423161</v>
       </c>
       <c r="B172" t="n">
-        <v>91429</v>
+        <v>79089</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17865,10 +17883,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>634705</v>
+        <v>634702</v>
       </c>
       <c r="R172" t="n">
-        <v>7087668</v>
+        <v>7087248</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17915,22 +17933,22 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128404367</v>
+        <v>128423181</v>
       </c>
       <c r="B173" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17956,23 +17974,16 @@
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>635556</v>
+        <v>635471</v>
       </c>
       <c r="R173" t="n">
-        <v>7087281</v>
+        <v>7087243</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18002,50 +18013,39 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AD173" t="b">
         <v>0</v>
       </c>
       <c r="AE173" t="b">
         <v>0</v>
       </c>
-      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128423161</v>
+        <v>128423603</v>
       </c>
       <c r="B174" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18053,34 +18053,38 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>634702</v>
+        <v>635240</v>
       </c>
       <c r="R174" t="n">
-        <v>7087248</v>
+        <v>7087224</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18115,6 +18119,11 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
@@ -18127,22 +18136,22 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128423603</v>
+        <v>128423614</v>
       </c>
       <c r="B175" t="n">
-        <v>57689</v>
+        <v>91480</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18150,38 +18159,34 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>635240</v>
+        <v>634673</v>
       </c>
       <c r="R175" t="n">
-        <v>7087224</v>
+        <v>7087631</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18214,11 +18219,6 @@
       <c r="AA175" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18245,10 +18245,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128423598</v>
+        <v>128423150</v>
       </c>
       <c r="B176" t="n">
-        <v>80193</v>
+        <v>91484</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18256,21 +18256,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18280,10 +18280,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>635632</v>
+        <v>634998</v>
       </c>
       <c r="R176" t="n">
-        <v>7087270</v>
+        <v>7087278</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18330,12 +18330,12 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
@@ -18345,7 +18345,7 @@
         <v>128423149</v>
       </c>
       <c r="B177" t="n">
-        <v>91478</v>
+        <v>91480</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>128423111</v>
       </c>
       <c r="B178" t="n">
-        <v>91475</v>
+        <v>91477</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>128423599</v>
       </c>
       <c r="B179" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18633,10 +18633,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128423150</v>
+        <v>128423598</v>
       </c>
       <c r="B180" t="n">
-        <v>91482</v>
+        <v>80195</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18644,21 +18644,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18668,10 +18668,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>634998</v>
+        <v>635632</v>
       </c>
       <c r="R180" t="n">
-        <v>7087278</v>
+        <v>7087270</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18718,65 +18718,57 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128411527</v>
+        <v>128423592</v>
       </c>
       <c r="B181" t="n">
-        <v>57689</v>
+        <v>80223</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>634480</v>
+        <v>635454</v>
       </c>
       <c r="R181" t="n">
-        <v>7087349</v>
+        <v>7087257</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18806,24 +18798,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -18838,19 +18815,19 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128423120</v>
+        <v>128411527</v>
       </c>
       <c r="B182" t="n">
         <v>57689</v>
@@ -18881,18 +18858,22 @@
       <c r="I182" t="inlineStr"/>
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>635205</v>
+        <v>634480</v>
       </c>
       <c r="R182" t="n">
-        <v>7087342</v>
+        <v>7087349</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18922,14 +18903,24 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -18944,19 +18935,19 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128423115</v>
+        <v>128423120</v>
       </c>
       <c r="B183" t="n">
         <v>57689</v>
@@ -18985,16 +18976,20 @@
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>635461</v>
+        <v>635205</v>
       </c>
       <c r="R183" t="n">
-        <v>7087189</v>
+        <v>7087342</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19058,32 +19053,32 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128423592</v>
+        <v>128423115</v>
       </c>
       <c r="B184" t="n">
-        <v>80221</v>
+        <v>57689</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19093,10 +19088,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>635454</v>
+        <v>635461</v>
       </c>
       <c r="R184" t="n">
-        <v>7087257</v>
+        <v>7087189</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19131,6 +19126,11 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD184" t="b">
         <v>0</v>
       </c>
@@ -19143,12 +19143,12 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
@@ -19273,7 +19273,7 @@
         <v>128423088</v>
       </c>
       <c r="B186" t="n">
-        <v>96835</v>
+        <v>96837</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>128423190</v>
       </c>
       <c r="B187" t="n">
-        <v>88865</v>
+        <v>88867</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19464,32 +19464,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128423137</v>
+        <v>128423604</v>
       </c>
       <c r="B188" t="n">
-        <v>80192</v>
+        <v>95817</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19499,10 +19499,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>635683</v>
+        <v>634948</v>
       </c>
       <c r="R188" t="n">
-        <v>7087267</v>
+        <v>7087579</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19549,22 +19549,22 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128423186</v>
+        <v>128423137</v>
       </c>
       <c r="B189" t="n">
-        <v>79087</v>
+        <v>80194</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19572,21 +19572,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19596,10 +19596,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>635555</v>
+        <v>635683</v>
       </c>
       <c r="R189" t="n">
-        <v>7087248</v>
+        <v>7087267</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19658,32 +19658,32 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128423129</v>
+        <v>128423186</v>
       </c>
       <c r="B190" t="n">
-        <v>80220</v>
+        <v>79089</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19693,10 +19693,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>635614</v>
+        <v>635555</v>
       </c>
       <c r="R190" t="n">
-        <v>7087262</v>
+        <v>7087248</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19755,32 +19755,32 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128423198</v>
+        <v>128423129</v>
       </c>
       <c r="B191" t="n">
-        <v>57689</v>
+        <v>80222</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19790,10 +19790,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>635595</v>
+        <v>635614</v>
       </c>
       <c r="R191" t="n">
-        <v>7087277</v>
+        <v>7087262</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19826,11 +19826,6 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -19857,32 +19852,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128423604</v>
+        <v>128423198</v>
       </c>
       <c r="B192" t="n">
-        <v>95815</v>
+        <v>57689</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -19892,10 +19887,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>634948</v>
+        <v>635595</v>
       </c>
       <c r="R192" t="n">
-        <v>7087579</v>
+        <v>7087277</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19930,6 +19925,11 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD192" t="b">
         <v>0</v>
       </c>
@@ -19942,22 +19942,22 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128423172</v>
+        <v>128423590</v>
       </c>
       <c r="B193" t="n">
-        <v>79087</v>
+        <v>92748</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19965,21 +19965,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19989,10 +19989,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>635010</v>
+        <v>635182</v>
       </c>
       <c r="R193" t="n">
-        <v>7087362</v>
+        <v>7087227</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20039,44 +20039,44 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128423138</v>
+        <v>128423596</v>
       </c>
       <c r="B194" t="n">
-        <v>80228</v>
+        <v>57686</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20086,10 +20086,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>635160</v>
+        <v>634648</v>
       </c>
       <c r="R194" t="n">
-        <v>7087012</v>
+        <v>7087590</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20136,22 +20136,22 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128423168</v>
+        <v>128423172</v>
       </c>
       <c r="B195" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20183,10 +20183,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>634865</v>
+        <v>635010</v>
       </c>
       <c r="R195" t="n">
-        <v>7087586</v>
+        <v>7087362</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20245,10 +20245,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>128423109</v>
+        <v>128423138</v>
       </c>
       <c r="B196" t="n">
-        <v>80221</v>
+        <v>80230</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20256,21 +20256,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20280,10 +20280,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>635407</v>
+        <v>635160</v>
       </c>
       <c r="R196" t="n">
-        <v>7087128</v>
+        <v>7087012</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20342,10 +20342,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>128423135</v>
+        <v>128423168</v>
       </c>
       <c r="B197" t="n">
-        <v>80192</v>
+        <v>79089</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20353,21 +20353,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20377,10 +20377,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>635412</v>
+        <v>634865</v>
       </c>
       <c r="R197" t="n">
-        <v>7087118</v>
+        <v>7087586</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20439,32 +20439,32 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>128423118</v>
+        <v>128423109</v>
       </c>
       <c r="B198" t="n">
-        <v>57689</v>
+        <v>80223</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -20474,10 +20474,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>634924</v>
+        <v>635407</v>
       </c>
       <c r="R198" t="n">
-        <v>7087288</v>
+        <v>7087128</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20512,11 +20512,6 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD198" t="b">
         <v>0</v>
       </c>
@@ -20525,21 +20520,6 @@
       </c>
       <c r="AG198" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ198" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK198" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO198" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
@@ -20556,10 +20536,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>128423590</v>
+        <v>128423160</v>
       </c>
       <c r="B199" t="n">
-        <v>92746</v>
+        <v>79089</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20567,21 +20547,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -20591,10 +20571,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>635182</v>
+        <v>634916</v>
       </c>
       <c r="R199" t="n">
-        <v>7087227</v>
+        <v>7087311</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20641,22 +20621,22 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>128423160</v>
+        <v>128423135</v>
       </c>
       <c r="B200" t="n">
-        <v>79087</v>
+        <v>80194</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20664,21 +20644,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20688,10 +20668,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>634916</v>
+        <v>635412</v>
       </c>
       <c r="R200" t="n">
-        <v>7087311</v>
+        <v>7087118</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20750,10 +20730,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>128423596</v>
+        <v>128423118</v>
       </c>
       <c r="B201" t="n">
-        <v>57686</v>
+        <v>57689</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20761,16 +20741,16 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -20785,10 +20765,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>634648</v>
+        <v>634924</v>
       </c>
       <c r="R201" t="n">
-        <v>7087590</v>
+        <v>7087288</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20823,6 +20803,11 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD201" t="b">
         <v>0</v>
       </c>
@@ -20831,16 +20816,31 @@
       </c>
       <c r="AG201" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ201" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK201" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO201" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
@@ -20944,32 +20944,32 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>128423156</v>
+        <v>128423580</v>
       </c>
       <c r="B203" t="n">
-        <v>79087</v>
+        <v>91431</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -20979,10 +20979,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>635300</v>
+        <v>635478</v>
       </c>
       <c r="R203" t="n">
-        <v>7087123</v>
+        <v>7087280</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21029,12 +21029,12 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
@@ -21044,7 +21044,7 @@
         <v>128423579</v>
       </c>
       <c r="B204" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -21141,7 +21141,7 @@
         <v>128423151</v>
       </c>
       <c r="B205" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -21235,32 +21235,32 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>128423580</v>
+        <v>128423132</v>
       </c>
       <c r="B206" t="n">
-        <v>91429</v>
+        <v>80194</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -21270,10 +21270,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>635478</v>
+        <v>635159</v>
       </c>
       <c r="R206" t="n">
-        <v>7087280</v>
+        <v>7087014</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21320,22 +21320,22 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>128423132</v>
+        <v>128406204</v>
       </c>
       <c r="B207" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21363,14 +21363,14 @@
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>635159</v>
+        <v>635335</v>
       </c>
       <c r="R207" t="n">
-        <v>7087014</v>
+        <v>7087214</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21400,9 +21400,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -21417,22 +21427,22 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>128406204</v>
+        <v>128423156</v>
       </c>
       <c r="B208" t="n">
-        <v>80192</v>
+        <v>79089</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -21440,34 +21450,34 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>635335</v>
+        <v>635300</v>
       </c>
       <c r="R208" t="n">
-        <v>7087214</v>
+        <v>7087123</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21497,19 +21507,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z208" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB208" t="inlineStr">
-        <is>
-          <t>11:43</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -21524,12 +21524,12 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
@@ -21638,10 +21638,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128423171</v>
+        <v>128423188</v>
       </c>
       <c r="B210" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21673,10 +21673,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>634973</v>
+        <v>635610</v>
       </c>
       <c r="R210" t="n">
-        <v>7087410</v>
+        <v>7087261</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21738,7 +21738,7 @@
         <v>128423170</v>
       </c>
       <c r="B211" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21832,10 +21832,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>128423188</v>
+        <v>128423171</v>
       </c>
       <c r="B212" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -21867,10 +21867,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>635610</v>
+        <v>634973</v>
       </c>
       <c r="R212" t="n">
-        <v>7087261</v>
+        <v>7087410</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21932,7 +21932,7 @@
         <v>128423595</v>
       </c>
       <c r="B213" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -22234,32 +22234,32 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>128423601</v>
+        <v>128423094</v>
       </c>
       <c r="B216" t="n">
-        <v>91760</v>
+        <v>91431</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -22269,10 +22269,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>634475</v>
+        <v>635358</v>
       </c>
       <c r="R216" t="n">
-        <v>7087365</v>
+        <v>7087128</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22319,44 +22319,44 @@
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>128423130</v>
+        <v>128423574</v>
       </c>
       <c r="B217" t="n">
-        <v>80192</v>
+        <v>91431</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -22366,10 +22366,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>635267</v>
+        <v>634571</v>
       </c>
       <c r="R217" t="n">
-        <v>7087054</v>
+        <v>7087253</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22413,62 +22413,47 @@
       <c r="AG217" t="b">
         <v>0</v>
       </c>
-      <c r="AJ217" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK217" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO217" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT217" t="inlineStr"/>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>128423094</v>
+        <v>128423601</v>
       </c>
       <c r="B218" t="n">
-        <v>91429</v>
+        <v>91762</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -22478,10 +22463,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>635358</v>
+        <v>634475</v>
       </c>
       <c r="R218" t="n">
-        <v>7087128</v>
+        <v>7087365</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -22528,44 +22513,44 @@
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>128423574</v>
+        <v>128423183</v>
       </c>
       <c r="B219" t="n">
-        <v>91429</v>
+        <v>79089</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -22575,10 +22560,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>634571</v>
+        <v>635482</v>
       </c>
       <c r="R219" t="n">
-        <v>7087253</v>
+        <v>7087300</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22625,22 +22610,22 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>128423183</v>
+        <v>128423130</v>
       </c>
       <c r="B220" t="n">
-        <v>79087</v>
+        <v>80194</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -22648,21 +22633,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -22672,10 +22657,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>635482</v>
+        <v>635267</v>
       </c>
       <c r="R220" t="n">
-        <v>7087300</v>
+        <v>7087054</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22718,6 +22703,21 @@
       </c>
       <c r="AG220" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ220" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK220" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO220" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
@@ -22737,7 +22737,7 @@
         <v>128423613</v>
       </c>
       <c r="B221" t="n">
-        <v>91478</v>
+        <v>91480</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>128423087</v>
       </c>
       <c r="B222" t="n">
-        <v>79119</v>
+        <v>79121</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -22928,10 +22928,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>128405308</v>
+        <v>128407951</v>
       </c>
       <c r="B223" t="n">
-        <v>80192</v>
+        <v>79089</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -22939,34 +22939,34 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>635477</v>
+        <v>635217</v>
       </c>
       <c r="R223" t="n">
-        <v>7087164</v>
+        <v>7087316</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -22998,7 +22998,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -23008,7 +23008,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -23035,10 +23035,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>128423173</v>
+        <v>128405308</v>
       </c>
       <c r="B224" t="n">
-        <v>79087</v>
+        <v>80194</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -23046,34 +23046,34 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>635138</v>
+        <v>635477</v>
       </c>
       <c r="R224" t="n">
-        <v>7087339</v>
+        <v>7087164</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23103,9 +23103,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA224" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -23120,22 +23130,22 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>128423134</v>
+        <v>128423173</v>
       </c>
       <c r="B225" t="n">
-        <v>80192</v>
+        <v>79089</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23143,21 +23153,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23167,10 +23177,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>635231</v>
+        <v>635138</v>
       </c>
       <c r="R225" t="n">
-        <v>7087059</v>
+        <v>7087339</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23229,10 +23239,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>128407951</v>
+        <v>128423134</v>
       </c>
       <c r="B226" t="n">
-        <v>79087</v>
+        <v>80194</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23240,34 +23250,34 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>635217</v>
+        <v>635231</v>
       </c>
       <c r="R226" t="n">
-        <v>7087316</v>
+        <v>7087059</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23297,19 +23307,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z226" t="inlineStr">
-        <is>
-          <t>12:49</t>
-        </is>
-      </c>
       <c r="AA226" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB226" t="inlineStr">
-        <is>
-          <t>12:49</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -23324,12 +23324,12 @@
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
@@ -23339,7 +23339,7 @@
         <v>128428584</v>
       </c>
       <c r="B227" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23436,7 +23436,7 @@
         <v>128428573</v>
       </c>
       <c r="B228" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>128428570</v>
       </c>
       <c r="B229" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>128428595</v>
       </c>
       <c r="B231" t="n">
-        <v>75167</v>
+        <v>75169</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -23824,7 +23824,7 @@
         <v>128428547</v>
       </c>
       <c r="B232" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>128428530</v>
       </c>
       <c r="B234" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>128428575</v>
       </c>
       <c r="B237" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
         <v>128428546</v>
       </c>
       <c r="B238" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24520,7 +24520,7 @@
         <v>128428568</v>
       </c>
       <c r="B239" t="n">
-        <v>91478</v>
+        <v>91480</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -24617,7 +24617,7 @@
         <v>128428554</v>
       </c>
       <c r="B240" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>128428571</v>
       </c>
       <c r="B241" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>128428594</v>
       </c>
       <c r="B243" t="n">
-        <v>75167</v>
+        <v>75169</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -25018,7 +25018,7 @@
         <v>128428533</v>
       </c>
       <c r="B244" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -25115,7 +25115,7 @@
         <v>128428577</v>
       </c>
       <c r="B245" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -25212,7 +25212,7 @@
         <v>128428589</v>
       </c>
       <c r="B246" t="n">
-        <v>88865</v>
+        <v>88867</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -25414,7 +25414,7 @@
         <v>128428557</v>
       </c>
       <c r="B248" t="n">
-        <v>79111</v>
+        <v>79113</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>128428564</v>
       </c>
       <c r="B249" t="n">
-        <v>80096</v>
+        <v>80098</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -25611,32 +25611,32 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>128428529</v>
+        <v>128428559</v>
       </c>
       <c r="B250" t="n">
-        <v>91429</v>
+        <v>80194</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -25646,10 +25646,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>634593</v>
+        <v>635416</v>
       </c>
       <c r="R250" t="n">
-        <v>7087306</v>
+        <v>7087178</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -25708,32 +25708,32 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>128428559</v>
+        <v>128428529</v>
       </c>
       <c r="B251" t="n">
-        <v>80192</v>
+        <v>91431</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -25743,10 +25743,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>635416</v>
+        <v>634593</v>
       </c>
       <c r="R251" t="n">
-        <v>7087178</v>
+        <v>7087306</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -25808,7 +25808,7 @@
         <v>128428596</v>
       </c>
       <c r="B252" t="n">
-        <v>75167</v>
+        <v>75169</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>128428590</v>
       </c>
       <c r="B253" t="n">
-        <v>88865</v>
+        <v>88867</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -26002,7 +26002,7 @@
         <v>128428581</v>
       </c>
       <c r="B254" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -26096,32 +26096,32 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>128428583</v>
+        <v>128428566</v>
       </c>
       <c r="B255" t="n">
-        <v>82946</v>
+        <v>58059</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>1312</v>
+        <v>103015</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -26131,10 +26131,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>634880</v>
+        <v>634515</v>
       </c>
       <c r="R255" t="n">
-        <v>7087375</v>
+        <v>7087381</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26196,7 +26196,7 @@
         <v>128428569</v>
       </c>
       <c r="B256" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -26290,32 +26290,32 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128428566</v>
+        <v>128428583</v>
       </c>
       <c r="B257" t="n">
-        <v>58059</v>
+        <v>82948</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>103015</v>
+        <v>1312</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -26325,10 +26325,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>634515</v>
+        <v>634880</v>
       </c>
       <c r="R257" t="n">
-        <v>7087381</v>
+        <v>7087375</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -26390,7 +26390,7 @@
         <v>128428579</v>
       </c>
       <c r="B258" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -26487,7 +26487,7 @@
         <v>128428549</v>
       </c>
       <c r="B259" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>128428558</v>
       </c>
       <c r="B261" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -26778,7 +26778,7 @@
         <v>128428532</v>
       </c>
       <c r="B262" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -26982,10 +26982,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>128428592</v>
+        <v>128428531</v>
       </c>
       <c r="B264" t="n">
-        <v>80227</v>
+        <v>91431</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -26993,21 +26993,21 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -27017,10 +27017,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>635304</v>
+        <v>634717</v>
       </c>
       <c r="R264" t="n">
-        <v>7087222</v>
+        <v>7087633</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27079,27 +27079,27 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>128428578</v>
+        <v>128428592</v>
       </c>
       <c r="B265" t="n">
-        <v>79087</v>
+        <v>80229</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -27114,10 +27114,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>634686</v>
+        <v>635304</v>
       </c>
       <c r="R265" t="n">
-        <v>7087331</v>
+        <v>7087222</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27176,32 +27176,32 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>128428531</v>
+        <v>128428578</v>
       </c>
       <c r="B266" t="n">
-        <v>91429</v>
+        <v>79089</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
@@ -27211,10 +27211,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>634717</v>
+        <v>634686</v>
       </c>
       <c r="R266" t="n">
-        <v>7087633</v>
+        <v>7087331</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -27276,7 +27276,7 @@
         <v>128428545</v>
       </c>
       <c r="B267" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -27370,32 +27370,32 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>128428567</v>
+        <v>128428541</v>
       </c>
       <c r="B268" t="n">
-        <v>75158</v>
+        <v>57849</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6439</v>
+        <v>103021</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -27405,10 +27405,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>635532</v>
+        <v>635537</v>
       </c>
       <c r="R268" t="n">
-        <v>7087324</v>
+        <v>7087207</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -27467,10 +27467,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>128428561</v>
+        <v>128428567</v>
       </c>
       <c r="B269" t="n">
-        <v>80228</v>
+        <v>75160</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -27478,21 +27478,21 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6464</v>
+        <v>6439</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -27502,10 +27502,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>634879</v>
+        <v>635532</v>
       </c>
       <c r="R269" t="n">
-        <v>7087368</v>
+        <v>7087324</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -27564,10 +27564,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>128428565</v>
+        <v>128428561</v>
       </c>
       <c r="B270" t="n">
-        <v>58059</v>
+        <v>80230</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -27575,46 +27575,34 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>103015</v>
+        <v>6464</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I270" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K270" t="inlineStr"/>
-      <c r="L270" t="inlineStr"/>
-      <c r="M270" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N270" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>635275</v>
+        <v>634879</v>
       </c>
       <c r="R270" t="n">
-        <v>7087098</v>
+        <v>7087368</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -27673,45 +27661,57 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>128428541</v>
+        <v>128428565</v>
       </c>
       <c r="B271" t="n">
-        <v>57849</v>
+        <v>58059</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I271" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr"/>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>635537</v>
+        <v>635275</v>
       </c>
       <c r="R271" t="n">
-        <v>7087207</v>
+        <v>7087098</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -27773,7 +27773,7 @@
         <v>128428585</v>
       </c>
       <c r="B272" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -27867,27 +27867,27 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>128428572</v>
+        <v>128428593</v>
       </c>
       <c r="B273" t="n">
-        <v>79087</v>
+        <v>80229</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -27902,10 +27902,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>634969</v>
+        <v>635390</v>
       </c>
       <c r="R273" t="n">
-        <v>7087325</v>
+        <v>7087179</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -27964,10 +27964,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>128428593</v>
+        <v>128428544</v>
       </c>
       <c r="B274" t="n">
-        <v>80227</v>
+        <v>80223</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -27975,21 +27975,21 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -27999,10 +27999,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>635390</v>
+        <v>635039</v>
       </c>
       <c r="R274" t="n">
-        <v>7087179</v>
+        <v>7087283</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28061,32 +28061,32 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>128428544</v>
+        <v>128428572</v>
       </c>
       <c r="B275" t="n">
-        <v>80221</v>
+        <v>79089</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -28096,10 +28096,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>635039</v>
+        <v>634969</v>
       </c>
       <c r="R275" t="n">
-        <v>7087283</v>
+        <v>7087325</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -28158,45 +28158,53 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>128428562</v>
+        <v>128428550</v>
       </c>
       <c r="B276" t="n">
-        <v>80228</v>
+        <v>57686</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr"/>
       <c r="P276" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>635398</v>
+        <v>634487</v>
       </c>
       <c r="R276" t="n">
-        <v>7087183</v>
+        <v>7087401</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -28255,7 +28263,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>128428550</v>
+        <v>128428552</v>
       </c>
       <c r="B277" t="n">
         <v>57686</v>
@@ -28298,10 +28306,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>634487</v>
+        <v>635170</v>
       </c>
       <c r="R277" t="n">
-        <v>7087401</v>
+        <v>7087231</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -28360,53 +28368,45 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>128428552</v>
+        <v>128428562</v>
       </c>
       <c r="B278" t="n">
-        <v>57686</v>
+        <v>80230</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>635170</v>
+        <v>635398</v>
       </c>
       <c r="R278" t="n">
-        <v>7087231</v>
+        <v>7087183</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -28468,7 +28468,7 @@
         <v>128428582</v>
       </c>
       <c r="B279" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -28565,7 +28565,7 @@
         <v>128428580</v>
       </c>
       <c r="B280" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -28659,10 +28659,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>128428535</v>
+        <v>128428574</v>
       </c>
       <c r="B281" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -28670,42 +28670,34 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>635058</v>
+        <v>635129</v>
       </c>
       <c r="R281" t="n">
-        <v>7087271</v>
+        <v>7087323</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -28738,11 +28730,6 @@
       <c r="AA281" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC281" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD281" t="b">
@@ -28769,7 +28756,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>128428536</v>
+        <v>128428535</v>
       </c>
       <c r="B282" t="n">
         <v>57689</v>
@@ -28812,10 +28799,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>634669</v>
+        <v>635058</v>
       </c>
       <c r="R282" t="n">
-        <v>7087314</v>
+        <v>7087271</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -28879,10 +28866,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>128428574</v>
+        <v>128428536</v>
       </c>
       <c r="B283" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -28890,34 +28877,42 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
+      <c r="K283" t="inlineStr"/>
+      <c r="L283" t="inlineStr"/>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr"/>
       <c r="P283" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>635129</v>
+        <v>634669</v>
       </c>
       <c r="R283" t="n">
-        <v>7087323</v>
+        <v>7087314</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -28950,6 +28945,11 @@
       <c r="AA283" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC283" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD283" t="b">
@@ -28979,7 +28979,7 @@
         <v>128492196</v>
       </c>
       <c r="B284" t="n">
-        <v>95827</v>
+        <v>95829</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>128492197</v>
       </c>
       <c r="B285" t="n">
-        <v>95815</v>
+        <v>95817</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>128651017</v>
       </c>
       <c r="B286" t="n">
-        <v>96930</v>
+        <v>96932</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>

--- a/artfynd/A 30047-2025 artfynd.xlsx
+++ b/artfynd/A 30047-2025 artfynd.xlsx
@@ -8178,10 +8178,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128411934</v>
+        <v>128423142</v>
       </c>
       <c r="B75" t="n">
-        <v>91431</v>
+        <v>80230</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8189,34 +8189,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5447</v>
+        <v>6464</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>634525</v>
+        <v>635234</v>
       </c>
       <c r="R75" t="n">
-        <v>7087336</v>
+        <v>7087170</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8246,19 +8246,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8273,44 +8263,44 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128423165</v>
+        <v>128423140</v>
       </c>
       <c r="B76" t="n">
-        <v>79089</v>
+        <v>80230</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8320,10 +8310,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>634654</v>
+        <v>635608</v>
       </c>
       <c r="R76" t="n">
-        <v>7087545</v>
+        <v>7087280</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8382,32 +8372,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128423159</v>
+        <v>128423591</v>
       </c>
       <c r="B77" t="n">
-        <v>79089</v>
+        <v>80223</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8417,10 +8407,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>635080</v>
+        <v>635451</v>
       </c>
       <c r="R77" t="n">
-        <v>7087206</v>
+        <v>7087225</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8467,22 +8457,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128423597</v>
+        <v>128423621</v>
       </c>
       <c r="B78" t="n">
-        <v>57686</v>
+        <v>82948</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8490,21 +8480,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8514,10 +8504,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>634913</v>
+        <v>634525</v>
       </c>
       <c r="R78" t="n">
-        <v>7087585</v>
+        <v>7087295</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8576,10 +8566,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128423142</v>
+        <v>128423612</v>
       </c>
       <c r="B79" t="n">
-        <v>80230</v>
+        <v>58059</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8587,21 +8577,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6464</v>
+        <v>103015</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8611,10 +8601,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>635234</v>
+        <v>634913</v>
       </c>
       <c r="R79" t="n">
-        <v>7087170</v>
+        <v>7087585</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8661,22 +8651,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128423140</v>
+        <v>128411934</v>
       </c>
       <c r="B80" t="n">
-        <v>80230</v>
+        <v>91431</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8684,34 +8674,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>635608</v>
+        <v>634525</v>
       </c>
       <c r="R80" t="n">
-        <v>7087280</v>
+        <v>7087336</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8741,9 +8731,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8758,44 +8758,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128423591</v>
+        <v>128423165</v>
       </c>
       <c r="B81" t="n">
-        <v>80223</v>
+        <v>79089</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>635451</v>
+        <v>634654</v>
       </c>
       <c r="R81" t="n">
-        <v>7087225</v>
+        <v>7087545</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8855,22 +8855,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128423621</v>
+        <v>128423159</v>
       </c>
       <c r="B82" t="n">
-        <v>82948</v>
+        <v>79089</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8878,21 +8878,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8902,10 +8902,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>634525</v>
+        <v>635080</v>
       </c>
       <c r="R82" t="n">
-        <v>7087295</v>
+        <v>7087206</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8952,39 +8952,39 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128423612</v>
+        <v>128423597</v>
       </c>
       <c r="B83" t="n">
-        <v>58059</v>
+        <v>57686</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -9837,32 +9837,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128423155</v>
+        <v>128423099</v>
       </c>
       <c r="B92" t="n">
-        <v>79089</v>
+        <v>92163</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9872,10 +9872,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>635294</v>
+        <v>634570</v>
       </c>
       <c r="R92" t="n">
-        <v>7087064</v>
+        <v>7087303</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9927,14 +9927,14 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Amanda Portström, Isac Enetjärn, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128423175</v>
+        <v>128423155</v>
       </c>
       <c r="B93" t="n">
         <v>79089</v>
@@ -9969,10 +9969,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>635169</v>
+        <v>635294</v>
       </c>
       <c r="R93" t="n">
-        <v>7087269</v>
+        <v>7087064</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10031,32 +10031,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128423092</v>
+        <v>128423175</v>
       </c>
       <c r="B94" t="n">
-        <v>91431</v>
+        <v>79089</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10066,10 +10066,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>634661</v>
+        <v>635169</v>
       </c>
       <c r="R94" t="n">
-        <v>7087688</v>
+        <v>7087269</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10121,39 +10121,39 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Amanda Portström, Isac Enetjärn, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128423189</v>
+        <v>128423092</v>
       </c>
       <c r="B95" t="n">
-        <v>79089</v>
+        <v>91431</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10163,10 +10163,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>635678</v>
+        <v>634661</v>
       </c>
       <c r="R95" t="n">
-        <v>7087274</v>
+        <v>7087688</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10218,17 +10218,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Amanda Portström, Isac Enetjärn, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128404903</v>
+        <v>128423189</v>
       </c>
       <c r="B96" t="n">
-        <v>91484</v>
+        <v>79089</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10236,34 +10236,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>635552</v>
+        <v>635678</v>
       </c>
       <c r="R96" t="n">
-        <v>7087334</v>
+        <v>7087274</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10293,19 +10293,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10320,57 +10310,57 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128423099</v>
+        <v>128404903</v>
       </c>
       <c r="B97" t="n">
-        <v>92163</v>
+        <v>91484</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>634570</v>
+        <v>635552</v>
       </c>
       <c r="R97" t="n">
-        <v>7087303</v>
+        <v>7087334</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10400,9 +10390,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10417,12 +10417,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Amanda Portström, Isac Enetjärn, Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -12720,32 +12720,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128423620</v>
+        <v>128423585</v>
       </c>
       <c r="B121" t="n">
-        <v>79089</v>
+        <v>92163</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12755,10 +12755,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>634756</v>
+        <v>634942</v>
       </c>
       <c r="R121" t="n">
-        <v>7087642</v>
+        <v>7087590</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12817,45 +12817,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128423619</v>
+        <v>128408809</v>
       </c>
       <c r="B122" t="n">
-        <v>79089</v>
+        <v>80223</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>635513</v>
+        <v>635017</v>
       </c>
       <c r="R122" t="n">
-        <v>7087316</v>
+        <v>7087370</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12885,14 +12885,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12901,51 +12906,50 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128423577</v>
+        <v>128423131</v>
       </c>
       <c r="B123" t="n">
-        <v>91431</v>
+        <v>80194</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12955,10 +12959,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>635153</v>
+        <v>635236</v>
       </c>
       <c r="R123" t="n">
-        <v>7087180</v>
+        <v>7087039</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13005,44 +13009,44 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Amanda Portström, Isac Enetjärn, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128423616</v>
+        <v>128423594</v>
       </c>
       <c r="B124" t="n">
-        <v>91484</v>
+        <v>80223</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13052,10 +13056,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>634993</v>
+        <v>634527</v>
       </c>
       <c r="R124" t="n">
-        <v>7087294</v>
+        <v>7087301</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13114,10 +13118,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128423153</v>
+        <v>128423620</v>
       </c>
       <c r="B125" t="n">
-        <v>91484</v>
+        <v>79089</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13125,21 +13129,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13149,10 +13153,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>634880</v>
+        <v>634756</v>
       </c>
       <c r="R125" t="n">
-        <v>7087564</v>
+        <v>7087642</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13199,44 +13203,44 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128423585</v>
+        <v>128423619</v>
       </c>
       <c r="B126" t="n">
-        <v>92163</v>
+        <v>79089</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13246,10 +13250,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>634942</v>
+        <v>635513</v>
       </c>
       <c r="R126" t="n">
-        <v>7087590</v>
+        <v>7087316</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13284,12 +13288,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13308,10 +13318,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128408809</v>
+        <v>128423577</v>
       </c>
       <c r="B127" t="n">
-        <v>80223</v>
+        <v>91431</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13319,34 +13329,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>635017</v>
+        <v>635153</v>
       </c>
       <c r="R127" t="n">
-        <v>7087370</v>
+        <v>7087180</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13376,19 +13386,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>13:18</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13403,22 +13403,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128423131</v>
+        <v>128423616</v>
       </c>
       <c r="B128" t="n">
-        <v>80194</v>
+        <v>91484</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13426,21 +13426,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13450,10 +13450,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>635236</v>
+        <v>634993</v>
       </c>
       <c r="R128" t="n">
-        <v>7087039</v>
+        <v>7087294</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13500,44 +13500,44 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Amanda Portström, Isac Enetjärn, Elin Kannerby</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128423594</v>
+        <v>128423153</v>
       </c>
       <c r="B129" t="n">
-        <v>80223</v>
+        <v>91484</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13547,10 +13547,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>634527</v>
+        <v>634880</v>
       </c>
       <c r="R129" t="n">
-        <v>7087301</v>
+        <v>7087564</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13597,12 +13597,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
@@ -16753,32 +16753,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128423113</v>
+        <v>128423090</v>
       </c>
       <c r="B161" t="n">
-        <v>80195</v>
+        <v>91431</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16788,10 +16788,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>635240</v>
+        <v>635155</v>
       </c>
       <c r="R161" t="n">
-        <v>7087040</v>
+        <v>7087185</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16850,10 +16850,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128423572</v>
+        <v>128423185</v>
       </c>
       <c r="B162" t="n">
-        <v>96837</v>
+        <v>79089</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16861,21 +16861,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16885,10 +16885,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>634574</v>
+        <v>635559</v>
       </c>
       <c r="R162" t="n">
-        <v>7087286</v>
+        <v>7087269</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16935,44 +16935,44 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128423191</v>
+        <v>128423126</v>
       </c>
       <c r="B163" t="n">
-        <v>88867</v>
+        <v>79113</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>510</v>
+        <v>6434</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16982,10 +16982,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>634676</v>
+        <v>635212</v>
       </c>
       <c r="R163" t="n">
-        <v>7087233</v>
+        <v>7087212</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17037,17 +17037,17 @@
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Amanda Portström, Isac Enetjärn, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128423185</v>
+        <v>128423101</v>
       </c>
       <c r="B164" t="n">
-        <v>79089</v>
+        <v>57849</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17055,21 +17055,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17079,10 +17079,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>635559</v>
+        <v>634716</v>
       </c>
       <c r="R164" t="n">
-        <v>7087269</v>
+        <v>7087613</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17134,39 +17134,39 @@
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Amanda Portström, Isac Enetjärn, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128423126</v>
+        <v>128423113</v>
       </c>
       <c r="B165" t="n">
-        <v>79113</v>
+        <v>80195</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6434</v>
+        <v>2081</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17176,10 +17176,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>635212</v>
+        <v>635240</v>
       </c>
       <c r="R165" t="n">
-        <v>7087212</v>
+        <v>7087040</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17238,10 +17238,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128423101</v>
+        <v>128423572</v>
       </c>
       <c r="B166" t="n">
-        <v>57849</v>
+        <v>96837</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17249,21 +17249,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17273,10 +17273,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>634716</v>
+        <v>634574</v>
       </c>
       <c r="R166" t="n">
-        <v>7087613</v>
+        <v>7087286</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17323,44 +17323,44 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Amanda Portström, Isac Enetjärn, Elin Kannerby</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128423090</v>
+        <v>128423191</v>
       </c>
       <c r="B167" t="n">
-        <v>91431</v>
+        <v>88867</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17370,10 +17370,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>635155</v>
+        <v>634676</v>
       </c>
       <c r="R167" t="n">
-        <v>7087185</v>
+        <v>7087233</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17425,7 +17425,7 @@
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Amanda Portström, Isac Enetjärn, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
@@ -18245,10 +18245,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128411527</v>
+        <v>128423598</v>
       </c>
       <c r="B176" t="n">
-        <v>57689</v>
+        <v>80195</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18256,42 +18256,34 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>634480</v>
+        <v>635632</v>
       </c>
       <c r="R176" t="n">
-        <v>7087349</v>
+        <v>7087270</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18321,24 +18313,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z176" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB176" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18353,22 +18330,22 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128423120</v>
+        <v>128423149</v>
       </c>
       <c r="B177" t="n">
-        <v>57689</v>
+        <v>91480</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18376,38 +18353,34 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>635205</v>
+        <v>634942</v>
       </c>
       <c r="R177" t="n">
-        <v>7087342</v>
+        <v>7087434</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18442,11 +18415,6 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD177" t="b">
         <v>0</v>
       </c>
@@ -18464,39 +18432,39 @@
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Amanda Portström, Isac Enetjärn, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128423115</v>
+        <v>128423111</v>
       </c>
       <c r="B178" t="n">
-        <v>57689</v>
+        <v>91477</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18506,10 +18474,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>635461</v>
+        <v>635441</v>
       </c>
       <c r="R178" t="n">
-        <v>7087189</v>
+        <v>7087163</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18542,11 +18510,6 @@
       <c r="AA178" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -18573,32 +18536,32 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128423598</v>
+        <v>128423599</v>
       </c>
       <c r="B179" t="n">
-        <v>80195</v>
+        <v>91920</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>2081</v>
+        <v>1209</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18608,10 +18571,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>635632</v>
+        <v>635464</v>
       </c>
       <c r="R179" t="n">
-        <v>7087270</v>
+        <v>7087275</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18670,10 +18633,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128423149</v>
+        <v>128423150</v>
       </c>
       <c r="B180" t="n">
-        <v>91480</v>
+        <v>91484</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18681,21 +18644,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18705,10 +18668,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>634942</v>
+        <v>634998</v>
       </c>
       <c r="R180" t="n">
-        <v>7087434</v>
+        <v>7087278</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18767,10 +18730,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128423111</v>
+        <v>128423592</v>
       </c>
       <c r="B181" t="n">
-        <v>91477</v>
+        <v>80223</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18778,21 +18741,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1205</v>
+        <v>6462</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18802,10 +18765,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>635441</v>
+        <v>635454</v>
       </c>
       <c r="R181" t="n">
-        <v>7087163</v>
+        <v>7087257</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18852,22 +18815,22 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Amanda Portström, Isac Enetjärn, Elin Kannerby</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128423150</v>
+        <v>128411527</v>
       </c>
       <c r="B182" t="n">
-        <v>91484</v>
+        <v>57689</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18875,34 +18838,42 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>634998</v>
+        <v>634480</v>
       </c>
       <c r="R182" t="n">
-        <v>7087278</v>
+        <v>7087349</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18932,9 +18903,24 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -18949,57 +18935,61 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128423599</v>
+        <v>128423120</v>
       </c>
       <c r="B183" t="n">
-        <v>91920</v>
+        <v>57689</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>635464</v>
+        <v>635205</v>
       </c>
       <c r="R183" t="n">
-        <v>7087275</v>
+        <v>7087342</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19034,6 +19024,11 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD183" t="b">
         <v>0</v>
       </c>
@@ -19046,44 +19041,44 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Amanda Portström, Isac Enetjärn, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128423592</v>
+        <v>128423115</v>
       </c>
       <c r="B184" t="n">
-        <v>80223</v>
+        <v>57689</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19093,10 +19088,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>635454</v>
+        <v>635461</v>
       </c>
       <c r="R184" t="n">
-        <v>7087257</v>
+        <v>7087189</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19131,6 +19126,11 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD184" t="b">
         <v>0</v>
       </c>
@@ -19143,12 +19143,12 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Amanda Portström, Isac Enetjärn, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
@@ -19954,10 +19954,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128423590</v>
+        <v>128423596</v>
       </c>
       <c r="B193" t="n">
-        <v>92748</v>
+        <v>57686</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19965,21 +19965,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4361</v>
+        <v>100049</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19989,10 +19989,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>635182</v>
+        <v>634648</v>
       </c>
       <c r="R193" t="n">
-        <v>7087227</v>
+        <v>7087590</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20051,10 +20051,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128423172</v>
+        <v>128423118</v>
       </c>
       <c r="B194" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20062,21 +20062,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20086,10 +20086,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>635010</v>
+        <v>634924</v>
       </c>
       <c r="R194" t="n">
-        <v>7087362</v>
+        <v>7087288</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20124,6 +20124,11 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD194" t="b">
         <v>0</v>
       </c>
@@ -20132,6 +20137,21 @@
       </c>
       <c r="AG194" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO194" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
@@ -20141,17 +20161,17 @@
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Amanda Portström, Isac Enetjärn, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128423160</v>
+        <v>128423590</v>
       </c>
       <c r="B195" t="n">
-        <v>79089</v>
+        <v>92748</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20159,21 +20179,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20183,10 +20203,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>634916</v>
+        <v>635182</v>
       </c>
       <c r="R195" t="n">
-        <v>7087311</v>
+        <v>7087227</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20233,19 +20253,19 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>128423168</v>
+        <v>128423172</v>
       </c>
       <c r="B196" t="n">
         <v>79089</v>
@@ -20280,10 +20300,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>634865</v>
+        <v>635010</v>
       </c>
       <c r="R196" t="n">
-        <v>7087586</v>
+        <v>7087362</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20342,10 +20362,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>128423596</v>
+        <v>128423160</v>
       </c>
       <c r="B197" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20353,21 +20373,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20377,10 +20397,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>634648</v>
+        <v>634916</v>
       </c>
       <c r="R197" t="n">
-        <v>7087590</v>
+        <v>7087311</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20427,44 +20447,44 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>128423138</v>
+        <v>128423168</v>
       </c>
       <c r="B198" t="n">
-        <v>80230</v>
+        <v>79089</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -20474,10 +20494,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>635160</v>
+        <v>634865</v>
       </c>
       <c r="R198" t="n">
-        <v>7087012</v>
+        <v>7087586</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20536,10 +20556,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>128423109</v>
+        <v>128423138</v>
       </c>
       <c r="B199" t="n">
-        <v>80223</v>
+        <v>80230</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20547,21 +20567,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -20571,10 +20591,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>635407</v>
+        <v>635160</v>
       </c>
       <c r="R199" t="n">
-        <v>7087128</v>
+        <v>7087012</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20626,39 +20646,39 @@
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Amanda Portström, Isac Enetjärn, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>128423135</v>
+        <v>128423109</v>
       </c>
       <c r="B200" t="n">
-        <v>80194</v>
+        <v>80223</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20668,10 +20688,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>635412</v>
+        <v>635407</v>
       </c>
       <c r="R200" t="n">
-        <v>7087118</v>
+        <v>7087128</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20730,10 +20750,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>128423118</v>
+        <v>128423135</v>
       </c>
       <c r="B201" t="n">
-        <v>57689</v>
+        <v>80194</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20741,21 +20761,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20765,10 +20785,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>634924</v>
+        <v>635412</v>
       </c>
       <c r="R201" t="n">
-        <v>7087288</v>
+        <v>7087118</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20803,11 +20823,6 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD201" t="b">
         <v>0</v>
       </c>
@@ -20816,21 +20831,6 @@
       </c>
       <c r="AG201" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ201" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK201" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO201" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
@@ -22234,32 +22234,32 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>128423094</v>
+        <v>128423601</v>
       </c>
       <c r="B216" t="n">
-        <v>91431</v>
+        <v>91762</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -22269,10 +22269,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>635358</v>
+        <v>634475</v>
       </c>
       <c r="R216" t="n">
-        <v>7087128</v>
+        <v>7087365</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22319,19 +22319,19 @@
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Amanda Portström, Isac Enetjärn, Elin Kannerby</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>128423574</v>
+        <v>128423094</v>
       </c>
       <c r="B217" t="n">
         <v>91431</v>
@@ -22366,10 +22366,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>634571</v>
+        <v>635358</v>
       </c>
       <c r="R217" t="n">
-        <v>7087253</v>
+        <v>7087128</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22416,44 +22416,44 @@
       <c r="AT217" t="inlineStr"/>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Amanda Portström, Isac Enetjärn, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>128423183</v>
+        <v>128423574</v>
       </c>
       <c r="B218" t="n">
-        <v>79089</v>
+        <v>91431</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -22463,10 +22463,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>635482</v>
+        <v>634571</v>
       </c>
       <c r="R218" t="n">
-        <v>7087300</v>
+        <v>7087253</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -22513,22 +22513,22 @@
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>128423130</v>
+        <v>128423183</v>
       </c>
       <c r="B219" t="n">
-        <v>80194</v>
+        <v>79089</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -22536,21 +22536,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -22560,10 +22560,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>635267</v>
+        <v>635482</v>
       </c>
       <c r="R219" t="n">
-        <v>7087054</v>
+        <v>7087300</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22607,21 +22607,6 @@
       <c r="AG219" t="b">
         <v>0</v>
       </c>
-      <c r="AJ219" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK219" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO219" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
@@ -22630,17 +22615,17 @@
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Amanda Portström, Isac Enetjärn, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>128423601</v>
+        <v>128423130</v>
       </c>
       <c r="B220" t="n">
-        <v>91762</v>
+        <v>80194</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -22648,21 +22633,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -22672,10 +22657,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>634475</v>
+        <v>635267</v>
       </c>
       <c r="R220" t="n">
-        <v>7087365</v>
+        <v>7087054</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22719,15 +22704,30 @@
       <c r="AG220" t="b">
         <v>0</v>
       </c>
+      <c r="AJ220" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK220" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO220" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Amanda Portström, Isac Enetjärn, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
@@ -24517,10 +24517,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>128428571</v>
+        <v>128428568</v>
       </c>
       <c r="B239" t="n">
-        <v>79089</v>
+        <v>91480</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -24528,21 +24528,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -24552,10 +24552,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>635190</v>
+        <v>634725</v>
       </c>
       <c r="R239" t="n">
-        <v>7087142</v>
+        <v>7087631</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24614,10 +24614,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>128428568</v>
+        <v>128428554</v>
       </c>
       <c r="B240" t="n">
-        <v>91480</v>
+        <v>80195</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -24625,21 +24625,21 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -24649,10 +24649,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>634725</v>
+        <v>635037</v>
       </c>
       <c r="R240" t="n">
-        <v>7087631</v>
+        <v>7087279</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24711,10 +24711,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>128428554</v>
+        <v>128428571</v>
       </c>
       <c r="B241" t="n">
-        <v>80195</v>
+        <v>79089</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24722,21 +24722,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -24746,10 +24746,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>635037</v>
+        <v>635190</v>
       </c>
       <c r="R241" t="n">
-        <v>7087279</v>
+        <v>7087142</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25015,10 +25015,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>128428594</v>
+        <v>128428577</v>
       </c>
       <c r="B244" t="n">
-        <v>75169</v>
+        <v>79089</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -25026,21 +25026,21 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -25050,10 +25050,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>635258</v>
+        <v>635291</v>
       </c>
       <c r="R244" t="n">
-        <v>7087144</v>
+        <v>7087126</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25112,10 +25112,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>128428577</v>
+        <v>128428594</v>
       </c>
       <c r="B245" t="n">
-        <v>79089</v>
+        <v>75169</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -25123,21 +25123,21 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -25147,10 +25147,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>635291</v>
+        <v>635258</v>
       </c>
       <c r="R245" t="n">
-        <v>7087126</v>
+        <v>7087144</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25209,10 +25209,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>128428551</v>
+        <v>128428589</v>
       </c>
       <c r="B246" t="n">
-        <v>57686</v>
+        <v>88867</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -25220,42 +25220,34 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
-      <c r="L246" t="inlineStr"/>
-      <c r="M246" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>634768</v>
+        <v>634679</v>
       </c>
       <c r="R246" t="n">
-        <v>7087607</v>
+        <v>7087311</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25314,10 +25306,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>128428589</v>
+        <v>128428551</v>
       </c>
       <c r="B247" t="n">
-        <v>88867</v>
+        <v>57686</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -25325,34 +25317,42 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>634679</v>
+        <v>634768</v>
       </c>
       <c r="R247" t="n">
-        <v>7087311</v>
+        <v>7087607</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -28465,10 +28465,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>128428580</v>
+        <v>128428582</v>
       </c>
       <c r="B279" t="n">
-        <v>79089</v>
+        <v>82948</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -28476,21 +28476,21 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
@@ -28500,10 +28500,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>634932</v>
+        <v>635259</v>
       </c>
       <c r="R279" t="n">
-        <v>7087436</v>
+        <v>7087140</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -28562,10 +28562,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>128428582</v>
+        <v>128428580</v>
       </c>
       <c r="B280" t="n">
-        <v>82948</v>
+        <v>79089</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -28573,21 +28573,21 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -28597,10 +28597,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>635259</v>
+        <v>634932</v>
       </c>
       <c r="R280" t="n">
-        <v>7087140</v>
+        <v>7087436</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -28659,10 +28659,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>128428574</v>
+        <v>128428535</v>
       </c>
       <c r="B281" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -28670,34 +28670,42 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>635129</v>
+        <v>635058</v>
       </c>
       <c r="R281" t="n">
-        <v>7087323</v>
+        <v>7087271</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -28730,6 +28738,11 @@
       <c r="AA281" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC281" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD281" t="b">
@@ -28756,7 +28769,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>128428535</v>
+        <v>128428536</v>
       </c>
       <c r="B282" t="n">
         <v>57689</v>
@@ -28799,10 +28812,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>635058</v>
+        <v>634669</v>
       </c>
       <c r="R282" t="n">
-        <v>7087271</v>
+        <v>7087314</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -28866,10 +28879,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>128428536</v>
+        <v>128428574</v>
       </c>
       <c r="B283" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -28877,42 +28890,34 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
-      <c r="K283" t="inlineStr"/>
-      <c r="L283" t="inlineStr"/>
-      <c r="M283" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N283" t="inlineStr"/>
       <c r="P283" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>634669</v>
+        <v>635129</v>
       </c>
       <c r="R283" t="n">
-        <v>7087314</v>
+        <v>7087323</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -28945,11 +28950,6 @@
       <c r="AA283" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC283" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD283" t="b">

--- a/artfynd/A 30047-2025 artfynd.xlsx
+++ b/artfynd/A 30047-2025 artfynd.xlsx
@@ -9061,32 +9061,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128423618</v>
+        <v>128423106</v>
       </c>
       <c r="B84" t="n">
-        <v>91485</v>
+        <v>80223</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9096,10 +9096,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>634676</v>
+        <v>634926</v>
       </c>
       <c r="R84" t="n">
-        <v>7087616</v>
+        <v>7087292</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9146,44 +9146,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128423575</v>
+        <v>128423166</v>
       </c>
       <c r="B85" t="n">
-        <v>91432</v>
+        <v>79089</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9193,10 +9193,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>634574</v>
+        <v>634652</v>
       </c>
       <c r="R85" t="n">
-        <v>7087286</v>
+        <v>7087690</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9243,44 +9243,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128423106</v>
+        <v>128423606</v>
       </c>
       <c r="B86" t="n">
-        <v>80223</v>
+        <v>80194</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9290,10 +9290,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>634926</v>
+        <v>635122</v>
       </c>
       <c r="R86" t="n">
-        <v>7087292</v>
+        <v>7087242</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9340,22 +9340,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128423166</v>
+        <v>128423618</v>
       </c>
       <c r="B87" t="n">
-        <v>79089</v>
+        <v>91485</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9363,21 +9363,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9387,10 +9387,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>634652</v>
+        <v>634676</v>
       </c>
       <c r="R87" t="n">
-        <v>7087690</v>
+        <v>7087616</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9437,44 +9437,44 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128423606</v>
+        <v>128423575</v>
       </c>
       <c r="B88" t="n">
-        <v>80194</v>
+        <v>91432</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9484,10 +9484,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>635122</v>
+        <v>634574</v>
       </c>
       <c r="R88" t="n">
-        <v>7087242</v>
+        <v>7087286</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9546,10 +9546,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128423615</v>
+        <v>128404903</v>
       </c>
       <c r="B89" t="n">
-        <v>91481</v>
+        <v>91485</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9557,34 +9557,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>634897</v>
+        <v>635552</v>
       </c>
       <c r="R89" t="n">
-        <v>7087591</v>
+        <v>7087334</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9614,9 +9614,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9631,44 +9641,44 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128423097</v>
+        <v>128423092</v>
       </c>
       <c r="B90" t="n">
-        <v>91467</v>
+        <v>91432</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9678,10 +9688,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>635320</v>
+        <v>634661</v>
       </c>
       <c r="R90" t="n">
-        <v>7087069</v>
+        <v>7087688</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9740,32 +9750,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128423099</v>
+        <v>128423624</v>
       </c>
       <c r="B91" t="n">
-        <v>92164</v>
+        <v>88867</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3298</v>
+        <v>510</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9775,10 +9785,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>634570</v>
+        <v>634461</v>
       </c>
       <c r="R91" t="n">
-        <v>7087303</v>
+        <v>7087363</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9825,44 +9835,44 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128423092</v>
+        <v>128423615</v>
       </c>
       <c r="B92" t="n">
-        <v>91432</v>
+        <v>91481</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9872,10 +9882,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>634661</v>
+        <v>634897</v>
       </c>
       <c r="R92" t="n">
-        <v>7087688</v>
+        <v>7087591</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9922,22 +9932,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128423155</v>
+        <v>128423097</v>
       </c>
       <c r="B93" t="n">
-        <v>79089</v>
+        <v>91467</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9945,21 +9955,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9969,10 +9979,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>635294</v>
+        <v>635320</v>
       </c>
       <c r="R93" t="n">
-        <v>7087064</v>
+        <v>7087069</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10031,10 +10041,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128423127</v>
+        <v>128423099</v>
       </c>
       <c r="B94" t="n">
-        <v>79113</v>
+        <v>92164</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10042,21 +10052,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6434</v>
+        <v>3298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10066,10 +10076,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>635508</v>
+        <v>634570</v>
       </c>
       <c r="R94" t="n">
-        <v>7087301</v>
+        <v>7087303</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10128,27 +10138,27 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128423628</v>
+        <v>128423155</v>
       </c>
       <c r="B95" t="n">
-        <v>80229</v>
+        <v>79089</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -10163,10 +10173,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>635451</v>
+        <v>635294</v>
       </c>
       <c r="R95" t="n">
-        <v>7087225</v>
+        <v>7087064</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10213,44 +10223,44 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128423175</v>
+        <v>128423127</v>
       </c>
       <c r="B96" t="n">
-        <v>79089</v>
+        <v>79113</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10260,10 +10270,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>635169</v>
+        <v>635508</v>
       </c>
       <c r="R96" t="n">
-        <v>7087269</v>
+        <v>7087301</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10322,10 +10332,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128409643</v>
+        <v>128423628</v>
       </c>
       <c r="B97" t="n">
-        <v>80223</v>
+        <v>80229</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10333,34 +10343,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>634947</v>
+        <v>635451</v>
       </c>
       <c r="R97" t="n">
-        <v>7087432</v>
+        <v>7087225</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10390,19 +10400,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>13:43</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10417,22 +10417,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128404903</v>
+        <v>128423175</v>
       </c>
       <c r="B98" t="n">
-        <v>91485</v>
+        <v>79089</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10440,34 +10440,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>635552</v>
+        <v>635169</v>
       </c>
       <c r="R98" t="n">
-        <v>7087334</v>
+        <v>7087269</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10497,19 +10497,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10524,57 +10514,57 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128423189</v>
+        <v>128409643</v>
       </c>
       <c r="B99" t="n">
-        <v>79089</v>
+        <v>80223</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>635678</v>
+        <v>634947</v>
       </c>
       <c r="R99" t="n">
-        <v>7087274</v>
+        <v>7087432</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10604,9 +10594,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10621,22 +10621,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128423624</v>
+        <v>128423189</v>
       </c>
       <c r="B100" t="n">
-        <v>88867</v>
+        <v>79089</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10644,21 +10644,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10668,10 +10668,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>634461</v>
+        <v>635678</v>
       </c>
       <c r="R100" t="n">
-        <v>7087363</v>
+        <v>7087274</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10718,12 +10718,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -10832,10 +10832,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128423622</v>
+        <v>128423617</v>
       </c>
       <c r="B102" t="n">
-        <v>88867</v>
+        <v>91485</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10843,21 +10843,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>634642</v>
+        <v>634507</v>
       </c>
       <c r="R102" t="n">
-        <v>7087251</v>
+        <v>7087328</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10929,7 +10929,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128423625</v>
+        <v>128423622</v>
       </c>
       <c r="B103" t="n">
         <v>88867</v>
@@ -10964,10 +10964,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>634494</v>
+        <v>634642</v>
       </c>
       <c r="R103" t="n">
-        <v>7087408</v>
+        <v>7087251</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11026,10 +11026,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128423148</v>
+        <v>128423625</v>
       </c>
       <c r="B104" t="n">
-        <v>91481</v>
+        <v>88867</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11037,21 +11037,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1204</v>
+        <v>510</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11061,10 +11061,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>634924</v>
+        <v>634494</v>
       </c>
       <c r="R104" t="n">
-        <v>7087448</v>
+        <v>7087408</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11111,22 +11111,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128423176</v>
+        <v>128423148</v>
       </c>
       <c r="B105" t="n">
-        <v>79089</v>
+        <v>91481</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11134,21 +11134,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11158,10 +11158,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>635233</v>
+        <v>634924</v>
       </c>
       <c r="R105" t="n">
-        <v>7087199</v>
+        <v>7087448</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11220,27 +11220,27 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128423629</v>
+        <v>128423176</v>
       </c>
       <c r="B106" t="n">
-        <v>80229</v>
+        <v>79089</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -11255,10 +11255,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>635454</v>
+        <v>635233</v>
       </c>
       <c r="R106" t="n">
-        <v>7087257</v>
+        <v>7087199</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11305,39 +11305,39 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128405478</v>
+        <v>128423629</v>
       </c>
       <c r="B107" t="n">
-        <v>79089</v>
+        <v>80229</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -11346,21 +11346,16 @@
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>635443</v>
+        <v>635454</v>
       </c>
       <c r="R107" t="n">
-        <v>7087145</v>
+        <v>7087257</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11390,19 +11385,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>11:18</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11417,57 +11402,62 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128423110</v>
+        <v>128405478</v>
       </c>
       <c r="B108" t="n">
-        <v>80223</v>
+        <v>79089</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>635475</v>
+        <v>635443</v>
       </c>
       <c r="R108" t="n">
-        <v>7087242</v>
+        <v>7087145</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11497,9 +11487,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11514,19 +11514,19 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128423593</v>
+        <v>128423110</v>
       </c>
       <c r="B109" t="n">
         <v>80223</v>
@@ -11561,10 +11561,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>635471</v>
+        <v>635475</v>
       </c>
       <c r="R109" t="n">
-        <v>7087281</v>
+        <v>7087242</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11611,44 +11611,44 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128423617</v>
+        <v>128423593</v>
       </c>
       <c r="B110" t="n">
-        <v>91485</v>
+        <v>80223</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11658,10 +11658,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>634507</v>
+        <v>635471</v>
       </c>
       <c r="R110" t="n">
-        <v>7087328</v>
+        <v>7087281</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13609,32 +13609,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128423105</v>
+        <v>128423163</v>
       </c>
       <c r="B130" t="n">
-        <v>80223</v>
+        <v>79089</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13644,10 +13644,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>634980</v>
+        <v>634542</v>
       </c>
       <c r="R130" t="n">
-        <v>7087289</v>
+        <v>7087338</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13706,32 +13706,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128423174</v>
+        <v>128423105</v>
       </c>
       <c r="B131" t="n">
-        <v>79089</v>
+        <v>80223</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13741,10 +13741,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>635174</v>
+        <v>634980</v>
       </c>
       <c r="R131" t="n">
-        <v>7087358</v>
+        <v>7087289</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13803,32 +13803,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128423108</v>
+        <v>128423174</v>
       </c>
       <c r="B132" t="n">
-        <v>80223</v>
+        <v>79089</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13838,10 +13838,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>635235</v>
+        <v>635174</v>
       </c>
       <c r="R132" t="n">
-        <v>7087170</v>
+        <v>7087358</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13900,32 +13900,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128423184</v>
+        <v>128423108</v>
       </c>
       <c r="B133" t="n">
-        <v>79089</v>
+        <v>80223</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13935,10 +13935,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>635557</v>
+        <v>635235</v>
       </c>
       <c r="R133" t="n">
-        <v>7087287</v>
+        <v>7087170</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13997,10 +13997,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128413206</v>
+        <v>128423184</v>
       </c>
       <c r="B134" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14008,39 +14008,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>634574</v>
+        <v>635557</v>
       </c>
       <c r="R134" t="n">
-        <v>7087273</v>
+        <v>7087287</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14070,19 +14065,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>16:13</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14097,22 +14082,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128423117</v>
+        <v>128413206</v>
       </c>
       <c r="B135" t="n">
-        <v>57689</v>
+        <v>57686</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14120,16 +14105,16 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -14138,16 +14123,21 @@
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>635201</v>
+        <v>634574</v>
       </c>
       <c r="R135" t="n">
-        <v>7087140</v>
+        <v>7087273</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14177,14 +14167,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14195,41 +14190,26 @@
       </c>
       <c r="AG135" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK135" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO135" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128423163</v>
+        <v>128423117</v>
       </c>
       <c r="B136" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14237,21 +14217,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14261,10 +14241,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>634542</v>
+        <v>635201</v>
       </c>
       <c r="R136" t="n">
-        <v>7087338</v>
+        <v>7087140</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14299,6 +14279,11 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
@@ -14307,6 +14292,21 @@
       </c>
       <c r="AG136" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
@@ -19954,10 +19954,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128423590</v>
+        <v>128423168</v>
       </c>
       <c r="B193" t="n">
-        <v>92749</v>
+        <v>79089</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19965,21 +19965,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19989,10 +19989,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>635182</v>
+        <v>634865</v>
       </c>
       <c r="R193" t="n">
-        <v>7087227</v>
+        <v>7087586</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20039,44 +20039,44 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128423138</v>
+        <v>128423596</v>
       </c>
       <c r="B194" t="n">
-        <v>80230</v>
+        <v>57686</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20086,10 +20086,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>635160</v>
+        <v>634648</v>
       </c>
       <c r="R194" t="n">
-        <v>7087012</v>
+        <v>7087590</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20136,22 +20136,22 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128423172</v>
+        <v>128423588</v>
       </c>
       <c r="B195" t="n">
-        <v>79089</v>
+        <v>57849</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20159,21 +20159,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20183,10 +20183,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>635010</v>
+        <v>634560</v>
       </c>
       <c r="R195" t="n">
-        <v>7087362</v>
+        <v>7087311</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20233,44 +20233,44 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>128423109</v>
+        <v>128423590</v>
       </c>
       <c r="B196" t="n">
-        <v>80223</v>
+        <v>92749</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6462</v>
+        <v>4361</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20280,10 +20280,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>635407</v>
+        <v>635182</v>
       </c>
       <c r="R196" t="n">
-        <v>7087128</v>
+        <v>7087227</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20330,44 +20330,44 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>128423160</v>
+        <v>128423138</v>
       </c>
       <c r="B197" t="n">
-        <v>79089</v>
+        <v>80230</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20377,10 +20377,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>634916</v>
+        <v>635160</v>
       </c>
       <c r="R197" t="n">
-        <v>7087311</v>
+        <v>7087012</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20439,10 +20439,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>128423135</v>
+        <v>128423172</v>
       </c>
       <c r="B198" t="n">
-        <v>80194</v>
+        <v>79089</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20450,21 +20450,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -20474,10 +20474,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>635412</v>
+        <v>635010</v>
       </c>
       <c r="R198" t="n">
-        <v>7087118</v>
+        <v>7087362</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20536,32 +20536,32 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>128423168</v>
+        <v>128423109</v>
       </c>
       <c r="B199" t="n">
-        <v>79089</v>
+        <v>80223</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -20571,10 +20571,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>634865</v>
+        <v>635407</v>
       </c>
       <c r="R199" t="n">
-        <v>7087586</v>
+        <v>7087128</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20633,10 +20633,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>128423596</v>
+        <v>128423160</v>
       </c>
       <c r="B200" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20644,21 +20644,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20668,10 +20668,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>634648</v>
+        <v>634916</v>
       </c>
       <c r="R200" t="n">
-        <v>7087590</v>
+        <v>7087311</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20718,22 +20718,22 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>128423118</v>
+        <v>128423135</v>
       </c>
       <c r="B201" t="n">
-        <v>57689</v>
+        <v>80194</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20741,21 +20741,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20765,10 +20765,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>634924</v>
+        <v>635412</v>
       </c>
       <c r="R201" t="n">
-        <v>7087288</v>
+        <v>7087118</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20803,11 +20803,6 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD201" t="b">
         <v>0</v>
       </c>
@@ -20816,21 +20811,6 @@
       </c>
       <c r="AG201" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ201" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK201" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO201" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
@@ -20847,10 +20827,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>128423588</v>
+        <v>128423118</v>
       </c>
       <c r="B202" t="n">
-        <v>57849</v>
+        <v>57689</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20858,21 +20838,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -20882,10 +20862,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>634560</v>
+        <v>634924</v>
       </c>
       <c r="R202" t="n">
-        <v>7087311</v>
+        <v>7087288</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20920,6 +20900,11 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD202" t="b">
         <v>0</v>
       </c>
@@ -20928,16 +20913,31 @@
       </c>
       <c r="AG202" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO202" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
@@ -21638,10 +21638,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128423199</v>
+        <v>128423170</v>
       </c>
       <c r="B210" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21649,38 +21649,34 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="K210" t="inlineStr"/>
-      <c r="L210" t="inlineStr"/>
-      <c r="M210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>635298</v>
+        <v>634897</v>
       </c>
       <c r="R210" t="n">
-        <v>7087096</v>
+        <v>7087496</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21713,11 +21709,6 @@
       <c r="AA210" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -21744,10 +21735,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>128423121</v>
+        <v>128423188</v>
       </c>
       <c r="B211" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21755,21 +21746,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -21779,10 +21770,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>635167</v>
+        <v>635610</v>
       </c>
       <c r="R211" t="n">
-        <v>7087269</v>
+        <v>7087261</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21815,11 +21806,6 @@
       <c r="AA211" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -21846,45 +21832,49 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>128423595</v>
+        <v>128423199</v>
       </c>
       <c r="B212" t="n">
-        <v>80223</v>
+        <v>57689</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>635632</v>
+        <v>635298</v>
       </c>
       <c r="R212" t="n">
-        <v>7087270</v>
+        <v>7087096</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21919,6 +21909,11 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD212" t="b">
         <v>0</v>
       </c>
@@ -21931,22 +21926,22 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>128423171</v>
+        <v>128423121</v>
       </c>
       <c r="B213" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -21954,21 +21949,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -21978,10 +21973,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>634973</v>
+        <v>635167</v>
       </c>
       <c r="R213" t="n">
-        <v>7087410</v>
+        <v>7087269</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22014,6 +22009,11 @@
       <c r="AA213" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -22040,32 +22040,32 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>128423170</v>
+        <v>128423595</v>
       </c>
       <c r="B214" t="n">
-        <v>79089</v>
+        <v>80223</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -22075,10 +22075,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>634897</v>
+        <v>635632</v>
       </c>
       <c r="R214" t="n">
-        <v>7087496</v>
+        <v>7087270</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22125,19 +22125,19 @@
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>128423188</v>
+        <v>128423171</v>
       </c>
       <c r="B215" t="n">
         <v>79089</v>
@@ -22172,10 +22172,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>635610</v>
+        <v>634973</v>
       </c>
       <c r="R215" t="n">
-        <v>7087261</v>
+        <v>7087410</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23142,10 +23142,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>128423087</v>
+        <v>128423173</v>
       </c>
       <c r="B225" t="n">
-        <v>79121</v>
+        <v>79089</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23153,21 +23153,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23177,10 +23177,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>634647</v>
+        <v>635138</v>
       </c>
       <c r="R225" t="n">
-        <v>7087542</v>
+        <v>7087339</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23239,10 +23239,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>128423173</v>
+        <v>128423087</v>
       </c>
       <c r="B226" t="n">
-        <v>79089</v>
+        <v>79121</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23250,21 +23250,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23274,10 +23274,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>635138</v>
+        <v>634647</v>
       </c>
       <c r="R226" t="n">
-        <v>7087339</v>
+        <v>7087542</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23336,10 +23336,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128428584</v>
+        <v>128428573</v>
       </c>
       <c r="B227" t="n">
-        <v>82948</v>
+        <v>79089</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23347,21 +23347,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23371,10 +23371,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>634824</v>
+        <v>634610</v>
       </c>
       <c r="R227" t="n">
-        <v>7087360</v>
+        <v>7087361</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23433,10 +23433,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128428573</v>
+        <v>128428584</v>
       </c>
       <c r="B228" t="n">
-        <v>79089</v>
+        <v>82948</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -23444,21 +23444,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -23468,10 +23468,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>634610</v>
+        <v>634824</v>
       </c>
       <c r="R228" t="n">
-        <v>7087361</v>
+        <v>7087360</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24517,10 +24517,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>128428554</v>
+        <v>128428537</v>
       </c>
       <c r="B239" t="n">
-        <v>80195</v>
+        <v>57689</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -24528,34 +24528,42 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>635037</v>
+        <v>635466</v>
       </c>
       <c r="R239" t="n">
-        <v>7087279</v>
+        <v>7087249</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24588,6 +24596,11 @@
       <c r="AA239" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC239" t="inlineStr">
+        <is>
+          <t>Ca 3 m upp på liggande granlåga. Runt bohål, omkr 45 mm i diameter.</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -24614,10 +24627,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>128428568</v>
+        <v>128428554</v>
       </c>
       <c r="B240" t="n">
-        <v>91481</v>
+        <v>80195</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -24625,21 +24638,21 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -24649,10 +24662,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>634725</v>
+        <v>635037</v>
       </c>
       <c r="R240" t="n">
-        <v>7087631</v>
+        <v>7087279</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24711,10 +24724,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>128428571</v>
+        <v>128428568</v>
       </c>
       <c r="B241" t="n">
-        <v>79089</v>
+        <v>91481</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24722,21 +24735,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -24746,10 +24759,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>635190</v>
+        <v>634725</v>
       </c>
       <c r="R241" t="n">
-        <v>7087142</v>
+        <v>7087631</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -24808,10 +24821,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>128428537</v>
+        <v>128428571</v>
       </c>
       <c r="B242" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -24819,42 +24832,34 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
-      <c r="K242" t="inlineStr"/>
-      <c r="L242" t="inlineStr"/>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>635466</v>
+        <v>635190</v>
       </c>
       <c r="R242" t="n">
-        <v>7087249</v>
+        <v>7087142</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24887,11 +24892,6 @@
       <c r="AA242" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC242" t="inlineStr">
-        <is>
-          <t>Ca 3 m upp på liggande granlåga. Runt bohål, omkr 45 mm i diameter.</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -25611,10 +25611,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>128428581</v>
+        <v>128428596</v>
       </c>
       <c r="B250" t="n">
-        <v>82948</v>
+        <v>75169</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -25622,21 +25622,21 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -25646,10 +25646,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>635622</v>
+        <v>635551</v>
       </c>
       <c r="R250" t="n">
-        <v>7087310</v>
+        <v>7087334</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -25708,10 +25708,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>128428559</v>
+        <v>128428590</v>
       </c>
       <c r="B251" t="n">
-        <v>80194</v>
+        <v>88867</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -25719,21 +25719,21 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -25743,10 +25743,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>635416</v>
+        <v>634658</v>
       </c>
       <c r="R251" t="n">
-        <v>7087178</v>
+        <v>7087313</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -25805,10 +25805,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>128428596</v>
+        <v>128428581</v>
       </c>
       <c r="B252" t="n">
-        <v>75169</v>
+        <v>82948</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -25816,21 +25816,21 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -25840,10 +25840,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>635551</v>
+        <v>635622</v>
       </c>
       <c r="R252" t="n">
-        <v>7087334</v>
+        <v>7087310</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -25902,10 +25902,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>128428590</v>
+        <v>128428559</v>
       </c>
       <c r="B253" t="n">
-        <v>88867</v>
+        <v>80194</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -25913,21 +25913,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -25937,10 +25937,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>634658</v>
+        <v>635416</v>
       </c>
       <c r="R253" t="n">
-        <v>7087313</v>
+        <v>7087178</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26678,10 +26678,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128428532</v>
+        <v>128428558</v>
       </c>
       <c r="B261" t="n">
-        <v>91467</v>
+        <v>80194</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -26689,21 +26689,21 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -26713,10 +26713,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>634476</v>
+        <v>635306</v>
       </c>
       <c r="R261" t="n">
-        <v>7087366</v>
+        <v>7087221</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26775,10 +26775,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128428558</v>
+        <v>128428532</v>
       </c>
       <c r="B262" t="n">
-        <v>80194</v>
+        <v>91467</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -26786,21 +26786,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -26810,10 +26810,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>635306</v>
+        <v>634476</v>
       </c>
       <c r="R262" t="n">
-        <v>7087221</v>
+        <v>7087366</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -28158,53 +28158,45 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>128428550</v>
+        <v>128428562</v>
       </c>
       <c r="B276" t="n">
-        <v>57686</v>
+        <v>80230</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N276" t="inlineStr"/>
       <c r="P276" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>634487</v>
+        <v>635398</v>
       </c>
       <c r="R276" t="n">
-        <v>7087401</v>
+        <v>7087183</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -28263,7 +28255,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>128428552</v>
+        <v>128428550</v>
       </c>
       <c r="B277" t="n">
         <v>57686</v>
@@ -28306,10 +28298,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>635170</v>
+        <v>634487</v>
       </c>
       <c r="R277" t="n">
-        <v>7087231</v>
+        <v>7087401</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -28368,45 +28360,53 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>128428562</v>
+        <v>128428552</v>
       </c>
       <c r="B278" t="n">
-        <v>80230</v>
+        <v>57686</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>635398</v>
+        <v>635170</v>
       </c>
       <c r="R278" t="n">
-        <v>7087183</v>
+        <v>7087231</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -28979,7 +28979,7 @@
         <v>128492196</v>
       </c>
       <c r="B284" t="n">
-        <v>95830</v>
+        <v>95857</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>128492197</v>
       </c>
       <c r="B285" t="n">
-        <v>95818</v>
+        <v>95845</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>128651017</v>
       </c>
       <c r="B286" t="n">
-        <v>96933</v>
+        <v>96960</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>

--- a/artfynd/A 30047-2025 artfynd.xlsx
+++ b/artfynd/A 30047-2025 artfynd.xlsx
@@ -7004,10 +7004,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128423158</v>
+        <v>128408152</v>
       </c>
       <c r="B63" t="n">
-        <v>79120</v>
+        <v>91522</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7015,34 +7015,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>635124</v>
+        <v>635231</v>
       </c>
       <c r="R63" t="n">
-        <v>7087198</v>
+        <v>7087279</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7072,9 +7072,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7089,44 +7099,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128423091</v>
+        <v>128423158</v>
       </c>
       <c r="B64" t="n">
-        <v>91469</v>
+        <v>79120</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7136,10 +7146,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>634922</v>
+        <v>635124</v>
       </c>
       <c r="R64" t="n">
-        <v>7087295</v>
+        <v>7087198</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7198,45 +7208,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128408152</v>
+        <v>128423091</v>
       </c>
       <c r="B65" t="n">
-        <v>91522</v>
+        <v>91469</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>635231</v>
+        <v>634922</v>
       </c>
       <c r="R65" t="n">
-        <v>7087279</v>
+        <v>7087295</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7266,19 +7276,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>12:54</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7293,12 +7293,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7499,7 +7499,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128423178</v>
+        <v>128423179</v>
       </c>
       <c r="B68" t="n">
         <v>79120</v>
@@ -7534,10 +7534,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>635318</v>
+        <v>635348</v>
       </c>
       <c r="R68" t="n">
-        <v>7087158</v>
+        <v>7087138</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7596,7 +7596,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128423179</v>
+        <v>128423178</v>
       </c>
       <c r="B69" t="n">
         <v>79120</v>
@@ -7631,10 +7631,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>635348</v>
+        <v>635318</v>
       </c>
       <c r="R69" t="n">
-        <v>7087138</v>
+        <v>7087158</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7693,10 +7693,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128423142</v>
+        <v>128411934</v>
       </c>
       <c r="B70" t="n">
-        <v>80261</v>
+        <v>91469</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7704,34 +7704,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>635234</v>
+        <v>634525</v>
       </c>
       <c r="R70" t="n">
-        <v>7087170</v>
+        <v>7087336</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7761,9 +7761,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7778,19 +7788,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128423159</v>
+        <v>128423165</v>
       </c>
       <c r="B71" t="n">
         <v>79120</v>
@@ -7825,10 +7835,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>635080</v>
+        <v>634654</v>
       </c>
       <c r="R71" t="n">
-        <v>7087206</v>
+        <v>7087545</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7887,32 +7897,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128423140</v>
+        <v>128423159</v>
       </c>
       <c r="B72" t="n">
-        <v>80261</v>
+        <v>79120</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7922,10 +7932,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>635608</v>
+        <v>635080</v>
       </c>
       <c r="R72" t="n">
-        <v>7087280</v>
+        <v>7087206</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7984,32 +7994,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128423165</v>
+        <v>128423142</v>
       </c>
       <c r="B73" t="n">
-        <v>79120</v>
+        <v>80261</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8019,10 +8029,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>634654</v>
+        <v>635234</v>
       </c>
       <c r="R73" t="n">
-        <v>7087545</v>
+        <v>7087170</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8081,10 +8091,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128411934</v>
+        <v>128423140</v>
       </c>
       <c r="B74" t="n">
-        <v>91469</v>
+        <v>80261</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8092,34 +8102,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>6464</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>634525</v>
+        <v>635608</v>
       </c>
       <c r="R74" t="n">
-        <v>7087336</v>
+        <v>7087280</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8149,19 +8159,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8176,44 +8176,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128423106</v>
+        <v>128423166</v>
       </c>
       <c r="B75" t="n">
-        <v>80254</v>
+        <v>79120</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8223,10 +8223,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>634926</v>
+        <v>634652</v>
       </c>
       <c r="R75" t="n">
-        <v>7087292</v>
+        <v>7087690</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8285,32 +8285,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128423166</v>
+        <v>128423106</v>
       </c>
       <c r="B76" t="n">
-        <v>79120</v>
+        <v>80254</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8320,10 +8320,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>634652</v>
+        <v>634926</v>
       </c>
       <c r="R76" t="n">
-        <v>7087690</v>
+        <v>7087292</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8382,32 +8382,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128423099</v>
+        <v>128423097</v>
       </c>
       <c r="B77" t="n">
-        <v>92201</v>
+        <v>91504</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8417,10 +8417,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>634570</v>
+        <v>635320</v>
       </c>
       <c r="R77" t="n">
-        <v>7087303</v>
+        <v>7087069</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8479,45 +8479,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128423097</v>
+        <v>128409643</v>
       </c>
       <c r="B78" t="n">
-        <v>91504</v>
+        <v>80254</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>635320</v>
+        <v>634947</v>
       </c>
       <c r="R78" t="n">
-        <v>7087069</v>
+        <v>7087432</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8547,9 +8547,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8564,22 +8574,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128409643</v>
+        <v>128423127</v>
       </c>
       <c r="B79" t="n">
-        <v>80254</v>
+        <v>79144</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8587,34 +8597,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>6434</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>634947</v>
+        <v>635508</v>
       </c>
       <c r="R79" t="n">
-        <v>7087432</v>
+        <v>7087301</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8644,19 +8654,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13:43</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8671,22 +8671,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128423127</v>
+        <v>128423099</v>
       </c>
       <c r="B80" t="n">
-        <v>79144</v>
+        <v>92201</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8694,21 +8694,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6434</v>
+        <v>3298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8718,10 +8718,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>635508</v>
+        <v>634570</v>
       </c>
       <c r="R80" t="n">
-        <v>7087301</v>
+        <v>7087303</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8780,10 +8780,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128423189</v>
+        <v>128404903</v>
       </c>
       <c r="B81" t="n">
-        <v>79120</v>
+        <v>91522</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8791,34 +8791,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>635678</v>
+        <v>635552</v>
       </c>
       <c r="R81" t="n">
-        <v>7087274</v>
+        <v>7087334</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8848,9 +8848,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8865,44 +8875,44 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128423155</v>
+        <v>128423092</v>
       </c>
       <c r="B82" t="n">
-        <v>79120</v>
+        <v>91469</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8912,10 +8922,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>635294</v>
+        <v>634661</v>
       </c>
       <c r="R82" t="n">
-        <v>7087064</v>
+        <v>7087688</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8974,7 +8984,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128423175</v>
+        <v>128423155</v>
       </c>
       <c r="B83" t="n">
         <v>79120</v>
@@ -9009,10 +9019,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>635169</v>
+        <v>635294</v>
       </c>
       <c r="R83" t="n">
-        <v>7087269</v>
+        <v>7087064</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9071,10 +9081,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128404903</v>
+        <v>128423175</v>
       </c>
       <c r="B84" t="n">
-        <v>91522</v>
+        <v>79120</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9082,34 +9092,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>635552</v>
+        <v>635169</v>
       </c>
       <c r="R84" t="n">
-        <v>7087334</v>
+        <v>7087269</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9139,19 +9149,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9166,44 +9166,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128423092</v>
+        <v>128423189</v>
       </c>
       <c r="B85" t="n">
-        <v>91469</v>
+        <v>79120</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9213,10 +9213,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>634661</v>
+        <v>635678</v>
       </c>
       <c r="R85" t="n">
-        <v>7087688</v>
+        <v>7087274</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9275,10 +9275,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128423119</v>
+        <v>128423148</v>
       </c>
       <c r="B86" t="n">
-        <v>57716</v>
+        <v>91518</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9286,21 +9286,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9310,10 +9310,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>634914</v>
+        <v>634924</v>
       </c>
       <c r="R86" t="n">
-        <v>7087316</v>
+        <v>7087448</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9346,11 +9346,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9377,10 +9372,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128423148</v>
+        <v>128423119</v>
       </c>
       <c r="B87" t="n">
-        <v>91518</v>
+        <v>57716</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9388,21 +9383,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9412,10 +9407,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>634924</v>
+        <v>634914</v>
       </c>
       <c r="R87" t="n">
-        <v>7087448</v>
+        <v>7087316</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9448,6 +9443,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9586,32 +9586,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128423110</v>
+        <v>128423176</v>
       </c>
       <c r="B89" t="n">
-        <v>80254</v>
+        <v>79120</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9621,10 +9621,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>635475</v>
+        <v>635233</v>
       </c>
       <c r="R89" t="n">
-        <v>7087242</v>
+        <v>7087199</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9683,32 +9683,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128423176</v>
+        <v>128423110</v>
       </c>
       <c r="B90" t="n">
-        <v>79120</v>
+        <v>80254</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9718,10 +9718,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>635233</v>
+        <v>635475</v>
       </c>
       <c r="R90" t="n">
-        <v>7087199</v>
+        <v>7087242</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9780,32 +9780,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128423089</v>
+        <v>128423193</v>
       </c>
       <c r="B91" t="n">
-        <v>91469</v>
+        <v>88904</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9815,10 +9815,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>635295</v>
+        <v>634638</v>
       </c>
       <c r="R91" t="n">
-        <v>7087129</v>
+        <v>7087656</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9877,32 +9877,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128423116</v>
+        <v>128423195</v>
       </c>
       <c r="B92" t="n">
-        <v>57716</v>
+        <v>80260</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9912,10 +9912,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>635330</v>
+        <v>635228</v>
       </c>
       <c r="R92" t="n">
-        <v>7087114</v>
+        <v>7087058</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9948,11 +9948,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9979,7 +9974,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128423085</v>
+        <v>128423116</v>
       </c>
       <c r="B93" t="n">
         <v>57716</v>
@@ -10014,10 +10009,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>635508</v>
+        <v>635330</v>
       </c>
       <c r="R93" t="n">
-        <v>7087292</v>
+        <v>7087114</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10081,45 +10076,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128409304</v>
+        <v>128423085</v>
       </c>
       <c r="B94" t="n">
-        <v>56907</v>
+        <v>57716</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>634947</v>
+        <v>635508</v>
       </c>
       <c r="R94" t="n">
-        <v>7087432</v>
+        <v>7087292</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10149,19 +10144,14 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>13:34</t>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10176,57 +10166,57 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128423193</v>
+        <v>128409304</v>
       </c>
       <c r="B95" t="n">
-        <v>88904</v>
+        <v>56907</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>510</v>
+        <v>100138</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>634638</v>
+        <v>634947</v>
       </c>
       <c r="R95" t="n">
-        <v>7087656</v>
+        <v>7087432</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10256,9 +10246,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10273,44 +10273,44 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128423136</v>
+        <v>128423089</v>
       </c>
       <c r="B96" t="n">
-        <v>80225</v>
+        <v>91469</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10320,10 +10320,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>635422</v>
+        <v>635295</v>
       </c>
       <c r="R96" t="n">
-        <v>7087149</v>
+        <v>7087129</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10382,10 +10382,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128410776</v>
+        <v>128423136</v>
       </c>
       <c r="B97" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10393,34 +10393,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>634709</v>
+        <v>635422</v>
       </c>
       <c r="R97" t="n">
-        <v>7087670</v>
+        <v>7087149</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10450,19 +10450,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>14:41</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>14:41</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10477,39 +10467,39 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128423195</v>
+        <v>128410776</v>
       </c>
       <c r="B98" t="n">
-        <v>80260</v>
+        <v>79120</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -10520,14 +10510,14 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>635228</v>
+        <v>634709</v>
       </c>
       <c r="R98" t="n">
-        <v>7087058</v>
+        <v>7087670</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10557,9 +10547,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10574,12 +10574,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -10984,32 +10984,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128423108</v>
+        <v>128423117</v>
       </c>
       <c r="B103" t="n">
-        <v>80254</v>
+        <v>57716</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11019,10 +11019,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>635235</v>
+        <v>635201</v>
       </c>
       <c r="R103" t="n">
-        <v>7087170</v>
+        <v>7087140</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11057,6 +11057,11 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -11065,6 +11070,21 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -11178,32 +11198,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128423105</v>
+        <v>128423184</v>
       </c>
       <c r="B105" t="n">
-        <v>80254</v>
+        <v>79120</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11213,10 +11233,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>634980</v>
+        <v>635557</v>
       </c>
       <c r="R105" t="n">
-        <v>7087289</v>
+        <v>7087287</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11275,50 +11295,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128413206</v>
+        <v>128423108</v>
       </c>
       <c r="B106" t="n">
-        <v>57713</v>
+        <v>80254</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>634574</v>
+        <v>635235</v>
       </c>
       <c r="R106" t="n">
-        <v>7087273</v>
+        <v>7087170</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11348,19 +11363,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>16:13</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11375,19 +11380,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128423184</v>
+        <v>128423174</v>
       </c>
       <c r="B107" t="n">
         <v>79120</v>
@@ -11422,10 +11427,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>635557</v>
+        <v>635174</v>
       </c>
       <c r="R107" t="n">
-        <v>7087287</v>
+        <v>7087358</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11484,32 +11489,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128423174</v>
+        <v>128423105</v>
       </c>
       <c r="B108" t="n">
-        <v>79120</v>
+        <v>80254</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11519,10 +11524,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>635174</v>
+        <v>634980</v>
       </c>
       <c r="R108" t="n">
-        <v>7087358</v>
+        <v>7087289</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11581,10 +11586,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128423117</v>
+        <v>128413206</v>
       </c>
       <c r="B109" t="n">
-        <v>57716</v>
+        <v>57713</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11592,16 +11597,16 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -11610,16 +11615,21 @@
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>635201</v>
+        <v>634574</v>
       </c>
       <c r="R109" t="n">
-        <v>7087140</v>
+        <v>7087273</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11649,14 +11659,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11667,41 +11682,26 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128423096</v>
+        <v>128413141</v>
       </c>
       <c r="B110" t="n">
-        <v>91504</v>
+        <v>57716</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11709,34 +11709,42 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>635249</v>
+        <v>634574</v>
       </c>
       <c r="R110" t="n">
-        <v>7087032</v>
+        <v>7087273</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11766,9 +11774,24 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11783,19 +11806,19 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128423098</v>
+        <v>128423096</v>
       </c>
       <c r="B111" t="n">
         <v>91504</v>
@@ -11830,10 +11853,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>635186</v>
+        <v>635249</v>
       </c>
       <c r="R111" t="n">
-        <v>7087317</v>
+        <v>7087032</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11892,32 +11915,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128423128</v>
+        <v>128423098</v>
       </c>
       <c r="B112" t="n">
-        <v>80253</v>
+        <v>91504</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11927,10 +11950,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>634915</v>
+        <v>635186</v>
       </c>
       <c r="R112" t="n">
-        <v>7087322</v>
+        <v>7087317</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11989,32 +12012,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128423157</v>
+        <v>128423128</v>
       </c>
       <c r="B113" t="n">
-        <v>79120</v>
+        <v>80253</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12024,10 +12047,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>635204</v>
+        <v>634915</v>
       </c>
       <c r="R113" t="n">
-        <v>7087134</v>
+        <v>7087322</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12086,7 +12109,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128423187</v>
+        <v>128404427</v>
       </c>
       <c r="B114" t="n">
         <v>79120</v>
@@ -12115,16 +12138,21 @@
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>635591</v>
+        <v>635552</v>
       </c>
       <c r="R114" t="n">
-        <v>7087249</v>
+        <v>7087334</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12154,9 +12182,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12171,12 +12209,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -12280,32 +12318,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128423139</v>
+        <v>128423187</v>
       </c>
       <c r="B116" t="n">
-        <v>80261</v>
+        <v>79120</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12315,10 +12353,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>635237</v>
+        <v>635591</v>
       </c>
       <c r="R116" t="n">
-        <v>7087043</v>
+        <v>7087249</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12377,27 +12415,27 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128423194</v>
+        <v>128423157</v>
       </c>
       <c r="B117" t="n">
-        <v>80260</v>
+        <v>79120</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -12412,10 +12450,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>635234</v>
+        <v>635204</v>
       </c>
       <c r="R117" t="n">
-        <v>7087032</v>
+        <v>7087134</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12474,7 +12512,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128404427</v>
+        <v>128423167</v>
       </c>
       <c r="B118" t="n">
         <v>79120</v>
@@ -12503,21 +12541,16 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>635552</v>
+        <v>634719</v>
       </c>
       <c r="R118" t="n">
-        <v>7087334</v>
+        <v>7087623</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12547,19 +12580,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>10:33</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12574,44 +12597,44 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128423167</v>
+        <v>128423139</v>
       </c>
       <c r="B119" t="n">
-        <v>79120</v>
+        <v>80261</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12621,10 +12644,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>634719</v>
+        <v>635237</v>
       </c>
       <c r="R119" t="n">
-        <v>7087623</v>
+        <v>7087043</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12683,53 +12706,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128413141</v>
+        <v>128423194</v>
       </c>
       <c r="B120" t="n">
-        <v>57716</v>
+        <v>80260</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>634574</v>
+        <v>635234</v>
       </c>
       <c r="R120" t="n">
-        <v>7087273</v>
+        <v>7087032</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12759,24 +12774,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12791,12 +12791,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -12910,45 +12910,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128409243</v>
+        <v>128423107</v>
       </c>
       <c r="B122" t="n">
-        <v>91518</v>
+        <v>80254</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1204</v>
+        <v>6462</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>634946</v>
+        <v>634931</v>
       </c>
       <c r="R122" t="n">
-        <v>7087431</v>
+        <v>7087432</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12978,19 +12978,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>13:33</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13005,44 +12995,44 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128423162</v>
+        <v>128423141</v>
       </c>
       <c r="B123" t="n">
-        <v>79120</v>
+        <v>80261</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13052,10 +13042,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>634580</v>
+        <v>635232</v>
       </c>
       <c r="R123" t="n">
-        <v>7087268</v>
+        <v>7087062</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13114,10 +13104,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128423107</v>
+        <v>128409160</v>
       </c>
       <c r="B124" t="n">
-        <v>80254</v>
+        <v>91469</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13125,34 +13115,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>634931</v>
+        <v>634944</v>
       </c>
       <c r="R124" t="n">
-        <v>7087432</v>
+        <v>7087430</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13182,9 +13172,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13199,22 +13199,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128423141</v>
+        <v>128423093</v>
       </c>
       <c r="B125" t="n">
-        <v>80261</v>
+        <v>91469</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13222,21 +13222,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13246,10 +13246,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>635232</v>
+        <v>634938</v>
       </c>
       <c r="R125" t="n">
-        <v>7087062</v>
+        <v>7087435</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13308,32 +13308,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128409160</v>
+        <v>128409243</v>
       </c>
       <c r="B126" t="n">
-        <v>91469</v>
+        <v>91518</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13343,10 +13343,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>634944</v>
+        <v>634946</v>
       </c>
       <c r="R126" t="n">
-        <v>7087430</v>
+        <v>7087431</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13378,7 +13378,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13415,32 +13415,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128423093</v>
+        <v>128423162</v>
       </c>
       <c r="B127" t="n">
-        <v>91469</v>
+        <v>79120</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13450,10 +13450,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>634938</v>
+        <v>634580</v>
       </c>
       <c r="R127" t="n">
-        <v>7087435</v>
+        <v>7087268</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13832,10 +13832,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128423101</v>
+        <v>128423113</v>
       </c>
       <c r="B131" t="n">
-        <v>57876</v>
+        <v>80226</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13843,21 +13843,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13867,10 +13867,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>634716</v>
+        <v>635240</v>
       </c>
       <c r="R131" t="n">
-        <v>7087613</v>
+        <v>7087040</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13929,32 +13929,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128423113</v>
+        <v>128423090</v>
       </c>
       <c r="B132" t="n">
-        <v>80226</v>
+        <v>91469</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13964,10 +13964,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>635240</v>
+        <v>635155</v>
       </c>
       <c r="R132" t="n">
-        <v>7087040</v>
+        <v>7087185</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14026,10 +14026,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128423191</v>
+        <v>128423185</v>
       </c>
       <c r="B133" t="n">
-        <v>88904</v>
+        <v>79120</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14037,21 +14037,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14061,10 +14061,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>634676</v>
+        <v>635559</v>
       </c>
       <c r="R133" t="n">
-        <v>7087233</v>
+        <v>7087269</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14123,10 +14123,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128423185</v>
+        <v>128423101</v>
       </c>
       <c r="B134" t="n">
-        <v>79120</v>
+        <v>57876</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14134,21 +14134,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14158,10 +14158,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>635559</v>
+        <v>634716</v>
       </c>
       <c r="R134" t="n">
-        <v>7087269</v>
+        <v>7087613</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14220,32 +14220,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128423126</v>
+        <v>128423191</v>
       </c>
       <c r="B135" t="n">
-        <v>79144</v>
+        <v>88904</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6434</v>
+        <v>510</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14255,10 +14255,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>635212</v>
+        <v>634676</v>
       </c>
       <c r="R135" t="n">
-        <v>7087212</v>
+        <v>7087233</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14317,10 +14317,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128423090</v>
+        <v>128423126</v>
       </c>
       <c r="B136" t="n">
-        <v>91469</v>
+        <v>79144</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14328,21 +14328,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5447</v>
+        <v>6434</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14352,10 +14352,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>635155</v>
+        <v>635212</v>
       </c>
       <c r="R136" t="n">
-        <v>7087185</v>
+        <v>7087212</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14414,10 +14414,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128423161</v>
+        <v>128423147</v>
       </c>
       <c r="B137" t="n">
-        <v>79120</v>
+        <v>91518</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14425,21 +14425,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14449,10 +14449,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>634702</v>
+        <v>634571</v>
       </c>
       <c r="R137" t="n">
-        <v>7087248</v>
+        <v>7087288</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14511,10 +14511,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128423147</v>
+        <v>128404367</v>
       </c>
       <c r="B138" t="n">
-        <v>91518</v>
+        <v>79120</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14522,34 +14522,41 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>634571</v>
+        <v>635556</v>
       </c>
       <c r="R138" t="n">
-        <v>7087288</v>
+        <v>7087281</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14579,39 +14586,50 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128412855</v>
+        <v>128423161</v>
       </c>
       <c r="B139" t="n">
-        <v>91800</v>
+        <v>79120</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14619,34 +14637,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>634574</v>
+        <v>634702</v>
       </c>
       <c r="R139" t="n">
-        <v>7087273</v>
+        <v>7087248</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14676,19 +14694,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>16:03</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14703,22 +14711,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128404367</v>
+        <v>128412855</v>
       </c>
       <c r="B140" t="n">
-        <v>79120</v>
+        <v>91800</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14726,41 +14734,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>635556</v>
+        <v>634574</v>
       </c>
       <c r="R140" t="n">
-        <v>7087281</v>
+        <v>7087273</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14792,7 +14793,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -14802,7 +14803,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14811,7 +14812,6 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -15024,10 +15024,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128411794</v>
+        <v>128423149</v>
       </c>
       <c r="B143" t="n">
-        <v>57876</v>
+        <v>91518</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15035,42 +15035,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>103021</v>
+        <v>1204</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>634505</v>
+        <v>634942</v>
       </c>
       <c r="R143" t="n">
-        <v>7087326</v>
+        <v>7087434</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15100,19 +15092,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>15:28</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15127,44 +15109,44 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128423149</v>
+        <v>128423111</v>
       </c>
       <c r="B144" t="n">
-        <v>91518</v>
+        <v>91515</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15174,10 +15156,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>634942</v>
+        <v>635441</v>
       </c>
       <c r="R144" t="n">
-        <v>7087434</v>
+        <v>7087163</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15236,45 +15218,53 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128423111</v>
+        <v>128411527</v>
       </c>
       <c r="B145" t="n">
-        <v>91515</v>
+        <v>57716</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>635441</v>
+        <v>634480</v>
       </c>
       <c r="R145" t="n">
-        <v>7087163</v>
+        <v>7087349</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15304,9 +15294,24 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15321,19 +15326,19 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128411527</v>
+        <v>128423120</v>
       </c>
       <c r="B146" t="n">
         <v>57716</v>
@@ -15364,22 +15369,18 @@
       <c r="I146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>634480</v>
+        <v>635205</v>
       </c>
       <c r="R146" t="n">
-        <v>7087349</v>
+        <v>7087342</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15409,24 +15410,14 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15441,19 +15432,19 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128423120</v>
+        <v>128423115</v>
       </c>
       <c r="B147" t="n">
         <v>57716</v>
@@ -15482,20 +15473,16 @@
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>635205</v>
+        <v>635461</v>
       </c>
       <c r="R147" t="n">
-        <v>7087342</v>
+        <v>7087189</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15559,10 +15546,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128423115</v>
+        <v>128411794</v>
       </c>
       <c r="B148" t="n">
-        <v>57716</v>
+        <v>57876</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15570,34 +15557,42 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>635461</v>
+        <v>634505</v>
       </c>
       <c r="R148" t="n">
-        <v>7087189</v>
+        <v>7087326</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15627,14 +15622,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15649,12 +15649,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
@@ -15952,32 +15952,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128423129</v>
+        <v>128423186</v>
       </c>
       <c r="B152" t="n">
-        <v>80253</v>
+        <v>79120</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15987,10 +15987,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>635614</v>
+        <v>635555</v>
       </c>
       <c r="R152" t="n">
-        <v>7087262</v>
+        <v>7087248</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16049,32 +16049,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128423186</v>
+        <v>128423129</v>
       </c>
       <c r="B153" t="n">
-        <v>79120</v>
+        <v>80253</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16084,10 +16084,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>635555</v>
+        <v>635614</v>
       </c>
       <c r="R153" t="n">
-        <v>7087248</v>
+        <v>7087262</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16248,32 +16248,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128423138</v>
+        <v>128423118</v>
       </c>
       <c r="B155" t="n">
-        <v>80261</v>
+        <v>57716</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16283,10 +16283,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>635160</v>
+        <v>634924</v>
       </c>
       <c r="R155" t="n">
-        <v>7087012</v>
+        <v>7087288</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16321,6 +16321,11 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD155" t="b">
         <v>0</v>
       </c>
@@ -16329,6 +16334,21 @@
       </c>
       <c r="AG155" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
@@ -16345,32 +16365,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128423168</v>
+        <v>128423109</v>
       </c>
       <c r="B156" t="n">
-        <v>79120</v>
+        <v>80254</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16380,10 +16400,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>634865</v>
+        <v>635407</v>
       </c>
       <c r="R156" t="n">
-        <v>7087586</v>
+        <v>7087128</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16442,10 +16462,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128423160</v>
+        <v>128423135</v>
       </c>
       <c r="B157" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16453,21 +16473,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16477,10 +16497,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>634916</v>
+        <v>635412</v>
       </c>
       <c r="R157" t="n">
-        <v>7087311</v>
+        <v>7087118</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16539,10 +16559,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128423118</v>
+        <v>128423172</v>
       </c>
       <c r="B158" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16550,21 +16570,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16574,10 +16594,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>634924</v>
+        <v>635010</v>
       </c>
       <c r="R158" t="n">
-        <v>7087288</v>
+        <v>7087362</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16612,11 +16632,6 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
@@ -16625,21 +16640,6 @@
       </c>
       <c r="AG158" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ158" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK158" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO158" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
@@ -16656,7 +16656,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128423172</v>
+        <v>128423160</v>
       </c>
       <c r="B159" t="n">
         <v>79120</v>
@@ -16691,10 +16691,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>635010</v>
+        <v>634916</v>
       </c>
       <c r="R159" t="n">
-        <v>7087362</v>
+        <v>7087311</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16753,32 +16753,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128423109</v>
+        <v>128423168</v>
       </c>
       <c r="B160" t="n">
-        <v>80254</v>
+        <v>79120</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16788,10 +16788,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>635407</v>
+        <v>634865</v>
       </c>
       <c r="R160" t="n">
-        <v>7087128</v>
+        <v>7087586</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16850,32 +16850,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128423135</v>
+        <v>128423138</v>
       </c>
       <c r="B161" t="n">
-        <v>80225</v>
+        <v>80261</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16885,10 +16885,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>635412</v>
+        <v>635160</v>
       </c>
       <c r="R161" t="n">
-        <v>7087118</v>
+        <v>7087012</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16947,10 +16947,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128423132</v>
+        <v>128423114</v>
       </c>
       <c r="B162" t="n">
-        <v>80225</v>
+        <v>57716</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16958,21 +16958,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16982,10 +16982,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>635159</v>
+        <v>635207</v>
       </c>
       <c r="R162" t="n">
-        <v>7087014</v>
+        <v>7087210</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17018,6 +17018,11 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17044,10 +17049,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128406204</v>
+        <v>128423151</v>
       </c>
       <c r="B163" t="n">
-        <v>80225</v>
+        <v>91522</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17055,34 +17060,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>635335</v>
+        <v>634546</v>
       </c>
       <c r="R163" t="n">
-        <v>7087214</v>
+        <v>7087320</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17112,19 +17117,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>11:43</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17139,22 +17134,22 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128423156</v>
+        <v>128423132</v>
       </c>
       <c r="B164" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17162,21 +17157,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17186,10 +17181,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>635300</v>
+        <v>635159</v>
       </c>
       <c r="R164" t="n">
-        <v>7087123</v>
+        <v>7087014</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17248,10 +17243,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128423151</v>
+        <v>128406204</v>
       </c>
       <c r="B165" t="n">
-        <v>91522</v>
+        <v>80225</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17259,34 +17254,34 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>634546</v>
+        <v>635335</v>
       </c>
       <c r="R165" t="n">
-        <v>7087320</v>
+        <v>7087214</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17316,9 +17311,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17333,22 +17338,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128423114</v>
+        <v>128423156</v>
       </c>
       <c r="B166" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17356,21 +17361,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17380,10 +17385,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>635207</v>
+        <v>635300</v>
       </c>
       <c r="R166" t="n">
-        <v>7087210</v>
+        <v>7087123</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17416,11 +17421,6 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17447,10 +17447,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128423199</v>
+        <v>128423171</v>
       </c>
       <c r="B167" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17458,38 +17458,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>635298</v>
+        <v>634973</v>
       </c>
       <c r="R167" t="n">
-        <v>7087096</v>
+        <v>7087410</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17522,11 +17518,6 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17553,10 +17544,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128423121</v>
+        <v>128423188</v>
       </c>
       <c r="B168" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17564,21 +17555,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17588,10 +17579,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>635167</v>
+        <v>635610</v>
       </c>
       <c r="R168" t="n">
-        <v>7087269</v>
+        <v>7087261</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17624,11 +17615,6 @@
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17655,7 +17641,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128423171</v>
+        <v>128423170</v>
       </c>
       <c r="B169" t="n">
         <v>79120</v>
@@ -17690,10 +17676,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>634973</v>
+        <v>634897</v>
       </c>
       <c r="R169" t="n">
-        <v>7087410</v>
+        <v>7087496</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17752,10 +17738,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128423188</v>
+        <v>128423199</v>
       </c>
       <c r="B170" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17763,34 +17749,38 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>635610</v>
+        <v>635298</v>
       </c>
       <c r="R170" t="n">
-        <v>7087261</v>
+        <v>7087096</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17823,6 +17813,11 @@
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -17849,10 +17844,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128423170</v>
+        <v>128423121</v>
       </c>
       <c r="B171" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17860,21 +17855,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17884,10 +17879,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>634897</v>
+        <v>635167</v>
       </c>
       <c r="R171" t="n">
-        <v>7087496</v>
+        <v>7087269</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17920,6 +17915,11 @@
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18058,32 +18058,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128423183</v>
+        <v>128423094</v>
       </c>
       <c r="B173" t="n">
-        <v>79120</v>
+        <v>91469</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18093,10 +18093,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>635482</v>
+        <v>635358</v>
       </c>
       <c r="R173" t="n">
-        <v>7087300</v>
+        <v>7087128</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18155,32 +18155,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128423094</v>
+        <v>128423183</v>
       </c>
       <c r="B174" t="n">
-        <v>91469</v>
+        <v>79120</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18190,10 +18190,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>635358</v>
+        <v>635482</v>
       </c>
       <c r="R174" t="n">
-        <v>7087128</v>
+        <v>7087300</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18252,10 +18252,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128405308</v>
+        <v>128423087</v>
       </c>
       <c r="B175" t="n">
-        <v>80225</v>
+        <v>79152</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18263,34 +18263,34 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>635477</v>
+        <v>634647</v>
       </c>
       <c r="R175" t="n">
-        <v>7087164</v>
+        <v>7087542</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18320,19 +18320,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z175" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t>11:11</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18347,22 +18337,22 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128423134</v>
+        <v>128423173</v>
       </c>
       <c r="B176" t="n">
-        <v>80225</v>
+        <v>79120</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18370,21 +18360,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18394,10 +18384,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>635231</v>
+        <v>635138</v>
       </c>
       <c r="R176" t="n">
-        <v>7087059</v>
+        <v>7087339</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18456,10 +18446,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128407951</v>
+        <v>128405308</v>
       </c>
       <c r="B177" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18467,34 +18457,34 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>635217</v>
+        <v>635477</v>
       </c>
       <c r="R177" t="n">
-        <v>7087316</v>
+        <v>7087164</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18526,7 +18516,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -18536,7 +18526,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -18563,10 +18553,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128423173</v>
+        <v>128423134</v>
       </c>
       <c r="B178" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18574,21 +18564,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18598,10 +18588,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>635138</v>
+        <v>635231</v>
       </c>
       <c r="R178" t="n">
-        <v>7087339</v>
+        <v>7087059</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18660,10 +18650,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128423087</v>
+        <v>128407951</v>
       </c>
       <c r="B179" t="n">
-        <v>79152</v>
+        <v>79120</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18671,34 +18661,34 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>634647</v>
+        <v>635217</v>
       </c>
       <c r="R179" t="n">
-        <v>7087542</v>
+        <v>7087316</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18728,9 +18718,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -18745,22 +18745,22 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128428584</v>
+        <v>128428573</v>
       </c>
       <c r="B180" t="n">
-        <v>82979</v>
+        <v>79120</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18768,21 +18768,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18792,10 +18792,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>634824</v>
+        <v>634610</v>
       </c>
       <c r="R180" t="n">
-        <v>7087360</v>
+        <v>7087361</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18854,10 +18854,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128428573</v>
+        <v>128428584</v>
       </c>
       <c r="B181" t="n">
-        <v>79120</v>
+        <v>82979</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18865,21 +18865,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18889,10 +18889,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>634610</v>
+        <v>634824</v>
       </c>
       <c r="R181" t="n">
-        <v>7087361</v>
+        <v>7087360</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19436,45 +19436,49 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128428530</v>
+        <v>128428540</v>
       </c>
       <c r="B187" t="n">
-        <v>91469</v>
+        <v>57876</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>634478</v>
+        <v>634887</v>
       </c>
       <c r="R187" t="n">
-        <v>7087363</v>
+        <v>7087502</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19643,49 +19647,45 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128428540</v>
+        <v>128428530</v>
       </c>
       <c r="B189" t="n">
-        <v>57876</v>
+        <v>91469</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>634887</v>
+        <v>634478</v>
       </c>
       <c r="R189" t="n">
-        <v>7087502</v>
+        <v>7087363</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19938,10 +19938,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128428537</v>
+        <v>128428554</v>
       </c>
       <c r="B192" t="n">
-        <v>57716</v>
+        <v>80226</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19949,42 +19949,34 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>635466</v>
+        <v>635037</v>
       </c>
       <c r="R192" t="n">
-        <v>7087249</v>
+        <v>7087279</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20017,11 +20009,6 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>Ca 3 m upp på liggande granlåga. Runt bohål, omkr 45 mm i diameter.</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20048,10 +20035,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128428568</v>
+        <v>128428571</v>
       </c>
       <c r="B193" t="n">
-        <v>91518</v>
+        <v>79120</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20059,21 +20046,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20083,10 +20070,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>634725</v>
+        <v>635190</v>
       </c>
       <c r="R193" t="n">
-        <v>7087631</v>
+        <v>7087142</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20145,10 +20132,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128428571</v>
+        <v>128428568</v>
       </c>
       <c r="B194" t="n">
-        <v>79120</v>
+        <v>91518</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20156,21 +20143,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20180,10 +20167,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>635190</v>
+        <v>634725</v>
       </c>
       <c r="R194" t="n">
-        <v>7087142</v>
+        <v>7087631</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20242,10 +20229,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128428554</v>
+        <v>128428537</v>
       </c>
       <c r="B195" t="n">
-        <v>80226</v>
+        <v>57716</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20253,34 +20240,42 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>635037</v>
+        <v>635466</v>
       </c>
       <c r="R195" t="n">
-        <v>7087279</v>
+        <v>7087249</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20313,6 +20308,11 @@
       <c r="AA195" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>Ca 3 m upp på liggande granlåga. Runt bohål, omkr 45 mm i diameter.</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20830,10 +20830,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>128428551</v>
+        <v>128428589</v>
       </c>
       <c r="B201" t="n">
-        <v>57713</v>
+        <v>88904</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20841,42 +20841,34 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
-      <c r="K201" t="inlineStr"/>
-      <c r="L201" t="inlineStr"/>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>634768</v>
+        <v>634679</v>
       </c>
       <c r="R201" t="n">
-        <v>7087607</v>
+        <v>7087311</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20935,10 +20927,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>128428589</v>
+        <v>128428551</v>
       </c>
       <c r="B202" t="n">
-        <v>88904</v>
+        <v>57713</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20946,34 +20938,42 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>634679</v>
+        <v>634768</v>
       </c>
       <c r="R202" t="n">
-        <v>7087311</v>
+        <v>7087607</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21032,10 +21032,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>128428596</v>
+        <v>128428590</v>
       </c>
       <c r="B203" t="n">
-        <v>75197</v>
+        <v>88904</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -21043,21 +21043,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>308</v>
+        <v>510</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -21067,10 +21067,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>635551</v>
+        <v>634658</v>
       </c>
       <c r="R203" t="n">
-        <v>7087334</v>
+        <v>7087313</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21129,10 +21129,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>128428590</v>
+        <v>128428596</v>
       </c>
       <c r="B204" t="n">
-        <v>88904</v>
+        <v>75197</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -21140,21 +21140,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>510</v>
+        <v>308</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -21164,10 +21164,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>634658</v>
+        <v>635551</v>
       </c>
       <c r="R204" t="n">
-        <v>7087313</v>
+        <v>7087334</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21226,32 +21226,32 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>128428559</v>
+        <v>128428529</v>
       </c>
       <c r="B205" t="n">
-        <v>80225</v>
+        <v>91469</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -21261,10 +21261,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>635416</v>
+        <v>634593</v>
       </c>
       <c r="R205" t="n">
-        <v>7087178</v>
+        <v>7087306</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21323,32 +21323,32 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>128428529</v>
+        <v>128428581</v>
       </c>
       <c r="B206" t="n">
-        <v>91469</v>
+        <v>82979</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -21358,10 +21358,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>634593</v>
+        <v>635622</v>
       </c>
       <c r="R206" t="n">
-        <v>7087306</v>
+        <v>7087310</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21420,10 +21420,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>128428581</v>
+        <v>128428559</v>
       </c>
       <c r="B207" t="n">
-        <v>82979</v>
+        <v>80225</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21431,21 +21431,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -21455,10 +21455,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>635622</v>
+        <v>635416</v>
       </c>
       <c r="R207" t="n">
-        <v>7087310</v>
+        <v>7087178</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21614,32 +21614,32 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>128428566</v>
+        <v>128428583</v>
       </c>
       <c r="B209" t="n">
-        <v>58086</v>
+        <v>82979</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>103015</v>
+        <v>1312</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -21649,10 +21649,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>634515</v>
+        <v>634880</v>
       </c>
       <c r="R209" t="n">
-        <v>7087381</v>
+        <v>7087375</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21711,32 +21711,32 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128428583</v>
+        <v>128428566</v>
       </c>
       <c r="B210" t="n">
-        <v>82979</v>
+        <v>58086</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>1312</v>
+        <v>103015</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -21746,10 +21746,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>634880</v>
+        <v>634515</v>
       </c>
       <c r="R210" t="n">
-        <v>7087375</v>
+        <v>7087381</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22791,10 +22791,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>128428561</v>
+        <v>128428567</v>
       </c>
       <c r="B221" t="n">
-        <v>80261</v>
+        <v>75188</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -22802,21 +22802,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6464</v>
+        <v>6439</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -22826,10 +22826,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>634879</v>
+        <v>635532</v>
       </c>
       <c r="R221" t="n">
-        <v>7087368</v>
+        <v>7087324</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22888,10 +22888,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>128428565</v>
+        <v>128428561</v>
       </c>
       <c r="B222" t="n">
-        <v>58086</v>
+        <v>80261</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -22899,46 +22899,34 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>103015</v>
+        <v>6464</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K222" t="inlineStr"/>
-      <c r="L222" t="inlineStr"/>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N222" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>635275</v>
+        <v>634879</v>
       </c>
       <c r="R222" t="n">
-        <v>7087098</v>
+        <v>7087368</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -22997,10 +22985,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>128428567</v>
+        <v>128428565</v>
       </c>
       <c r="B223" t="n">
-        <v>75188</v>
+        <v>58086</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -23008,34 +22996,46 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6439</v>
+        <v>103015</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>635532</v>
+        <v>635275</v>
       </c>
       <c r="R223" t="n">
-        <v>7087324</v>
+        <v>7087098</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23288,27 +23288,27 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>128428593</v>
+        <v>128428572</v>
       </c>
       <c r="B226" t="n">
-        <v>80260</v>
+        <v>79120</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -23323,10 +23323,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>635390</v>
+        <v>634969</v>
       </c>
       <c r="R226" t="n">
-        <v>7087179</v>
+        <v>7087325</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23385,10 +23385,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128428544</v>
+        <v>128428593</v>
       </c>
       <c r="B227" t="n">
-        <v>80254</v>
+        <v>80260</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23396,21 +23396,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23420,10 +23420,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>635039</v>
+        <v>635390</v>
       </c>
       <c r="R227" t="n">
-        <v>7087283</v>
+        <v>7087179</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23482,32 +23482,32 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128428572</v>
+        <v>128428544</v>
       </c>
       <c r="B228" t="n">
-        <v>79120</v>
+        <v>80254</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -23517,10 +23517,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>634969</v>
+        <v>635039</v>
       </c>
       <c r="R228" t="n">
-        <v>7087325</v>
+        <v>7087283</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24080,10 +24080,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>128428574</v>
+        <v>128428535</v>
       </c>
       <c r="B234" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -24091,34 +24091,42 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>635129</v>
+        <v>635058</v>
       </c>
       <c r="R234" t="n">
-        <v>7087323</v>
+        <v>7087271</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24151,6 +24159,11 @@
       <c r="AA234" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -24177,7 +24190,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>128428535</v>
+        <v>128428536</v>
       </c>
       <c r="B235" t="n">
         <v>57716</v>
@@ -24220,10 +24233,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>635058</v>
+        <v>634669</v>
       </c>
       <c r="R235" t="n">
-        <v>7087271</v>
+        <v>7087314</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24287,10 +24300,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>128428536</v>
+        <v>128428574</v>
       </c>
       <c r="B236" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24298,42 +24311,34 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
-      <c r="K236" t="inlineStr"/>
-      <c r="L236" t="inlineStr"/>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>634669</v>
+        <v>635129</v>
       </c>
       <c r="R236" t="n">
-        <v>7087314</v>
+        <v>7087323</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24366,11 +24371,6 @@
       <c r="AA236" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC236" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -24400,7 +24400,7 @@
         <v>128651017</v>
       </c>
       <c r="B237" t="n">
-        <v>96973</v>
+        <v>96977</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>128651018</v>
       </c>
       <c r="B238" t="n">
-        <v>95870</v>
+        <v>95874</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24591,10 +24591,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>128423582</v>
+        <v>128423605</v>
       </c>
       <c r="B239" t="n">
-        <v>91786</v>
+        <v>80229</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -24602,21 +24602,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>73</v>
+        <v>6458</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -24626,10 +24626,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>635466</v>
+        <v>635331</v>
       </c>
       <c r="R239" t="n">
-        <v>7087277</v>
+        <v>7087194</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24688,10 +24688,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>128423605</v>
+        <v>128423608</v>
       </c>
       <c r="B240" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -24723,10 +24723,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>635331</v>
+        <v>635603</v>
       </c>
       <c r="R240" t="n">
-        <v>7087194</v>
+        <v>7087226</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24785,10 +24785,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>128423608</v>
+        <v>128423582</v>
       </c>
       <c r="B241" t="n">
-        <v>80225</v>
+        <v>91790</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24796,21 +24796,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6458</v>
+        <v>73</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -24820,10 +24820,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>635603</v>
+        <v>635466</v>
       </c>
       <c r="R241" t="n">
-        <v>7087226</v>
+        <v>7087277</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -24882,32 +24882,32 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>128423573</v>
+        <v>128423623</v>
       </c>
       <c r="B242" t="n">
-        <v>91469</v>
+        <v>88908</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -24917,10 +24917,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>634599</v>
+        <v>634583</v>
       </c>
       <c r="R242" t="n">
-        <v>7087225</v>
+        <v>7087261</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24979,32 +24979,32 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>128423623</v>
+        <v>128423573</v>
       </c>
       <c r="B243" t="n">
-        <v>88904</v>
+        <v>91473</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -25014,10 +25014,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>634583</v>
+        <v>634599</v>
       </c>
       <c r="R243" t="n">
-        <v>7087261</v>
+        <v>7087225</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25076,27 +25076,27 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>128423597</v>
+        <v>128423612</v>
       </c>
       <c r="B244" t="n">
-        <v>57713</v>
+        <v>58090</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -25176,7 +25176,7 @@
         <v>128423621</v>
       </c>
       <c r="B245" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -25270,27 +25270,27 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>128423612</v>
+        <v>128423597</v>
       </c>
       <c r="B246" t="n">
-        <v>58086</v>
+        <v>57717</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -25370,7 +25370,7 @@
         <v>128423591</v>
       </c>
       <c r="B247" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -25467,7 +25467,7 @@
         <v>128423618</v>
       </c>
       <c r="B248" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>128423575</v>
       </c>
       <c r="B249" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>128423606</v>
       </c>
       <c r="B250" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -25755,32 +25755,32 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>128423624</v>
+        <v>128423628</v>
       </c>
       <c r="B251" t="n">
-        <v>88904</v>
+        <v>80264</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>510</v>
+        <v>6463</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -25790,10 +25790,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>634461</v>
+        <v>635451</v>
       </c>
       <c r="R251" t="n">
-        <v>7087363</v>
+        <v>7087225</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -25852,32 +25852,32 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>128423628</v>
+        <v>128423624</v>
       </c>
       <c r="B252" t="n">
-        <v>80260</v>
+        <v>88908</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>6463</v>
+        <v>510</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -25887,10 +25887,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>635451</v>
+        <v>634461</v>
       </c>
       <c r="R252" t="n">
-        <v>7087225</v>
+        <v>7087363</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -25952,7 +25952,7 @@
         <v>128423615</v>
       </c>
       <c r="B253" t="n">
-        <v>91518</v>
+        <v>91522</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -26049,7 +26049,7 @@
         <v>128423617</v>
       </c>
       <c r="B254" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -26143,32 +26143,32 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>128423593</v>
+        <v>128423625</v>
       </c>
       <c r="B255" t="n">
-        <v>80254</v>
+        <v>88908</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>6462</v>
+        <v>510</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -26178,10 +26178,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>635471</v>
+        <v>634494</v>
       </c>
       <c r="R255" t="n">
-        <v>7087281</v>
+        <v>7087408</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26243,7 +26243,7 @@
         <v>128423622</v>
       </c>
       <c r="B256" t="n">
-        <v>88904</v>
+        <v>88908</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -26337,32 +26337,32 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128423625</v>
+        <v>128423593</v>
       </c>
       <c r="B257" t="n">
-        <v>88904</v>
+        <v>80258</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>510</v>
+        <v>6462</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -26372,10 +26372,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>634494</v>
+        <v>635471</v>
       </c>
       <c r="R257" t="n">
-        <v>7087408</v>
+        <v>7087281</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -26437,7 +26437,7 @@
         <v>128423629</v>
       </c>
       <c r="B258" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>128423626</v>
       </c>
       <c r="B259" t="n">
-        <v>88904</v>
+        <v>88908</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -26628,10 +26628,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>128423585</v>
+        <v>128423577</v>
       </c>
       <c r="B260" t="n">
-        <v>92201</v>
+        <v>91473</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -26639,21 +26639,21 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -26663,10 +26663,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>634942</v>
+        <v>635153</v>
       </c>
       <c r="R260" t="n">
-        <v>7087590</v>
+        <v>7087180</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -26725,32 +26725,32 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128423577</v>
+        <v>128423616</v>
       </c>
       <c r="B261" t="n">
-        <v>91469</v>
+        <v>91526</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -26760,10 +26760,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>635153</v>
+        <v>634993</v>
       </c>
       <c r="R261" t="n">
-        <v>7087180</v>
+        <v>7087294</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26822,10 +26822,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128423616</v>
+        <v>128423619</v>
       </c>
       <c r="B262" t="n">
-        <v>91522</v>
+        <v>79124</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -26833,21 +26833,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -26857,10 +26857,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>634993</v>
+        <v>635513</v>
       </c>
       <c r="R262" t="n">
-        <v>7087294</v>
+        <v>7087316</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -26895,12 +26895,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC262" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD262" t="b">
         <v>0</v>
       </c>
       <c r="AE262" t="b">
         <v>0</v>
       </c>
+      <c r="AF262" t="inlineStr"/>
       <c r="AG262" t="b">
         <v>0</v>
       </c>
@@ -26919,49 +26925,45 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>128492197</v>
+        <v>128423620</v>
       </c>
       <c r="B263" t="n">
-        <v>95858</v>
+        <v>79124</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
-      <c r="J263" t="inlineStr"/>
-      <c r="K263" t="inlineStr"/>
-      <c r="L263" t="inlineStr"/>
-      <c r="N263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>635110</v>
+        <v>634756</v>
       </c>
       <c r="R263" t="n">
-        <v>7087251</v>
+        <v>7087642</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27002,7 +27004,6 @@
       <c r="AE263" t="b">
         <v>0</v>
       </c>
-      <c r="AF263" t="inlineStr"/>
       <c r="AG263" t="b">
         <v>0</v>
       </c>
@@ -27021,32 +27022,32 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>128423619</v>
+        <v>128423594</v>
       </c>
       <c r="B264" t="n">
-        <v>79120</v>
+        <v>80258</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -27056,10 +27057,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>635513</v>
+        <v>634527</v>
       </c>
       <c r="R264" t="n">
-        <v>7087316</v>
+        <v>7087301</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27094,18 +27095,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC264" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD264" t="b">
         <v>0</v>
       </c>
       <c r="AE264" t="b">
         <v>0</v>
       </c>
-      <c r="AF264" t="inlineStr"/>
       <c r="AG264" t="b">
         <v>0</v>
       </c>
@@ -27124,10 +27119,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>128423594</v>
+        <v>128492197</v>
       </c>
       <c r="B265" t="n">
-        <v>80254</v>
+        <v>95862</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -27135,34 +27130,38 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>6462</v>
+        <v>2809</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
+      <c r="J265" t="inlineStr"/>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
+      <c r="N265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>634527</v>
+        <v>635110</v>
       </c>
       <c r="R265" t="n">
-        <v>7087301</v>
+        <v>7087251</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27203,6 +27202,7 @@
       <c r="AE265" t="b">
         <v>0</v>
       </c>
+      <c r="AF265" t="inlineStr"/>
       <c r="AG265" t="b">
         <v>0</v>
       </c>
@@ -27221,32 +27221,32 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>128423620</v>
+        <v>128423585</v>
       </c>
       <c r="B266" t="n">
-        <v>79120</v>
+        <v>92205</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
@@ -27256,10 +27256,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>634756</v>
+        <v>634942</v>
       </c>
       <c r="R266" t="n">
-        <v>7087642</v>
+        <v>7087590</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -27318,32 +27318,32 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>128423607</v>
+        <v>128423578</v>
       </c>
       <c r="B267" t="n">
-        <v>80225</v>
+        <v>91473</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -27353,10 +27353,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>635459</v>
+        <v>635327</v>
       </c>
       <c r="R267" t="n">
-        <v>7087231</v>
+        <v>7087158</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -27415,10 +27415,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>128423602</v>
+        <v>128423607</v>
       </c>
       <c r="B268" t="n">
-        <v>57716</v>
+        <v>80229</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -27426,21 +27426,21 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -27450,10 +27450,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>635210</v>
+        <v>635459</v>
       </c>
       <c r="R268" t="n">
-        <v>7087158</v>
+        <v>7087231</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -27486,11 +27486,6 @@
       <c r="AA268" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC268" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -27517,32 +27512,32 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>128423578</v>
+        <v>128423602</v>
       </c>
       <c r="B269" t="n">
-        <v>91469</v>
+        <v>57720</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -27552,7 +27547,7 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>635327</v>
+        <v>635210</v>
       </c>
       <c r="R269" t="n">
         <v>7087158</v>
@@ -27588,6 +27583,11 @@
       <c r="AA269" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -27617,7 +27617,7 @@
         <v>128423572</v>
       </c>
       <c r="B270" t="n">
-        <v>96878</v>
+        <v>96882</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -27711,32 +27711,32 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>128423614</v>
+        <v>128423576</v>
       </c>
       <c r="B271" t="n">
-        <v>91518</v>
+        <v>91473</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
@@ -27746,10 +27746,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>634673</v>
+        <v>634705</v>
       </c>
       <c r="R271" t="n">
-        <v>7087631</v>
+        <v>7087668</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -27808,32 +27808,32 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>128423576</v>
+        <v>128423614</v>
       </c>
       <c r="B272" t="n">
-        <v>91469</v>
+        <v>91522</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
@@ -27843,10 +27843,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>634705</v>
+        <v>634673</v>
       </c>
       <c r="R272" t="n">
-        <v>7087668</v>
+        <v>7087631</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -27908,7 +27908,7 @@
         <v>128423603</v>
       </c>
       <c r="B273" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -28011,32 +28011,32 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>128423592</v>
+        <v>128423598</v>
       </c>
       <c r="B274" t="n">
-        <v>80254</v>
+        <v>80230</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -28046,10 +28046,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>635454</v>
+        <v>635632</v>
       </c>
       <c r="R274" t="n">
-        <v>7087257</v>
+        <v>7087270</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28108,32 +28108,32 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>128423598</v>
+        <v>128423599</v>
       </c>
       <c r="B275" t="n">
-        <v>80226</v>
+        <v>91962</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>2081</v>
+        <v>1209</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -28143,10 +28143,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>635632</v>
+        <v>635464</v>
       </c>
       <c r="R275" t="n">
-        <v>7087270</v>
+        <v>7087275</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -28205,32 +28205,32 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>128423599</v>
+        <v>128423592</v>
       </c>
       <c r="B276" t="n">
-        <v>91958</v>
+        <v>80258</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>1209</v>
+        <v>6462</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -28240,10 +28240,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>635464</v>
+        <v>635454</v>
       </c>
       <c r="R276" t="n">
-        <v>7087275</v>
+        <v>7087257</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -28305,7 +28305,7 @@
         <v>128423604</v>
       </c>
       <c r="B277" t="n">
-        <v>95858</v>
+        <v>95862</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -28399,10 +28399,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>128423596</v>
+        <v>128423590</v>
       </c>
       <c r="B278" t="n">
-        <v>57713</v>
+        <v>92790</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -28410,21 +28410,21 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>100049</v>
+        <v>4361</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
@@ -28434,10 +28434,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>634648</v>
+        <v>635182</v>
       </c>
       <c r="R278" t="n">
-        <v>7087590</v>
+        <v>7087227</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -28496,10 +28496,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>128423588</v>
+        <v>128423596</v>
       </c>
       <c r="B279" t="n">
-        <v>57876</v>
+        <v>57717</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -28507,21 +28507,21 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
@@ -28531,10 +28531,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>634560</v>
+        <v>634648</v>
       </c>
       <c r="R279" t="n">
-        <v>7087311</v>
+        <v>7087590</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -28593,10 +28593,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>128423590</v>
+        <v>128423588</v>
       </c>
       <c r="B280" t="n">
-        <v>92786</v>
+        <v>57880</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -28604,21 +28604,21 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>4361</v>
+        <v>103021</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -28628,10 +28628,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>635182</v>
+        <v>634560</v>
       </c>
       <c r="R280" t="n">
-        <v>7087227</v>
+        <v>7087311</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -28693,7 +28693,7 @@
         <v>128423580</v>
       </c>
       <c r="B281" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>128423579</v>
       </c>
       <c r="B282" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>128423595</v>
       </c>
       <c r="B283" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -28984,7 +28984,7 @@
         <v>128423574</v>
       </c>
       <c r="B284" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>128423601</v>
       </c>
       <c r="B285" t="n">
-        <v>91800</v>
+        <v>91804</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>128423613</v>
       </c>
       <c r="B286" t="n">
-        <v>91518</v>
+        <v>91522</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>

--- a/artfynd/A 30047-2025 artfynd.xlsx
+++ b/artfynd/A 30047-2025 artfynd.xlsx
@@ -8382,32 +8382,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128423097</v>
+        <v>128423099</v>
       </c>
       <c r="B77" t="n">
-        <v>91508</v>
+        <v>92205</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8417,10 +8417,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>635320</v>
+        <v>634570</v>
       </c>
       <c r="R77" t="n">
-        <v>7087069</v>
+        <v>7087303</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8479,32 +8479,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128423099</v>
+        <v>128423155</v>
       </c>
       <c r="B78" t="n">
-        <v>92205</v>
+        <v>79124</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8514,10 +8514,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>634570</v>
+        <v>635294</v>
       </c>
       <c r="R78" t="n">
-        <v>7087303</v>
+        <v>7087064</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8576,32 +8576,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128423155</v>
+        <v>128423092</v>
       </c>
       <c r="B79" t="n">
-        <v>79124</v>
+        <v>91473</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8611,10 +8611,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>635294</v>
+        <v>634661</v>
       </c>
       <c r="R79" t="n">
-        <v>7087064</v>
+        <v>7087688</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8673,32 +8673,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128423092</v>
+        <v>128423189</v>
       </c>
       <c r="B80" t="n">
-        <v>91473</v>
+        <v>79124</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8708,10 +8708,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>634661</v>
+        <v>635678</v>
       </c>
       <c r="R80" t="n">
-        <v>7087688</v>
+        <v>7087274</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8770,10 +8770,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128423189</v>
+        <v>128404903</v>
       </c>
       <c r="B81" t="n">
-        <v>79124</v>
+        <v>91526</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8781,34 +8781,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>635678</v>
+        <v>635552</v>
       </c>
       <c r="R81" t="n">
-        <v>7087274</v>
+        <v>7087334</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8838,9 +8838,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8855,57 +8865,57 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128404903</v>
+        <v>128409643</v>
       </c>
       <c r="B82" t="n">
-        <v>91526</v>
+        <v>80258</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>635552</v>
+        <v>634947</v>
       </c>
       <c r="R82" t="n">
-        <v>7087334</v>
+        <v>7087432</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8937,7 +8947,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -8947,7 +8957,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8974,10 +8984,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128409643</v>
+        <v>128423127</v>
       </c>
       <c r="B83" t="n">
-        <v>80258</v>
+        <v>79148</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8985,34 +8995,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6462</v>
+        <v>6434</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>634947</v>
+        <v>635508</v>
       </c>
       <c r="R83" t="n">
-        <v>7087432</v>
+        <v>7087301</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9042,19 +9052,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>13:43</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9069,44 +9069,44 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128423127</v>
+        <v>128423175</v>
       </c>
       <c r="B84" t="n">
-        <v>79148</v>
+        <v>79124</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9116,10 +9116,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>635508</v>
+        <v>635169</v>
       </c>
       <c r="R84" t="n">
-        <v>7087301</v>
+        <v>7087269</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9178,10 +9178,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128423175</v>
+        <v>128423097</v>
       </c>
       <c r="B85" t="n">
-        <v>79124</v>
+        <v>91508</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9189,21 +9189,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9213,10 +9213,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>635169</v>
+        <v>635320</v>
       </c>
       <c r="R85" t="n">
-        <v>7087269</v>
+        <v>7087069</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11698,10 +11698,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128413141</v>
+        <v>128423096</v>
       </c>
       <c r="B110" t="n">
-        <v>57720</v>
+        <v>91508</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11709,42 +11709,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>634574</v>
+        <v>635249</v>
       </c>
       <c r="R110" t="n">
-        <v>7087273</v>
+        <v>7087032</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11774,24 +11766,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11806,22 +11783,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128423177</v>
+        <v>128423098</v>
       </c>
       <c r="B111" t="n">
-        <v>79124</v>
+        <v>91508</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11829,21 +11806,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11853,10 +11830,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>635285</v>
+        <v>635186</v>
       </c>
       <c r="R111" t="n">
-        <v>7087169</v>
+        <v>7087317</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11915,7 +11892,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128423187</v>
+        <v>128423167</v>
       </c>
       <c r="B112" t="n">
         <v>79124</v>
@@ -11950,10 +11927,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>635591</v>
+        <v>634719</v>
       </c>
       <c r="R112" t="n">
-        <v>7087249</v>
+        <v>7087623</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12012,32 +11989,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128423096</v>
+        <v>128423128</v>
       </c>
       <c r="B113" t="n">
-        <v>91508</v>
+        <v>80257</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12047,10 +12024,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>635249</v>
+        <v>634915</v>
       </c>
       <c r="R113" t="n">
-        <v>7087032</v>
+        <v>7087322</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12109,10 +12086,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128423098</v>
+        <v>128423157</v>
       </c>
       <c r="B114" t="n">
-        <v>91508</v>
+        <v>79124</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12120,21 +12097,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12144,10 +12121,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>635186</v>
+        <v>635204</v>
       </c>
       <c r="R114" t="n">
-        <v>7087317</v>
+        <v>7087134</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12206,32 +12183,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128423167</v>
+        <v>128423139</v>
       </c>
       <c r="B115" t="n">
-        <v>79124</v>
+        <v>80265</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12241,10 +12218,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>634719</v>
+        <v>635237</v>
       </c>
       <c r="R115" t="n">
-        <v>7087623</v>
+        <v>7087043</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12303,10 +12280,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128423128</v>
+        <v>128423194</v>
       </c>
       <c r="B116" t="n">
-        <v>80257</v>
+        <v>80264</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12314,21 +12291,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6461</v>
+        <v>6463</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12338,10 +12315,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>634915</v>
+        <v>635234</v>
       </c>
       <c r="R116" t="n">
-        <v>7087322</v>
+        <v>7087032</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12400,7 +12377,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128423157</v>
+        <v>128404427</v>
       </c>
       <c r="B117" t="n">
         <v>79124</v>
@@ -12429,16 +12406,21 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>635204</v>
+        <v>635552</v>
       </c>
       <c r="R117" t="n">
-        <v>7087134</v>
+        <v>7087334</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12468,9 +12450,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12485,57 +12477,65 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128423139</v>
+        <v>128413141</v>
       </c>
       <c r="B118" t="n">
-        <v>80265</v>
+        <v>57720</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>635237</v>
+        <v>634574</v>
       </c>
       <c r="R118" t="n">
-        <v>7087043</v>
+        <v>7087273</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12565,9 +12565,24 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12582,39 +12597,39 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128423194</v>
+        <v>128423177</v>
       </c>
       <c r="B119" t="n">
-        <v>80264</v>
+        <v>79124</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -12629,10 +12644,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>635234</v>
+        <v>635285</v>
       </c>
       <c r="R119" t="n">
-        <v>7087032</v>
+        <v>7087169</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12691,7 +12706,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128404427</v>
+        <v>128423187</v>
       </c>
       <c r="B120" t="n">
         <v>79124</v>
@@ -12720,21 +12735,16 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>635552</v>
+        <v>635591</v>
       </c>
       <c r="R120" t="n">
-        <v>7087334</v>
+        <v>7087249</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12764,19 +12774,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>10:33</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12791,12 +12791,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -15661,10 +15661,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128423137</v>
+        <v>128423088</v>
       </c>
       <c r="B149" t="n">
-        <v>80229</v>
+        <v>96882</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15672,21 +15672,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15696,10 +15696,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>635683</v>
+        <v>634571</v>
       </c>
       <c r="R149" t="n">
-        <v>7087267</v>
+        <v>7087288</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15758,32 +15758,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128423129</v>
+        <v>128423190</v>
       </c>
       <c r="B150" t="n">
-        <v>80257</v>
+        <v>88908</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6461</v>
+        <v>510</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15793,10 +15793,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>635614</v>
+        <v>634804</v>
       </c>
       <c r="R150" t="n">
-        <v>7087262</v>
+        <v>7087321</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15855,10 +15855,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128423088</v>
+        <v>128423198</v>
       </c>
       <c r="B151" t="n">
-        <v>96882</v>
+        <v>57720</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15866,21 +15866,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15890,10 +15890,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>634571</v>
+        <v>635595</v>
       </c>
       <c r="R151" t="n">
-        <v>7087288</v>
+        <v>7087277</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15926,6 +15926,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15952,10 +15957,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128423190</v>
+        <v>128423186</v>
       </c>
       <c r="B152" t="n">
-        <v>88908</v>
+        <v>79124</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15963,21 +15968,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15987,10 +15992,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>634804</v>
+        <v>635555</v>
       </c>
       <c r="R152" t="n">
-        <v>7087321</v>
+        <v>7087248</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16049,10 +16054,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128423198</v>
+        <v>128423137</v>
       </c>
       <c r="B153" t="n">
-        <v>57720</v>
+        <v>80229</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16060,21 +16065,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16084,10 +16089,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>635595</v>
+        <v>635683</v>
       </c>
       <c r="R153" t="n">
-        <v>7087277</v>
+        <v>7087267</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16120,11 +16125,6 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16151,32 +16151,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128423186</v>
+        <v>128423129</v>
       </c>
       <c r="B154" t="n">
-        <v>79124</v>
+        <v>80257</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16186,10 +16186,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>635555</v>
+        <v>635614</v>
       </c>
       <c r="R154" t="n">
-        <v>7087248</v>
+        <v>7087262</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16248,32 +16248,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128423138</v>
+        <v>128423118</v>
       </c>
       <c r="B155" t="n">
-        <v>80265</v>
+        <v>57720</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16283,10 +16283,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>635160</v>
+        <v>634924</v>
       </c>
       <c r="R155" t="n">
-        <v>7087012</v>
+        <v>7087288</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16321,6 +16321,11 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD155" t="b">
         <v>0</v>
       </c>
@@ -16329,6 +16334,21 @@
       </c>
       <c r="AG155" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
@@ -16345,7 +16365,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128423168</v>
+        <v>128423172</v>
       </c>
       <c r="B156" t="n">
         <v>79124</v>
@@ -16380,10 +16400,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>634865</v>
+        <v>635010</v>
       </c>
       <c r="R156" t="n">
-        <v>7087586</v>
+        <v>7087362</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16442,10 +16462,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128423109</v>
+        <v>128423138</v>
       </c>
       <c r="B157" t="n">
-        <v>80258</v>
+        <v>80265</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16453,21 +16473,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16477,10 +16497,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>635407</v>
+        <v>635160</v>
       </c>
       <c r="R157" t="n">
-        <v>7087128</v>
+        <v>7087012</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16539,7 +16559,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128423160</v>
+        <v>128423168</v>
       </c>
       <c r="B158" t="n">
         <v>79124</v>
@@ -16574,10 +16594,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>634916</v>
+        <v>634865</v>
       </c>
       <c r="R158" t="n">
-        <v>7087311</v>
+        <v>7087586</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16636,32 +16656,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128423135</v>
+        <v>128423109</v>
       </c>
       <c r="B159" t="n">
-        <v>80229</v>
+        <v>80258</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16671,10 +16691,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>635412</v>
+        <v>635407</v>
       </c>
       <c r="R159" t="n">
-        <v>7087118</v>
+        <v>7087128</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16733,10 +16753,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128423118</v>
+        <v>128423160</v>
       </c>
       <c r="B160" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16744,21 +16764,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16768,10 +16788,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>634924</v>
+        <v>634916</v>
       </c>
       <c r="R160" t="n">
-        <v>7087288</v>
+        <v>7087311</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16806,11 +16826,6 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
@@ -16819,21 +16834,6 @@
       </c>
       <c r="AG160" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ160" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK160" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO160" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
@@ -16850,10 +16850,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128423172</v>
+        <v>128423135</v>
       </c>
       <c r="B161" t="n">
-        <v>79124</v>
+        <v>80229</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16861,21 +16861,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16885,10 +16885,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>635010</v>
+        <v>635412</v>
       </c>
       <c r="R161" t="n">
-        <v>7087362</v>
+        <v>7087118</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17447,10 +17447,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128423199</v>
+        <v>128423171</v>
       </c>
       <c r="B167" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17458,38 +17458,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>635298</v>
+        <v>634973</v>
       </c>
       <c r="R167" t="n">
-        <v>7087096</v>
+        <v>7087410</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17522,11 +17518,6 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17553,10 +17544,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128423121</v>
+        <v>128423170</v>
       </c>
       <c r="B168" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17564,21 +17555,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17588,10 +17579,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>635167</v>
+        <v>634897</v>
       </c>
       <c r="R168" t="n">
-        <v>7087269</v>
+        <v>7087496</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17624,11 +17615,6 @@
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17655,10 +17641,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128423188</v>
+        <v>128423199</v>
       </c>
       <c r="B169" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17666,34 +17652,38 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>635610</v>
+        <v>635298</v>
       </c>
       <c r="R169" t="n">
-        <v>7087261</v>
+        <v>7087096</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17726,6 +17716,11 @@
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17752,10 +17747,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128423171</v>
+        <v>128423121</v>
       </c>
       <c r="B170" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17763,21 +17758,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17787,10 +17782,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>634973</v>
+        <v>635167</v>
       </c>
       <c r="R170" t="n">
-        <v>7087410</v>
+        <v>7087269</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17823,6 +17818,11 @@
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -17849,7 +17849,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128423170</v>
+        <v>128423188</v>
       </c>
       <c r="B171" t="n">
         <v>79124</v>
@@ -17884,10 +17884,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>634897</v>
+        <v>635610</v>
       </c>
       <c r="R171" t="n">
-        <v>7087496</v>
+        <v>7087261</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19145,32 +19145,32 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128428547</v>
+        <v>128428595</v>
       </c>
       <c r="B184" t="n">
-        <v>80258</v>
+        <v>75201</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6462</v>
+        <v>308</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19180,10 +19180,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>635305</v>
+        <v>634678</v>
       </c>
       <c r="R184" t="n">
-        <v>7087219</v>
+        <v>7087320</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19242,32 +19242,32 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128428595</v>
+        <v>128428563</v>
       </c>
       <c r="B185" t="n">
-        <v>75201</v>
+        <v>57824</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>308</v>
+        <v>103031</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19277,10 +19277,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>634678</v>
+        <v>635011</v>
       </c>
       <c r="R185" t="n">
-        <v>7087320</v>
+        <v>7087362</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19339,10 +19339,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128428563</v>
+        <v>128428547</v>
       </c>
       <c r="B186" t="n">
-        <v>57824</v>
+        <v>80258</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19350,21 +19350,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>103031</v>
+        <v>6462</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19374,10 +19374,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>635011</v>
+        <v>635305</v>
       </c>
       <c r="R186" t="n">
-        <v>7087362</v>
+        <v>7087219</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21032,10 +21032,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>128428596</v>
+        <v>128428559</v>
       </c>
       <c r="B203" t="n">
-        <v>75201</v>
+        <v>80229</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -21043,21 +21043,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -21067,10 +21067,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>635551</v>
+        <v>635416</v>
       </c>
       <c r="R203" t="n">
-        <v>7087334</v>
+        <v>7087178</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21129,10 +21129,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>128428590</v>
+        <v>128428596</v>
       </c>
       <c r="B204" t="n">
-        <v>88908</v>
+        <v>75201</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -21140,21 +21140,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>510</v>
+        <v>308</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -21164,10 +21164,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>634658</v>
+        <v>635551</v>
       </c>
       <c r="R204" t="n">
-        <v>7087313</v>
+        <v>7087334</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21226,10 +21226,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>128428581</v>
+        <v>128428590</v>
       </c>
       <c r="B205" t="n">
-        <v>82983</v>
+        <v>88908</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -21237,21 +21237,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -21261,10 +21261,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>635622</v>
+        <v>634658</v>
       </c>
       <c r="R205" t="n">
-        <v>7087310</v>
+        <v>7087313</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21323,10 +21323,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>128428559</v>
+        <v>128428581</v>
       </c>
       <c r="B206" t="n">
-        <v>80229</v>
+        <v>82983</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21334,21 +21334,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -21358,10 +21358,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>635416</v>
+        <v>635622</v>
       </c>
       <c r="R206" t="n">
-        <v>7087178</v>
+        <v>7087310</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21517,10 +21517,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>128428569</v>
+        <v>128428583</v>
       </c>
       <c r="B208" t="n">
-        <v>91526</v>
+        <v>82983</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -21528,21 +21528,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -21552,10 +21552,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>635359</v>
+        <v>634880</v>
       </c>
       <c r="R208" t="n">
-        <v>7087150</v>
+        <v>7087375</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21614,32 +21614,32 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>128428583</v>
+        <v>128428566</v>
       </c>
       <c r="B209" t="n">
-        <v>82983</v>
+        <v>58090</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>1312</v>
+        <v>103015</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -21649,10 +21649,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>634880</v>
+        <v>634515</v>
       </c>
       <c r="R209" t="n">
-        <v>7087375</v>
+        <v>7087381</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21711,32 +21711,32 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128428566</v>
+        <v>128428569</v>
       </c>
       <c r="B210" t="n">
-        <v>58090</v>
+        <v>91526</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -21746,10 +21746,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>634515</v>
+        <v>635359</v>
       </c>
       <c r="R210" t="n">
-        <v>7087381</v>
+        <v>7087150</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23579,45 +23579,53 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>128428562</v>
+        <v>128428550</v>
       </c>
       <c r="B229" t="n">
-        <v>80265</v>
+        <v>57717</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>635398</v>
+        <v>634487</v>
       </c>
       <c r="R229" t="n">
-        <v>7087183</v>
+        <v>7087401</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23676,7 +23684,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>128428550</v>
+        <v>128428552</v>
       </c>
       <c r="B230" t="n">
         <v>57717</v>
@@ -23719,10 +23727,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>634487</v>
+        <v>635170</v>
       </c>
       <c r="R230" t="n">
-        <v>7087401</v>
+        <v>7087231</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -23781,53 +23789,45 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>128428552</v>
+        <v>128428562</v>
       </c>
       <c r="B231" t="n">
-        <v>57717</v>
+        <v>80265</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
-      <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr"/>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>635170</v>
+        <v>635398</v>
       </c>
       <c r="R231" t="n">
-        <v>7087231</v>
+        <v>7087183</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24882,32 +24882,32 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>128423573</v>
+        <v>128423623</v>
       </c>
       <c r="B242" t="n">
-        <v>91473</v>
+        <v>88908</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -24917,10 +24917,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>634599</v>
+        <v>634583</v>
       </c>
       <c r="R242" t="n">
-        <v>7087225</v>
+        <v>7087261</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24979,32 +24979,32 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>128423623</v>
+        <v>128423573</v>
       </c>
       <c r="B243" t="n">
-        <v>88908</v>
+        <v>91473</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -25014,10 +25014,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>634583</v>
+        <v>634599</v>
       </c>
       <c r="R243" t="n">
-        <v>7087261</v>
+        <v>7087225</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25076,32 +25076,32 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>128423612</v>
+        <v>128423621</v>
       </c>
       <c r="B244" t="n">
-        <v>58090</v>
+        <v>82983</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>103015</v>
+        <v>1312</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -25111,10 +25111,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>634913</v>
+        <v>634525</v>
       </c>
       <c r="R244" t="n">
-        <v>7087585</v>
+        <v>7087295</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25173,32 +25173,32 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>128423597</v>
+        <v>128423591</v>
       </c>
       <c r="B245" t="n">
-        <v>57717</v>
+        <v>80258</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -25208,10 +25208,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>634913</v>
+        <v>635451</v>
       </c>
       <c r="R245" t="n">
-        <v>7087585</v>
+        <v>7087225</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25270,10 +25270,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>128423621</v>
+        <v>128423597</v>
       </c>
       <c r="B246" t="n">
-        <v>82983</v>
+        <v>57717</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -25281,21 +25281,21 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -25305,10 +25305,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>634525</v>
+        <v>634913</v>
       </c>
       <c r="R246" t="n">
-        <v>7087295</v>
+        <v>7087585</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25367,10 +25367,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>128423591</v>
+        <v>128423612</v>
       </c>
       <c r="B247" t="n">
-        <v>80258</v>
+        <v>58090</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -25378,21 +25378,21 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6462</v>
+        <v>103015</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -25402,10 +25402,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>635451</v>
+        <v>634913</v>
       </c>
       <c r="R247" t="n">
-        <v>7087225</v>
+        <v>7087585</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25464,32 +25464,32 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>128423575</v>
+        <v>128423618</v>
       </c>
       <c r="B248" t="n">
-        <v>91473</v>
+        <v>91526</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -25499,10 +25499,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>634574</v>
+        <v>634676</v>
       </c>
       <c r="R248" t="n">
-        <v>7087286</v>
+        <v>7087616</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25561,32 +25561,32 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>128423618</v>
+        <v>128423575</v>
       </c>
       <c r="B249" t="n">
-        <v>91526</v>
+        <v>91473</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -25596,10 +25596,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>634676</v>
+        <v>634574</v>
       </c>
       <c r="R249" t="n">
-        <v>7087616</v>
+        <v>7087286</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -26046,10 +26046,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128423617</v>
+        <v>128423622</v>
       </c>
       <c r="B254" t="n">
-        <v>91526</v>
+        <v>88908</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -26057,21 +26057,21 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -26081,10 +26081,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>634507</v>
+        <v>634642</v>
       </c>
       <c r="R254" t="n">
-        <v>7087328</v>
+        <v>7087251</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26143,7 +26143,7 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>128423622</v>
+        <v>128423625</v>
       </c>
       <c r="B255" t="n">
         <v>88908</v>
@@ -26178,10 +26178,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>634642</v>
+        <v>634494</v>
       </c>
       <c r="R255" t="n">
-        <v>7087251</v>
+        <v>7087408</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26240,10 +26240,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>128423625</v>
+        <v>128423617</v>
       </c>
       <c r="B256" t="n">
-        <v>88908</v>
+        <v>91526</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -26251,21 +26251,21 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -26275,10 +26275,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>634494</v>
+        <v>634507</v>
       </c>
       <c r="R256" t="n">
-        <v>7087408</v>
+        <v>7087328</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26628,10 +26628,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>128423585</v>
+        <v>128423577</v>
       </c>
       <c r="B260" t="n">
-        <v>92205</v>
+        <v>91473</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -26639,21 +26639,21 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -26663,10 +26663,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>634942</v>
+        <v>635153</v>
       </c>
       <c r="R260" t="n">
-        <v>7087590</v>
+        <v>7087180</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -26725,10 +26725,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128423620</v>
+        <v>128423616</v>
       </c>
       <c r="B261" t="n">
-        <v>79124</v>
+        <v>91526</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -26736,21 +26736,21 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -26760,10 +26760,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>634756</v>
+        <v>634993</v>
       </c>
       <c r="R261" t="n">
-        <v>7087642</v>
+        <v>7087294</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26925,32 +26925,32 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>128423577</v>
+        <v>128423620</v>
       </c>
       <c r="B263" t="n">
-        <v>91473</v>
+        <v>79124</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -26960,10 +26960,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>635153</v>
+        <v>634756</v>
       </c>
       <c r="R263" t="n">
-        <v>7087180</v>
+        <v>7087642</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27022,32 +27022,32 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>128423616</v>
+        <v>128423594</v>
       </c>
       <c r="B264" t="n">
-        <v>91526</v>
+        <v>80258</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -27057,10 +27057,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>634993</v>
+        <v>634527</v>
       </c>
       <c r="R264" t="n">
-        <v>7087294</v>
+        <v>7087301</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27119,10 +27119,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>128492197</v>
+        <v>128423585</v>
       </c>
       <c r="B265" t="n">
-        <v>95862</v>
+        <v>92205</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -27130,38 +27130,34 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>2809</v>
+        <v>3298</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
-      <c r="J265" t="inlineStr"/>
-      <c r="K265" t="inlineStr"/>
-      <c r="L265" t="inlineStr"/>
-      <c r="N265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>635110</v>
+        <v>634942</v>
       </c>
       <c r="R265" t="n">
-        <v>7087251</v>
+        <v>7087590</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27202,7 +27198,6 @@
       <c r="AE265" t="b">
         <v>0</v>
       </c>
-      <c r="AF265" t="inlineStr"/>
       <c r="AG265" t="b">
         <v>0</v>
       </c>
@@ -27221,10 +27216,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>128423594</v>
+        <v>128492197</v>
       </c>
       <c r="B266" t="n">
-        <v>80258</v>
+        <v>95862</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -27232,34 +27227,38 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>6462</v>
+        <v>2809</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
+      <c r="J266" t="inlineStr"/>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr"/>
+      <c r="N266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>634527</v>
+        <v>635110</v>
       </c>
       <c r="R266" t="n">
-        <v>7087301</v>
+        <v>7087251</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -27300,6 +27299,7 @@
       <c r="AE266" t="b">
         <v>0</v>
       </c>
+      <c r="AF266" t="inlineStr"/>
       <c r="AG266" t="b">
         <v>0</v>
       </c>
@@ -27318,32 +27318,32 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>128423602</v>
+        <v>128423578</v>
       </c>
       <c r="B267" t="n">
-        <v>57720</v>
+        <v>91473</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -27353,7 +27353,7 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>635210</v>
+        <v>635327</v>
       </c>
       <c r="R267" t="n">
         <v>7087158</v>
@@ -27389,11 +27389,6 @@
       <c r="AA267" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC267" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -27420,32 +27415,32 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>128423578</v>
+        <v>128423602</v>
       </c>
       <c r="B268" t="n">
-        <v>91473</v>
+        <v>57720</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -27455,7 +27450,7 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>635327</v>
+        <v>635210</v>
       </c>
       <c r="R268" t="n">
         <v>7087158</v>
@@ -27491,6 +27486,11 @@
       <c r="AA268" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC268" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -27808,49 +27808,45 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>128423603</v>
+        <v>128423576</v>
       </c>
       <c r="B272" t="n">
-        <v>57720</v>
+        <v>91473</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="inlineStr"/>
-      <c r="N272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>635240</v>
+        <v>634705</v>
       </c>
       <c r="R272" t="n">
-        <v>7087224</v>
+        <v>7087668</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -27883,11 +27879,6 @@
       <c r="AA272" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC272" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -27914,45 +27905,49 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>128423576</v>
+        <v>128423603</v>
       </c>
       <c r="B273" t="n">
-        <v>91473</v>
+        <v>57720</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr"/>
+      <c r="N273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>634705</v>
+        <v>635240</v>
       </c>
       <c r="R273" t="n">
-        <v>7087668</v>
+        <v>7087224</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -27985,6 +27980,11 @@
       <c r="AA273" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -28011,32 +28011,32 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>128423599</v>
+        <v>128423592</v>
       </c>
       <c r="B274" t="n">
-        <v>91962</v>
+        <v>80258</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>1209</v>
+        <v>6462</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -28046,10 +28046,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>635464</v>
+        <v>635454</v>
       </c>
       <c r="R274" t="n">
-        <v>7087275</v>
+        <v>7087257</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28108,32 +28108,32 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>128423598</v>
+        <v>128423599</v>
       </c>
       <c r="B275" t="n">
-        <v>80230</v>
+        <v>91962</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>2081</v>
+        <v>1209</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -28143,10 +28143,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>635632</v>
+        <v>635464</v>
       </c>
       <c r="R275" t="n">
-        <v>7087270</v>
+        <v>7087275</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -28205,32 +28205,32 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>128423592</v>
+        <v>128423598</v>
       </c>
       <c r="B276" t="n">
-        <v>80258</v>
+        <v>80230</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -28240,10 +28240,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>635454</v>
+        <v>635632</v>
       </c>
       <c r="R276" t="n">
-        <v>7087257</v>
+        <v>7087270</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -28399,10 +28399,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>128423588</v>
+        <v>128423596</v>
       </c>
       <c r="B278" t="n">
-        <v>57880</v>
+        <v>57717</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -28410,21 +28410,21 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
@@ -28434,10 +28434,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>634560</v>
+        <v>634648</v>
       </c>
       <c r="R278" t="n">
-        <v>7087311</v>
+        <v>7087590</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -28593,10 +28593,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>128423596</v>
+        <v>128423588</v>
       </c>
       <c r="B280" t="n">
-        <v>57717</v>
+        <v>57880</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -28604,21 +28604,21 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -28628,10 +28628,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>634648</v>
+        <v>634560</v>
       </c>
       <c r="R280" t="n">
-        <v>7087590</v>
+        <v>7087311</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -28690,7 +28690,7 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>128423579</v>
+        <v>128423580</v>
       </c>
       <c r="B281" t="n">
         <v>91473</v>
@@ -28725,10 +28725,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>635424</v>
+        <v>635478</v>
       </c>
       <c r="R281" t="n">
-        <v>7087198</v>
+        <v>7087280</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -28787,7 +28787,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>128423580</v>
+        <v>128423579</v>
       </c>
       <c r="B282" t="n">
         <v>91473</v>
@@ -28822,10 +28822,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>635478</v>
+        <v>635424</v>
       </c>
       <c r="R282" t="n">
-        <v>7087280</v>
+        <v>7087198</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>

--- a/artfynd/A 30047-2025 artfynd.xlsx
+++ b/artfynd/A 30047-2025 artfynd.xlsx
@@ -6800,10 +6800,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128423112</v>
+        <v>128408718</v>
       </c>
       <c r="B61" t="n">
-        <v>91458</v>
+        <v>91531</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6811,34 +6811,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>112</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>634544</v>
+        <v>635017</v>
       </c>
       <c r="R61" t="n">
-        <v>7087320</v>
+        <v>7087370</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6868,9 +6868,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6885,22 +6895,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128408718</v>
+        <v>128423158</v>
       </c>
       <c r="B62" t="n">
-        <v>91526</v>
+        <v>79029</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6908,34 +6918,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>635017</v>
+        <v>635124</v>
       </c>
       <c r="R62" t="n">
-        <v>7087370</v>
+        <v>7087198</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6965,19 +6975,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>13:16</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6992,12 +6992,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7007,7 +7007,7 @@
         <v>128423091</v>
       </c>
       <c r="B63" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>128408152</v>
       </c>
       <c r="B64" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7208,10 +7208,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128423158</v>
+        <v>128423112</v>
       </c>
       <c r="B65" t="n">
-        <v>79124</v>
+        <v>91463</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7219,21 +7219,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7243,10 +7243,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>635124</v>
+        <v>634544</v>
       </c>
       <c r="R65" t="n">
-        <v>7087198</v>
+        <v>7087320</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7305,10 +7305,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128423178</v>
+        <v>128423179</v>
       </c>
       <c r="B66" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7340,10 +7340,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>635318</v>
+        <v>635348</v>
       </c>
       <c r="R66" t="n">
-        <v>7087158</v>
+        <v>7087138</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7402,10 +7402,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128423192</v>
+        <v>128423180</v>
       </c>
       <c r="B67" t="n">
-        <v>88908</v>
+        <v>79029</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7413,21 +7413,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7437,10 +7437,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>634595</v>
+        <v>635376</v>
       </c>
       <c r="R67" t="n">
-        <v>7087268</v>
+        <v>7087128</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7499,10 +7499,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128423180</v>
+        <v>128423178</v>
       </c>
       <c r="B68" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7534,10 +7534,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>635376</v>
+        <v>635318</v>
       </c>
       <c r="R68" t="n">
-        <v>7087128</v>
+        <v>7087158</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7596,10 +7596,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128423179</v>
+        <v>128423192</v>
       </c>
       <c r="B69" t="n">
-        <v>79124</v>
+        <v>88913</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7607,21 +7607,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7631,10 +7631,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>635348</v>
+        <v>634595</v>
       </c>
       <c r="R69" t="n">
-        <v>7087138</v>
+        <v>7087268</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7696,7 +7696,7 @@
         <v>128411934</v>
       </c>
       <c r="B70" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>128423142</v>
       </c>
       <c r="B71" t="n">
-        <v>80265</v>
+        <v>80170</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>128423159</v>
       </c>
       <c r="B72" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>128423140</v>
       </c>
       <c r="B73" t="n">
-        <v>80265</v>
+        <v>80170</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>128423165</v>
       </c>
       <c r="B74" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8188,32 +8188,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128423166</v>
+        <v>128423106</v>
       </c>
       <c r="B75" t="n">
-        <v>79124</v>
+        <v>80163</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8223,10 +8223,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>634652</v>
+        <v>634926</v>
       </c>
       <c r="R75" t="n">
-        <v>7087690</v>
+        <v>7087292</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8285,32 +8285,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128423106</v>
+        <v>128423166</v>
       </c>
       <c r="B76" t="n">
-        <v>80258</v>
+        <v>79029</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8320,10 +8320,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>634926</v>
+        <v>634652</v>
       </c>
       <c r="R76" t="n">
-        <v>7087292</v>
+        <v>7087690</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8382,45 +8382,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128423099</v>
+        <v>128404903</v>
       </c>
       <c r="B77" t="n">
-        <v>92205</v>
+        <v>91531</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>634570</v>
+        <v>635552</v>
       </c>
       <c r="R77" t="n">
-        <v>7087303</v>
+        <v>7087334</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8450,9 +8450,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8467,44 +8477,44 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128423155</v>
+        <v>128423092</v>
       </c>
       <c r="B78" t="n">
-        <v>79124</v>
+        <v>91478</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8514,10 +8524,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>635294</v>
+        <v>634661</v>
       </c>
       <c r="R78" t="n">
-        <v>7087064</v>
+        <v>7087688</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8576,10 +8586,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128423092</v>
+        <v>128423099</v>
       </c>
       <c r="B79" t="n">
-        <v>91473</v>
+        <v>92210</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8587,21 +8597,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8611,10 +8621,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>634661</v>
+        <v>634570</v>
       </c>
       <c r="R79" t="n">
-        <v>7087688</v>
+        <v>7087303</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8673,10 +8683,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128423189</v>
+        <v>128423097</v>
       </c>
       <c r="B80" t="n">
-        <v>79124</v>
+        <v>91513</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8684,21 +8694,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8708,10 +8718,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>635678</v>
+        <v>635320</v>
       </c>
       <c r="R80" t="n">
-        <v>7087274</v>
+        <v>7087069</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8770,45 +8780,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128404903</v>
+        <v>128409643</v>
       </c>
       <c r="B81" t="n">
-        <v>91526</v>
+        <v>80163</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>635552</v>
+        <v>634947</v>
       </c>
       <c r="R81" t="n">
-        <v>7087334</v>
+        <v>7087432</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8840,7 +8850,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -8850,7 +8860,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8877,10 +8887,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128409643</v>
+        <v>128423127</v>
       </c>
       <c r="B82" t="n">
-        <v>80258</v>
+        <v>79053</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8888,34 +8898,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>6434</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>634947</v>
+        <v>635508</v>
       </c>
       <c r="R82" t="n">
-        <v>7087432</v>
+        <v>7087301</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8945,19 +8955,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>13:43</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8972,44 +8972,44 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128423127</v>
+        <v>128423189</v>
       </c>
       <c r="B83" t="n">
-        <v>79148</v>
+        <v>79029</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9019,10 +9019,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>635508</v>
+        <v>635678</v>
       </c>
       <c r="R83" t="n">
-        <v>7087301</v>
+        <v>7087274</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9081,10 +9081,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128423175</v>
+        <v>128423155</v>
       </c>
       <c r="B84" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9116,10 +9116,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>635169</v>
+        <v>635294</v>
       </c>
       <c r="R84" t="n">
-        <v>7087269</v>
+        <v>7087064</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9178,10 +9178,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128423097</v>
+        <v>128423175</v>
       </c>
       <c r="B85" t="n">
-        <v>91508</v>
+        <v>79029</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9189,21 +9189,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9213,10 +9213,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>635320</v>
+        <v>635169</v>
       </c>
       <c r="R85" t="n">
-        <v>7087069</v>
+        <v>7087269</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9275,10 +9275,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128423119</v>
+        <v>128405478</v>
       </c>
       <c r="B86" t="n">
-        <v>57720</v>
+        <v>79029</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9286,34 +9286,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>634914</v>
+        <v>635443</v>
       </c>
       <c r="R86" t="n">
-        <v>7087316</v>
+        <v>7087145</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9343,14 +9348,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9365,22 +9375,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128405478</v>
+        <v>128423176</v>
       </c>
       <c r="B87" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9406,21 +9416,16 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>635443</v>
+        <v>635233</v>
       </c>
       <c r="R87" t="n">
-        <v>7087145</v>
+        <v>7087199</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9450,19 +9455,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>11:18</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9477,44 +9472,44 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128423176</v>
+        <v>128423110</v>
       </c>
       <c r="B88" t="n">
-        <v>79124</v>
+        <v>80163</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9524,10 +9519,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>635233</v>
+        <v>635475</v>
       </c>
       <c r="R88" t="n">
-        <v>7087199</v>
+        <v>7087242</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9586,32 +9581,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128423110</v>
+        <v>128423148</v>
       </c>
       <c r="B89" t="n">
-        <v>80258</v>
+        <v>91527</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9621,10 +9616,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>635475</v>
+        <v>634924</v>
       </c>
       <c r="R89" t="n">
-        <v>7087242</v>
+        <v>7087448</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9683,10 +9678,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128423148</v>
+        <v>128423119</v>
       </c>
       <c r="B90" t="n">
-        <v>91522</v>
+        <v>57723</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9694,21 +9689,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9718,10 +9713,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>634924</v>
+        <v>634914</v>
       </c>
       <c r="R90" t="n">
-        <v>7087448</v>
+        <v>7087316</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9754,6 +9749,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9780,32 +9780,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128423195</v>
+        <v>128423193</v>
       </c>
       <c r="B91" t="n">
-        <v>80264</v>
+        <v>88913</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6463</v>
+        <v>510</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9815,10 +9815,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>635228</v>
+        <v>634638</v>
       </c>
       <c r="R91" t="n">
-        <v>7087058</v>
+        <v>7087656</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9877,32 +9877,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128423154</v>
+        <v>128423089</v>
       </c>
       <c r="B92" t="n">
-        <v>79124</v>
+        <v>91478</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9912,10 +9912,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>635479</v>
+        <v>635295</v>
       </c>
       <c r="R92" t="n">
-        <v>7087148</v>
+        <v>7087129</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9977,7 +9977,7 @@
         <v>128423136</v>
       </c>
       <c r="B93" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>128410776</v>
       </c>
       <c r="B94" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10178,32 +10178,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128423193</v>
+        <v>128423195</v>
       </c>
       <c r="B95" t="n">
-        <v>88908</v>
+        <v>80169</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>510</v>
+        <v>6463</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10213,10 +10213,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>634638</v>
+        <v>635228</v>
       </c>
       <c r="R95" t="n">
-        <v>7087656</v>
+        <v>7087058</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10275,10 +10275,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128423116</v>
+        <v>128423154</v>
       </c>
       <c r="B96" t="n">
-        <v>57720</v>
+        <v>79029</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10286,21 +10286,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10310,10 +10310,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>635330</v>
+        <v>635479</v>
       </c>
       <c r="R96" t="n">
-        <v>7087114</v>
+        <v>7087148</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10346,11 +10346,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10377,45 +10372,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128423085</v>
+        <v>128409304</v>
       </c>
       <c r="B97" t="n">
-        <v>57720</v>
+        <v>56913</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>635508</v>
+        <v>634947</v>
       </c>
       <c r="R97" t="n">
-        <v>7087292</v>
+        <v>7087432</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10445,14 +10440,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10467,44 +10467,44 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128423089</v>
+        <v>128423116</v>
       </c>
       <c r="B98" t="n">
-        <v>91473</v>
+        <v>57723</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10514,10 +10514,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>635295</v>
+        <v>635330</v>
       </c>
       <c r="R98" t="n">
-        <v>7087129</v>
+        <v>7087114</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10550,6 +10550,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10576,45 +10581,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128409304</v>
+        <v>128423085</v>
       </c>
       <c r="B99" t="n">
-        <v>56910</v>
+        <v>57723</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>634947</v>
+        <v>635508</v>
       </c>
       <c r="R99" t="n">
-        <v>7087432</v>
+        <v>7087292</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10644,19 +10649,14 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>13:34</t>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10671,12 +10671,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -10686,7 +10686,7 @@
         <v>128423153</v>
       </c>
       <c r="B100" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>128408809</v>
       </c>
       <c r="B101" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10890,7 +10890,7 @@
         <v>128423131</v>
       </c>
       <c r="B102" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10984,10 +10984,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128423117</v>
+        <v>128423184</v>
       </c>
       <c r="B103" t="n">
-        <v>57720</v>
+        <v>79029</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10995,21 +10995,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11019,10 +11019,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>635201</v>
+        <v>635557</v>
       </c>
       <c r="R103" t="n">
-        <v>7087140</v>
+        <v>7087287</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11057,11 +11057,6 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -11070,21 +11065,6 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -11101,50 +11081,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128413206</v>
+        <v>128423108</v>
       </c>
       <c r="B104" t="n">
-        <v>57717</v>
+        <v>80163</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>634574</v>
+        <v>635235</v>
       </c>
       <c r="R104" t="n">
-        <v>7087273</v>
+        <v>7087170</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11174,19 +11149,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>16:13</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11201,44 +11166,44 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128423108</v>
+        <v>128423163</v>
       </c>
       <c r="B105" t="n">
-        <v>80258</v>
+        <v>79029</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11248,10 +11213,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>635235</v>
+        <v>634542</v>
       </c>
       <c r="R105" t="n">
-        <v>7087170</v>
+        <v>7087338</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11310,10 +11275,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128423163</v>
+        <v>128423174</v>
       </c>
       <c r="B106" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11345,10 +11310,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>634542</v>
+        <v>635174</v>
       </c>
       <c r="R106" t="n">
-        <v>7087338</v>
+        <v>7087358</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11407,32 +11372,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128423174</v>
+        <v>128423105</v>
       </c>
       <c r="B107" t="n">
-        <v>79124</v>
+        <v>80163</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11442,10 +11407,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>635174</v>
+        <v>634980</v>
       </c>
       <c r="R107" t="n">
-        <v>7087358</v>
+        <v>7087289</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11504,32 +11469,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128423105</v>
+        <v>128423117</v>
       </c>
       <c r="B108" t="n">
-        <v>80258</v>
+        <v>57723</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11539,10 +11504,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>634980</v>
+        <v>635201</v>
       </c>
       <c r="R108" t="n">
-        <v>7087289</v>
+        <v>7087140</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11577,6 +11542,11 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
@@ -11585,6 +11555,21 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
@@ -11601,10 +11586,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128423184</v>
+        <v>128413206</v>
       </c>
       <c r="B109" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11612,34 +11597,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>635557</v>
+        <v>634574</v>
       </c>
       <c r="R109" t="n">
-        <v>7087287</v>
+        <v>7087273</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11669,9 +11659,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11686,12 +11686,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -11701,7 +11701,7 @@
         <v>128423096</v>
       </c>
       <c r="B110" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>128423098</v>
       </c>
       <c r="B111" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11895,7 +11895,7 @@
         <v>128423167</v>
       </c>
       <c r="B112" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>128423128</v>
       </c>
       <c r="B113" t="n">
-        <v>80257</v>
+        <v>80162</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
         <v>128423157</v>
       </c>
       <c r="B114" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12183,32 +12183,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128423139</v>
+        <v>128423187</v>
       </c>
       <c r="B115" t="n">
-        <v>80265</v>
+        <v>79029</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12218,10 +12218,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>635237</v>
+        <v>635591</v>
       </c>
       <c r="R115" t="n">
-        <v>7087043</v>
+        <v>7087249</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12280,27 +12280,27 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128423194</v>
+        <v>128423177</v>
       </c>
       <c r="B116" t="n">
-        <v>80264</v>
+        <v>79029</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12315,10 +12315,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>635234</v>
+        <v>635285</v>
       </c>
       <c r="R116" t="n">
-        <v>7087032</v>
+        <v>7087169</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12377,50 +12377,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128404427</v>
+        <v>128423139</v>
       </c>
       <c r="B117" t="n">
-        <v>79124</v>
+        <v>80170</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>635552</v>
+        <v>635237</v>
       </c>
       <c r="R117" t="n">
-        <v>7087334</v>
+        <v>7087043</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12450,19 +12445,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>10:33</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12477,65 +12462,57 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128413141</v>
+        <v>128423194</v>
       </c>
       <c r="B118" t="n">
-        <v>57720</v>
+        <v>80169</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>634574</v>
+        <v>635234</v>
       </c>
       <c r="R118" t="n">
-        <v>7087273</v>
+        <v>7087032</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12565,24 +12542,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12597,22 +12559,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128423177</v>
+        <v>128404427</v>
       </c>
       <c r="B119" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12638,16 +12600,21 @@
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>635285</v>
+        <v>635552</v>
       </c>
       <c r="R119" t="n">
-        <v>7087169</v>
+        <v>7087334</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12677,9 +12644,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12694,22 +12671,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128423187</v>
+        <v>128413141</v>
       </c>
       <c r="B120" t="n">
-        <v>79124</v>
+        <v>57723</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12717,34 +12694,42 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>635591</v>
+        <v>634574</v>
       </c>
       <c r="R120" t="n">
-        <v>7087249</v>
+        <v>7087273</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12774,9 +12759,24 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12791,39 +12791,39 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128423200</v>
+        <v>128409844</v>
       </c>
       <c r="B121" t="n">
-        <v>57720</v>
+        <v>57827</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -12831,17 +12831,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>635225</v>
+        <v>634713</v>
       </c>
       <c r="R121" t="n">
-        <v>7087115</v>
+        <v>7087635</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12871,14 +12885,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12898,39 +12917,39 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128423162</v>
+        <v>128423122</v>
       </c>
       <c r="B122" t="n">
-        <v>79124</v>
+        <v>97514</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12940,10 +12959,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>634580</v>
+        <v>634926</v>
       </c>
       <c r="R122" t="n">
-        <v>7087268</v>
+        <v>7087302</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13005,7 +13024,7 @@
         <v>128409160</v>
       </c>
       <c r="B123" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13112,7 +13131,7 @@
         <v>128423093</v>
       </c>
       <c r="B124" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13206,45 +13225,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128423107</v>
+        <v>128411777</v>
       </c>
       <c r="B125" t="n">
-        <v>80258</v>
+        <v>88913</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6462</v>
+        <v>510</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>634931</v>
+        <v>634505</v>
       </c>
       <c r="R125" t="n">
-        <v>7087432</v>
+        <v>7087326</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13274,9 +13293,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13291,57 +13320,57 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128423141</v>
+        <v>128409243</v>
       </c>
       <c r="B126" t="n">
-        <v>80265</v>
+        <v>91527</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6464</v>
+        <v>1204</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>635232</v>
+        <v>634946</v>
       </c>
       <c r="R126" t="n">
-        <v>7087062</v>
+        <v>7087431</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13371,9 +13400,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13388,22 +13427,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128411777</v>
+        <v>128423162</v>
       </c>
       <c r="B127" t="n">
-        <v>88908</v>
+        <v>79029</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13411,34 +13450,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>634505</v>
+        <v>634580</v>
       </c>
       <c r="R127" t="n">
-        <v>7087326</v>
+        <v>7087268</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13468,19 +13507,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>15:28</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13495,57 +13524,57 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128409243</v>
+        <v>128423107</v>
       </c>
       <c r="B128" t="n">
-        <v>91522</v>
+        <v>80163</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1204</v>
+        <v>6462</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>634946</v>
+        <v>634931</v>
       </c>
       <c r="R128" t="n">
-        <v>7087431</v>
+        <v>7087432</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13575,19 +13604,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>13:33</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13602,22 +13621,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128409844</v>
+        <v>128423141</v>
       </c>
       <c r="B129" t="n">
-        <v>57824</v>
+        <v>80170</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13625,48 +13644,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>103031</v>
+        <v>6464</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>634713</v>
+        <v>635232</v>
       </c>
       <c r="R129" t="n">
-        <v>7087635</v>
+        <v>7087062</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13696,19 +13701,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13728,39 +13723,39 @@
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128423122</v>
+        <v>128423200</v>
       </c>
       <c r="B130" t="n">
-        <v>97507</v>
+        <v>57723</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13770,10 +13765,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>634926</v>
+        <v>635225</v>
       </c>
       <c r="R130" t="n">
-        <v>7087302</v>
+        <v>7087115</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13806,6 +13801,11 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13832,10 +13832,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128423126</v>
+        <v>128423090</v>
       </c>
       <c r="B131" t="n">
-        <v>79148</v>
+        <v>91478</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13843,21 +13843,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6434</v>
+        <v>5447</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13867,10 +13867,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>635212</v>
+        <v>635155</v>
       </c>
       <c r="R131" t="n">
-        <v>7087212</v>
+        <v>7087185</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13929,10 +13929,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128423101</v>
+        <v>128423191</v>
       </c>
       <c r="B132" t="n">
-        <v>57880</v>
+        <v>88913</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13940,21 +13940,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>103021</v>
+        <v>510</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13964,10 +13964,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>634716</v>
+        <v>634676</v>
       </c>
       <c r="R132" t="n">
-        <v>7087613</v>
+        <v>7087233</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14026,10 +14026,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128423191</v>
+        <v>128423113</v>
       </c>
       <c r="B133" t="n">
-        <v>88908</v>
+        <v>80135</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14037,21 +14037,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>510</v>
+        <v>2081</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14061,10 +14061,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>634676</v>
+        <v>635240</v>
       </c>
       <c r="R133" t="n">
-        <v>7087233</v>
+        <v>7087040</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14123,10 +14123,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128423113</v>
+        <v>128423185</v>
       </c>
       <c r="B134" t="n">
-        <v>80230</v>
+        <v>79029</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14134,21 +14134,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14158,10 +14158,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>635240</v>
+        <v>635559</v>
       </c>
       <c r="R134" t="n">
-        <v>7087040</v>
+        <v>7087269</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14220,32 +14220,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128423185</v>
+        <v>128423126</v>
       </c>
       <c r="B135" t="n">
-        <v>79124</v>
+        <v>79053</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14255,10 +14255,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>635559</v>
+        <v>635212</v>
       </c>
       <c r="R135" t="n">
-        <v>7087269</v>
+        <v>7087212</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14317,32 +14317,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128423090</v>
+        <v>128423101</v>
       </c>
       <c r="B136" t="n">
-        <v>91473</v>
+        <v>57883</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14352,10 +14352,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>635155</v>
+        <v>634716</v>
       </c>
       <c r="R136" t="n">
-        <v>7087185</v>
+        <v>7087613</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14414,10 +14414,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128404367</v>
+        <v>128423161</v>
       </c>
       <c r="B137" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14443,23 +14443,16 @@
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>635556</v>
+        <v>634702</v>
       </c>
       <c r="R137" t="n">
-        <v>7087281</v>
+        <v>7087248</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14489,50 +14482,39 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AD137" t="b">
         <v>0</v>
       </c>
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128423147</v>
+        <v>128404367</v>
       </c>
       <c r="B138" t="n">
-        <v>91522</v>
+        <v>79029</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14540,34 +14522,41 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Kastjärnbäcken, Kastjärnbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>634571</v>
+        <v>635556</v>
       </c>
       <c r="R138" t="n">
-        <v>7087288</v>
+        <v>7087281</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14597,39 +14586,50 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128412855</v>
+        <v>128423181</v>
       </c>
       <c r="B139" t="n">
-        <v>91804</v>
+        <v>79029</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14637,34 +14637,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>634574</v>
+        <v>635471</v>
       </c>
       <c r="R139" t="n">
-        <v>7087273</v>
+        <v>7087243</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14694,19 +14694,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>16:03</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14721,22 +14711,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128423161</v>
+        <v>128423147</v>
       </c>
       <c r="B140" t="n">
-        <v>79124</v>
+        <v>91527</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14744,21 +14734,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14768,10 +14758,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>634702</v>
+        <v>634571</v>
       </c>
       <c r="R140" t="n">
-        <v>7087248</v>
+        <v>7087288</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14830,10 +14820,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128423181</v>
+        <v>128412855</v>
       </c>
       <c r="B141" t="n">
-        <v>79124</v>
+        <v>91809</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14841,34 +14831,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>635471</v>
+        <v>634574</v>
       </c>
       <c r="R141" t="n">
-        <v>7087243</v>
+        <v>7087273</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14898,9 +14888,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14915,22 +14915,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128423149</v>
+        <v>128423150</v>
       </c>
       <c r="B142" t="n">
-        <v>91522</v>
+        <v>91531</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14938,21 +14938,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14962,10 +14962,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>634942</v>
+        <v>634998</v>
       </c>
       <c r="R142" t="n">
-        <v>7087434</v>
+        <v>7087278</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15024,45 +15024,53 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128423111</v>
+        <v>128411527</v>
       </c>
       <c r="B143" t="n">
-        <v>91519</v>
+        <v>57723</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Hästryggen, Ås lm</t>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>635441</v>
+        <v>634480</v>
       </c>
       <c r="R143" t="n">
-        <v>7087163</v>
+        <v>7087349</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15092,9 +15100,24 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15109,22 +15132,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128423150</v>
+        <v>128423120</v>
       </c>
       <c r="B144" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15132,34 +15155,38 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>634998</v>
+        <v>635205</v>
       </c>
       <c r="R144" t="n">
-        <v>7087278</v>
+        <v>7087342</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15192,6 +15219,11 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15218,10 +15250,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128411527</v>
+        <v>128423115</v>
       </c>
       <c r="B145" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15247,24 +15279,16 @@
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Hästryggen, Hästryggen, Ås lm</t>
+          <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>634480</v>
+        <v>635461</v>
       </c>
       <c r="R145" t="n">
-        <v>7087349</v>
+        <v>7087189</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15294,24 +15318,14 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15326,22 +15340,22 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128423120</v>
+        <v>128423149</v>
       </c>
       <c r="B146" t="n">
-        <v>57720</v>
+        <v>91527</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15349,38 +15363,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>635205</v>
+        <v>634942</v>
       </c>
       <c r="R146" t="n">
-        <v>7087342</v>
+        <v>7087434</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15413,11 +15423,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15444,32 +15449,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128423115</v>
+        <v>128423111</v>
       </c>
       <c r="B147" t="n">
-        <v>57720</v>
+        <v>91524</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15479,10 +15484,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>635461</v>
+        <v>635441</v>
       </c>
       <c r="R147" t="n">
-        <v>7087189</v>
+        <v>7087163</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15515,11 +15520,6 @@
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15549,7 +15549,7 @@
         <v>128411794</v>
       </c>
       <c r="B148" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15661,10 +15661,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128423088</v>
+        <v>128423137</v>
       </c>
       <c r="B149" t="n">
-        <v>96882</v>
+        <v>80134</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15672,21 +15672,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15696,10 +15696,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>634571</v>
+        <v>635683</v>
       </c>
       <c r="R149" t="n">
-        <v>7087288</v>
+        <v>7087267</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15758,10 +15758,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128423190</v>
+        <v>128423186</v>
       </c>
       <c r="B150" t="n">
-        <v>88908</v>
+        <v>79029</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15769,21 +15769,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15793,10 +15793,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>634804</v>
+        <v>635555</v>
       </c>
       <c r="R150" t="n">
-        <v>7087321</v>
+        <v>7087248</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15855,32 +15855,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128423198</v>
+        <v>128423129</v>
       </c>
       <c r="B151" t="n">
-        <v>57720</v>
+        <v>80162</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15890,10 +15890,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>635595</v>
+        <v>635614</v>
       </c>
       <c r="R151" t="n">
-        <v>7087277</v>
+        <v>7087262</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15926,11 +15926,6 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15957,10 +15952,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128423186</v>
+        <v>128423198</v>
       </c>
       <c r="B152" t="n">
-        <v>79124</v>
+        <v>57723</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15968,21 +15963,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15992,10 +15987,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>635555</v>
+        <v>635595</v>
       </c>
       <c r="R152" t="n">
-        <v>7087248</v>
+        <v>7087277</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16028,6 +16023,11 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16054,10 +16054,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128423137</v>
+        <v>128423088</v>
       </c>
       <c r="B153" t="n">
-        <v>80229</v>
+        <v>96889</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16065,21 +16065,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16089,10 +16089,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>635683</v>
+        <v>634571</v>
       </c>
       <c r="R153" t="n">
-        <v>7087267</v>
+        <v>7087288</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16151,32 +16151,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128423129</v>
+        <v>128423190</v>
       </c>
       <c r="B154" t="n">
-        <v>80257</v>
+        <v>88913</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6461</v>
+        <v>510</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16186,10 +16186,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>635614</v>
+        <v>634804</v>
       </c>
       <c r="R154" t="n">
-        <v>7087262</v>
+        <v>7087321</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16248,10 +16248,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128423118</v>
+        <v>128423172</v>
       </c>
       <c r="B155" t="n">
-        <v>57720</v>
+        <v>79029</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16259,21 +16259,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16283,10 +16283,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>634924</v>
+        <v>635010</v>
       </c>
       <c r="R155" t="n">
-        <v>7087288</v>
+        <v>7087362</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16321,11 +16321,6 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD155" t="b">
         <v>0</v>
       </c>
@@ -16334,21 +16329,6 @@
       </c>
       <c r="AG155" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ155" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK155" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO155" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
@@ -16365,10 +16345,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128423172</v>
+        <v>128423118</v>
       </c>
       <c r="B156" t="n">
-        <v>79124</v>
+        <v>57723</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16376,21 +16356,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16400,10 +16380,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>635010</v>
+        <v>634924</v>
       </c>
       <c r="R156" t="n">
-        <v>7087362</v>
+        <v>7087288</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16438,6 +16418,11 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
@@ -16446,6 +16431,21 @@
       </c>
       <c r="AG156" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
@@ -16465,7 +16465,7 @@
         <v>128423138</v>
       </c>
       <c r="B157" t="n">
-        <v>80265</v>
+        <v>80170</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>128423168</v>
       </c>
       <c r="B158" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>128423109</v>
       </c>
       <c r="B159" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
         <v>128423160</v>
       </c>
       <c r="B160" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>128423135</v>
       </c>
       <c r="B161" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16947,10 +16947,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128423151</v>
+        <v>128423114</v>
       </c>
       <c r="B162" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16958,21 +16958,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16982,10 +16982,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>634546</v>
+        <v>635207</v>
       </c>
       <c r="R162" t="n">
-        <v>7087320</v>
+        <v>7087210</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17018,6 +17018,11 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17044,10 +17049,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128423114</v>
+        <v>128423151</v>
       </c>
       <c r="B163" t="n">
-        <v>57720</v>
+        <v>91531</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17055,21 +17060,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17079,10 +17084,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>635207</v>
+        <v>634546</v>
       </c>
       <c r="R163" t="n">
-        <v>7087210</v>
+        <v>7087320</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17115,11 +17120,6 @@
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17149,7 +17149,7 @@
         <v>128423132</v>
       </c>
       <c r="B164" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>128406204</v>
       </c>
       <c r="B165" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17353,7 +17353,7 @@
         <v>128423156</v>
       </c>
       <c r="B166" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17447,10 +17447,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128423171</v>
+        <v>128423188</v>
       </c>
       <c r="B167" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17482,10 +17482,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>634973</v>
+        <v>635610</v>
       </c>
       <c r="R167" t="n">
-        <v>7087410</v>
+        <v>7087261</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17547,7 +17547,7 @@
         <v>128423170</v>
       </c>
       <c r="B168" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17641,10 +17641,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128423199</v>
+        <v>128423171</v>
       </c>
       <c r="B169" t="n">
-        <v>57720</v>
+        <v>79029</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17652,38 +17652,34 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>635298</v>
+        <v>634973</v>
       </c>
       <c r="R169" t="n">
-        <v>7087096</v>
+        <v>7087410</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17716,11 +17712,6 @@
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17747,10 +17738,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128423121</v>
+        <v>128423199</v>
       </c>
       <c r="B170" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17776,16 +17767,20 @@
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>635167</v>
+        <v>635298</v>
       </c>
       <c r="R170" t="n">
-        <v>7087269</v>
+        <v>7087096</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17849,10 +17844,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128423188</v>
+        <v>128423121</v>
       </c>
       <c r="B171" t="n">
-        <v>79124</v>
+        <v>57723</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17860,21 +17855,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17884,10 +17879,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>635610</v>
+        <v>635167</v>
       </c>
       <c r="R171" t="n">
-        <v>7087261</v>
+        <v>7087269</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17920,6 +17915,11 @@
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -17949,7 +17949,7 @@
         <v>128423094</v>
       </c>
       <c r="B172" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18046,7 +18046,7 @@
         <v>128423183</v>
       </c>
       <c r="B173" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18143,7 +18143,7 @@
         <v>128423130</v>
       </c>
       <c r="B174" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>128423087</v>
       </c>
       <c r="B175" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18352,7 +18352,7 @@
         <v>128405308</v>
       </c>
       <c r="B176" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>128423173</v>
       </c>
       <c r="B177" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         <v>128423134</v>
       </c>
       <c r="B178" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>128407951</v>
       </c>
       <c r="B179" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>128428584</v>
       </c>
       <c r="B180" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18857,7 +18857,7 @@
         <v>128428573</v>
       </c>
       <c r="B181" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>128428570</v>
       </c>
       <c r="B182" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19051,7 +19051,7 @@
         <v>128428542</v>
       </c>
       <c r="B183" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>128428595</v>
       </c>
       <c r="B184" t="n">
-        <v>75201</v>
+        <v>82997</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19242,10 +19242,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128428563</v>
+        <v>128428547</v>
       </c>
       <c r="B185" t="n">
-        <v>57824</v>
+        <v>80163</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19253,21 +19253,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>103031</v>
+        <v>6462</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19277,10 +19277,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>635011</v>
+        <v>635305</v>
       </c>
       <c r="R185" t="n">
-        <v>7087362</v>
+        <v>7087219</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19339,10 +19339,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128428547</v>
+        <v>128428563</v>
       </c>
       <c r="B186" t="n">
-        <v>80258</v>
+        <v>57827</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19350,21 +19350,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6462</v>
+        <v>103031</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19374,10 +19374,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>635305</v>
+        <v>635011</v>
       </c>
       <c r="R186" t="n">
-        <v>7087219</v>
+        <v>7087362</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19439,7 +19439,7 @@
         <v>128428556</v>
       </c>
       <c r="B187" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19546,45 +19546,49 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128428530</v>
+        <v>128428540</v>
       </c>
       <c r="B188" t="n">
-        <v>91473</v>
+        <v>57883</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P188" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>634478</v>
+        <v>634887</v>
       </c>
       <c r="R188" t="n">
-        <v>7087363</v>
+        <v>7087502</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19643,49 +19647,45 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128428540</v>
+        <v>128428530</v>
       </c>
       <c r="B189" t="n">
-        <v>57880</v>
+        <v>91478</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>634887</v>
+        <v>634478</v>
       </c>
       <c r="R189" t="n">
-        <v>7087502</v>
+        <v>7087363</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19747,7 +19747,7 @@
         <v>128428575</v>
       </c>
       <c r="B190" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>128428546</v>
       </c>
       <c r="B191" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19938,10 +19938,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128428537</v>
+        <v>128428571</v>
       </c>
       <c r="B192" t="n">
-        <v>57720</v>
+        <v>79029</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19949,42 +19949,34 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>635466</v>
+        <v>635190</v>
       </c>
       <c r="R192" t="n">
-        <v>7087249</v>
+        <v>7087142</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20017,11 +20009,6 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>Ca 3 m upp på liggande granlåga. Runt bohål, omkr 45 mm i diameter.</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20051,7 +20038,7 @@
         <v>128428568</v>
       </c>
       <c r="B193" t="n">
-        <v>91522</v>
+        <v>91527</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20148,7 +20135,7 @@
         <v>128428554</v>
       </c>
       <c r="B194" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20242,10 +20229,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128428571</v>
+        <v>128428537</v>
       </c>
       <c r="B195" t="n">
-        <v>79124</v>
+        <v>57723</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20253,34 +20240,42 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>635190</v>
+        <v>635466</v>
       </c>
       <c r="R195" t="n">
-        <v>7087142</v>
+        <v>7087249</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20313,6 +20308,11 @@
       <c r="AA195" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>Ca 3 m upp på liggande granlåga. Runt bohål, omkr 45 mm i diameter.</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20342,7 +20342,7 @@
         <v>128428594</v>
       </c>
       <c r="B196" t="n">
-        <v>75201</v>
+        <v>82997</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>128428533</v>
       </c>
       <c r="B197" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20536,7 +20536,7 @@
         <v>128428577</v>
       </c>
       <c r="B198" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>128428551</v>
       </c>
       <c r="B199" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20735,32 +20735,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>128428589</v>
+        <v>128428557</v>
       </c>
       <c r="B200" t="n">
-        <v>88908</v>
+        <v>79053</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>510</v>
+        <v>6434</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20770,10 +20770,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>634679</v>
+        <v>635151</v>
       </c>
       <c r="R200" t="n">
-        <v>7087311</v>
+        <v>7087221</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20832,10 +20832,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>128428557</v>
+        <v>128428564</v>
       </c>
       <c r="B201" t="n">
-        <v>79148</v>
+        <v>80038</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20843,21 +20843,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6434</v>
+        <v>6456</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20867,10 +20867,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>635151</v>
+        <v>635518</v>
       </c>
       <c r="R201" t="n">
-        <v>7087221</v>
+        <v>7087188</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20905,12 +20905,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>På aspbark</t>
+        </is>
+      </c>
       <c r="AD201" t="b">
         <v>0</v>
       </c>
       <c r="AE201" t="b">
         <v>0</v>
       </c>
+      <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="b">
         <v>0</v>
       </c>
@@ -20929,32 +20935,32 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>128428564</v>
+        <v>128428589</v>
       </c>
       <c r="B202" t="n">
-        <v>80133</v>
+        <v>88913</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6456</v>
+        <v>510</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -20964,10 +20970,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>635518</v>
+        <v>634679</v>
       </c>
       <c r="R202" t="n">
-        <v>7087188</v>
+        <v>7087311</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21002,18 +21008,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>På aspbark</t>
-        </is>
-      </c>
       <c r="AD202" t="b">
         <v>0</v>
       </c>
       <c r="AE202" t="b">
         <v>0</v>
       </c>
-      <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="b">
         <v>0</v>
       </c>
@@ -21032,32 +21032,32 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>128428559</v>
+        <v>128428529</v>
       </c>
       <c r="B203" t="n">
-        <v>80229</v>
+        <v>91478</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -21067,10 +21067,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>635416</v>
+        <v>634593</v>
       </c>
       <c r="R203" t="n">
-        <v>7087178</v>
+        <v>7087306</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21132,7 +21132,7 @@
         <v>128428596</v>
       </c>
       <c r="B204" t="n">
-        <v>75201</v>
+        <v>82997</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>128428590</v>
       </c>
       <c r="B205" t="n">
-        <v>88908</v>
+        <v>88913</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         <v>128428581</v>
       </c>
       <c r="B206" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21420,32 +21420,32 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>128428529</v>
+        <v>128428559</v>
       </c>
       <c r="B207" t="n">
-        <v>91473</v>
+        <v>80134</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -21455,10 +21455,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>634593</v>
+        <v>635416</v>
       </c>
       <c r="R207" t="n">
-        <v>7087306</v>
+        <v>7087178</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21517,32 +21517,32 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>128428583</v>
+        <v>128428566</v>
       </c>
       <c r="B208" t="n">
-        <v>82983</v>
+        <v>58093</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>1312</v>
+        <v>103015</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -21552,10 +21552,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>634880</v>
+        <v>634515</v>
       </c>
       <c r="R208" t="n">
-        <v>7087375</v>
+        <v>7087381</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21614,32 +21614,32 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>128428566</v>
+        <v>128428569</v>
       </c>
       <c r="B209" t="n">
-        <v>58090</v>
+        <v>91531</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -21649,10 +21649,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>634515</v>
+        <v>635359</v>
       </c>
       <c r="R209" t="n">
-        <v>7087381</v>
+        <v>7087150</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21711,10 +21711,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128428569</v>
+        <v>128428583</v>
       </c>
       <c r="B210" t="n">
-        <v>91526</v>
+        <v>82892</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21722,21 +21722,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -21746,10 +21746,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>635359</v>
+        <v>634880</v>
       </c>
       <c r="R210" t="n">
-        <v>7087150</v>
+        <v>7087375</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21808,10 +21808,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>128428579</v>
+        <v>128428543</v>
       </c>
       <c r="B211" t="n">
-        <v>79124</v>
+        <v>57883</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21819,21 +21819,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -21843,10 +21843,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>634645</v>
+        <v>635352</v>
       </c>
       <c r="R211" t="n">
-        <v>7087310</v>
+        <v>7087202</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21905,32 +21905,32 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>128428549</v>
+        <v>128428579</v>
       </c>
       <c r="B212" t="n">
-        <v>80258</v>
+        <v>79029</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -21940,10 +21940,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>635412</v>
+        <v>634645</v>
       </c>
       <c r="R212" t="n">
-        <v>7087169</v>
+        <v>7087310</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22002,32 +22002,32 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>128428543</v>
+        <v>128428549</v>
       </c>
       <c r="B213" t="n">
-        <v>57880</v>
+        <v>80163</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -22037,10 +22037,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>635352</v>
+        <v>635412</v>
       </c>
       <c r="R213" t="n">
-        <v>7087202</v>
+        <v>7087169</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22099,10 +22099,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>128428558</v>
+        <v>128428532</v>
       </c>
       <c r="B214" t="n">
-        <v>80229</v>
+        <v>91513</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -22110,21 +22110,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -22134,10 +22134,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>635306</v>
+        <v>634476</v>
       </c>
       <c r="R214" t="n">
-        <v>7087221</v>
+        <v>7087366</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22196,10 +22196,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>128428532</v>
+        <v>128428558</v>
       </c>
       <c r="B215" t="n">
-        <v>91508</v>
+        <v>80134</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -22207,21 +22207,21 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -22231,10 +22231,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>634476</v>
+        <v>635306</v>
       </c>
       <c r="R215" t="n">
-        <v>7087366</v>
+        <v>7087221</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22296,7 +22296,7 @@
         <v>128428534</v>
       </c>
       <c r="B216" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -22403,32 +22403,32 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>128428531</v>
+        <v>128428578</v>
       </c>
       <c r="B217" t="n">
-        <v>91473</v>
+        <v>79029</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -22438,10 +22438,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>634717</v>
+        <v>634686</v>
       </c>
       <c r="R217" t="n">
-        <v>7087633</v>
+        <v>7087331</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22500,32 +22500,32 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>128428578</v>
+        <v>128428531</v>
       </c>
       <c r="B218" t="n">
-        <v>79124</v>
+        <v>91478</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -22535,10 +22535,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>634686</v>
+        <v>634717</v>
       </c>
       <c r="R218" t="n">
-        <v>7087331</v>
+        <v>7087633</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -22600,7 +22600,7 @@
         <v>128428592</v>
       </c>
       <c r="B219" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>128428545</v>
       </c>
       <c r="B220" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -22791,32 +22791,32 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>128428567</v>
+        <v>128428541</v>
       </c>
       <c r="B221" t="n">
-        <v>75192</v>
+        <v>57883</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6439</v>
+        <v>103021</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -22826,10 +22826,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>635532</v>
+        <v>635537</v>
       </c>
       <c r="R221" t="n">
-        <v>7087324</v>
+        <v>7087207</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22888,10 +22888,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>128428561</v>
+        <v>128428567</v>
       </c>
       <c r="B222" t="n">
-        <v>80265</v>
+        <v>82988</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -22899,21 +22899,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6464</v>
+        <v>6439</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -22923,10 +22923,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>634879</v>
+        <v>635532</v>
       </c>
       <c r="R222" t="n">
-        <v>7087368</v>
+        <v>7087324</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -22985,32 +22985,32 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>128428541</v>
+        <v>128428561</v>
       </c>
       <c r="B223" t="n">
-        <v>57880</v>
+        <v>80170</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -23020,10 +23020,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>635537</v>
+        <v>634879</v>
       </c>
       <c r="R223" t="n">
-        <v>7087207</v>
+        <v>7087368</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23085,7 +23085,7 @@
         <v>128428565</v>
       </c>
       <c r="B224" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -23191,10 +23191,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>128428572</v>
+        <v>128428585</v>
       </c>
       <c r="B225" t="n">
-        <v>79124</v>
+        <v>82892</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23202,21 +23202,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23226,10 +23226,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>634969</v>
+        <v>634615</v>
       </c>
       <c r="R225" t="n">
-        <v>7087325</v>
+        <v>7087516</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23288,32 +23288,32 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>128428585</v>
+        <v>128428593</v>
       </c>
       <c r="B226" t="n">
-        <v>82983</v>
+        <v>80169</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>1312</v>
+        <v>6463</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23323,10 +23323,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>634615</v>
+        <v>635390</v>
       </c>
       <c r="R226" t="n">
-        <v>7087516</v>
+        <v>7087179</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23385,10 +23385,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128428593</v>
+        <v>128428544</v>
       </c>
       <c r="B227" t="n">
-        <v>80264</v>
+        <v>80163</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23396,21 +23396,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23420,10 +23420,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>635390</v>
+        <v>635039</v>
       </c>
       <c r="R227" t="n">
-        <v>7087179</v>
+        <v>7087283</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23482,32 +23482,32 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128428544</v>
+        <v>128428572</v>
       </c>
       <c r="B228" t="n">
-        <v>80258</v>
+        <v>79029</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -23517,10 +23517,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>635039</v>
+        <v>634969</v>
       </c>
       <c r="R228" t="n">
-        <v>7087283</v>
+        <v>7087325</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23579,53 +23579,45 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>128428550</v>
+        <v>128428562</v>
       </c>
       <c r="B229" t="n">
-        <v>57717</v>
+        <v>80170</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
-      <c r="K229" t="inlineStr"/>
-      <c r="L229" t="inlineStr"/>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>634487</v>
+        <v>635398</v>
       </c>
       <c r="R229" t="n">
-        <v>7087401</v>
+        <v>7087183</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23684,10 +23676,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>128428552</v>
+        <v>128428550</v>
       </c>
       <c r="B230" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -23727,10 +23719,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>635170</v>
+        <v>634487</v>
       </c>
       <c r="R230" t="n">
-        <v>7087231</v>
+        <v>7087401</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -23789,45 +23781,53 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>128428562</v>
+        <v>128428552</v>
       </c>
       <c r="B231" t="n">
-        <v>80265</v>
+        <v>57720</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>635398</v>
+        <v>635170</v>
       </c>
       <c r="R231" t="n">
-        <v>7087183</v>
+        <v>7087231</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -23889,7 +23889,7 @@
         <v>128428582</v>
       </c>
       <c r="B232" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -23986,7 +23986,7 @@
         <v>128428580</v>
       </c>
       <c r="B233" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -24083,7 +24083,7 @@
         <v>128428535</v>
       </c>
       <c r="B234" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -24193,7 +24193,7 @@
         <v>128428536</v>
       </c>
       <c r="B235" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -24303,7 +24303,7 @@
         <v>128428574</v>
       </c>
       <c r="B236" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24400,7 +24400,7 @@
         <v>128651017</v>
       </c>
       <c r="B237" t="n">
-        <v>96977</v>
+        <v>96984</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>128651018</v>
       </c>
       <c r="B238" t="n">
-        <v>95874</v>
+        <v>95881</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24594,7 +24594,7 @@
         <v>128423582</v>
       </c>
       <c r="B239" t="n">
-        <v>91790</v>
+        <v>91795</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         <v>128423605</v>
       </c>
       <c r="B240" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -24788,7 +24788,7 @@
         <v>128423608</v>
       </c>
       <c r="B241" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24882,32 +24882,32 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>128423623</v>
+        <v>128423573</v>
       </c>
       <c r="B242" t="n">
-        <v>88908</v>
+        <v>91478</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -24917,10 +24917,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>634583</v>
+        <v>634599</v>
       </c>
       <c r="R242" t="n">
-        <v>7087261</v>
+        <v>7087225</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24979,32 +24979,32 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>128423573</v>
+        <v>128423623</v>
       </c>
       <c r="B243" t="n">
-        <v>91473</v>
+        <v>88913</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -25014,10 +25014,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>634599</v>
+        <v>634583</v>
       </c>
       <c r="R243" t="n">
-        <v>7087225</v>
+        <v>7087261</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25079,7 +25079,7 @@
         <v>128423621</v>
       </c>
       <c r="B244" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -25173,32 +25173,32 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>128423591</v>
+        <v>128423597</v>
       </c>
       <c r="B245" t="n">
-        <v>80258</v>
+        <v>57720</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -25208,10 +25208,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>635451</v>
+        <v>634913</v>
       </c>
       <c r="R245" t="n">
-        <v>7087225</v>
+        <v>7087585</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25270,32 +25270,32 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>128423597</v>
+        <v>128423591</v>
       </c>
       <c r="B246" t="n">
-        <v>57717</v>
+        <v>80163</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -25305,10 +25305,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>634913</v>
+        <v>635451</v>
       </c>
       <c r="R246" t="n">
-        <v>7087585</v>
+        <v>7087225</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25370,7 +25370,7 @@
         <v>128423612</v>
       </c>
       <c r="B247" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -25464,32 +25464,32 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>128423618</v>
+        <v>128423575</v>
       </c>
       <c r="B248" t="n">
-        <v>91526</v>
+        <v>91478</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -25499,10 +25499,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>634676</v>
+        <v>634574</v>
       </c>
       <c r="R248" t="n">
-        <v>7087616</v>
+        <v>7087286</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25561,32 +25561,32 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>128423575</v>
+        <v>128423618</v>
       </c>
       <c r="B249" t="n">
-        <v>91473</v>
+        <v>91531</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -25596,10 +25596,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>634574</v>
+        <v>634676</v>
       </c>
       <c r="R249" t="n">
-        <v>7087286</v>
+        <v>7087616</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25661,7 +25661,7 @@
         <v>128423606</v>
       </c>
       <c r="B250" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         <v>128423624</v>
       </c>
       <c r="B251" t="n">
-        <v>88908</v>
+        <v>88913</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -25855,7 +25855,7 @@
         <v>128423615</v>
       </c>
       <c r="B252" t="n">
-        <v>91522</v>
+        <v>91527</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -25952,7 +25952,7 @@
         <v>128423628</v>
       </c>
       <c r="B253" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -26046,10 +26046,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128423622</v>
+        <v>128423617</v>
       </c>
       <c r="B254" t="n">
-        <v>88908</v>
+        <v>91531</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -26057,21 +26057,21 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -26081,10 +26081,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>634642</v>
+        <v>634507</v>
       </c>
       <c r="R254" t="n">
-        <v>7087251</v>
+        <v>7087328</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26143,32 +26143,32 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>128423625</v>
+        <v>128423593</v>
       </c>
       <c r="B255" t="n">
-        <v>88908</v>
+        <v>80163</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>510</v>
+        <v>6462</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -26178,10 +26178,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>634494</v>
+        <v>635471</v>
       </c>
       <c r="R255" t="n">
-        <v>7087408</v>
+        <v>7087281</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26240,32 +26240,32 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>128423617</v>
+        <v>128423629</v>
       </c>
       <c r="B256" t="n">
-        <v>91526</v>
+        <v>80169</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -26275,10 +26275,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>634507</v>
+        <v>635454</v>
       </c>
       <c r="R256" t="n">
-        <v>7087328</v>
+        <v>7087257</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26337,32 +26337,32 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128423593</v>
+        <v>128423622</v>
       </c>
       <c r="B257" t="n">
-        <v>80258</v>
+        <v>88913</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>6462</v>
+        <v>510</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -26372,10 +26372,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>635471</v>
+        <v>634642</v>
       </c>
       <c r="R257" t="n">
-        <v>7087281</v>
+        <v>7087251</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -26434,32 +26434,32 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128423629</v>
+        <v>128423625</v>
       </c>
       <c r="B258" t="n">
-        <v>80264</v>
+        <v>88913</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>6463</v>
+        <v>510</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -26469,10 +26469,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>635454</v>
+        <v>634494</v>
       </c>
       <c r="R258" t="n">
-        <v>7087257</v>
+        <v>7087408</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -26534,7 +26534,7 @@
         <v>128423626</v>
       </c>
       <c r="B259" t="n">
-        <v>88908</v>
+        <v>88913</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -26628,32 +26628,32 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>128423577</v>
+        <v>128423619</v>
       </c>
       <c r="B260" t="n">
-        <v>91473</v>
+        <v>79029</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -26663,10 +26663,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>635153</v>
+        <v>635513</v>
       </c>
       <c r="R260" t="n">
-        <v>7087180</v>
+        <v>7087316</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -26701,12 +26701,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC260" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD260" t="b">
         <v>0</v>
       </c>
       <c r="AE260" t="b">
         <v>0</v>
       </c>
+      <c r="AF260" t="inlineStr"/>
       <c r="AG260" t="b">
         <v>0</v>
       </c>
@@ -26725,32 +26731,32 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128423616</v>
+        <v>128423594</v>
       </c>
       <c r="B261" t="n">
-        <v>91526</v>
+        <v>80163</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -26760,10 +26766,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>634993</v>
+        <v>634527</v>
       </c>
       <c r="R261" t="n">
-        <v>7087294</v>
+        <v>7087301</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26822,10 +26828,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128423619</v>
+        <v>128423620</v>
       </c>
       <c r="B262" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -26857,10 +26863,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>635513</v>
+        <v>634756</v>
       </c>
       <c r="R262" t="n">
-        <v>7087316</v>
+        <v>7087642</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -26895,18 +26901,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC262" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD262" t="b">
         <v>0</v>
       </c>
       <c r="AE262" t="b">
         <v>0</v>
       </c>
-      <c r="AF262" t="inlineStr"/>
       <c r="AG262" t="b">
         <v>0</v>
       </c>
@@ -26925,45 +26925,49 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>128423620</v>
+        <v>128492197</v>
       </c>
       <c r="B263" t="n">
-        <v>79124</v>
+        <v>95869</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
+      <c r="J263" t="inlineStr"/>
+      <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr"/>
+      <c r="N263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>634756</v>
+        <v>635110</v>
       </c>
       <c r="R263" t="n">
-        <v>7087642</v>
+        <v>7087251</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27004,6 +27008,7 @@
       <c r="AE263" t="b">
         <v>0</v>
       </c>
+      <c r="AF263" t="inlineStr"/>
       <c r="AG263" t="b">
         <v>0</v>
       </c>
@@ -27022,10 +27027,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>128423594</v>
+        <v>128423577</v>
       </c>
       <c r="B264" t="n">
-        <v>80258</v>
+        <v>91478</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -27033,21 +27038,21 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -27057,10 +27062,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>634527</v>
+        <v>635153</v>
       </c>
       <c r="R264" t="n">
-        <v>7087301</v>
+        <v>7087180</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27119,32 +27124,32 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>128423585</v>
+        <v>128423616</v>
       </c>
       <c r="B265" t="n">
-        <v>92205</v>
+        <v>91531</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -27154,10 +27159,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>634942</v>
+        <v>634993</v>
       </c>
       <c r="R265" t="n">
-        <v>7087590</v>
+        <v>7087294</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27216,10 +27221,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>128492197</v>
+        <v>128423585</v>
       </c>
       <c r="B266" t="n">
-        <v>95862</v>
+        <v>92210</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -27227,38 +27232,34 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>2809</v>
+        <v>3298</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
-      <c r="J266" t="inlineStr"/>
-      <c r="K266" t="inlineStr"/>
-      <c r="L266" t="inlineStr"/>
-      <c r="N266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>635110</v>
+        <v>634942</v>
       </c>
       <c r="R266" t="n">
-        <v>7087251</v>
+        <v>7087590</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -27299,7 +27300,6 @@
       <c r="AE266" t="b">
         <v>0</v>
       </c>
-      <c r="AF266" t="inlineStr"/>
       <c r="AG266" t="b">
         <v>0</v>
       </c>
@@ -27321,7 +27321,7 @@
         <v>128423578</v>
       </c>
       <c r="B267" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>128423602</v>
       </c>
       <c r="B268" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -27520,7 +27520,7 @@
         <v>128423607</v>
       </c>
       <c r="B269" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -27617,7 +27617,7 @@
         <v>128423572</v>
       </c>
       <c r="B270" t="n">
-        <v>96882</v>
+        <v>96889</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -27711,32 +27711,32 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>128423614</v>
+        <v>128423576</v>
       </c>
       <c r="B271" t="n">
-        <v>91522</v>
+        <v>91478</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
@@ -27746,10 +27746,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>634673</v>
+        <v>634705</v>
       </c>
       <c r="R271" t="n">
-        <v>7087631</v>
+        <v>7087668</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -27808,45 +27808,49 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>128423576</v>
+        <v>128423603</v>
       </c>
       <c r="B272" t="n">
-        <v>91473</v>
+        <v>57723</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="inlineStr"/>
+      <c r="N272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>634705</v>
+        <v>635240</v>
       </c>
       <c r="R272" t="n">
-        <v>7087668</v>
+        <v>7087224</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -27879,6 +27883,11 @@
       <c r="AA272" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC272" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -27905,10 +27914,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>128423603</v>
+        <v>128423614</v>
       </c>
       <c r="B273" t="n">
-        <v>57720</v>
+        <v>91527</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -27916,38 +27925,34 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="inlineStr"/>
-      <c r="N273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>635240</v>
+        <v>634673</v>
       </c>
       <c r="R273" t="n">
-        <v>7087224</v>
+        <v>7087631</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -27980,11 +27985,6 @@
       <c r="AA273" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC273" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -28011,32 +28011,32 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>128423592</v>
+        <v>128423598</v>
       </c>
       <c r="B274" t="n">
-        <v>80258</v>
+        <v>80135</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -28046,10 +28046,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>635454</v>
+        <v>635632</v>
       </c>
       <c r="R274" t="n">
-        <v>7087257</v>
+        <v>7087270</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28111,7 +28111,7 @@
         <v>128423599</v>
       </c>
       <c r="B275" t="n">
-        <v>91962</v>
+        <v>91967</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -28205,32 +28205,32 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>128423598</v>
+        <v>128423592</v>
       </c>
       <c r="B276" t="n">
-        <v>80230</v>
+        <v>80163</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -28240,10 +28240,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>635632</v>
+        <v>635454</v>
       </c>
       <c r="R276" t="n">
-        <v>7087270</v>
+        <v>7087257</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -28305,7 +28305,7 @@
         <v>128423604</v>
       </c>
       <c r="B277" t="n">
-        <v>95862</v>
+        <v>95869</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -28399,10 +28399,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>128423596</v>
+        <v>128423588</v>
       </c>
       <c r="B278" t="n">
-        <v>57717</v>
+        <v>57883</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -28410,21 +28410,21 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
@@ -28434,10 +28434,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>634648</v>
+        <v>634560</v>
       </c>
       <c r="R278" t="n">
-        <v>7087590</v>
+        <v>7087311</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -28499,7 +28499,7 @@
         <v>128423590</v>
       </c>
       <c r="B279" t="n">
-        <v>92790</v>
+        <v>92795</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -28593,10 +28593,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>128423588</v>
+        <v>128423596</v>
       </c>
       <c r="B280" t="n">
-        <v>57880</v>
+        <v>57720</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -28604,21 +28604,21 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -28628,10 +28628,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>634560</v>
+        <v>634648</v>
       </c>
       <c r="R280" t="n">
-        <v>7087311</v>
+        <v>7087590</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -28693,7 +28693,7 @@
         <v>128423580</v>
       </c>
       <c r="B281" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>128423579</v>
       </c>
       <c r="B282" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>128423595</v>
       </c>
       <c r="B283" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -28981,32 +28981,32 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>128423601</v>
+        <v>128423574</v>
       </c>
       <c r="B284" t="n">
-        <v>91804</v>
+        <v>91478</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -29016,10 +29016,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>634475</v>
+        <v>634571</v>
       </c>
       <c r="R284" t="n">
-        <v>7087365</v>
+        <v>7087253</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -29078,32 +29078,32 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>128423574</v>
+        <v>128423601</v>
       </c>
       <c r="B285" t="n">
-        <v>91473</v>
+        <v>91809</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -29113,10 +29113,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>634571</v>
+        <v>634475</v>
       </c>
       <c r="R285" t="n">
-        <v>7087253</v>
+        <v>7087365</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -29178,7 +29178,7 @@
         <v>128423613</v>
       </c>
       <c r="B286" t="n">
-        <v>91522</v>
+        <v>91527</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>

--- a/artfynd/A 30047-2025 artfynd.xlsx
+++ b/artfynd/A 30047-2025 artfynd.xlsx
@@ -25852,32 +25852,32 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>128423624</v>
+        <v>128423628</v>
       </c>
       <c r="B252" t="n">
-        <v>88920</v>
+        <v>80174</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>510</v>
+        <v>6463</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -25887,10 +25887,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>634461</v>
+        <v>635451</v>
       </c>
       <c r="R252" t="n">
-        <v>7087363</v>
+        <v>7087225</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -25949,32 +25949,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>128423628</v>
+        <v>128423624</v>
       </c>
       <c r="B253" t="n">
-        <v>80174</v>
+        <v>88920</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>6463</v>
+        <v>510</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -25984,10 +25984,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>635451</v>
+        <v>634461</v>
       </c>
       <c r="R253" t="n">
-        <v>7087225</v>
+        <v>7087363</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -27415,10 +27415,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>128423602</v>
+        <v>128423607</v>
       </c>
       <c r="B268" t="n">
-        <v>57723</v>
+        <v>80139</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -27426,21 +27426,21 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -27450,10 +27450,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>635210</v>
+        <v>635459</v>
       </c>
       <c r="R268" t="n">
-        <v>7087158</v>
+        <v>7087231</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -27486,11 +27486,6 @@
       <c r="AA268" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC268" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -27517,10 +27512,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>128423607</v>
+        <v>128423602</v>
       </c>
       <c r="B269" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -27528,21 +27523,21 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -27552,10 +27547,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>635459</v>
+        <v>635210</v>
       </c>
       <c r="R269" t="n">
-        <v>7087231</v>
+        <v>7087158</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -27588,6 +27583,11 @@
       <c r="AA269" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD269" t="b">

--- a/artfynd/A 30047-2025 artfynd.xlsx
+++ b/artfynd/A 30047-2025 artfynd.xlsx
@@ -24400,7 +24400,7 @@
         <v>128651017</v>
       </c>
       <c r="B237" t="n">
-        <v>96992</v>
+        <v>96997</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>128651018</v>
       </c>
       <c r="B238" t="n">
-        <v>95889</v>
+        <v>95894</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24594,7 +24594,7 @@
         <v>128423582</v>
       </c>
       <c r="B239" t="n">
-        <v>91802</v>
+        <v>91805</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>128423573</v>
       </c>
       <c r="B242" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>128423623</v>
       </c>
       <c r="B243" t="n">
-        <v>88920</v>
+        <v>88923</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -25173,32 +25173,32 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>128423591</v>
+        <v>128423597</v>
       </c>
       <c r="B245" t="n">
-        <v>80168</v>
+        <v>57720</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -25208,10 +25208,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>635451</v>
+        <v>634913</v>
       </c>
       <c r="R245" t="n">
-        <v>7087225</v>
+        <v>7087585</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25270,27 +25270,27 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>128423597</v>
+        <v>128423612</v>
       </c>
       <c r="B246" t="n">
-        <v>57720</v>
+        <v>58093</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -25367,10 +25367,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>128423612</v>
+        <v>128423591</v>
       </c>
       <c r="B247" t="n">
-        <v>58093</v>
+        <v>80168</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -25378,21 +25378,21 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>103015</v>
+        <v>6462</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -25402,10 +25402,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>634913</v>
+        <v>635451</v>
       </c>
       <c r="R247" t="n">
-        <v>7087585</v>
+        <v>7087225</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25464,32 +25464,32 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>128423575</v>
+        <v>128423618</v>
       </c>
       <c r="B248" t="n">
-        <v>91485</v>
+        <v>91541</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -25499,10 +25499,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>634574</v>
+        <v>634676</v>
       </c>
       <c r="R248" t="n">
-        <v>7087286</v>
+        <v>7087616</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25561,32 +25561,32 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>128423618</v>
+        <v>128423575</v>
       </c>
       <c r="B249" t="n">
-        <v>91538</v>
+        <v>91488</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -25596,10 +25596,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>634676</v>
+        <v>634574</v>
       </c>
       <c r="R249" t="n">
-        <v>7087616</v>
+        <v>7087286</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25758,7 +25758,7 @@
         <v>128423615</v>
       </c>
       <c r="B251" t="n">
-        <v>91534</v>
+        <v>91537</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -25952,7 +25952,7 @@
         <v>128423624</v>
       </c>
       <c r="B253" t="n">
-        <v>88920</v>
+        <v>88923</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -26046,10 +26046,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128423622</v>
+        <v>128423617</v>
       </c>
       <c r="B254" t="n">
-        <v>88920</v>
+        <v>91541</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -26057,21 +26057,21 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -26081,10 +26081,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>634642</v>
+        <v>634507</v>
       </c>
       <c r="R254" t="n">
-        <v>7087251</v>
+        <v>7087328</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26337,10 +26337,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128423617</v>
+        <v>128423622</v>
       </c>
       <c r="B257" t="n">
-        <v>91538</v>
+        <v>88923</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -26348,21 +26348,21 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -26372,10 +26372,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>634507</v>
+        <v>634642</v>
       </c>
       <c r="R257" t="n">
-        <v>7087328</v>
+        <v>7087251</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -26437,7 +26437,7 @@
         <v>128423625</v>
       </c>
       <c r="B258" t="n">
-        <v>88920</v>
+        <v>88923</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>128423626</v>
       </c>
       <c r="B259" t="n">
-        <v>88920</v>
+        <v>88923</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -26628,10 +26628,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>128423577</v>
+        <v>128492197</v>
       </c>
       <c r="B260" t="n">
-        <v>91485</v>
+        <v>95882</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -26639,34 +26639,38 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
+      <c r="J260" t="inlineStr"/>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr"/>
+      <c r="N260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>635153</v>
+        <v>635110</v>
       </c>
       <c r="R260" t="n">
-        <v>7087180</v>
+        <v>7087251</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -26707,6 +26711,7 @@
       <c r="AE260" t="b">
         <v>0</v>
       </c>
+      <c r="AF260" t="inlineStr"/>
       <c r="AG260" t="b">
         <v>0</v>
       </c>
@@ -26725,32 +26730,32 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128423616</v>
+        <v>128423585</v>
       </c>
       <c r="B261" t="n">
-        <v>91538</v>
+        <v>92223</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -26760,10 +26765,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>634993</v>
+        <v>634942</v>
       </c>
       <c r="R261" t="n">
-        <v>7087294</v>
+        <v>7087590</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26822,32 +26827,32 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128423619</v>
+        <v>128423577</v>
       </c>
       <c r="B262" t="n">
-        <v>79034</v>
+        <v>91488</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -26857,10 +26862,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>635513</v>
+        <v>635153</v>
       </c>
       <c r="R262" t="n">
-        <v>7087316</v>
+        <v>7087180</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -26895,18 +26900,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC262" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD262" t="b">
         <v>0</v>
       </c>
       <c r="AE262" t="b">
         <v>0</v>
       </c>
-      <c r="AF262" t="inlineStr"/>
       <c r="AG262" t="b">
         <v>0</v>
       </c>
@@ -26925,32 +26924,32 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>128423585</v>
+        <v>128423616</v>
       </c>
       <c r="B263" t="n">
-        <v>92218</v>
+        <v>91541</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -26960,10 +26959,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>634942</v>
+        <v>634993</v>
       </c>
       <c r="R263" t="n">
-        <v>7087590</v>
+        <v>7087294</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27022,32 +27021,32 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>128423594</v>
+        <v>128423619</v>
       </c>
       <c r="B264" t="n">
-        <v>80168</v>
+        <v>79034</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -27057,10 +27056,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>634527</v>
+        <v>635513</v>
       </c>
       <c r="R264" t="n">
-        <v>7087301</v>
+        <v>7087316</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27095,12 +27094,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD264" t="b">
         <v>0</v>
       </c>
       <c r="AE264" t="b">
         <v>0</v>
       </c>
+      <c r="AF264" t="inlineStr"/>
       <c r="AG264" t="b">
         <v>0</v>
       </c>
@@ -27119,32 +27124,32 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>128423620</v>
+        <v>128423594</v>
       </c>
       <c r="B265" t="n">
-        <v>79034</v>
+        <v>80168</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -27154,10 +27159,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>634756</v>
+        <v>634527</v>
       </c>
       <c r="R265" t="n">
-        <v>7087642</v>
+        <v>7087301</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27216,49 +27221,45 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>128492197</v>
+        <v>128423620</v>
       </c>
       <c r="B266" t="n">
-        <v>95877</v>
+        <v>79034</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
-      <c r="J266" t="inlineStr"/>
-      <c r="K266" t="inlineStr"/>
-      <c r="L266" t="inlineStr"/>
-      <c r="N266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>635110</v>
+        <v>634756</v>
       </c>
       <c r="R266" t="n">
-        <v>7087251</v>
+        <v>7087642</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -27299,7 +27300,6 @@
       <c r="AE266" t="b">
         <v>0</v>
       </c>
-      <c r="AF266" t="inlineStr"/>
       <c r="AG266" t="b">
         <v>0</v>
       </c>
@@ -27318,32 +27318,32 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>128423578</v>
+        <v>128423607</v>
       </c>
       <c r="B267" t="n">
-        <v>91485</v>
+        <v>80139</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -27353,10 +27353,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>635327</v>
+        <v>635459</v>
       </c>
       <c r="R267" t="n">
-        <v>7087158</v>
+        <v>7087231</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -27415,32 +27415,32 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>128423607</v>
+        <v>128423578</v>
       </c>
       <c r="B268" t="n">
-        <v>80139</v>
+        <v>91488</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -27450,10 +27450,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>635459</v>
+        <v>635327</v>
       </c>
       <c r="R268" t="n">
-        <v>7087231</v>
+        <v>7087158</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -27617,7 +27617,7 @@
         <v>128423572</v>
       </c>
       <c r="B270" t="n">
-        <v>96897</v>
+        <v>96902</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -27711,10 +27711,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>128423614</v>
+        <v>128423603</v>
       </c>
       <c r="B271" t="n">
-        <v>91534</v>
+        <v>57723</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -27722,34 +27722,38 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr"/>
+      <c r="M271" t="inlineStr"/>
+      <c r="N271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>634673</v>
+        <v>635240</v>
       </c>
       <c r="R271" t="n">
-        <v>7087631</v>
+        <v>7087224</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -27782,6 +27786,11 @@
       <c r="AA271" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -27808,32 +27817,32 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>128423576</v>
+        <v>128423614</v>
       </c>
       <c r="B272" t="n">
-        <v>91485</v>
+        <v>91537</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
@@ -27843,10 +27852,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>634705</v>
+        <v>634673</v>
       </c>
       <c r="R272" t="n">
-        <v>7087668</v>
+        <v>7087631</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -27905,49 +27914,45 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>128423603</v>
+        <v>128423576</v>
       </c>
       <c r="B273" t="n">
-        <v>57723</v>
+        <v>91488</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="inlineStr"/>
-      <c r="N273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>635240</v>
+        <v>634705</v>
       </c>
       <c r="R273" t="n">
-        <v>7087224</v>
+        <v>7087668</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -27980,11 +27985,6 @@
       <c r="AA273" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC273" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -28111,7 +28111,7 @@
         <v>128423599</v>
       </c>
       <c r="B275" t="n">
-        <v>91975</v>
+        <v>91978</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>128423604</v>
       </c>
       <c r="B277" t="n">
-        <v>95877</v>
+        <v>95882</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -28399,10 +28399,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>128423590</v>
+        <v>128423588</v>
       </c>
       <c r="B278" t="n">
-        <v>92803</v>
+        <v>57883</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -28410,21 +28410,21 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>4361</v>
+        <v>103021</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
@@ -28434,10 +28434,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>635182</v>
+        <v>634560</v>
       </c>
       <c r="R278" t="n">
-        <v>7087227</v>
+        <v>7087311</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -28496,10 +28496,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>128423588</v>
+        <v>128423596</v>
       </c>
       <c r="B279" t="n">
-        <v>57883</v>
+        <v>57720</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -28507,21 +28507,21 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
@@ -28531,10 +28531,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>634560</v>
+        <v>634648</v>
       </c>
       <c r="R279" t="n">
-        <v>7087311</v>
+        <v>7087590</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -28593,10 +28593,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>128423596</v>
+        <v>128423590</v>
       </c>
       <c r="B280" t="n">
-        <v>57720</v>
+        <v>92808</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -28604,21 +28604,21 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>100049</v>
+        <v>4361</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -28628,10 +28628,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>634648</v>
+        <v>635182</v>
       </c>
       <c r="R280" t="n">
-        <v>7087590</v>
+        <v>7087227</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -28690,10 +28690,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>128423579</v>
+        <v>128423580</v>
       </c>
       <c r="B281" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -28725,10 +28725,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>635424</v>
+        <v>635478</v>
       </c>
       <c r="R281" t="n">
-        <v>7087198</v>
+        <v>7087280</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -28787,10 +28787,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>128423580</v>
+        <v>128423579</v>
       </c>
       <c r="B282" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -28822,10 +28822,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>635478</v>
+        <v>635424</v>
       </c>
       <c r="R282" t="n">
-        <v>7087280</v>
+        <v>7087198</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -28981,32 +28981,32 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>128423601</v>
+        <v>128423574</v>
       </c>
       <c r="B284" t="n">
-        <v>91805</v>
+        <v>91488</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -29016,10 +29016,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>634475</v>
+        <v>634571</v>
       </c>
       <c r="R284" t="n">
-        <v>7087365</v>
+        <v>7087253</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -29078,32 +29078,32 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>128423574</v>
+        <v>128423601</v>
       </c>
       <c r="B285" t="n">
-        <v>91485</v>
+        <v>91808</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -29113,10 +29113,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>634571</v>
+        <v>634475</v>
       </c>
       <c r="R285" t="n">
-        <v>7087253</v>
+        <v>7087365</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -29178,7 +29178,7 @@
         <v>128423613</v>
       </c>
       <c r="B286" t="n">
-        <v>91534</v>
+        <v>91537</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>

--- a/artfynd/A 30047-2025 artfynd.xlsx
+++ b/artfynd/A 30047-2025 artfynd.xlsx
@@ -24400,7 +24400,7 @@
         <v>128651017</v>
       </c>
       <c r="B237" t="n">
-        <v>96997</v>
+        <v>97000</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>128651018</v>
       </c>
       <c r="B238" t="n">
-        <v>95894</v>
+        <v>95897</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24591,10 +24591,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>128423582</v>
+        <v>128423605</v>
       </c>
       <c r="B239" t="n">
-        <v>91805</v>
+        <v>80140</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -24602,21 +24602,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>73</v>
+        <v>6458</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -24626,10 +24626,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>635466</v>
+        <v>635331</v>
       </c>
       <c r="R239" t="n">
-        <v>7087277</v>
+        <v>7087194</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24688,10 +24688,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>128423605</v>
+        <v>128423608</v>
       </c>
       <c r="B240" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -24723,10 +24723,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>635331</v>
+        <v>635603</v>
       </c>
       <c r="R240" t="n">
-        <v>7087194</v>
+        <v>7087226</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24785,10 +24785,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>128423608</v>
+        <v>128423582</v>
       </c>
       <c r="B241" t="n">
-        <v>80139</v>
+        <v>91808</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24796,21 +24796,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6458</v>
+        <v>73</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -24820,10 +24820,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>635603</v>
+        <v>635466</v>
       </c>
       <c r="R241" t="n">
-        <v>7087226</v>
+        <v>7087277</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -24882,32 +24882,32 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>128423573</v>
+        <v>128423623</v>
       </c>
       <c r="B242" t="n">
-        <v>91488</v>
+        <v>88926</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -24917,10 +24917,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>634599</v>
+        <v>634583</v>
       </c>
       <c r="R242" t="n">
-        <v>7087225</v>
+        <v>7087261</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24979,32 +24979,32 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>128423623</v>
+        <v>128423573</v>
       </c>
       <c r="B243" t="n">
-        <v>88923</v>
+        <v>91491</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -25014,10 +25014,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>634583</v>
+        <v>634599</v>
       </c>
       <c r="R243" t="n">
-        <v>7087261</v>
+        <v>7087225</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25076,32 +25076,32 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>128423621</v>
+        <v>128423591</v>
       </c>
       <c r="B244" t="n">
-        <v>82897</v>
+        <v>80169</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -25111,10 +25111,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>634525</v>
+        <v>635451</v>
       </c>
       <c r="R244" t="n">
-        <v>7087295</v>
+        <v>7087225</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25173,27 +25173,27 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>128423597</v>
+        <v>128423612</v>
       </c>
       <c r="B245" t="n">
-        <v>57720</v>
+        <v>58093</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -25270,27 +25270,27 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>128423612</v>
+        <v>128423597</v>
       </c>
       <c r="B246" t="n">
-        <v>58093</v>
+        <v>57720</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -25367,32 +25367,32 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>128423591</v>
+        <v>128423621</v>
       </c>
       <c r="B247" t="n">
-        <v>80168</v>
+        <v>82898</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -25402,10 +25402,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>635451</v>
+        <v>634525</v>
       </c>
       <c r="R247" t="n">
-        <v>7087225</v>
+        <v>7087295</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25464,10 +25464,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>128423618</v>
+        <v>128423606</v>
       </c>
       <c r="B248" t="n">
-        <v>91541</v>
+        <v>80140</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -25475,21 +25475,21 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -25499,10 +25499,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>634676</v>
+        <v>635122</v>
       </c>
       <c r="R248" t="n">
-        <v>7087616</v>
+        <v>7087242</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25564,7 +25564,7 @@
         <v>128423575</v>
       </c>
       <c r="B249" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -25658,10 +25658,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>128423606</v>
+        <v>128423618</v>
       </c>
       <c r="B250" t="n">
-        <v>80139</v>
+        <v>91544</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -25669,21 +25669,21 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -25693,10 +25693,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>635122</v>
+        <v>634676</v>
       </c>
       <c r="R250" t="n">
-        <v>7087242</v>
+        <v>7087616</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -25755,10 +25755,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>128423615</v>
+        <v>128423624</v>
       </c>
       <c r="B251" t="n">
-        <v>91537</v>
+        <v>88926</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -25766,21 +25766,21 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>1204</v>
+        <v>510</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -25790,10 +25790,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>634897</v>
+        <v>634461</v>
       </c>
       <c r="R251" t="n">
-        <v>7087591</v>
+        <v>7087363</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -25852,32 +25852,32 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>128423628</v>
+        <v>128423615</v>
       </c>
       <c r="B252" t="n">
-        <v>80174</v>
+        <v>91540</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>6463</v>
+        <v>1204</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -25887,10 +25887,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>635451</v>
+        <v>634897</v>
       </c>
       <c r="R252" t="n">
-        <v>7087225</v>
+        <v>7087591</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -25949,32 +25949,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>128423624</v>
+        <v>128423628</v>
       </c>
       <c r="B253" t="n">
-        <v>88923</v>
+        <v>80175</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>510</v>
+        <v>6463</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -25984,10 +25984,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>634461</v>
+        <v>635451</v>
       </c>
       <c r="R253" t="n">
-        <v>7087363</v>
+        <v>7087225</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26046,10 +26046,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128423617</v>
+        <v>128423622</v>
       </c>
       <c r="B254" t="n">
-        <v>91541</v>
+        <v>88926</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -26057,21 +26057,21 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -26081,10 +26081,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>634507</v>
+        <v>634642</v>
       </c>
       <c r="R254" t="n">
-        <v>7087328</v>
+        <v>7087251</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26143,32 +26143,32 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>128423593</v>
+        <v>128423625</v>
       </c>
       <c r="B255" t="n">
-        <v>80168</v>
+        <v>88926</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>6462</v>
+        <v>510</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -26178,10 +26178,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>635471</v>
+        <v>634494</v>
       </c>
       <c r="R255" t="n">
-        <v>7087281</v>
+        <v>7087408</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26240,10 +26240,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>128423629</v>
+        <v>128423593</v>
       </c>
       <c r="B256" t="n">
-        <v>80174</v>
+        <v>80169</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -26251,21 +26251,21 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -26275,10 +26275,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>635454</v>
+        <v>635471</v>
       </c>
       <c r="R256" t="n">
-        <v>7087257</v>
+        <v>7087281</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26337,32 +26337,32 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128423622</v>
+        <v>128423629</v>
       </c>
       <c r="B257" t="n">
-        <v>88923</v>
+        <v>80175</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>510</v>
+        <v>6463</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -26372,10 +26372,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>634642</v>
+        <v>635454</v>
       </c>
       <c r="R257" t="n">
-        <v>7087251</v>
+        <v>7087257</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -26434,10 +26434,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128423625</v>
+        <v>128423617</v>
       </c>
       <c r="B258" t="n">
-        <v>88923</v>
+        <v>91544</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -26445,21 +26445,21 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -26469,10 +26469,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>634494</v>
+        <v>634507</v>
       </c>
       <c r="R258" t="n">
-        <v>7087408</v>
+        <v>7087328</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -26534,7 +26534,7 @@
         <v>128423626</v>
       </c>
       <c r="B259" t="n">
-        <v>88923</v>
+        <v>88926</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -26628,10 +26628,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>128492197</v>
+        <v>128423585</v>
       </c>
       <c r="B260" t="n">
-        <v>95882</v>
+        <v>92226</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -26639,38 +26639,34 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>2809</v>
+        <v>3298</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
-      <c r="J260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
-      <c r="L260" t="inlineStr"/>
-      <c r="N260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>635110</v>
+        <v>634942</v>
       </c>
       <c r="R260" t="n">
-        <v>7087251</v>
+        <v>7087590</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -26711,7 +26707,6 @@
       <c r="AE260" t="b">
         <v>0</v>
       </c>
-      <c r="AF260" t="inlineStr"/>
       <c r="AG260" t="b">
         <v>0</v>
       </c>
@@ -26730,32 +26725,32 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128423585</v>
+        <v>128423619</v>
       </c>
       <c r="B261" t="n">
-        <v>92223</v>
+        <v>79035</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -26765,10 +26760,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>634942</v>
+        <v>635513</v>
       </c>
       <c r="R261" t="n">
-        <v>7087590</v>
+        <v>7087316</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26803,12 +26798,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD261" t="b">
         <v>0</v>
       </c>
       <c r="AE261" t="b">
         <v>0</v>
       </c>
+      <c r="AF261" t="inlineStr"/>
       <c r="AG261" t="b">
         <v>0</v>
       </c>
@@ -26827,10 +26828,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128423577</v>
+        <v>128423594</v>
       </c>
       <c r="B262" t="n">
-        <v>91488</v>
+        <v>80169</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -26838,21 +26839,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -26862,10 +26863,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>635153</v>
+        <v>634527</v>
       </c>
       <c r="R262" t="n">
-        <v>7087180</v>
+        <v>7087301</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -26924,10 +26925,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>128423616</v>
+        <v>128423620</v>
       </c>
       <c r="B263" t="n">
-        <v>91541</v>
+        <v>79035</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -26935,21 +26936,21 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -26959,10 +26960,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>634993</v>
+        <v>634756</v>
       </c>
       <c r="R263" t="n">
-        <v>7087294</v>
+        <v>7087642</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27021,32 +27022,32 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>128423619</v>
+        <v>128423577</v>
       </c>
       <c r="B264" t="n">
-        <v>79034</v>
+        <v>91491</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -27056,10 +27057,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>635513</v>
+        <v>635153</v>
       </c>
       <c r="R264" t="n">
-        <v>7087316</v>
+        <v>7087180</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27094,18 +27095,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC264" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD264" t="b">
         <v>0</v>
       </c>
       <c r="AE264" t="b">
         <v>0</v>
       </c>
-      <c r="AF264" t="inlineStr"/>
       <c r="AG264" t="b">
         <v>0</v>
       </c>
@@ -27124,32 +27119,32 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>128423594</v>
+        <v>128423616</v>
       </c>
       <c r="B265" t="n">
-        <v>80168</v>
+        <v>91544</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -27159,10 +27154,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>634527</v>
+        <v>634993</v>
       </c>
       <c r="R265" t="n">
-        <v>7087301</v>
+        <v>7087294</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27221,45 +27216,49 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>128423620</v>
+        <v>128492197</v>
       </c>
       <c r="B266" t="n">
-        <v>79034</v>
+        <v>95885</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
+      <c r="J266" t="inlineStr"/>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr"/>
+      <c r="N266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>634756</v>
+        <v>635110</v>
       </c>
       <c r="R266" t="n">
-        <v>7087642</v>
+        <v>7087251</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -27300,6 +27299,7 @@
       <c r="AE266" t="b">
         <v>0</v>
       </c>
+      <c r="AF266" t="inlineStr"/>
       <c r="AG266" t="b">
         <v>0</v>
       </c>
@@ -27318,32 +27318,32 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>128423607</v>
+        <v>128423578</v>
       </c>
       <c r="B267" t="n">
-        <v>80139</v>
+        <v>91491</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -27353,10 +27353,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>635459</v>
+        <v>635327</v>
       </c>
       <c r="R267" t="n">
-        <v>7087231</v>
+        <v>7087158</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -27415,32 +27415,32 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>128423578</v>
+        <v>128423607</v>
       </c>
       <c r="B268" t="n">
-        <v>91488</v>
+        <v>80140</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -27450,10 +27450,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>635327</v>
+        <v>635459</v>
       </c>
       <c r="R268" t="n">
-        <v>7087158</v>
+        <v>7087231</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -27617,7 +27617,7 @@
         <v>128423572</v>
       </c>
       <c r="B270" t="n">
-        <v>96902</v>
+        <v>96905</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -27820,7 +27820,7 @@
         <v>128423614</v>
       </c>
       <c r="B272" t="n">
-        <v>91537</v>
+        <v>91540</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -27917,7 +27917,7 @@
         <v>128423576</v>
       </c>
       <c r="B273" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -28014,7 +28014,7 @@
         <v>128423598</v>
       </c>
       <c r="B274" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -28111,7 +28111,7 @@
         <v>128423599</v>
       </c>
       <c r="B275" t="n">
-        <v>91978</v>
+        <v>91981</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -28208,7 +28208,7 @@
         <v>128423592</v>
       </c>
       <c r="B276" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>128423604</v>
       </c>
       <c r="B277" t="n">
-        <v>95882</v>
+        <v>95885</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -28399,10 +28399,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>128423588</v>
+        <v>128423590</v>
       </c>
       <c r="B278" t="n">
-        <v>57883</v>
+        <v>92811</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -28410,21 +28410,21 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
@@ -28434,10 +28434,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>634560</v>
+        <v>635182</v>
       </c>
       <c r="R278" t="n">
-        <v>7087311</v>
+        <v>7087227</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -28593,10 +28593,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>128423590</v>
+        <v>128423588</v>
       </c>
       <c r="B280" t="n">
-        <v>92808</v>
+        <v>57883</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -28604,21 +28604,21 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>4361</v>
+        <v>103021</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -28628,10 +28628,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>635182</v>
+        <v>634560</v>
       </c>
       <c r="R280" t="n">
-        <v>7087227</v>
+        <v>7087311</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -28690,10 +28690,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>128423580</v>
+        <v>128423579</v>
       </c>
       <c r="B281" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -28725,10 +28725,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>635478</v>
+        <v>635424</v>
       </c>
       <c r="R281" t="n">
-        <v>7087280</v>
+        <v>7087198</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -28787,10 +28787,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>128423579</v>
+        <v>128423580</v>
       </c>
       <c r="B282" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -28822,10 +28822,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>635424</v>
+        <v>635478</v>
       </c>
       <c r="R282" t="n">
-        <v>7087198</v>
+        <v>7087280</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -28887,7 +28887,7 @@
         <v>128423595</v>
       </c>
       <c r="B283" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -28981,32 +28981,32 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>128423574</v>
+        <v>128423601</v>
       </c>
       <c r="B284" t="n">
-        <v>91488</v>
+        <v>91811</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -29016,10 +29016,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>634571</v>
+        <v>634475</v>
       </c>
       <c r="R284" t="n">
-        <v>7087253</v>
+        <v>7087365</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -29078,32 +29078,32 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>128423601</v>
+        <v>128423574</v>
       </c>
       <c r="B285" t="n">
-        <v>91808</v>
+        <v>91491</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -29113,10 +29113,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>634475</v>
+        <v>634571</v>
       </c>
       <c r="R285" t="n">
-        <v>7087365</v>
+        <v>7087253</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -29178,7 +29178,7 @@
         <v>128423613</v>
       </c>
       <c r="B286" t="n">
-        <v>91537</v>
+        <v>91540</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>

--- a/artfynd/A 30047-2025 artfynd.xlsx
+++ b/artfynd/A 30047-2025 artfynd.xlsx
@@ -24882,32 +24882,32 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>128423623</v>
+        <v>128423573</v>
       </c>
       <c r="B242" t="n">
-        <v>88926</v>
+        <v>91491</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -24917,10 +24917,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>634583</v>
+        <v>634599</v>
       </c>
       <c r="R242" t="n">
-        <v>7087261</v>
+        <v>7087225</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24979,32 +24979,32 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>128423573</v>
+        <v>128423623</v>
       </c>
       <c r="B243" t="n">
-        <v>91491</v>
+        <v>88926</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -25014,10 +25014,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>634599</v>
+        <v>634583</v>
       </c>
       <c r="R243" t="n">
-        <v>7087225</v>
+        <v>7087261</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25173,32 +25173,32 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>128423612</v>
+        <v>128423621</v>
       </c>
       <c r="B245" t="n">
-        <v>58093</v>
+        <v>82898</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>103015</v>
+        <v>1312</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -25208,10 +25208,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>634913</v>
+        <v>634525</v>
       </c>
       <c r="R245" t="n">
-        <v>7087585</v>
+        <v>7087295</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25270,27 +25270,27 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>128423597</v>
+        <v>128423612</v>
       </c>
       <c r="B246" t="n">
-        <v>57720</v>
+        <v>58093</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -25367,10 +25367,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>128423621</v>
+        <v>128423597</v>
       </c>
       <c r="B247" t="n">
-        <v>82898</v>
+        <v>57720</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -25378,21 +25378,21 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -25402,10 +25402,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>634525</v>
+        <v>634913</v>
       </c>
       <c r="R247" t="n">
-        <v>7087295</v>
+        <v>7087585</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25755,32 +25755,32 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>128423624</v>
+        <v>128423628</v>
       </c>
       <c r="B251" t="n">
-        <v>88926</v>
+        <v>80175</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>510</v>
+        <v>6463</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -25790,10 +25790,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>634461</v>
+        <v>635451</v>
       </c>
       <c r="R251" t="n">
-        <v>7087363</v>
+        <v>7087225</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -25852,10 +25852,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>128423615</v>
+        <v>128423624</v>
       </c>
       <c r="B252" t="n">
-        <v>91540</v>
+        <v>88926</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -25863,21 +25863,21 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>1204</v>
+        <v>510</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -25887,10 +25887,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>634897</v>
+        <v>634461</v>
       </c>
       <c r="R252" t="n">
-        <v>7087591</v>
+        <v>7087363</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -25949,32 +25949,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>128423628</v>
+        <v>128423615</v>
       </c>
       <c r="B253" t="n">
-        <v>80175</v>
+        <v>91540</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>6463</v>
+        <v>1204</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -25984,10 +25984,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>635451</v>
+        <v>634897</v>
       </c>
       <c r="R253" t="n">
-        <v>7087225</v>
+        <v>7087591</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26046,10 +26046,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128423622</v>
+        <v>128423617</v>
       </c>
       <c r="B254" t="n">
-        <v>88926</v>
+        <v>91544</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -26057,21 +26057,21 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -26081,10 +26081,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>634642</v>
+        <v>634507</v>
       </c>
       <c r="R254" t="n">
-        <v>7087251</v>
+        <v>7087328</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26143,32 +26143,32 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>128423625</v>
+        <v>128423593</v>
       </c>
       <c r="B255" t="n">
-        <v>88926</v>
+        <v>80169</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>510</v>
+        <v>6462</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -26178,10 +26178,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>634494</v>
+        <v>635471</v>
       </c>
       <c r="R255" t="n">
-        <v>7087408</v>
+        <v>7087281</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26240,10 +26240,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>128423593</v>
+        <v>128423629</v>
       </c>
       <c r="B256" t="n">
-        <v>80169</v>
+        <v>80175</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -26251,21 +26251,21 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -26275,10 +26275,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>635471</v>
+        <v>635454</v>
       </c>
       <c r="R256" t="n">
-        <v>7087281</v>
+        <v>7087257</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26337,32 +26337,32 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128423629</v>
+        <v>128423622</v>
       </c>
       <c r="B257" t="n">
-        <v>80175</v>
+        <v>88926</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>6463</v>
+        <v>510</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -26372,10 +26372,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>635454</v>
+        <v>634642</v>
       </c>
       <c r="R257" t="n">
-        <v>7087257</v>
+        <v>7087251</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -26434,10 +26434,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128423617</v>
+        <v>128423625</v>
       </c>
       <c r="B258" t="n">
-        <v>91544</v>
+        <v>88926</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -26445,21 +26445,21 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -26469,10 +26469,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>634507</v>
+        <v>634494</v>
       </c>
       <c r="R258" t="n">
-        <v>7087328</v>
+        <v>7087408</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -26628,32 +26628,32 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>128423585</v>
+        <v>128423619</v>
       </c>
       <c r="B260" t="n">
-        <v>92226</v>
+        <v>79035</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -26663,10 +26663,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>634942</v>
+        <v>635513</v>
       </c>
       <c r="R260" t="n">
-        <v>7087590</v>
+        <v>7087316</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -26701,12 +26701,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC260" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD260" t="b">
         <v>0</v>
       </c>
       <c r="AE260" t="b">
         <v>0</v>
       </c>
+      <c r="AF260" t="inlineStr"/>
       <c r="AG260" t="b">
         <v>0</v>
       </c>
@@ -26725,32 +26731,32 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128423619</v>
+        <v>128423594</v>
       </c>
       <c r="B261" t="n">
-        <v>79035</v>
+        <v>80169</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -26760,10 +26766,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>635513</v>
+        <v>634527</v>
       </c>
       <c r="R261" t="n">
-        <v>7087316</v>
+        <v>7087301</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26798,18 +26804,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC261" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD261" t="b">
         <v>0</v>
       </c>
       <c r="AE261" t="b">
         <v>0</v>
       </c>
-      <c r="AF261" t="inlineStr"/>
       <c r="AG261" t="b">
         <v>0</v>
       </c>
@@ -26828,32 +26828,32 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128423594</v>
+        <v>128423620</v>
       </c>
       <c r="B262" t="n">
-        <v>80169</v>
+        <v>79035</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -26863,10 +26863,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>634527</v>
+        <v>634756</v>
       </c>
       <c r="R262" t="n">
-        <v>7087301</v>
+        <v>7087642</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -26925,32 +26925,32 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>128423620</v>
+        <v>128423577</v>
       </c>
       <c r="B263" t="n">
-        <v>79035</v>
+        <v>91491</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -26960,10 +26960,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>634756</v>
+        <v>635153</v>
       </c>
       <c r="R263" t="n">
-        <v>7087642</v>
+        <v>7087180</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27022,32 +27022,32 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>128423577</v>
+        <v>128423616</v>
       </c>
       <c r="B264" t="n">
-        <v>91491</v>
+        <v>91544</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -27057,10 +27057,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>635153</v>
+        <v>634993</v>
       </c>
       <c r="R264" t="n">
-        <v>7087180</v>
+        <v>7087294</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27119,32 +27119,32 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>128423616</v>
+        <v>128423585</v>
       </c>
       <c r="B265" t="n">
-        <v>91544</v>
+        <v>92226</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -27154,10 +27154,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>634993</v>
+        <v>634942</v>
       </c>
       <c r="R265" t="n">
-        <v>7087294</v>
+        <v>7087590</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27318,32 +27318,32 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>128423578</v>
+        <v>128423607</v>
       </c>
       <c r="B267" t="n">
-        <v>91491</v>
+        <v>80140</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -27353,10 +27353,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>635327</v>
+        <v>635459</v>
       </c>
       <c r="R267" t="n">
-        <v>7087158</v>
+        <v>7087231</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -27415,32 +27415,32 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>128423607</v>
+        <v>128423578</v>
       </c>
       <c r="B268" t="n">
-        <v>80140</v>
+        <v>91491</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -27450,10 +27450,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>635459</v>
+        <v>635327</v>
       </c>
       <c r="R268" t="n">
-        <v>7087231</v>
+        <v>7087158</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -27817,32 +27817,32 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>128423614</v>
+        <v>128423576</v>
       </c>
       <c r="B272" t="n">
-        <v>91540</v>
+        <v>91491</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
@@ -27852,10 +27852,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>634673</v>
+        <v>634705</v>
       </c>
       <c r="R272" t="n">
-        <v>7087631</v>
+        <v>7087668</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -27914,32 +27914,32 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>128423576</v>
+        <v>128423614</v>
       </c>
       <c r="B273" t="n">
-        <v>91491</v>
+        <v>91540</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
@@ -27949,10 +27949,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>634705</v>
+        <v>634673</v>
       </c>
       <c r="R273" t="n">
-        <v>7087668</v>
+        <v>7087631</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -28011,32 +28011,32 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>128423598</v>
+        <v>128423592</v>
       </c>
       <c r="B274" t="n">
-        <v>80141</v>
+        <v>80169</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -28046,10 +28046,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>635632</v>
+        <v>635454</v>
       </c>
       <c r="R274" t="n">
-        <v>7087270</v>
+        <v>7087257</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28108,32 +28108,32 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>128423599</v>
+        <v>128423598</v>
       </c>
       <c r="B275" t="n">
-        <v>91981</v>
+        <v>80141</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>1209</v>
+        <v>2081</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -28143,10 +28143,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>635464</v>
+        <v>635632</v>
       </c>
       <c r="R275" t="n">
-        <v>7087275</v>
+        <v>7087270</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -28205,32 +28205,32 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>128423592</v>
+        <v>128423599</v>
       </c>
       <c r="B276" t="n">
-        <v>80169</v>
+        <v>91981</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>6462</v>
+        <v>1209</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -28240,10 +28240,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>635454</v>
+        <v>635464</v>
       </c>
       <c r="R276" t="n">
-        <v>7087257</v>
+        <v>7087275</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>

--- a/artfynd/A 30047-2025 artfynd.xlsx
+++ b/artfynd/A 30047-2025 artfynd.xlsx
@@ -24882,32 +24882,32 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>128423573</v>
+        <v>128423623</v>
       </c>
       <c r="B242" t="n">
-        <v>91491</v>
+        <v>88926</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -24917,10 +24917,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>634599</v>
+        <v>634583</v>
       </c>
       <c r="R242" t="n">
-        <v>7087225</v>
+        <v>7087261</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24979,32 +24979,32 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>128423623</v>
+        <v>128423573</v>
       </c>
       <c r="B243" t="n">
-        <v>88926</v>
+        <v>91491</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -25014,10 +25014,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>634583</v>
+        <v>634599</v>
       </c>
       <c r="R243" t="n">
-        <v>7087261</v>
+        <v>7087225</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -26046,32 +26046,32 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128423617</v>
+        <v>128423593</v>
       </c>
       <c r="B254" t="n">
-        <v>91544</v>
+        <v>80169</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -26081,10 +26081,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>634507</v>
+        <v>635471</v>
       </c>
       <c r="R254" t="n">
-        <v>7087328</v>
+        <v>7087281</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26143,10 +26143,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>128423593</v>
+        <v>128423629</v>
       </c>
       <c r="B255" t="n">
-        <v>80169</v>
+        <v>80175</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -26154,21 +26154,21 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -26178,10 +26178,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>635471</v>
+        <v>635454</v>
       </c>
       <c r="R255" t="n">
-        <v>7087281</v>
+        <v>7087257</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26240,32 +26240,32 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>128423629</v>
+        <v>128423622</v>
       </c>
       <c r="B256" t="n">
-        <v>80175</v>
+        <v>88926</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>6463</v>
+        <v>510</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -26275,10 +26275,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>635454</v>
+        <v>634642</v>
       </c>
       <c r="R256" t="n">
-        <v>7087257</v>
+        <v>7087251</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26337,7 +26337,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128423622</v>
+        <v>128423625</v>
       </c>
       <c r="B257" t="n">
         <v>88926</v>
@@ -26372,10 +26372,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>634642</v>
+        <v>634494</v>
       </c>
       <c r="R257" t="n">
-        <v>7087251</v>
+        <v>7087408</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -26434,10 +26434,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128423625</v>
+        <v>128423617</v>
       </c>
       <c r="B258" t="n">
-        <v>88926</v>
+        <v>91544</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -26445,21 +26445,21 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -26469,10 +26469,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>634494</v>
+        <v>634507</v>
       </c>
       <c r="R258" t="n">
-        <v>7087408</v>
+        <v>7087328</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -26628,10 +26628,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>128423619</v>
+        <v>128423616</v>
       </c>
       <c r="B260" t="n">
-        <v>79035</v>
+        <v>91544</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -26639,21 +26639,21 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -26663,10 +26663,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>635513</v>
+        <v>634993</v>
       </c>
       <c r="R260" t="n">
-        <v>7087316</v>
+        <v>7087294</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -26701,18 +26701,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC260" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD260" t="b">
         <v>0</v>
       </c>
       <c r="AE260" t="b">
         <v>0</v>
       </c>
-      <c r="AF260" t="inlineStr"/>
       <c r="AG260" t="b">
         <v>0</v>
       </c>
@@ -26731,10 +26725,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128423594</v>
+        <v>128423585</v>
       </c>
       <c r="B261" t="n">
-        <v>80169</v>
+        <v>92226</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -26742,21 +26736,21 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -26766,10 +26760,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>634527</v>
+        <v>634942</v>
       </c>
       <c r="R261" t="n">
-        <v>7087301</v>
+        <v>7087590</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26828,45 +26822,49 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128423620</v>
+        <v>128492197</v>
       </c>
       <c r="B262" t="n">
-        <v>79035</v>
+        <v>95885</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
+      <c r="J262" t="inlineStr"/>
+      <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr"/>
+      <c r="N262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>634756</v>
+        <v>635110</v>
       </c>
       <c r="R262" t="n">
-        <v>7087642</v>
+        <v>7087251</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -26907,6 +26905,7 @@
       <c r="AE262" t="b">
         <v>0</v>
       </c>
+      <c r="AF262" t="inlineStr"/>
       <c r="AG262" t="b">
         <v>0</v>
       </c>
@@ -26925,32 +26924,32 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>128423577</v>
+        <v>128423619</v>
       </c>
       <c r="B263" t="n">
-        <v>91491</v>
+        <v>79035</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -26960,10 +26959,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>635153</v>
+        <v>635513</v>
       </c>
       <c r="R263" t="n">
-        <v>7087180</v>
+        <v>7087316</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -26998,12 +26997,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC263" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD263" t="b">
         <v>0</v>
       </c>
       <c r="AE263" t="b">
         <v>0</v>
       </c>
+      <c r="AF263" t="inlineStr"/>
       <c r="AG263" t="b">
         <v>0</v>
       </c>
@@ -27022,32 +27027,32 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>128423616</v>
+        <v>128423594</v>
       </c>
       <c r="B264" t="n">
-        <v>91544</v>
+        <v>80169</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -27057,10 +27062,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>634993</v>
+        <v>634527</v>
       </c>
       <c r="R264" t="n">
-        <v>7087294</v>
+        <v>7087301</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27119,32 +27124,32 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>128423585</v>
+        <v>128423620</v>
       </c>
       <c r="B265" t="n">
-        <v>92226</v>
+        <v>79035</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -27154,10 +27159,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>634942</v>
+        <v>634756</v>
       </c>
       <c r="R265" t="n">
-        <v>7087590</v>
+        <v>7087642</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27216,10 +27221,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>128492197</v>
+        <v>128423577</v>
       </c>
       <c r="B266" t="n">
-        <v>95885</v>
+        <v>91491</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -27227,38 +27232,34 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>2809</v>
+        <v>5447</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
-      <c r="J266" t="inlineStr"/>
-      <c r="K266" t="inlineStr"/>
-      <c r="L266" t="inlineStr"/>
-      <c r="N266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>635110</v>
+        <v>635153</v>
       </c>
       <c r="R266" t="n">
-        <v>7087251</v>
+        <v>7087180</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -27299,7 +27300,6 @@
       <c r="AE266" t="b">
         <v>0</v>
       </c>
-      <c r="AF266" t="inlineStr"/>
       <c r="AG266" t="b">
         <v>0</v>
       </c>
@@ -28011,32 +28011,32 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>128423592</v>
+        <v>128423598</v>
       </c>
       <c r="B274" t="n">
-        <v>80169</v>
+        <v>80141</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -28046,10 +28046,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>635454</v>
+        <v>635632</v>
       </c>
       <c r="R274" t="n">
-        <v>7087257</v>
+        <v>7087270</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28108,32 +28108,32 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>128423598</v>
+        <v>128423599</v>
       </c>
       <c r="B275" t="n">
-        <v>80141</v>
+        <v>91981</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>2081</v>
+        <v>1209</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -28143,10 +28143,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>635632</v>
+        <v>635464</v>
       </c>
       <c r="R275" t="n">
-        <v>7087270</v>
+        <v>7087275</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -28205,32 +28205,32 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>128423599</v>
+        <v>128423592</v>
       </c>
       <c r="B276" t="n">
-        <v>91981</v>
+        <v>80169</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>1209</v>
+        <v>6462</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -28240,10 +28240,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>635464</v>
+        <v>635454</v>
       </c>
       <c r="R276" t="n">
-        <v>7087275</v>
+        <v>7087257</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>

--- a/artfynd/A 30047-2025 artfynd.xlsx
+++ b/artfynd/A 30047-2025 artfynd.xlsx
@@ -24591,10 +24591,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>128423605</v>
+        <v>128423582</v>
       </c>
       <c r="B239" t="n">
-        <v>80140</v>
+        <v>91808</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -24602,21 +24602,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>6458</v>
+        <v>73</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -24626,10 +24626,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>635331</v>
+        <v>635466</v>
       </c>
       <c r="R239" t="n">
-        <v>7087194</v>
+        <v>7087277</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24688,7 +24688,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>128423608</v>
+        <v>128423605</v>
       </c>
       <c r="B240" t="n">
         <v>80140</v>
@@ -24723,10 +24723,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>635603</v>
+        <v>635331</v>
       </c>
       <c r="R240" t="n">
-        <v>7087226</v>
+        <v>7087194</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24778,17 +24778,17 @@
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>128423582</v>
+        <v>128423608</v>
       </c>
       <c r="B241" t="n">
-        <v>91808</v>
+        <v>80140</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24796,21 +24796,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>73</v>
+        <v>6458</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -24820,10 +24820,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>635466</v>
+        <v>635603</v>
       </c>
       <c r="R241" t="n">
-        <v>7087277</v>
+        <v>7087226</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -24875,7 +24875,7 @@
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
@@ -24972,7 +24972,7 @@
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
@@ -25069,39 +25069,39 @@
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>128423591</v>
+        <v>128423621</v>
       </c>
       <c r="B244" t="n">
-        <v>80169</v>
+        <v>82898</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -25111,10 +25111,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>635451</v>
+        <v>634525</v>
       </c>
       <c r="R244" t="n">
-        <v>7087225</v>
+        <v>7087295</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25166,39 +25166,39 @@
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>128423621</v>
+        <v>128423591</v>
       </c>
       <c r="B245" t="n">
-        <v>82898</v>
+        <v>80169</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -25208,10 +25208,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>634525</v>
+        <v>635451</v>
       </c>
       <c r="R245" t="n">
-        <v>7087295</v>
+        <v>7087225</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25263,34 +25263,34 @@
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>128423612</v>
+        <v>128423597</v>
       </c>
       <c r="B246" t="n">
-        <v>58093</v>
+        <v>57720</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -25360,34 +25360,34 @@
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>128423597</v>
+        <v>128423612</v>
       </c>
       <c r="B247" t="n">
-        <v>57720</v>
+        <v>58093</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -25457,7 +25457,7 @@
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
@@ -25554,39 +25554,39 @@
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>128423575</v>
+        <v>128423618</v>
       </c>
       <c r="B249" t="n">
-        <v>91491</v>
+        <v>91544</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -25596,10 +25596,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>634574</v>
+        <v>634676</v>
       </c>
       <c r="R249" t="n">
-        <v>7087286</v>
+        <v>7087616</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25651,39 +25651,39 @@
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>128423618</v>
+        <v>128423575</v>
       </c>
       <c r="B250" t="n">
-        <v>91544</v>
+        <v>91491</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -25693,10 +25693,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>634676</v>
+        <v>634574</v>
       </c>
       <c r="R250" t="n">
-        <v>7087616</v>
+        <v>7087286</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -25748,7 +25748,7 @@
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
@@ -25845,7 +25845,7 @@
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
@@ -25942,7 +25942,7 @@
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
@@ -26039,39 +26039,39 @@
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128423593</v>
+        <v>128423622</v>
       </c>
       <c r="B254" t="n">
-        <v>80169</v>
+        <v>88926</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>6462</v>
+        <v>510</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -26081,10 +26081,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>635471</v>
+        <v>634642</v>
       </c>
       <c r="R254" t="n">
-        <v>7087281</v>
+        <v>7087251</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26136,17 +26136,17 @@
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>128423629</v>
+        <v>128423593</v>
       </c>
       <c r="B255" t="n">
-        <v>80175</v>
+        <v>80169</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -26154,21 +26154,21 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -26178,10 +26178,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>635454</v>
+        <v>635471</v>
       </c>
       <c r="R255" t="n">
-        <v>7087257</v>
+        <v>7087281</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26233,39 +26233,39 @@
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>128423622</v>
+        <v>128423629</v>
       </c>
       <c r="B256" t="n">
-        <v>88926</v>
+        <v>80175</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>510</v>
+        <v>6463</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -26275,10 +26275,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>634642</v>
+        <v>635454</v>
       </c>
       <c r="R256" t="n">
-        <v>7087251</v>
+        <v>7087257</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26330,17 +26330,17 @@
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128423625</v>
+        <v>128423617</v>
       </c>
       <c r="B257" t="n">
-        <v>88926</v>
+        <v>91544</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -26348,21 +26348,21 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -26372,10 +26372,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>634494</v>
+        <v>634507</v>
       </c>
       <c r="R257" t="n">
-        <v>7087408</v>
+        <v>7087328</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -26427,17 +26427,17 @@
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128423617</v>
+        <v>128423625</v>
       </c>
       <c r="B258" t="n">
-        <v>91544</v>
+        <v>88926</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -26445,21 +26445,21 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -26469,10 +26469,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>634507</v>
+        <v>634494</v>
       </c>
       <c r="R258" t="n">
-        <v>7087328</v>
+        <v>7087408</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -26524,7 +26524,7 @@
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
@@ -26621,52 +26621,56 @@
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>128423616</v>
+        <v>128492197</v>
       </c>
       <c r="B260" t="n">
-        <v>91544</v>
+        <v>95885</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
+      <c r="J260" t="inlineStr"/>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr"/>
+      <c r="N260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>634993</v>
+        <v>635110</v>
       </c>
       <c r="R260" t="n">
-        <v>7087294</v>
+        <v>7087251</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -26707,6 +26711,7 @@
       <c r="AE260" t="b">
         <v>0</v>
       </c>
+      <c r="AF260" t="inlineStr"/>
       <c r="AG260" t="b">
         <v>0</v>
       </c>
@@ -26822,49 +26827,45 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128492197</v>
+        <v>128423619</v>
       </c>
       <c r="B262" t="n">
-        <v>95885</v>
+        <v>79035</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
-      <c r="J262" t="inlineStr"/>
-      <c r="K262" t="inlineStr"/>
-      <c r="L262" t="inlineStr"/>
-      <c r="N262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>635110</v>
+        <v>635513</v>
       </c>
       <c r="R262" t="n">
-        <v>7087251</v>
+        <v>7087316</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -26899,6 +26900,11 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC262" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD262" t="b">
         <v>0</v>
       </c>
@@ -26917,39 +26923,39 @@
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>128423619</v>
+        <v>128423594</v>
       </c>
       <c r="B263" t="n">
-        <v>79035</v>
+        <v>80169</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -26959,10 +26965,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>635513</v>
+        <v>634527</v>
       </c>
       <c r="R263" t="n">
-        <v>7087316</v>
+        <v>7087301</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -26997,18 +27003,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC263" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD263" t="b">
         <v>0</v>
       </c>
       <c r="AE263" t="b">
         <v>0</v>
       </c>
-      <c r="AF263" t="inlineStr"/>
       <c r="AG263" t="b">
         <v>0</v>
       </c>
@@ -27020,39 +27020,39 @@
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>128423594</v>
+        <v>128423620</v>
       </c>
       <c r="B264" t="n">
-        <v>80169</v>
+        <v>79035</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -27062,10 +27062,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>634527</v>
+        <v>634756</v>
       </c>
       <c r="R264" t="n">
-        <v>7087301</v>
+        <v>7087642</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27117,39 +27117,39 @@
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>128423620</v>
+        <v>128423577</v>
       </c>
       <c r="B265" t="n">
-        <v>79035</v>
+        <v>91491</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -27159,10 +27159,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>634756</v>
+        <v>635153</v>
       </c>
       <c r="R265" t="n">
-        <v>7087642</v>
+        <v>7087180</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27214,39 +27214,39 @@
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>128423577</v>
+        <v>128423616</v>
       </c>
       <c r="B266" t="n">
-        <v>91491</v>
+        <v>91544</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
@@ -27256,10 +27256,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>635153</v>
+        <v>634993</v>
       </c>
       <c r="R266" t="n">
-        <v>7087180</v>
+        <v>7087294</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -27311,7 +27311,7 @@
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
@@ -27408,39 +27408,39 @@
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>128423578</v>
+        <v>128423602</v>
       </c>
       <c r="B268" t="n">
-        <v>91491</v>
+        <v>57723</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -27450,7 +27450,7 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>635327</v>
+        <v>635210</v>
       </c>
       <c r="R268" t="n">
         <v>7087158</v>
@@ -27488,6 +27488,11 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC268" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD268" t="b">
         <v>0</v>
       </c>
@@ -27505,39 +27510,39 @@
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>128423602</v>
+        <v>128423578</v>
       </c>
       <c r="B269" t="n">
-        <v>57723</v>
+        <v>91491</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -27547,7 +27552,7 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>635210</v>
+        <v>635327</v>
       </c>
       <c r="R269" t="n">
         <v>7087158</v>
@@ -27585,11 +27590,6 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC269" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD269" t="b">
         <v>0</v>
       </c>
@@ -27607,7 +27607,7 @@
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
@@ -27704,17 +27704,17 @@
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>128423603</v>
+        <v>128423614</v>
       </c>
       <c r="B271" t="n">
-        <v>57723</v>
+        <v>91540</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -27722,38 +27722,34 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
-      <c r="K271" t="inlineStr"/>
-      <c r="L271" t="inlineStr"/>
-      <c r="M271" t="inlineStr"/>
-      <c r="N271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>635240</v>
+        <v>634673</v>
       </c>
       <c r="R271" t="n">
-        <v>7087224</v>
+        <v>7087631</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -27788,11 +27784,6 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC271" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD271" t="b">
         <v>0</v>
       </c>
@@ -27810,7 +27801,7 @@
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
@@ -27907,17 +27898,17 @@
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>128423614</v>
+        <v>128423603</v>
       </c>
       <c r="B273" t="n">
-        <v>91540</v>
+        <v>57723</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -27925,34 +27916,38 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr"/>
+      <c r="N273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>634673</v>
+        <v>635240</v>
       </c>
       <c r="R273" t="n">
-        <v>7087631</v>
+        <v>7087224</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -27987,6 +27982,11 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD273" t="b">
         <v>0</v>
       </c>
@@ -28004,39 +28004,39 @@
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>128423598</v>
+        <v>128423599</v>
       </c>
       <c r="B274" t="n">
-        <v>80141</v>
+        <v>91981</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>2081</v>
+        <v>1209</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -28046,10 +28046,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>635632</v>
+        <v>635464</v>
       </c>
       <c r="R274" t="n">
-        <v>7087270</v>
+        <v>7087275</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28101,39 +28101,39 @@
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>128423599</v>
+        <v>128423598</v>
       </c>
       <c r="B275" t="n">
-        <v>91981</v>
+        <v>80141</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>1209</v>
+        <v>2081</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -28143,10 +28143,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>635464</v>
+        <v>635632</v>
       </c>
       <c r="R275" t="n">
-        <v>7087275</v>
+        <v>7087270</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -28198,7 +28198,7 @@
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
@@ -28295,7 +28295,7 @@
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
@@ -28392,7 +28392,7 @@
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
@@ -28489,7 +28489,7 @@
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
@@ -28586,7 +28586,7 @@
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
@@ -28690,7 +28690,7 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>128423579</v>
+        <v>128423580</v>
       </c>
       <c r="B281" t="n">
         <v>91491</v>
@@ -28725,10 +28725,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>635424</v>
+        <v>635478</v>
       </c>
       <c r="R281" t="n">
-        <v>7087198</v>
+        <v>7087280</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -28787,7 +28787,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>128423580</v>
+        <v>128423579</v>
       </c>
       <c r="B282" t="n">
         <v>91491</v>
@@ -28822,10 +28822,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>635478</v>
+        <v>635424</v>
       </c>
       <c r="R282" t="n">
-        <v>7087280</v>
+        <v>7087198</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -28877,7 +28877,7 @@
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
@@ -28974,7 +28974,7 @@
       </c>
       <c r="AX283" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
@@ -29071,7 +29071,7 @@
       </c>
       <c r="AX284" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
@@ -29168,7 +29168,7 @@
       </c>
       <c r="AX285" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
@@ -29265,7 +29265,7 @@
       </c>
       <c r="AX286" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>

--- a/artfynd/A 30047-2025 artfynd.xlsx
+++ b/artfynd/A 30047-2025 artfynd.xlsx
@@ -24400,7 +24400,7 @@
         <v>128651017</v>
       </c>
       <c r="B237" t="n">
-        <v>97000</v>
+        <v>97010</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>128651018</v>
       </c>
       <c r="B238" t="n">
-        <v>95897</v>
+        <v>95907</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24591,10 +24591,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>128423582</v>
+        <v>128423605</v>
       </c>
       <c r="B239" t="n">
-        <v>91808</v>
+        <v>80144</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -24602,21 +24602,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>73</v>
+        <v>6458</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -24626,10 +24626,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>635466</v>
+        <v>635331</v>
       </c>
       <c r="R239" t="n">
-        <v>7087277</v>
+        <v>7087194</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24688,10 +24688,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>128423605</v>
+        <v>128423608</v>
       </c>
       <c r="B240" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -24723,10 +24723,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>635331</v>
+        <v>635603</v>
       </c>
       <c r="R240" t="n">
-        <v>7087194</v>
+        <v>7087226</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24778,17 +24778,17 @@
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>128423608</v>
+        <v>128423582</v>
       </c>
       <c r="B241" t="n">
-        <v>80140</v>
+        <v>91815</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24796,21 +24796,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6458</v>
+        <v>73</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -24820,10 +24820,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>635603</v>
+        <v>635466</v>
       </c>
       <c r="R241" t="n">
-        <v>7087226</v>
+        <v>7087277</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -24875,39 +24875,39 @@
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>128423623</v>
+        <v>128423573</v>
       </c>
       <c r="B242" t="n">
-        <v>88926</v>
+        <v>91497</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -24917,10 +24917,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>634583</v>
+        <v>634599</v>
       </c>
       <c r="R242" t="n">
-        <v>7087261</v>
+        <v>7087225</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24972,39 +24972,39 @@
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>128423573</v>
+        <v>128423623</v>
       </c>
       <c r="B243" t="n">
-        <v>91491</v>
+        <v>88930</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -25014,10 +25014,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>634599</v>
+        <v>634583</v>
       </c>
       <c r="R243" t="n">
-        <v>7087225</v>
+        <v>7087261</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25069,7 +25069,7 @@
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
@@ -25079,7 +25079,7 @@
         <v>128423621</v>
       </c>
       <c r="B244" t="n">
-        <v>82898</v>
+        <v>82902</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
@@ -25176,7 +25176,7 @@
         <v>128423591</v>
       </c>
       <c r="B245" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -25263,7 +25263,7 @@
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
@@ -25273,7 +25273,7 @@
         <v>128423597</v>
       </c>
       <c r="B246" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
@@ -25370,7 +25370,7 @@
         <v>128423612</v>
       </c>
       <c r="B247" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -25457,17 +25457,17 @@
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>128423606</v>
+        <v>128423618</v>
       </c>
       <c r="B248" t="n">
-        <v>80140</v>
+        <v>91551</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -25475,21 +25475,21 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -25499,10 +25499,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>635122</v>
+        <v>634676</v>
       </c>
       <c r="R248" t="n">
-        <v>7087242</v>
+        <v>7087616</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25554,39 +25554,39 @@
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>128423618</v>
+        <v>128423575</v>
       </c>
       <c r="B249" t="n">
-        <v>91544</v>
+        <v>91497</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -25596,10 +25596,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>634676</v>
+        <v>634574</v>
       </c>
       <c r="R249" t="n">
-        <v>7087616</v>
+        <v>7087286</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25651,39 +25651,39 @@
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>128423575</v>
+        <v>128423606</v>
       </c>
       <c r="B250" t="n">
-        <v>91491</v>
+        <v>80144</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -25693,10 +25693,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>634574</v>
+        <v>635122</v>
       </c>
       <c r="R250" t="n">
-        <v>7087286</v>
+        <v>7087242</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -25748,7 +25748,7 @@
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
@@ -25758,7 +25758,7 @@
         <v>128423628</v>
       </c>
       <c r="B251" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
@@ -25855,7 +25855,7 @@
         <v>128423624</v>
       </c>
       <c r="B252" t="n">
-        <v>88926</v>
+        <v>88930</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
@@ -25952,7 +25952,7 @@
         <v>128423615</v>
       </c>
       <c r="B253" t="n">
-        <v>91540</v>
+        <v>91547</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -26039,17 +26039,17 @@
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128423622</v>
+        <v>128423617</v>
       </c>
       <c r="B254" t="n">
-        <v>88926</v>
+        <v>91551</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -26057,21 +26057,21 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -26081,10 +26081,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>634642</v>
+        <v>634507</v>
       </c>
       <c r="R254" t="n">
-        <v>7087251</v>
+        <v>7087328</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26136,7 +26136,7 @@
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
@@ -26146,7 +26146,7 @@
         <v>128423593</v>
       </c>
       <c r="B255" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -26233,7 +26233,7 @@
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
@@ -26243,7 +26243,7 @@
         <v>128423629</v>
       </c>
       <c r="B256" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -26330,17 +26330,17 @@
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128423617</v>
+        <v>128423622</v>
       </c>
       <c r="B257" t="n">
-        <v>91544</v>
+        <v>88930</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -26348,21 +26348,21 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -26372,10 +26372,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>634507</v>
+        <v>634642</v>
       </c>
       <c r="R257" t="n">
-        <v>7087328</v>
+        <v>7087251</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -26427,7 +26427,7 @@
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
@@ -26437,7 +26437,7 @@
         <v>128423625</v>
       </c>
       <c r="B258" t="n">
-        <v>88926</v>
+        <v>88930</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
@@ -26534,7 +26534,7 @@
         <v>128423626</v>
       </c>
       <c r="B259" t="n">
-        <v>88926</v>
+        <v>88930</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
@@ -26631,7 +26631,7 @@
         <v>128492197</v>
       </c>
       <c r="B260" t="n">
-        <v>95885</v>
+        <v>95895</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -26730,10 +26730,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128423585</v>
+        <v>128423577</v>
       </c>
       <c r="B261" t="n">
-        <v>92226</v>
+        <v>91497</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -26741,21 +26741,21 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -26765,10 +26765,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>634942</v>
+        <v>635153</v>
       </c>
       <c r="R261" t="n">
-        <v>7087590</v>
+        <v>7087180</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26827,10 +26827,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128423619</v>
+        <v>128423616</v>
       </c>
       <c r="B262" t="n">
-        <v>79035</v>
+        <v>91551</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -26838,21 +26838,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -26862,10 +26862,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>635513</v>
+        <v>634993</v>
       </c>
       <c r="R262" t="n">
-        <v>7087316</v>
+        <v>7087294</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -26900,18 +26900,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC262" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD262" t="b">
         <v>0</v>
       </c>
       <c r="AE262" t="b">
         <v>0</v>
       </c>
-      <c r="AF262" t="inlineStr"/>
       <c r="AG262" t="b">
         <v>0</v>
       </c>
@@ -26923,17 +26917,17 @@
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>128423594</v>
+        <v>128423585</v>
       </c>
       <c r="B263" t="n">
-        <v>80169</v>
+        <v>92233</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -26941,21 +26935,21 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -26965,10 +26959,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>634527</v>
+        <v>634942</v>
       </c>
       <c r="R263" t="n">
-        <v>7087301</v>
+        <v>7087590</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27020,17 +27014,17 @@
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>128423620</v>
+        <v>128423619</v>
       </c>
       <c r="B264" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -27062,10 +27056,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>634756</v>
+        <v>635513</v>
       </c>
       <c r="R264" t="n">
-        <v>7087642</v>
+        <v>7087316</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27100,12 +27094,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD264" t="b">
         <v>0</v>
       </c>
       <c r="AE264" t="b">
         <v>0</v>
       </c>
+      <c r="AF264" t="inlineStr"/>
       <c r="AG264" t="b">
         <v>0</v>
       </c>
@@ -27117,17 +27117,17 @@
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>128423577</v>
+        <v>128423594</v>
       </c>
       <c r="B265" t="n">
-        <v>91491</v>
+        <v>80173</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -27135,21 +27135,21 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -27159,10 +27159,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>635153</v>
+        <v>634527</v>
       </c>
       <c r="R265" t="n">
-        <v>7087180</v>
+        <v>7087301</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27214,17 +27214,17 @@
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>128423616</v>
+        <v>128423620</v>
       </c>
       <c r="B266" t="n">
-        <v>91544</v>
+        <v>79039</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -27232,21 +27232,21 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
@@ -27256,10 +27256,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>634993</v>
+        <v>634756</v>
       </c>
       <c r="R266" t="n">
-        <v>7087294</v>
+        <v>7087642</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -27311,17 +27311,17 @@
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>128423607</v>
+        <v>128423602</v>
       </c>
       <c r="B267" t="n">
-        <v>80140</v>
+        <v>57725</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -27329,21 +27329,21 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -27353,10 +27353,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>635459</v>
+        <v>635210</v>
       </c>
       <c r="R267" t="n">
-        <v>7087231</v>
+        <v>7087158</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -27391,6 +27391,11 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC267" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD267" t="b">
         <v>0</v>
       </c>
@@ -27408,39 +27413,39 @@
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>128423602</v>
+        <v>128423578</v>
       </c>
       <c r="B268" t="n">
-        <v>57723</v>
+        <v>91497</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -27450,7 +27455,7 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>635210</v>
+        <v>635327</v>
       </c>
       <c r="R268" t="n">
         <v>7087158</v>
@@ -27488,11 +27493,6 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC268" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD268" t="b">
         <v>0</v>
       </c>
@@ -27510,39 +27510,39 @@
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>128423578</v>
+        <v>128423607</v>
       </c>
       <c r="B269" t="n">
-        <v>91491</v>
+        <v>80144</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -27552,10 +27552,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>635327</v>
+        <v>635459</v>
       </c>
       <c r="R269" t="n">
-        <v>7087158</v>
+        <v>7087231</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -27607,7 +27607,7 @@
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
@@ -27617,7 +27617,7 @@
         <v>128423572</v>
       </c>
       <c r="B270" t="n">
-        <v>96905</v>
+        <v>96915</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -27704,7 +27704,7 @@
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
@@ -27714,7 +27714,7 @@
         <v>128423614</v>
       </c>
       <c r="B271" t="n">
-        <v>91540</v>
+        <v>91547</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -27801,52 +27801,56 @@
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>128423576</v>
+        <v>128423603</v>
       </c>
       <c r="B272" t="n">
-        <v>91491</v>
+        <v>57725</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="inlineStr"/>
+      <c r="N272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>634705</v>
+        <v>635240</v>
       </c>
       <c r="R272" t="n">
-        <v>7087668</v>
+        <v>7087224</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -27881,6 +27885,11 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC272" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD272" t="b">
         <v>0</v>
       </c>
@@ -27898,56 +27907,52 @@
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>128423603</v>
+        <v>128423576</v>
       </c>
       <c r="B273" t="n">
-        <v>57723</v>
+        <v>91497</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="inlineStr"/>
-      <c r="N273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>635240</v>
+        <v>634705</v>
       </c>
       <c r="R273" t="n">
-        <v>7087224</v>
+        <v>7087668</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -27982,11 +27987,6 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC273" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD273" t="b">
         <v>0</v>
       </c>
@@ -28004,7 +28004,7 @@
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
@@ -28014,7 +28014,7 @@
         <v>128423599</v>
       </c>
       <c r="B274" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -28101,7 +28101,7 @@
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
@@ -28111,7 +28111,7 @@
         <v>128423598</v>
       </c>
       <c r="B275" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -28198,7 +28198,7 @@
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
@@ -28208,7 +28208,7 @@
         <v>128423592</v>
       </c>
       <c r="B276" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -28295,7 +28295,7 @@
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
@@ -28305,7 +28305,7 @@
         <v>128423604</v>
       </c>
       <c r="B277" t="n">
-        <v>95885</v>
+        <v>95895</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -28392,7 +28392,7 @@
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
@@ -28402,7 +28402,7 @@
         <v>128423590</v>
       </c>
       <c r="B278" t="n">
-        <v>92811</v>
+        <v>92818</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
@@ -28499,7 +28499,7 @@
         <v>128423596</v>
       </c>
       <c r="B279" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -28586,7 +28586,7 @@
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
@@ -28596,7 +28596,7 @@
         <v>128423588</v>
       </c>
       <c r="B280" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>128423580</v>
       </c>
       <c r="B281" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>128423579</v>
       </c>
       <c r="B282" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -28877,7 +28877,7 @@
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
@@ -28887,7 +28887,7 @@
         <v>128423595</v>
       </c>
       <c r="B283" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -28974,39 +28974,39 @@
       </c>
       <c r="AX283" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>128423601</v>
+        <v>128423574</v>
       </c>
       <c r="B284" t="n">
-        <v>91811</v>
+        <v>91497</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -29016,10 +29016,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>634475</v>
+        <v>634571</v>
       </c>
       <c r="R284" t="n">
-        <v>7087365</v>
+        <v>7087253</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -29071,39 +29071,39 @@
       </c>
       <c r="AX284" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>128423574</v>
+        <v>128423601</v>
       </c>
       <c r="B285" t="n">
-        <v>91491</v>
+        <v>91818</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -29113,10 +29113,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>634571</v>
+        <v>634475</v>
       </c>
       <c r="R285" t="n">
-        <v>7087253</v>
+        <v>7087365</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -29168,7 +29168,7 @@
       </c>
       <c r="AX285" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
@@ -29178,7 +29178,7 @@
         <v>128423613</v>
       </c>
       <c r="B286" t="n">
-        <v>91540</v>
+        <v>91547</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -29265,7 +29265,7 @@
       </c>
       <c r="AX286" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Isac Enetjärn, Amanda Portström, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>

--- a/artfynd/A 30047-2025 artfynd.xlsx
+++ b/artfynd/A 30047-2025 artfynd.xlsx
@@ -26628,10 +26628,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>128492197</v>
+        <v>128423577</v>
       </c>
       <c r="B260" t="n">
-        <v>95895</v>
+        <v>91497</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -26639,38 +26639,34 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>2809</v>
+        <v>5447</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
-      <c r="J260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
-      <c r="L260" t="inlineStr"/>
-      <c r="N260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>635110</v>
+        <v>635153</v>
       </c>
       <c r="R260" t="n">
-        <v>7087251</v>
+        <v>7087180</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -26711,7 +26707,6 @@
       <c r="AE260" t="b">
         <v>0</v>
       </c>
-      <c r="AF260" t="inlineStr"/>
       <c r="AG260" t="b">
         <v>0</v>
       </c>
@@ -26730,32 +26725,32 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128423577</v>
+        <v>128423616</v>
       </c>
       <c r="B261" t="n">
-        <v>91497</v>
+        <v>91551</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -26765,10 +26760,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>635153</v>
+        <v>634993</v>
       </c>
       <c r="R261" t="n">
-        <v>7087180</v>
+        <v>7087294</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26827,10 +26822,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128423616</v>
+        <v>128423619</v>
       </c>
       <c r="B262" t="n">
-        <v>91551</v>
+        <v>79039</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -26838,21 +26833,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -26862,10 +26857,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>634993</v>
+        <v>635513</v>
       </c>
       <c r="R262" t="n">
-        <v>7087294</v>
+        <v>7087316</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -26900,12 +26895,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC262" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD262" t="b">
         <v>0</v>
       </c>
       <c r="AE262" t="b">
         <v>0</v>
       </c>
+      <c r="AF262" t="inlineStr"/>
       <c r="AG262" t="b">
         <v>0</v>
       </c>
@@ -26924,10 +26925,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>128423585</v>
+        <v>128423594</v>
       </c>
       <c r="B263" t="n">
-        <v>92233</v>
+        <v>80173</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -26935,21 +26936,21 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -26959,10 +26960,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>634942</v>
+        <v>634527</v>
       </c>
       <c r="R263" t="n">
-        <v>7087590</v>
+        <v>7087301</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27021,7 +27022,7 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>128423619</v>
+        <v>128423620</v>
       </c>
       <c r="B264" t="n">
         <v>79039</v>
@@ -27056,10 +27057,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>635513</v>
+        <v>634756</v>
       </c>
       <c r="R264" t="n">
-        <v>7087316</v>
+        <v>7087642</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27094,18 +27095,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC264" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD264" t="b">
         <v>0</v>
       </c>
       <c r="AE264" t="b">
         <v>0</v>
       </c>
-      <c r="AF264" t="inlineStr"/>
       <c r="AG264" t="b">
         <v>0</v>
       </c>
@@ -27124,10 +27119,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>128423594</v>
+        <v>128492197</v>
       </c>
       <c r="B265" t="n">
-        <v>80173</v>
+        <v>95895</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -27135,34 +27130,38 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>6462</v>
+        <v>2809</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
+      <c r="J265" t="inlineStr"/>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
+      <c r="N265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>634527</v>
+        <v>635110</v>
       </c>
       <c r="R265" t="n">
-        <v>7087301</v>
+        <v>7087251</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27203,6 +27202,7 @@
       <c r="AE265" t="b">
         <v>0</v>
       </c>
+      <c r="AF265" t="inlineStr"/>
       <c r="AG265" t="b">
         <v>0</v>
       </c>
@@ -27221,32 +27221,32 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>128423620</v>
+        <v>128423585</v>
       </c>
       <c r="B266" t="n">
-        <v>79039</v>
+        <v>92233</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
@@ -27256,10 +27256,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>634756</v>
+        <v>634942</v>
       </c>
       <c r="R266" t="n">
-        <v>7087642</v>
+        <v>7087590</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -27318,32 +27318,32 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>128423602</v>
+        <v>128423578</v>
       </c>
       <c r="B267" t="n">
-        <v>57725</v>
+        <v>91497</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -27353,7 +27353,7 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>635210</v>
+        <v>635327</v>
       </c>
       <c r="R267" t="n">
         <v>7087158</v>
@@ -27389,11 +27389,6 @@
       <c r="AA267" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC267" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -27420,32 +27415,32 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>128423578</v>
+        <v>128423607</v>
       </c>
       <c r="B268" t="n">
-        <v>91497</v>
+        <v>80144</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -27455,10 +27450,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>635327</v>
+        <v>635459</v>
       </c>
       <c r="R268" t="n">
-        <v>7087158</v>
+        <v>7087231</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -27517,10 +27512,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>128423607</v>
+        <v>128423602</v>
       </c>
       <c r="B269" t="n">
-        <v>80144</v>
+        <v>57725</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -27528,21 +27523,21 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -27552,10 +27547,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>635459</v>
+        <v>635210</v>
       </c>
       <c r="R269" t="n">
-        <v>7087231</v>
+        <v>7087158</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -27588,6 +27583,11 @@
       <c r="AA269" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD269" t="b">

--- a/artfynd/A 30047-2025 artfynd.xlsx
+++ b/artfynd/A 30047-2025 artfynd.xlsx
@@ -24400,7 +24400,7 @@
         <v>128651017</v>
       </c>
       <c r="B237" t="n">
-        <v>97010</v>
+        <v>97017</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>128651018</v>
       </c>
       <c r="B238" t="n">
-        <v>95907</v>
+        <v>95914</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24591,10 +24591,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>128423605</v>
+        <v>128423582</v>
       </c>
       <c r="B239" t="n">
-        <v>80144</v>
+        <v>91822</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -24602,21 +24602,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>6458</v>
+        <v>73</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -24626,10 +24626,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>635331</v>
+        <v>635466</v>
       </c>
       <c r="R239" t="n">
-        <v>7087194</v>
+        <v>7087277</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24688,7 +24688,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>128423608</v>
+        <v>128423605</v>
       </c>
       <c r="B240" t="n">
         <v>80144</v>
@@ -24723,10 +24723,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>635603</v>
+        <v>635331</v>
       </c>
       <c r="R240" t="n">
-        <v>7087226</v>
+        <v>7087194</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24785,10 +24785,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>128423582</v>
+        <v>128423608</v>
       </c>
       <c r="B241" t="n">
-        <v>91815</v>
+        <v>80144</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24796,21 +24796,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>73</v>
+        <v>6458</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -24820,10 +24820,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>635466</v>
+        <v>635603</v>
       </c>
       <c r="R241" t="n">
-        <v>7087277</v>
+        <v>7087226</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -24885,7 +24885,7 @@
         <v>128423573</v>
       </c>
       <c r="B242" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>128423623</v>
       </c>
       <c r="B243" t="n">
-        <v>88930</v>
+        <v>88937</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -25076,32 +25076,32 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>128423621</v>
+        <v>128423591</v>
       </c>
       <c r="B244" t="n">
-        <v>82902</v>
+        <v>80173</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -25111,10 +25111,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>634525</v>
+        <v>635451</v>
       </c>
       <c r="R244" t="n">
-        <v>7087295</v>
+        <v>7087225</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25173,32 +25173,32 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>128423591</v>
+        <v>128423597</v>
       </c>
       <c r="B245" t="n">
-        <v>80173</v>
+        <v>57722</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -25208,10 +25208,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>635451</v>
+        <v>634913</v>
       </c>
       <c r="R245" t="n">
-        <v>7087225</v>
+        <v>7087585</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25270,10 +25270,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>128423597</v>
+        <v>128423621</v>
       </c>
       <c r="B246" t="n">
-        <v>57722</v>
+        <v>82871</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -25281,21 +25281,21 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -25305,10 +25305,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>634913</v>
+        <v>634525</v>
       </c>
       <c r="R246" t="n">
-        <v>7087585</v>
+        <v>7087295</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25464,10 +25464,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>128423618</v>
+        <v>128423606</v>
       </c>
       <c r="B248" t="n">
-        <v>91551</v>
+        <v>80144</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -25475,21 +25475,21 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -25499,10 +25499,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>634676</v>
+        <v>635122</v>
       </c>
       <c r="R248" t="n">
-        <v>7087616</v>
+        <v>7087242</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25561,32 +25561,32 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>128423575</v>
+        <v>128423618</v>
       </c>
       <c r="B249" t="n">
-        <v>91497</v>
+        <v>91558</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -25596,10 +25596,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>634574</v>
+        <v>634676</v>
       </c>
       <c r="R249" t="n">
-        <v>7087286</v>
+        <v>7087616</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25658,32 +25658,32 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>128423606</v>
+        <v>128423575</v>
       </c>
       <c r="B250" t="n">
-        <v>80144</v>
+        <v>91504</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -25693,10 +25693,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>635122</v>
+        <v>634574</v>
       </c>
       <c r="R250" t="n">
-        <v>7087242</v>
+        <v>7087286</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -25755,32 +25755,32 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>128423628</v>
+        <v>128423615</v>
       </c>
       <c r="B251" t="n">
-        <v>80179</v>
+        <v>91554</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>6463</v>
+        <v>1204</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -25790,10 +25790,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>635451</v>
+        <v>634897</v>
       </c>
       <c r="R251" t="n">
-        <v>7087225</v>
+        <v>7087591</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -25855,7 +25855,7 @@
         <v>128423624</v>
       </c>
       <c r="B252" t="n">
-        <v>88930</v>
+        <v>88937</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -25949,32 +25949,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>128423615</v>
+        <v>128423628</v>
       </c>
       <c r="B253" t="n">
-        <v>91547</v>
+        <v>80179</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>1204</v>
+        <v>6463</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -25984,10 +25984,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>634897</v>
+        <v>635451</v>
       </c>
       <c r="R253" t="n">
-        <v>7087591</v>
+        <v>7087225</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26046,10 +26046,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128423617</v>
+        <v>128423625</v>
       </c>
       <c r="B254" t="n">
-        <v>91551</v>
+        <v>88937</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -26057,21 +26057,21 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -26081,10 +26081,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>634507</v>
+        <v>634494</v>
       </c>
       <c r="R254" t="n">
-        <v>7087328</v>
+        <v>7087408</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26143,32 +26143,32 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>128423593</v>
+        <v>128423622</v>
       </c>
       <c r="B255" t="n">
-        <v>80173</v>
+        <v>88937</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>6462</v>
+        <v>510</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -26178,10 +26178,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>635471</v>
+        <v>634642</v>
       </c>
       <c r="R255" t="n">
-        <v>7087281</v>
+        <v>7087251</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26240,32 +26240,32 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>128423629</v>
+        <v>128423617</v>
       </c>
       <c r="B256" t="n">
-        <v>80179</v>
+        <v>91558</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -26275,10 +26275,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>635454</v>
+        <v>634507</v>
       </c>
       <c r="R256" t="n">
-        <v>7087257</v>
+        <v>7087328</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26337,32 +26337,32 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128423622</v>
+        <v>128423593</v>
       </c>
       <c r="B257" t="n">
-        <v>88930</v>
+        <v>80173</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>510</v>
+        <v>6462</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -26372,10 +26372,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>634642</v>
+        <v>635471</v>
       </c>
       <c r="R257" t="n">
-        <v>7087251</v>
+        <v>7087281</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -26434,32 +26434,32 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128423625</v>
+        <v>128423629</v>
       </c>
       <c r="B258" t="n">
-        <v>88930</v>
+        <v>80179</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>510</v>
+        <v>6463</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -26469,10 +26469,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>634494</v>
+        <v>635454</v>
       </c>
       <c r="R258" t="n">
-        <v>7087408</v>
+        <v>7087257</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -26534,7 +26534,7 @@
         <v>128423626</v>
       </c>
       <c r="B259" t="n">
-        <v>88930</v>
+        <v>88937</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>128423577</v>
       </c>
       <c r="B260" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -26728,7 +26728,7 @@
         <v>128423616</v>
       </c>
       <c r="B261" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -27119,10 +27119,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>128492197</v>
+        <v>128423585</v>
       </c>
       <c r="B265" t="n">
-        <v>95895</v>
+        <v>92240</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -27130,38 +27130,34 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>2809</v>
+        <v>3298</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
-      <c r="J265" t="inlineStr"/>
-      <c r="K265" t="inlineStr"/>
-      <c r="L265" t="inlineStr"/>
-      <c r="N265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>635110</v>
+        <v>634942</v>
       </c>
       <c r="R265" t="n">
-        <v>7087251</v>
+        <v>7087590</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27202,7 +27198,6 @@
       <c r="AE265" t="b">
         <v>0</v>
       </c>
-      <c r="AF265" t="inlineStr"/>
       <c r="AG265" t="b">
         <v>0</v>
       </c>
@@ -27221,10 +27216,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>128423585</v>
+        <v>128492197</v>
       </c>
       <c r="B266" t="n">
-        <v>92233</v>
+        <v>95902</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -27232,34 +27227,38 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>3298</v>
+        <v>2809</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
+      <c r="J266" t="inlineStr"/>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr"/>
+      <c r="N266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>634942</v>
+        <v>635110</v>
       </c>
       <c r="R266" t="n">
-        <v>7087590</v>
+        <v>7087251</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -27300,6 +27299,7 @@
       <c r="AE266" t="b">
         <v>0</v>
       </c>
+      <c r="AF266" t="inlineStr"/>
       <c r="AG266" t="b">
         <v>0</v>
       </c>
@@ -27321,7 +27321,7 @@
         <v>128423578</v>
       </c>
       <c r="B267" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -27617,7 +27617,7 @@
         <v>128423572</v>
       </c>
       <c r="B270" t="n">
-        <v>96915</v>
+        <v>96922</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -27711,32 +27711,32 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>128423614</v>
+        <v>128423576</v>
       </c>
       <c r="B271" t="n">
-        <v>91547</v>
+        <v>91504</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
@@ -27746,10 +27746,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>634673</v>
+        <v>634705</v>
       </c>
       <c r="R271" t="n">
-        <v>7087631</v>
+        <v>7087668</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -27914,32 +27914,32 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>128423576</v>
+        <v>128423614</v>
       </c>
       <c r="B273" t="n">
-        <v>91497</v>
+        <v>91554</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
@@ -27949,10 +27949,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>634705</v>
+        <v>634673</v>
       </c>
       <c r="R273" t="n">
-        <v>7087668</v>
+        <v>7087631</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -28011,32 +28011,32 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>128423599</v>
+        <v>128423598</v>
       </c>
       <c r="B274" t="n">
-        <v>91988</v>
+        <v>80145</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>1209</v>
+        <v>2081</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -28046,10 +28046,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>635464</v>
+        <v>635632</v>
       </c>
       <c r="R274" t="n">
-        <v>7087275</v>
+        <v>7087270</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28108,32 +28108,32 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>128423598</v>
+        <v>128423599</v>
       </c>
       <c r="B275" t="n">
-        <v>80145</v>
+        <v>91995</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>2081</v>
+        <v>1209</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -28143,10 +28143,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>635632</v>
+        <v>635464</v>
       </c>
       <c r="R275" t="n">
-        <v>7087270</v>
+        <v>7087275</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -28305,7 +28305,7 @@
         <v>128423604</v>
       </c>
       <c r="B277" t="n">
-        <v>95895</v>
+        <v>95902</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -28399,10 +28399,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>128423590</v>
+        <v>128423596</v>
       </c>
       <c r="B278" t="n">
-        <v>92818</v>
+        <v>57722</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -28410,21 +28410,21 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>4361</v>
+        <v>100049</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
@@ -28434,10 +28434,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>635182</v>
+        <v>634648</v>
       </c>
       <c r="R278" t="n">
-        <v>7087227</v>
+        <v>7087590</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -28496,10 +28496,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>128423596</v>
+        <v>128423588</v>
       </c>
       <c r="B279" t="n">
-        <v>57722</v>
+        <v>57885</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -28507,21 +28507,21 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
@@ -28531,10 +28531,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>634648</v>
+        <v>634560</v>
       </c>
       <c r="R279" t="n">
-        <v>7087590</v>
+        <v>7087311</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -28593,10 +28593,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>128423588</v>
+        <v>128423590</v>
       </c>
       <c r="B280" t="n">
-        <v>57885</v>
+        <v>92825</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -28604,21 +28604,21 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -28628,10 +28628,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>634560</v>
+        <v>635182</v>
       </c>
       <c r="R280" t="n">
-        <v>7087311</v>
+        <v>7087227</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -28693,7 +28693,7 @@
         <v>128423580</v>
       </c>
       <c r="B281" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>128423579</v>
       </c>
       <c r="B282" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -28981,32 +28981,32 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>128423574</v>
+        <v>128423601</v>
       </c>
       <c r="B284" t="n">
-        <v>91497</v>
+        <v>91825</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -29016,10 +29016,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>634571</v>
+        <v>634475</v>
       </c>
       <c r="R284" t="n">
-        <v>7087253</v>
+        <v>7087365</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -29078,32 +29078,32 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>128423601</v>
+        <v>128423574</v>
       </c>
       <c r="B285" t="n">
-        <v>91818</v>
+        <v>91504</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -29113,10 +29113,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>634475</v>
+        <v>634571</v>
       </c>
       <c r="R285" t="n">
-        <v>7087365</v>
+        <v>7087253</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -29178,7 +29178,7 @@
         <v>128423613</v>
       </c>
       <c r="B286" t="n">
-        <v>91547</v>
+        <v>91554</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>

--- a/artfynd/A 30047-2025 artfynd.xlsx
+++ b/artfynd/A 30047-2025 artfynd.xlsx
@@ -24400,7 +24400,7 @@
         <v>128651017</v>
       </c>
       <c r="B237" t="n">
-        <v>97017</v>
+        <v>97019</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>128651018</v>
       </c>
       <c r="B238" t="n">
-        <v>95914</v>
+        <v>95916</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24594,7 +24594,7 @@
         <v>128423582</v>
       </c>
       <c r="B239" t="n">
-        <v>91822</v>
+        <v>91824</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         <v>128423605</v>
       </c>
       <c r="B240" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -24788,7 +24788,7 @@
         <v>128423608</v>
       </c>
       <c r="B241" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24882,32 +24882,32 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>128423573</v>
+        <v>128423623</v>
       </c>
       <c r="B242" t="n">
-        <v>91504</v>
+        <v>88939</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -24917,10 +24917,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>634599</v>
+        <v>634583</v>
       </c>
       <c r="R242" t="n">
-        <v>7087225</v>
+        <v>7087261</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24979,32 +24979,32 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>128423623</v>
+        <v>128423573</v>
       </c>
       <c r="B243" t="n">
-        <v>88937</v>
+        <v>91506</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -25014,10 +25014,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>634583</v>
+        <v>634599</v>
       </c>
       <c r="R243" t="n">
-        <v>7087261</v>
+        <v>7087225</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25076,32 +25076,32 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>128423591</v>
+        <v>128423621</v>
       </c>
       <c r="B244" t="n">
-        <v>80173</v>
+        <v>82873</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -25111,10 +25111,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>635451</v>
+        <v>634525</v>
       </c>
       <c r="R244" t="n">
-        <v>7087225</v>
+        <v>7087295</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25173,27 +25173,27 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>128423597</v>
+        <v>128423612</v>
       </c>
       <c r="B245" t="n">
-        <v>57722</v>
+        <v>58097</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -25270,10 +25270,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>128423621</v>
+        <v>128423597</v>
       </c>
       <c r="B246" t="n">
-        <v>82871</v>
+        <v>57724</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -25281,21 +25281,21 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -25305,10 +25305,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>634525</v>
+        <v>634913</v>
       </c>
       <c r="R246" t="n">
-        <v>7087295</v>
+        <v>7087585</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25367,10 +25367,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>128423612</v>
+        <v>128423591</v>
       </c>
       <c r="B247" t="n">
-        <v>58095</v>
+        <v>80175</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -25378,21 +25378,21 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>103015</v>
+        <v>6462</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -25402,10 +25402,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>634913</v>
+        <v>635451</v>
       </c>
       <c r="R247" t="n">
-        <v>7087585</v>
+        <v>7087225</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25464,32 +25464,32 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>128423606</v>
+        <v>128423575</v>
       </c>
       <c r="B248" t="n">
-        <v>80144</v>
+        <v>91506</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -25499,10 +25499,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>635122</v>
+        <v>634574</v>
       </c>
       <c r="R248" t="n">
-        <v>7087242</v>
+        <v>7087286</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25564,7 +25564,7 @@
         <v>128423618</v>
       </c>
       <c r="B249" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -25658,32 +25658,32 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>128423575</v>
+        <v>128423606</v>
       </c>
       <c r="B250" t="n">
-        <v>91504</v>
+        <v>80146</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -25693,10 +25693,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>634574</v>
+        <v>635122</v>
       </c>
       <c r="R250" t="n">
-        <v>7087286</v>
+        <v>7087242</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -25758,7 +25758,7 @@
         <v>128423615</v>
       </c>
       <c r="B251" t="n">
-        <v>91554</v>
+        <v>91556</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -25855,7 +25855,7 @@
         <v>128423624</v>
       </c>
       <c r="B252" t="n">
-        <v>88937</v>
+        <v>88939</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -25952,7 +25952,7 @@
         <v>128423628</v>
       </c>
       <c r="B253" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -26046,32 +26046,32 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128423625</v>
+        <v>128423593</v>
       </c>
       <c r="B254" t="n">
-        <v>88937</v>
+        <v>80175</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>510</v>
+        <v>6462</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -26081,10 +26081,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>634494</v>
+        <v>635471</v>
       </c>
       <c r="R254" t="n">
-        <v>7087408</v>
+        <v>7087281</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26143,32 +26143,32 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>128423622</v>
+        <v>128423629</v>
       </c>
       <c r="B255" t="n">
-        <v>88937</v>
+        <v>80181</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>510</v>
+        <v>6463</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -26178,10 +26178,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>634642</v>
+        <v>635454</v>
       </c>
       <c r="R255" t="n">
-        <v>7087251</v>
+        <v>7087257</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26243,7 +26243,7 @@
         <v>128423617</v>
       </c>
       <c r="B256" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -26337,32 +26337,32 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128423593</v>
+        <v>128423622</v>
       </c>
       <c r="B257" t="n">
-        <v>80173</v>
+        <v>88939</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>6462</v>
+        <v>510</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -26372,10 +26372,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>635471</v>
+        <v>634642</v>
       </c>
       <c r="R257" t="n">
-        <v>7087281</v>
+        <v>7087251</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -26434,32 +26434,32 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128423629</v>
+        <v>128423625</v>
       </c>
       <c r="B258" t="n">
-        <v>80179</v>
+        <v>88939</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>6463</v>
+        <v>510</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -26469,10 +26469,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>635454</v>
+        <v>634494</v>
       </c>
       <c r="R258" t="n">
-        <v>7087257</v>
+        <v>7087408</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -26534,7 +26534,7 @@
         <v>128423626</v>
       </c>
       <c r="B259" t="n">
-        <v>88937</v>
+        <v>88939</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -26628,10 +26628,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>128423577</v>
+        <v>128423585</v>
       </c>
       <c r="B260" t="n">
-        <v>91504</v>
+        <v>92242</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -26639,21 +26639,21 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -26663,10 +26663,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>635153</v>
+        <v>634942</v>
       </c>
       <c r="R260" t="n">
-        <v>7087180</v>
+        <v>7087590</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -26728,7 +26728,7 @@
         <v>128423616</v>
       </c>
       <c r="B261" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -26822,32 +26822,32 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128423619</v>
+        <v>128423577</v>
       </c>
       <c r="B262" t="n">
-        <v>79039</v>
+        <v>91506</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -26857,10 +26857,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>635513</v>
+        <v>635153</v>
       </c>
       <c r="R262" t="n">
-        <v>7087316</v>
+        <v>7087180</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -26895,18 +26895,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC262" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD262" t="b">
         <v>0</v>
       </c>
       <c r="AE262" t="b">
         <v>0</v>
       </c>
-      <c r="AF262" t="inlineStr"/>
       <c r="AG262" t="b">
         <v>0</v>
       </c>
@@ -26925,32 +26919,32 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>128423594</v>
+        <v>128423619</v>
       </c>
       <c r="B263" t="n">
-        <v>80173</v>
+        <v>79041</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -26960,10 +26954,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>634527</v>
+        <v>635513</v>
       </c>
       <c r="R263" t="n">
-        <v>7087301</v>
+        <v>7087316</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -26998,12 +26992,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC263" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD263" t="b">
         <v>0</v>
       </c>
       <c r="AE263" t="b">
         <v>0</v>
       </c>
+      <c r="AF263" t="inlineStr"/>
       <c r="AG263" t="b">
         <v>0</v>
       </c>
@@ -27025,7 +27025,7 @@
         <v>128423620</v>
       </c>
       <c r="B264" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -27119,10 +27119,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>128423585</v>
+        <v>128423594</v>
       </c>
       <c r="B265" t="n">
-        <v>92240</v>
+        <v>80175</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -27130,21 +27130,21 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -27154,10 +27154,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>634942</v>
+        <v>634527</v>
       </c>
       <c r="R265" t="n">
-        <v>7087590</v>
+        <v>7087301</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27219,7 +27219,7 @@
         <v>128492197</v>
       </c>
       <c r="B266" t="n">
-        <v>95902</v>
+        <v>95904</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -27321,7 +27321,7 @@
         <v>128423578</v>
       </c>
       <c r="B267" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -27415,10 +27415,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>128423607</v>
+        <v>128423602</v>
       </c>
       <c r="B268" t="n">
-        <v>80144</v>
+        <v>57727</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -27426,21 +27426,21 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -27450,10 +27450,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>635459</v>
+        <v>635210</v>
       </c>
       <c r="R268" t="n">
-        <v>7087231</v>
+        <v>7087158</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -27486,6 +27486,11 @@
       <c r="AA268" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC268" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -27512,10 +27517,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>128423602</v>
+        <v>128423607</v>
       </c>
       <c r="B269" t="n">
-        <v>57725</v>
+        <v>80146</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -27523,21 +27528,21 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -27547,10 +27552,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>635210</v>
+        <v>635459</v>
       </c>
       <c r="R269" t="n">
-        <v>7087158</v>
+        <v>7087231</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -27583,11 +27588,6 @@
       <c r="AA269" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC269" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -27617,7 +27617,7 @@
         <v>128423572</v>
       </c>
       <c r="B270" t="n">
-        <v>96922</v>
+        <v>96924</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -27714,7 +27714,7 @@
         <v>128423576</v>
       </c>
       <c r="B271" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -27811,7 +27811,7 @@
         <v>128423603</v>
       </c>
       <c r="B272" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -27917,7 +27917,7 @@
         <v>128423614</v>
       </c>
       <c r="B273" t="n">
-        <v>91554</v>
+        <v>91556</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -28011,32 +28011,32 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>128423598</v>
+        <v>128423592</v>
       </c>
       <c r="B274" t="n">
-        <v>80145</v>
+        <v>80175</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -28046,10 +28046,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>635632</v>
+        <v>635454</v>
       </c>
       <c r="R274" t="n">
-        <v>7087270</v>
+        <v>7087257</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28108,32 +28108,32 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>128423599</v>
+        <v>128423598</v>
       </c>
       <c r="B275" t="n">
-        <v>91995</v>
+        <v>80147</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>1209</v>
+        <v>2081</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -28143,10 +28143,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>635464</v>
+        <v>635632</v>
       </c>
       <c r="R275" t="n">
-        <v>7087275</v>
+        <v>7087270</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -28205,32 +28205,32 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>128423592</v>
+        <v>128423599</v>
       </c>
       <c r="B276" t="n">
-        <v>80173</v>
+        <v>91997</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>6462</v>
+        <v>1209</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -28240,10 +28240,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>635454</v>
+        <v>635464</v>
       </c>
       <c r="R276" t="n">
-        <v>7087257</v>
+        <v>7087275</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -28305,7 +28305,7 @@
         <v>128423604</v>
       </c>
       <c r="B277" t="n">
-        <v>95902</v>
+        <v>95904</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -28399,10 +28399,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>128423596</v>
+        <v>128423588</v>
       </c>
       <c r="B278" t="n">
-        <v>57722</v>
+        <v>57887</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -28410,21 +28410,21 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
@@ -28434,10 +28434,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>634648</v>
+        <v>634560</v>
       </c>
       <c r="R278" t="n">
-        <v>7087590</v>
+        <v>7087311</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -28496,10 +28496,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>128423588</v>
+        <v>128423590</v>
       </c>
       <c r="B279" t="n">
-        <v>57885</v>
+        <v>92827</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -28507,21 +28507,21 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
@@ -28531,10 +28531,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>634560</v>
+        <v>635182</v>
       </c>
       <c r="R279" t="n">
-        <v>7087311</v>
+        <v>7087227</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -28593,10 +28593,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>128423590</v>
+        <v>128423596</v>
       </c>
       <c r="B280" t="n">
-        <v>92825</v>
+        <v>57724</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -28604,21 +28604,21 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>4361</v>
+        <v>100049</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -28628,10 +28628,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>635182</v>
+        <v>634648</v>
       </c>
       <c r="R280" t="n">
-        <v>7087227</v>
+        <v>7087590</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -28693,7 +28693,7 @@
         <v>128423580</v>
       </c>
       <c r="B281" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>128423579</v>
       </c>
       <c r="B282" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>128423595</v>
       </c>
       <c r="B283" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -28981,32 +28981,32 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>128423601</v>
+        <v>128423574</v>
       </c>
       <c r="B284" t="n">
-        <v>91825</v>
+        <v>91506</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -29016,10 +29016,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>634475</v>
+        <v>634571</v>
       </c>
       <c r="R284" t="n">
-        <v>7087365</v>
+        <v>7087253</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -29078,32 +29078,32 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>128423574</v>
+        <v>128423601</v>
       </c>
       <c r="B285" t="n">
-        <v>91504</v>
+        <v>91827</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -29113,10 +29113,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>634571</v>
+        <v>634475</v>
       </c>
       <c r="R285" t="n">
-        <v>7087253</v>
+        <v>7087365</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -29178,7 +29178,7 @@
         <v>128423613</v>
       </c>
       <c r="B286" t="n">
-        <v>91554</v>
+        <v>91556</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>

--- a/artfynd/A 30047-2025 artfynd.xlsx
+++ b/artfynd/A 30047-2025 artfynd.xlsx
@@ -25076,10 +25076,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>128423621</v>
+        <v>128423597</v>
       </c>
       <c r="B244" t="n">
-        <v>82873</v>
+        <v>57724</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -25087,21 +25087,21 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -25111,10 +25111,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>634525</v>
+        <v>634913</v>
       </c>
       <c r="R244" t="n">
-        <v>7087295</v>
+        <v>7087585</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25270,10 +25270,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>128423597</v>
+        <v>128423621</v>
       </c>
       <c r="B246" t="n">
-        <v>57724</v>
+        <v>82873</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -25281,21 +25281,21 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -25305,10 +25305,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>634913</v>
+        <v>634525</v>
       </c>
       <c r="R246" t="n">
-        <v>7087585</v>
+        <v>7087295</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25464,32 +25464,32 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>128423575</v>
+        <v>128423618</v>
       </c>
       <c r="B248" t="n">
-        <v>91506</v>
+        <v>91560</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -25499,10 +25499,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>634574</v>
+        <v>634676</v>
       </c>
       <c r="R248" t="n">
-        <v>7087286</v>
+        <v>7087616</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25561,32 +25561,32 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>128423618</v>
+        <v>128423575</v>
       </c>
       <c r="B249" t="n">
-        <v>91560</v>
+        <v>91506</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -25596,10 +25596,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>634676</v>
+        <v>634574</v>
       </c>
       <c r="R249" t="n">
-        <v>7087616</v>
+        <v>7087286</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25755,10 +25755,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>128423615</v>
+        <v>128423624</v>
       </c>
       <c r="B251" t="n">
-        <v>91556</v>
+        <v>88939</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -25766,21 +25766,21 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>1204</v>
+        <v>510</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -25790,10 +25790,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>634897</v>
+        <v>634461</v>
       </c>
       <c r="R251" t="n">
-        <v>7087591</v>
+        <v>7087363</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -25852,10 +25852,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>128423624</v>
+        <v>128423615</v>
       </c>
       <c r="B252" t="n">
-        <v>88939</v>
+        <v>91556</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -25863,21 +25863,21 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>510</v>
+        <v>1204</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -25887,10 +25887,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>634461</v>
+        <v>634897</v>
       </c>
       <c r="R252" t="n">
-        <v>7087363</v>
+        <v>7087591</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -26046,32 +26046,32 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128423593</v>
+        <v>128423622</v>
       </c>
       <c r="B254" t="n">
-        <v>80175</v>
+        <v>88939</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>6462</v>
+        <v>510</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -26081,10 +26081,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>635471</v>
+        <v>634642</v>
       </c>
       <c r="R254" t="n">
-        <v>7087281</v>
+        <v>7087251</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26143,32 +26143,32 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>128423629</v>
+        <v>128423625</v>
       </c>
       <c r="B255" t="n">
-        <v>80181</v>
+        <v>88939</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>6463</v>
+        <v>510</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -26178,10 +26178,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>635454</v>
+        <v>634494</v>
       </c>
       <c r="R255" t="n">
-        <v>7087257</v>
+        <v>7087408</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26240,32 +26240,32 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>128423617</v>
+        <v>128423593</v>
       </c>
       <c r="B256" t="n">
-        <v>91560</v>
+        <v>80175</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -26275,10 +26275,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>634507</v>
+        <v>635471</v>
       </c>
       <c r="R256" t="n">
-        <v>7087328</v>
+        <v>7087281</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26337,32 +26337,32 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128423622</v>
+        <v>128423629</v>
       </c>
       <c r="B257" t="n">
-        <v>88939</v>
+        <v>80181</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>510</v>
+        <v>6463</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -26372,10 +26372,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>634642</v>
+        <v>635454</v>
       </c>
       <c r="R257" t="n">
-        <v>7087251</v>
+        <v>7087257</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -26434,10 +26434,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128423625</v>
+        <v>128423617</v>
       </c>
       <c r="B258" t="n">
-        <v>88939</v>
+        <v>91560</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -26445,21 +26445,21 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -26469,10 +26469,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>634494</v>
+        <v>634507</v>
       </c>
       <c r="R258" t="n">
-        <v>7087408</v>
+        <v>7087328</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -26725,32 +26725,32 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128423616</v>
+        <v>128423577</v>
       </c>
       <c r="B261" t="n">
-        <v>91560</v>
+        <v>91506</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -26760,10 +26760,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>634993</v>
+        <v>635153</v>
       </c>
       <c r="R261" t="n">
-        <v>7087294</v>
+        <v>7087180</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26822,32 +26822,32 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128423577</v>
+        <v>128423616</v>
       </c>
       <c r="B262" t="n">
-        <v>91506</v>
+        <v>91560</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -26857,10 +26857,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>635153</v>
+        <v>634993</v>
       </c>
       <c r="R262" t="n">
-        <v>7087180</v>
+        <v>7087294</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27022,32 +27022,32 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>128423620</v>
+        <v>128423594</v>
       </c>
       <c r="B264" t="n">
-        <v>79041</v>
+        <v>80175</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -27057,10 +27057,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>634756</v>
+        <v>634527</v>
       </c>
       <c r="R264" t="n">
-        <v>7087642</v>
+        <v>7087301</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27119,32 +27119,32 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>128423594</v>
+        <v>128423620</v>
       </c>
       <c r="B265" t="n">
-        <v>80175</v>
+        <v>79041</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -27154,10 +27154,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>634527</v>
+        <v>634756</v>
       </c>
       <c r="R265" t="n">
-        <v>7087301</v>
+        <v>7087642</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27318,32 +27318,32 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>128423578</v>
+        <v>128423607</v>
       </c>
       <c r="B267" t="n">
-        <v>91506</v>
+        <v>80146</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -27353,10 +27353,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>635327</v>
+        <v>635459</v>
       </c>
       <c r="R267" t="n">
-        <v>7087158</v>
+        <v>7087231</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -27415,32 +27415,32 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>128423602</v>
+        <v>128423578</v>
       </c>
       <c r="B268" t="n">
-        <v>57727</v>
+        <v>91506</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -27450,7 +27450,7 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>635210</v>
+        <v>635327</v>
       </c>
       <c r="R268" t="n">
         <v>7087158</v>
@@ -27486,11 +27486,6 @@
       <c r="AA268" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC268" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -27517,10 +27512,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>128423607</v>
+        <v>128423602</v>
       </c>
       <c r="B269" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -27528,21 +27523,21 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -27552,10 +27547,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>635459</v>
+        <v>635210</v>
       </c>
       <c r="R269" t="n">
-        <v>7087231</v>
+        <v>7087158</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -27588,6 +27583,11 @@
       <c r="AA269" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -27711,32 +27711,32 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>128423576</v>
+        <v>128423614</v>
       </c>
       <c r="B271" t="n">
-        <v>91506</v>
+        <v>91556</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
@@ -27746,10 +27746,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>634705</v>
+        <v>634673</v>
       </c>
       <c r="R271" t="n">
-        <v>7087668</v>
+        <v>7087631</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -27914,32 +27914,32 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>128423614</v>
+        <v>128423576</v>
       </c>
       <c r="B273" t="n">
-        <v>91556</v>
+        <v>91506</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
@@ -27949,10 +27949,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>634673</v>
+        <v>634705</v>
       </c>
       <c r="R273" t="n">
-        <v>7087631</v>
+        <v>7087668</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -28011,32 +28011,32 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>128423592</v>
+        <v>128423598</v>
       </c>
       <c r="B274" t="n">
-        <v>80175</v>
+        <v>80147</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -28046,10 +28046,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>635454</v>
+        <v>635632</v>
       </c>
       <c r="R274" t="n">
-        <v>7087257</v>
+        <v>7087270</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28108,32 +28108,32 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>128423598</v>
+        <v>128423599</v>
       </c>
       <c r="B275" t="n">
-        <v>80147</v>
+        <v>91997</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>2081</v>
+        <v>1209</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -28143,10 +28143,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>635632</v>
+        <v>635464</v>
       </c>
       <c r="R275" t="n">
-        <v>7087270</v>
+        <v>7087275</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -28205,32 +28205,32 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>128423599</v>
+        <v>128423592</v>
       </c>
       <c r="B276" t="n">
-        <v>91997</v>
+        <v>80175</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>1209</v>
+        <v>6462</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -28240,10 +28240,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>635464</v>
+        <v>635454</v>
       </c>
       <c r="R276" t="n">
-        <v>7087275</v>
+        <v>7087257</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -28399,10 +28399,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>128423588</v>
+        <v>128423590</v>
       </c>
       <c r="B278" t="n">
-        <v>57887</v>
+        <v>92827</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -28410,21 +28410,21 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
@@ -28434,10 +28434,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>634560</v>
+        <v>635182</v>
       </c>
       <c r="R278" t="n">
-        <v>7087311</v>
+        <v>7087227</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -28496,10 +28496,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>128423590</v>
+        <v>128423596</v>
       </c>
       <c r="B279" t="n">
-        <v>92827</v>
+        <v>57724</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -28507,21 +28507,21 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>4361</v>
+        <v>100049</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
@@ -28531,10 +28531,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>635182</v>
+        <v>634648</v>
       </c>
       <c r="R279" t="n">
-        <v>7087227</v>
+        <v>7087590</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -28593,10 +28593,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>128423596</v>
+        <v>128423588</v>
       </c>
       <c r="B280" t="n">
-        <v>57724</v>
+        <v>57887</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -28604,21 +28604,21 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -28628,10 +28628,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>634648</v>
+        <v>634560</v>
       </c>
       <c r="R280" t="n">
-        <v>7087590</v>
+        <v>7087311</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -28981,32 +28981,32 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>128423574</v>
+        <v>128423601</v>
       </c>
       <c r="B284" t="n">
-        <v>91506</v>
+        <v>91827</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -29016,10 +29016,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>634571</v>
+        <v>634475</v>
       </c>
       <c r="R284" t="n">
-        <v>7087253</v>
+        <v>7087365</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -29078,32 +29078,32 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>128423601</v>
+        <v>128423574</v>
       </c>
       <c r="B285" t="n">
-        <v>91827</v>
+        <v>91506</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -29113,10 +29113,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>634475</v>
+        <v>634571</v>
       </c>
       <c r="R285" t="n">
-        <v>7087365</v>
+        <v>7087253</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>

--- a/artfynd/A 30047-2025 artfynd.xlsx
+++ b/artfynd/A 30047-2025 artfynd.xlsx
@@ -24591,10 +24591,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>128423582</v>
+        <v>128423605</v>
       </c>
       <c r="B239" t="n">
-        <v>91824</v>
+        <v>80146</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -24602,21 +24602,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>73</v>
+        <v>6458</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -24626,10 +24626,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>635466</v>
+        <v>635331</v>
       </c>
       <c r="R239" t="n">
-        <v>7087277</v>
+        <v>7087194</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24688,7 +24688,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>128423605</v>
+        <v>128423608</v>
       </c>
       <c r="B240" t="n">
         <v>80146</v>
@@ -24723,10 +24723,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>635331</v>
+        <v>635603</v>
       </c>
       <c r="R240" t="n">
-        <v>7087194</v>
+        <v>7087226</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24785,10 +24785,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>128423608</v>
+        <v>128423582</v>
       </c>
       <c r="B241" t="n">
-        <v>80146</v>
+        <v>91824</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24796,21 +24796,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6458</v>
+        <v>73</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -24820,10 +24820,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>635603</v>
+        <v>635466</v>
       </c>
       <c r="R241" t="n">
-        <v>7087226</v>
+        <v>7087277</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>

--- a/artfynd/A 30047-2025 artfynd.xlsx
+++ b/artfynd/A 30047-2025 artfynd.xlsx
@@ -24400,7 +24400,7 @@
         <v>128651017</v>
       </c>
       <c r="B237" t="n">
-        <v>97019</v>
+        <v>97045</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>128651018</v>
       </c>
       <c r="B238" t="n">
-        <v>95916</v>
+        <v>95942</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24788,7 +24788,7 @@
         <v>128423582</v>
       </c>
       <c r="B241" t="n">
-        <v>91824</v>
+        <v>91834</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24882,32 +24882,32 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>128423623</v>
+        <v>128423573</v>
       </c>
       <c r="B242" t="n">
-        <v>88939</v>
+        <v>91504</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -24917,10 +24917,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>634583</v>
+        <v>634599</v>
       </c>
       <c r="R242" t="n">
-        <v>7087261</v>
+        <v>7087225</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24979,32 +24979,32 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>128423573</v>
+        <v>128423623</v>
       </c>
       <c r="B243" t="n">
-        <v>91506</v>
+        <v>88940</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -25014,10 +25014,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>634599</v>
+        <v>634583</v>
       </c>
       <c r="R243" t="n">
-        <v>7087225</v>
+        <v>7087261</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25076,10 +25076,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>128423597</v>
+        <v>128423621</v>
       </c>
       <c r="B244" t="n">
-        <v>57724</v>
+        <v>82873</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -25087,21 +25087,21 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -25111,10 +25111,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>634913</v>
+        <v>634525</v>
       </c>
       <c r="R244" t="n">
-        <v>7087585</v>
+        <v>7087295</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25173,27 +25173,27 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>128423612</v>
+        <v>128423597</v>
       </c>
       <c r="B245" t="n">
-        <v>58097</v>
+        <v>57724</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -25270,32 +25270,32 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>128423621</v>
+        <v>128423591</v>
       </c>
       <c r="B246" t="n">
-        <v>82873</v>
+        <v>80175</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -25305,10 +25305,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>634525</v>
+        <v>635451</v>
       </c>
       <c r="R246" t="n">
-        <v>7087295</v>
+        <v>7087225</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25367,10 +25367,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>128423591</v>
+        <v>128423612</v>
       </c>
       <c r="B247" t="n">
-        <v>80175</v>
+        <v>58097</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -25378,21 +25378,21 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6462</v>
+        <v>103015</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -25402,10 +25402,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>635451</v>
+        <v>634913</v>
       </c>
       <c r="R247" t="n">
-        <v>7087225</v>
+        <v>7087585</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25467,7 +25467,7 @@
         <v>128423618</v>
       </c>
       <c r="B248" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>128423575</v>
       </c>
       <c r="B249" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         <v>128423624</v>
       </c>
       <c r="B251" t="n">
-        <v>88939</v>
+        <v>88940</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -25852,32 +25852,32 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>128423615</v>
+        <v>128423628</v>
       </c>
       <c r="B252" t="n">
-        <v>91556</v>
+        <v>80181</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>1204</v>
+        <v>6463</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -25887,10 +25887,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>634897</v>
+        <v>635451</v>
       </c>
       <c r="R252" t="n">
-        <v>7087591</v>
+        <v>7087225</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -25949,32 +25949,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>128423628</v>
+        <v>128423615</v>
       </c>
       <c r="B253" t="n">
-        <v>80181</v>
+        <v>91554</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>6463</v>
+        <v>1204</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -25984,10 +25984,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>635451</v>
+        <v>634897</v>
       </c>
       <c r="R253" t="n">
-        <v>7087225</v>
+        <v>7087591</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26046,10 +26046,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128423622</v>
+        <v>128423617</v>
       </c>
       <c r="B254" t="n">
-        <v>88939</v>
+        <v>91558</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -26057,21 +26057,21 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -26081,10 +26081,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>634642</v>
+        <v>634507</v>
       </c>
       <c r="R254" t="n">
-        <v>7087251</v>
+        <v>7087328</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26146,7 +26146,7 @@
         <v>128423625</v>
       </c>
       <c r="B255" t="n">
-        <v>88939</v>
+        <v>88940</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -26240,32 +26240,32 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>128423593</v>
+        <v>128423622</v>
       </c>
       <c r="B256" t="n">
-        <v>80175</v>
+        <v>88940</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>6462</v>
+        <v>510</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -26275,10 +26275,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>635471</v>
+        <v>634642</v>
       </c>
       <c r="R256" t="n">
-        <v>7087281</v>
+        <v>7087251</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26337,10 +26337,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128423629</v>
+        <v>128423593</v>
       </c>
       <c r="B257" t="n">
-        <v>80181</v>
+        <v>80175</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -26348,21 +26348,21 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -26372,10 +26372,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>635454</v>
+        <v>635471</v>
       </c>
       <c r="R257" t="n">
-        <v>7087257</v>
+        <v>7087281</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -26434,32 +26434,32 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128423617</v>
+        <v>128423629</v>
       </c>
       <c r="B258" t="n">
-        <v>91560</v>
+        <v>80181</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -26469,10 +26469,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>634507</v>
+        <v>635454</v>
       </c>
       <c r="R258" t="n">
-        <v>7087328</v>
+        <v>7087257</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -26534,7 +26534,7 @@
         <v>128423626</v>
       </c>
       <c r="B259" t="n">
-        <v>88939</v>
+        <v>88940</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>128423585</v>
       </c>
       <c r="B260" t="n">
-        <v>92242</v>
+        <v>92257</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -26728,7 +26728,7 @@
         <v>128423577</v>
       </c>
       <c r="B261" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>128423616</v>
       </c>
       <c r="B262" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>128492197</v>
       </c>
       <c r="B266" t="n">
-        <v>95904</v>
+        <v>95930</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -27318,32 +27318,32 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>128423607</v>
+        <v>128423578</v>
       </c>
       <c r="B267" t="n">
-        <v>80146</v>
+        <v>91504</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -27353,10 +27353,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>635459</v>
+        <v>635327</v>
       </c>
       <c r="R267" t="n">
-        <v>7087231</v>
+        <v>7087158</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -27415,32 +27415,32 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>128423578</v>
+        <v>128423607</v>
       </c>
       <c r="B268" t="n">
-        <v>91506</v>
+        <v>80146</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -27450,10 +27450,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>635327</v>
+        <v>635459</v>
       </c>
       <c r="R268" t="n">
-        <v>7087158</v>
+        <v>7087231</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -27617,7 +27617,7 @@
         <v>128423572</v>
       </c>
       <c r="B270" t="n">
-        <v>96924</v>
+        <v>96950</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -27714,7 +27714,7 @@
         <v>128423614</v>
       </c>
       <c r="B271" t="n">
-        <v>91556</v>
+        <v>91554</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -27917,7 +27917,7 @@
         <v>128423576</v>
       </c>
       <c r="B273" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -28011,32 +28011,32 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>128423598</v>
+        <v>128423592</v>
       </c>
       <c r="B274" t="n">
-        <v>80147</v>
+        <v>80175</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -28046,10 +28046,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>635632</v>
+        <v>635454</v>
       </c>
       <c r="R274" t="n">
-        <v>7087270</v>
+        <v>7087257</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28108,32 +28108,32 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>128423599</v>
+        <v>128423598</v>
       </c>
       <c r="B275" t="n">
-        <v>91997</v>
+        <v>80147</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>1209</v>
+        <v>2081</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -28143,10 +28143,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>635464</v>
+        <v>635632</v>
       </c>
       <c r="R275" t="n">
-        <v>7087275</v>
+        <v>7087270</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -28205,32 +28205,32 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>128423592</v>
+        <v>128423599</v>
       </c>
       <c r="B276" t="n">
-        <v>80175</v>
+        <v>91992</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>6462</v>
+        <v>1209</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -28240,10 +28240,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>635454</v>
+        <v>635464</v>
       </c>
       <c r="R276" t="n">
-        <v>7087257</v>
+        <v>7087275</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -28305,7 +28305,7 @@
         <v>128423604</v>
       </c>
       <c r="B277" t="n">
-        <v>95904</v>
+        <v>95930</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -28402,7 +28402,7 @@
         <v>128423590</v>
       </c>
       <c r="B278" t="n">
-        <v>92827</v>
+        <v>92813</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -28496,10 +28496,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>128423596</v>
+        <v>128423588</v>
       </c>
       <c r="B279" t="n">
-        <v>57724</v>
+        <v>57887</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -28507,21 +28507,21 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
@@ -28531,10 +28531,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>634648</v>
+        <v>634560</v>
       </c>
       <c r="R279" t="n">
-        <v>7087590</v>
+        <v>7087311</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -28593,10 +28593,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>128423588</v>
+        <v>128423596</v>
       </c>
       <c r="B280" t="n">
-        <v>57887</v>
+        <v>57724</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -28604,21 +28604,21 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -28628,10 +28628,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>634560</v>
+        <v>634648</v>
       </c>
       <c r="R280" t="n">
-        <v>7087311</v>
+        <v>7087590</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -28693,7 +28693,7 @@
         <v>128423580</v>
       </c>
       <c r="B281" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>128423579</v>
       </c>
       <c r="B282" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -28984,7 +28984,7 @@
         <v>128423601</v>
       </c>
       <c r="B284" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>128423574</v>
       </c>
       <c r="B285" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>128423613</v>
       </c>
       <c r="B286" t="n">
-        <v>91556</v>
+        <v>91554</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>

--- a/artfynd/A 30047-2025 artfynd.xlsx
+++ b/artfynd/A 30047-2025 artfynd.xlsx
@@ -24400,7 +24400,7 @@
         <v>128651017</v>
       </c>
       <c r="B237" t="n">
-        <v>97045</v>
+        <v>97046</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>128651018</v>
       </c>
       <c r="B238" t="n">
-        <v>95942</v>
+        <v>95943</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24788,7 +24788,7 @@
         <v>128423582</v>
       </c>
       <c r="B241" t="n">
-        <v>91834</v>
+        <v>91835</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -25076,32 +25076,32 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>128423621</v>
+        <v>128423591</v>
       </c>
       <c r="B244" t="n">
-        <v>82873</v>
+        <v>80175</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -25111,10 +25111,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>634525</v>
+        <v>635451</v>
       </c>
       <c r="R244" t="n">
-        <v>7087295</v>
+        <v>7087225</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25270,32 +25270,32 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>128423591</v>
+        <v>128423621</v>
       </c>
       <c r="B246" t="n">
-        <v>80175</v>
+        <v>82873</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -25305,10 +25305,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>635451</v>
+        <v>634525</v>
       </c>
       <c r="R246" t="n">
-        <v>7087225</v>
+        <v>7087295</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25464,10 +25464,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>128423618</v>
+        <v>128423606</v>
       </c>
       <c r="B248" t="n">
-        <v>91558</v>
+        <v>80146</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -25475,21 +25475,21 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -25499,10 +25499,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>634676</v>
+        <v>635122</v>
       </c>
       <c r="R248" t="n">
-        <v>7087616</v>
+        <v>7087242</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25561,34 +25561,30 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>128423575</v>
+        <v>128423618</v>
       </c>
       <c r="B249" t="n">
-        <v>91504</v>
+        <v>91560</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
@@ -25596,10 +25592,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>634574</v>
+        <v>634676</v>
       </c>
       <c r="R249" t="n">
-        <v>7087286</v>
+        <v>7087616</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25658,32 +25654,32 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>128423606</v>
+        <v>128423575</v>
       </c>
       <c r="B250" t="n">
-        <v>80146</v>
+        <v>91504</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -25693,10 +25689,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>635122</v>
+        <v>634574</v>
       </c>
       <c r="R250" t="n">
-        <v>7087242</v>
+        <v>7087286</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -25755,10 +25751,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>128423624</v>
+        <v>128423615</v>
       </c>
       <c r="B251" t="n">
-        <v>88940</v>
+        <v>91554</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -25766,21 +25762,21 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>510</v>
+        <v>1204</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -25790,10 +25786,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>634461</v>
+        <v>634897</v>
       </c>
       <c r="R251" t="n">
-        <v>7087363</v>
+        <v>7087591</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -25949,10 +25945,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>128423615</v>
+        <v>128423624</v>
       </c>
       <c r="B253" t="n">
-        <v>91554</v>
+        <v>88940</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -25960,21 +25956,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>1204</v>
+        <v>510</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -25984,10 +25980,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>634897</v>
+        <v>634461</v>
       </c>
       <c r="R253" t="n">
-        <v>7087591</v>
+        <v>7087363</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26046,32 +26042,32 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128423617</v>
+        <v>128423593</v>
       </c>
       <c r="B254" t="n">
-        <v>91558</v>
+        <v>80175</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -26081,10 +26077,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>634507</v>
+        <v>635471</v>
       </c>
       <c r="R254" t="n">
-        <v>7087328</v>
+        <v>7087281</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26143,32 +26139,32 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>128423625</v>
+        <v>128423629</v>
       </c>
       <c r="B255" t="n">
-        <v>88940</v>
+        <v>80181</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>510</v>
+        <v>6463</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -26178,10 +26174,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>634494</v>
+        <v>635454</v>
       </c>
       <c r="R255" t="n">
-        <v>7087408</v>
+        <v>7087257</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26337,32 +26333,32 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128423593</v>
+        <v>128423625</v>
       </c>
       <c r="B257" t="n">
-        <v>80175</v>
+        <v>88940</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>6462</v>
+        <v>510</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -26372,10 +26368,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>635471</v>
+        <v>634494</v>
       </c>
       <c r="R257" t="n">
-        <v>7087281</v>
+        <v>7087408</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -26434,34 +26430,30 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128423629</v>
+        <v>128423617</v>
       </c>
       <c r="B258" t="n">
-        <v>80181</v>
+        <v>91560</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
-        </is>
-      </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
@@ -26469,10 +26461,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>635454</v>
+        <v>634507</v>
       </c>
       <c r="R258" t="n">
-        <v>7087257</v>
+        <v>7087328</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -26628,32 +26620,32 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>128423585</v>
+        <v>128423619</v>
       </c>
       <c r="B260" t="n">
-        <v>92257</v>
+        <v>79041</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -26663,10 +26655,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>634942</v>
+        <v>635513</v>
       </c>
       <c r="R260" t="n">
-        <v>7087590</v>
+        <v>7087316</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -26701,12 +26693,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC260" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD260" t="b">
         <v>0</v>
       </c>
       <c r="AE260" t="b">
         <v>0</v>
       </c>
+      <c r="AF260" t="inlineStr"/>
       <c r="AG260" t="b">
         <v>0</v>
       </c>
@@ -26725,10 +26723,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128423577</v>
+        <v>128423594</v>
       </c>
       <c r="B261" t="n">
-        <v>91504</v>
+        <v>80175</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -26736,21 +26734,21 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -26760,10 +26758,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>635153</v>
+        <v>634527</v>
       </c>
       <c r="R261" t="n">
-        <v>7087180</v>
+        <v>7087301</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26822,10 +26820,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128423616</v>
+        <v>128423620</v>
       </c>
       <c r="B262" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -26833,21 +26831,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -26857,10 +26855,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>634993</v>
+        <v>634756</v>
       </c>
       <c r="R262" t="n">
-        <v>7087294</v>
+        <v>7087642</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -26919,32 +26917,32 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>128423619</v>
+        <v>128423577</v>
       </c>
       <c r="B263" t="n">
-        <v>79041</v>
+        <v>91504</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -26954,10 +26952,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>635513</v>
+        <v>635153</v>
       </c>
       <c r="R263" t="n">
-        <v>7087316</v>
+        <v>7087180</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -26992,18 +26990,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC263" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD263" t="b">
         <v>0</v>
       </c>
       <c r="AE263" t="b">
         <v>0</v>
       </c>
-      <c r="AF263" t="inlineStr"/>
       <c r="AG263" t="b">
         <v>0</v>
       </c>
@@ -27022,34 +27014,30 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>128423594</v>
+        <v>128423616</v>
       </c>
       <c r="B264" t="n">
-        <v>80175</v>
+        <v>91560</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr"/>
       <c r="I264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
@@ -27057,10 +27045,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>634527</v>
+        <v>634993</v>
       </c>
       <c r="R264" t="n">
-        <v>7087301</v>
+        <v>7087294</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27119,45 +27107,49 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>128423620</v>
+        <v>128492197</v>
       </c>
       <c r="B265" t="n">
-        <v>79041</v>
+        <v>95931</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
+      <c r="J265" t="inlineStr"/>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
+      <c r="N265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>634756</v>
+        <v>635110</v>
       </c>
       <c r="R265" t="n">
-        <v>7087642</v>
+        <v>7087251</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27198,6 +27190,7 @@
       <c r="AE265" t="b">
         <v>0</v>
       </c>
+      <c r="AF265" t="inlineStr"/>
       <c r="AG265" t="b">
         <v>0</v>
       </c>
@@ -27216,10 +27209,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>128492197</v>
+        <v>128423585</v>
       </c>
       <c r="B266" t="n">
-        <v>95930</v>
+        <v>92258</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -27227,38 +27220,34 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>2809</v>
+        <v>3298</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
-      <c r="J266" t="inlineStr"/>
-      <c r="K266" t="inlineStr"/>
-      <c r="L266" t="inlineStr"/>
-      <c r="N266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>635110</v>
+        <v>634942</v>
       </c>
       <c r="R266" t="n">
-        <v>7087251</v>
+        <v>7087590</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -27299,7 +27288,6 @@
       <c r="AE266" t="b">
         <v>0</v>
       </c>
-      <c r="AF266" t="inlineStr"/>
       <c r="AG266" t="b">
         <v>0</v>
       </c>
@@ -27318,32 +27306,32 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>128423578</v>
+        <v>128423602</v>
       </c>
       <c r="B267" t="n">
-        <v>91504</v>
+        <v>57727</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -27353,7 +27341,7 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>635327</v>
+        <v>635210</v>
       </c>
       <c r="R267" t="n">
         <v>7087158</v>
@@ -27389,6 +27377,11 @@
       <c r="AA267" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC267" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -27512,32 +27505,32 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>128423602</v>
+        <v>128423578</v>
       </c>
       <c r="B269" t="n">
-        <v>57727</v>
+        <v>91504</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -27547,7 +27540,7 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>635210</v>
+        <v>635327</v>
       </c>
       <c r="R269" t="n">
         <v>7087158</v>
@@ -27583,11 +27576,6 @@
       <c r="AA269" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC269" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -27617,7 +27605,7 @@
         <v>128423572</v>
       </c>
       <c r="B270" t="n">
-        <v>96950</v>
+        <v>96951</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -27711,10 +27699,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>128423614</v>
+        <v>128423603</v>
       </c>
       <c r="B271" t="n">
-        <v>91554</v>
+        <v>57727</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -27722,34 +27710,38 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr"/>
+      <c r="M271" t="inlineStr"/>
+      <c r="N271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>634673</v>
+        <v>635240</v>
       </c>
       <c r="R271" t="n">
-        <v>7087631</v>
+        <v>7087224</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -27782,6 +27774,11 @@
       <c r="AA271" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -27808,10 +27805,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>128423603</v>
+        <v>128423614</v>
       </c>
       <c r="B272" t="n">
-        <v>57727</v>
+        <v>91554</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -27819,38 +27816,34 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="inlineStr"/>
-      <c r="N272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>635240</v>
+        <v>634673</v>
       </c>
       <c r="R272" t="n">
-        <v>7087224</v>
+        <v>7087631</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -27883,11 +27876,6 @@
       <c r="AA272" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC272" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -28208,7 +28196,7 @@
         <v>128423599</v>
       </c>
       <c r="B276" t="n">
-        <v>91992</v>
+        <v>91993</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -28305,7 +28293,7 @@
         <v>128423604</v>
       </c>
       <c r="B277" t="n">
-        <v>95930</v>
+        <v>95931</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -28402,7 +28390,7 @@
         <v>128423590</v>
       </c>
       <c r="B278" t="n">
-        <v>92813</v>
+        <v>92814</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -28496,10 +28484,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>128423588</v>
+        <v>128423596</v>
       </c>
       <c r="B279" t="n">
-        <v>57887</v>
+        <v>57724</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -28507,21 +28495,21 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
@@ -28531,10 +28519,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>634560</v>
+        <v>634648</v>
       </c>
       <c r="R279" t="n">
-        <v>7087311</v>
+        <v>7087590</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -28593,10 +28581,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>128423596</v>
+        <v>128423588</v>
       </c>
       <c r="B280" t="n">
-        <v>57724</v>
+        <v>57887</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -28604,21 +28592,21 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -28628,10 +28616,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>634648</v>
+        <v>634560</v>
       </c>
       <c r="R280" t="n">
-        <v>7087590</v>
+        <v>7087311</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -28981,32 +28969,32 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>128423601</v>
+        <v>128423574</v>
       </c>
       <c r="B284" t="n">
-        <v>91837</v>
+        <v>91504</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -29016,10 +29004,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>634475</v>
+        <v>634571</v>
       </c>
       <c r="R284" t="n">
-        <v>7087365</v>
+        <v>7087253</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -29078,32 +29066,32 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>128423574</v>
+        <v>128423601</v>
       </c>
       <c r="B285" t="n">
-        <v>91504</v>
+        <v>91838</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -29113,10 +29101,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>634571</v>
+        <v>634475</v>
       </c>
       <c r="R285" t="n">
-        <v>7087253</v>
+        <v>7087365</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>

--- a/artfynd/A 30047-2025 artfynd.xlsx
+++ b/artfynd/A 30047-2025 artfynd.xlsx
@@ -24400,7 +24400,7 @@
         <v>128651017</v>
       </c>
       <c r="B237" t="n">
-        <v>97046</v>
+        <v>97047</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>128651018</v>
       </c>
       <c r="B238" t="n">
-        <v>95943</v>
+        <v>95944</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24591,10 +24591,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>128423605</v>
+        <v>128423582</v>
       </c>
       <c r="B239" t="n">
-        <v>80146</v>
+        <v>91835</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -24602,21 +24602,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>6458</v>
+        <v>73</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -24626,10 +24626,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>635331</v>
+        <v>635466</v>
       </c>
       <c r="R239" t="n">
-        <v>7087194</v>
+        <v>7087277</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24688,7 +24688,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>128423608</v>
+        <v>128423605</v>
       </c>
       <c r="B240" t="n">
         <v>80146</v>
@@ -24723,10 +24723,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>635603</v>
+        <v>635331</v>
       </c>
       <c r="R240" t="n">
-        <v>7087226</v>
+        <v>7087194</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24785,10 +24785,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>128423582</v>
+        <v>128423608</v>
       </c>
       <c r="B241" t="n">
-        <v>91835</v>
+        <v>80146</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24796,21 +24796,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>73</v>
+        <v>6458</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -24820,10 +24820,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>635466</v>
+        <v>635603</v>
       </c>
       <c r="R241" t="n">
-        <v>7087277</v>
+        <v>7087226</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25076,32 +25076,32 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>128423591</v>
+        <v>128423597</v>
       </c>
       <c r="B244" t="n">
-        <v>80175</v>
+        <v>57724</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -25111,10 +25111,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>635451</v>
+        <v>634913</v>
       </c>
       <c r="R244" t="n">
-        <v>7087225</v>
+        <v>7087585</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25173,32 +25173,32 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>128423597</v>
+        <v>128423591</v>
       </c>
       <c r="B245" t="n">
-        <v>57724</v>
+        <v>80175</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -25208,10 +25208,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>634913</v>
+        <v>635451</v>
       </c>
       <c r="R245" t="n">
-        <v>7087585</v>
+        <v>7087225</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25270,32 +25270,32 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>128423621</v>
+        <v>128423612</v>
       </c>
       <c r="B246" t="n">
-        <v>82873</v>
+        <v>58097</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>1312</v>
+        <v>103015</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -25305,10 +25305,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>634525</v>
+        <v>634913</v>
       </c>
       <c r="R246" t="n">
-        <v>7087295</v>
+        <v>7087585</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25367,32 +25367,32 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>128423612</v>
+        <v>128423621</v>
       </c>
       <c r="B247" t="n">
-        <v>58097</v>
+        <v>82873</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>103015</v>
+        <v>1312</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -25402,10 +25402,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>634913</v>
+        <v>634525</v>
       </c>
       <c r="R247" t="n">
-        <v>7087585</v>
+        <v>7087295</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25464,10 +25464,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>128423606</v>
+        <v>128423618</v>
       </c>
       <c r="B248" t="n">
-        <v>80146</v>
+        <v>91560</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -25475,23 +25475,19 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr"/>
       <c r="I248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
@@ -25499,10 +25495,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>635122</v>
+        <v>634676</v>
       </c>
       <c r="R248" t="n">
-        <v>7087242</v>
+        <v>7087616</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25561,30 +25557,34 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>128423618</v>
+        <v>128423575</v>
       </c>
       <c r="B249" t="n">
-        <v>91560</v>
+        <v>91504</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr"/>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
       <c r="I249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
@@ -25592,10 +25592,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>634676</v>
+        <v>634574</v>
       </c>
       <c r="R249" t="n">
-        <v>7087616</v>
+        <v>7087286</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25654,32 +25654,32 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>128423575</v>
+        <v>128423606</v>
       </c>
       <c r="B250" t="n">
-        <v>91504</v>
+        <v>80146</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -25689,10 +25689,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>634574</v>
+        <v>635122</v>
       </c>
       <c r="R250" t="n">
-        <v>7087286</v>
+        <v>7087242</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -25751,10 +25751,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>128423615</v>
+        <v>128423624</v>
       </c>
       <c r="B251" t="n">
-        <v>91554</v>
+        <v>88940</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -25762,21 +25762,21 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>1204</v>
+        <v>510</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -25786,10 +25786,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>634897</v>
+        <v>634461</v>
       </c>
       <c r="R251" t="n">
-        <v>7087591</v>
+        <v>7087363</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -25945,10 +25945,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>128423624</v>
+        <v>128423615</v>
       </c>
       <c r="B253" t="n">
-        <v>88940</v>
+        <v>91554</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -25956,21 +25956,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>510</v>
+        <v>1204</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -25980,10 +25980,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>634461</v>
+        <v>634897</v>
       </c>
       <c r="R253" t="n">
-        <v>7087363</v>
+        <v>7087591</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26042,34 +26042,30 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128423593</v>
+        <v>128423617</v>
       </c>
       <c r="B254" t="n">
-        <v>80175</v>
+        <v>91560</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr"/>
       <c r="I254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
@@ -26077,10 +26073,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>635471</v>
+        <v>634507</v>
       </c>
       <c r="R254" t="n">
-        <v>7087281</v>
+        <v>7087328</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26139,10 +26135,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>128423629</v>
+        <v>128423593</v>
       </c>
       <c r="B255" t="n">
-        <v>80181</v>
+        <v>80175</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -26150,21 +26146,21 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -26174,10 +26170,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>635454</v>
+        <v>635471</v>
       </c>
       <c r="R255" t="n">
-        <v>7087257</v>
+        <v>7087281</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26236,32 +26232,32 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>128423622</v>
+        <v>128423629</v>
       </c>
       <c r="B256" t="n">
-        <v>88940</v>
+        <v>80181</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>510</v>
+        <v>6463</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -26271,10 +26267,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>634642</v>
+        <v>635454</v>
       </c>
       <c r="R256" t="n">
-        <v>7087251</v>
+        <v>7087257</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26333,7 +26329,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128423625</v>
+        <v>128423622</v>
       </c>
       <c r="B257" t="n">
         <v>88940</v>
@@ -26368,10 +26364,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>634494</v>
+        <v>634642</v>
       </c>
       <c r="R257" t="n">
-        <v>7087408</v>
+        <v>7087251</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -26430,10 +26426,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128423617</v>
+        <v>128423625</v>
       </c>
       <c r="B258" t="n">
-        <v>91560</v>
+        <v>88940</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -26441,19 +26437,23 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H258" t="inlineStr"/>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
       <c r="I258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
@@ -26461,10 +26461,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>634507</v>
+        <v>634494</v>
       </c>
       <c r="R258" t="n">
-        <v>7087328</v>
+        <v>7087408</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -26620,32 +26620,32 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>128423619</v>
+        <v>128423577</v>
       </c>
       <c r="B260" t="n">
-        <v>79041</v>
+        <v>91504</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -26655,10 +26655,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>635513</v>
+        <v>635153</v>
       </c>
       <c r="R260" t="n">
-        <v>7087316</v>
+        <v>7087180</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -26693,18 +26693,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC260" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD260" t="b">
         <v>0</v>
       </c>
       <c r="AE260" t="b">
         <v>0</v>
       </c>
-      <c r="AF260" t="inlineStr"/>
       <c r="AG260" t="b">
         <v>0</v>
       </c>
@@ -26723,34 +26717,30 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128423594</v>
+        <v>128423616</v>
       </c>
       <c r="B261" t="n">
-        <v>80175</v>
+        <v>91560</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr"/>
       <c r="I261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
@@ -26758,10 +26748,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>634527</v>
+        <v>634993</v>
       </c>
       <c r="R261" t="n">
-        <v>7087301</v>
+        <v>7087294</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26820,7 +26810,7 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128423620</v>
+        <v>128423619</v>
       </c>
       <c r="B262" t="n">
         <v>79041</v>
@@ -26855,10 +26845,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>634756</v>
+        <v>635513</v>
       </c>
       <c r="R262" t="n">
-        <v>7087642</v>
+        <v>7087316</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -26893,12 +26883,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC262" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD262" t="b">
         <v>0</v>
       </c>
       <c r="AE262" t="b">
         <v>0</v>
       </c>
+      <c r="AF262" t="inlineStr"/>
       <c r="AG262" t="b">
         <v>0</v>
       </c>
@@ -26917,10 +26913,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>128423577</v>
+        <v>128423594</v>
       </c>
       <c r="B263" t="n">
-        <v>91504</v>
+        <v>80175</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -26928,21 +26924,21 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -26952,10 +26948,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>635153</v>
+        <v>634527</v>
       </c>
       <c r="R263" t="n">
-        <v>7087180</v>
+        <v>7087301</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27014,10 +27010,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>128423616</v>
+        <v>128423620</v>
       </c>
       <c r="B264" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -27025,19 +27021,23 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H264" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
@@ -27045,10 +27045,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>634993</v>
+        <v>634756</v>
       </c>
       <c r="R264" t="n">
-        <v>7087294</v>
+        <v>7087642</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27107,10 +27107,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>128492197</v>
+        <v>128423585</v>
       </c>
       <c r="B265" t="n">
-        <v>95931</v>
+        <v>92258</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -27118,38 +27118,34 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>2809</v>
+        <v>3298</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
-      <c r="J265" t="inlineStr"/>
-      <c r="K265" t="inlineStr"/>
-      <c r="L265" t="inlineStr"/>
-      <c r="N265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>635110</v>
+        <v>634942</v>
       </c>
       <c r="R265" t="n">
-        <v>7087251</v>
+        <v>7087590</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27190,7 +27186,6 @@
       <c r="AE265" t="b">
         <v>0</v>
       </c>
-      <c r="AF265" t="inlineStr"/>
       <c r="AG265" t="b">
         <v>0</v>
       </c>
@@ -27209,10 +27204,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>128423585</v>
+        <v>128492197</v>
       </c>
       <c r="B266" t="n">
-        <v>92258</v>
+        <v>95932</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -27220,34 +27215,38 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>3298</v>
+        <v>2809</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
+      <c r="J266" t="inlineStr"/>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr"/>
+      <c r="N266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>634942</v>
+        <v>635110</v>
       </c>
       <c r="R266" t="n">
-        <v>7087590</v>
+        <v>7087251</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -27288,6 +27287,7 @@
       <c r="AE266" t="b">
         <v>0</v>
       </c>
+      <c r="AF266" t="inlineStr"/>
       <c r="AG266" t="b">
         <v>0</v>
       </c>
@@ -27306,32 +27306,32 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>128423602</v>
+        <v>128423578</v>
       </c>
       <c r="B267" t="n">
-        <v>57727</v>
+        <v>91504</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -27341,7 +27341,7 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>635210</v>
+        <v>635327</v>
       </c>
       <c r="R267" t="n">
         <v>7087158</v>
@@ -27377,11 +27377,6 @@
       <c r="AA267" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC267" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -27408,10 +27403,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>128423607</v>
+        <v>128423602</v>
       </c>
       <c r="B268" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -27419,21 +27414,21 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -27443,10 +27438,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>635459</v>
+        <v>635210</v>
       </c>
       <c r="R268" t="n">
-        <v>7087231</v>
+        <v>7087158</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -27479,6 +27474,11 @@
       <c r="AA268" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC268" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -27505,32 +27505,32 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>128423578</v>
+        <v>128423607</v>
       </c>
       <c r="B269" t="n">
-        <v>91504</v>
+        <v>80146</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -27540,10 +27540,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>635327</v>
+        <v>635459</v>
       </c>
       <c r="R269" t="n">
-        <v>7087158</v>
+        <v>7087231</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -27605,7 +27605,7 @@
         <v>128423572</v>
       </c>
       <c r="B270" t="n">
-        <v>96951</v>
+        <v>96952</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -27699,49 +27699,45 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>128423603</v>
+        <v>128423576</v>
       </c>
       <c r="B271" t="n">
-        <v>57727</v>
+        <v>91504</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
-      <c r="K271" t="inlineStr"/>
-      <c r="L271" t="inlineStr"/>
-      <c r="M271" t="inlineStr"/>
-      <c r="N271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>635240</v>
+        <v>634705</v>
       </c>
       <c r="R271" t="n">
-        <v>7087224</v>
+        <v>7087668</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -27774,11 +27770,6 @@
       <c r="AA271" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC271" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -27805,10 +27796,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>128423614</v>
+        <v>128423603</v>
       </c>
       <c r="B272" t="n">
-        <v>91554</v>
+        <v>57727</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -27816,34 +27807,38 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="inlineStr"/>
+      <c r="N272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>634673</v>
+        <v>635240</v>
       </c>
       <c r="R272" t="n">
-        <v>7087631</v>
+        <v>7087224</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -27876,6 +27871,11 @@
       <c r="AA272" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC272" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -27902,32 +27902,32 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>128423576</v>
+        <v>128423614</v>
       </c>
       <c r="B273" t="n">
-        <v>91504</v>
+        <v>91554</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
@@ -27937,10 +27937,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>634705</v>
+        <v>634673</v>
       </c>
       <c r="R273" t="n">
-        <v>7087668</v>
+        <v>7087631</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -27999,32 +27999,32 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>128423592</v>
+        <v>128423598</v>
       </c>
       <c r="B274" t="n">
-        <v>80175</v>
+        <v>80147</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -28034,10 +28034,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>635454</v>
+        <v>635632</v>
       </c>
       <c r="R274" t="n">
-        <v>7087257</v>
+        <v>7087270</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28096,32 +28096,32 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>128423598</v>
+        <v>128423599</v>
       </c>
       <c r="B275" t="n">
-        <v>80147</v>
+        <v>91993</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>2081</v>
+        <v>1209</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -28131,10 +28131,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>635632</v>
+        <v>635464</v>
       </c>
       <c r="R275" t="n">
-        <v>7087270</v>
+        <v>7087275</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -28193,32 +28193,32 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>128423599</v>
+        <v>128423592</v>
       </c>
       <c r="B276" t="n">
-        <v>91993</v>
+        <v>80175</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>1209</v>
+        <v>6462</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -28228,10 +28228,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>635464</v>
+        <v>635454</v>
       </c>
       <c r="R276" t="n">
-        <v>7087275</v>
+        <v>7087257</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -28293,7 +28293,7 @@
         <v>128423604</v>
       </c>
       <c r="B277" t="n">
-        <v>95931</v>
+        <v>95932</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -28387,10 +28387,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>128423590</v>
+        <v>128423596</v>
       </c>
       <c r="B278" t="n">
-        <v>92814</v>
+        <v>57724</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -28398,21 +28398,21 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>4361</v>
+        <v>100049</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
@@ -28422,10 +28422,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>635182</v>
+        <v>634648</v>
       </c>
       <c r="R278" t="n">
-        <v>7087227</v>
+        <v>7087590</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -28484,10 +28484,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>128423596</v>
+        <v>128423590</v>
       </c>
       <c r="B279" t="n">
-        <v>57724</v>
+        <v>92814</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -28495,21 +28495,21 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>100049</v>
+        <v>4361</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
@@ -28519,10 +28519,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>634648</v>
+        <v>635182</v>
       </c>
       <c r="R279" t="n">
-        <v>7087590</v>
+        <v>7087227</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -28969,32 +28969,32 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>128423574</v>
+        <v>128423601</v>
       </c>
       <c r="B284" t="n">
-        <v>91504</v>
+        <v>91838</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -29004,10 +29004,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>634571</v>
+        <v>634475</v>
       </c>
       <c r="R284" t="n">
-        <v>7087253</v>
+        <v>7087365</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -29066,32 +29066,32 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>128423601</v>
+        <v>128423574</v>
       </c>
       <c r="B285" t="n">
-        <v>91838</v>
+        <v>91504</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -29101,10 +29101,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>634475</v>
+        <v>634571</v>
       </c>
       <c r="R285" t="n">
-        <v>7087365</v>
+        <v>7087253</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>

--- a/artfynd/A 30047-2025 artfynd.xlsx
+++ b/artfynd/A 30047-2025 artfynd.xlsx
@@ -24400,7 +24400,7 @@
         <v>128651017</v>
       </c>
       <c r="B237" t="n">
-        <v>97047</v>
+        <v>97051</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>128651018</v>
       </c>
       <c r="B238" t="n">
-        <v>95944</v>
+        <v>95948</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24594,7 +24594,7 @@
         <v>128423582</v>
       </c>
       <c r="B239" t="n">
-        <v>91835</v>
+        <v>91838</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         <v>128423605</v>
       </c>
       <c r="B240" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -24788,7 +24788,7 @@
         <v>128423608</v>
       </c>
       <c r="B241" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24882,32 +24882,32 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>128423573</v>
+        <v>128423623</v>
       </c>
       <c r="B242" t="n">
-        <v>91504</v>
+        <v>88943</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -24917,10 +24917,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>634599</v>
+        <v>634583</v>
       </c>
       <c r="R242" t="n">
-        <v>7087225</v>
+        <v>7087261</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24979,32 +24979,32 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>128423623</v>
+        <v>128423573</v>
       </c>
       <c r="B243" t="n">
-        <v>88940</v>
+        <v>91507</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -25014,10 +25014,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>634583</v>
+        <v>634599</v>
       </c>
       <c r="R243" t="n">
-        <v>7087261</v>
+        <v>7087225</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25076,10 +25076,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>128423597</v>
+        <v>128423621</v>
       </c>
       <c r="B244" t="n">
-        <v>57724</v>
+        <v>82877</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -25087,21 +25087,21 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -25111,10 +25111,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>634913</v>
+        <v>634525</v>
       </c>
       <c r="R244" t="n">
-        <v>7087585</v>
+        <v>7087295</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25176,7 +25176,7 @@
         <v>128423591</v>
       </c>
       <c r="B245" t="n">
-        <v>80175</v>
+        <v>80177</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -25270,27 +25270,27 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>128423612</v>
+        <v>128423597</v>
       </c>
       <c r="B246" t="n">
-        <v>58097</v>
+        <v>57724</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -25367,32 +25367,32 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>128423621</v>
+        <v>128423612</v>
       </c>
       <c r="B247" t="n">
-        <v>82873</v>
+        <v>58097</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>1312</v>
+        <v>103015</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -25402,10 +25402,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>634525</v>
+        <v>634913</v>
       </c>
       <c r="R247" t="n">
-        <v>7087295</v>
+        <v>7087585</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25467,7 +25467,7 @@
         <v>128423618</v>
       </c>
       <c r="B248" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -25560,7 +25560,7 @@
         <v>128423575</v>
       </c>
       <c r="B249" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>128423606</v>
       </c>
       <c r="B250" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -25754,7 +25754,7 @@
         <v>128423624</v>
       </c>
       <c r="B251" t="n">
-        <v>88940</v>
+        <v>88943</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -25848,32 +25848,32 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>128423628</v>
+        <v>128423615</v>
       </c>
       <c r="B252" t="n">
-        <v>80181</v>
+        <v>91557</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>6463</v>
+        <v>1204</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -25883,10 +25883,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>635451</v>
+        <v>634897</v>
       </c>
       <c r="R252" t="n">
-        <v>7087225</v>
+        <v>7087591</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -25945,32 +25945,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>128423615</v>
+        <v>128423628</v>
       </c>
       <c r="B253" t="n">
-        <v>91554</v>
+        <v>80183</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>1204</v>
+        <v>6463</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -25980,10 +25980,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>634897</v>
+        <v>635451</v>
       </c>
       <c r="R253" t="n">
-        <v>7087591</v>
+        <v>7087225</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26042,30 +26042,34 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128423617</v>
+        <v>128423593</v>
       </c>
       <c r="B254" t="n">
-        <v>91560</v>
+        <v>80177</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H254" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
@@ -26073,10 +26077,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>634507</v>
+        <v>635471</v>
       </c>
       <c r="R254" t="n">
-        <v>7087328</v>
+        <v>7087281</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26135,10 +26139,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>128423593</v>
+        <v>128423629</v>
       </c>
       <c r="B255" t="n">
-        <v>80175</v>
+        <v>80183</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -26146,21 +26150,21 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -26170,10 +26174,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>635471</v>
+        <v>635454</v>
       </c>
       <c r="R255" t="n">
-        <v>7087281</v>
+        <v>7087257</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26232,32 +26236,32 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>128423629</v>
+        <v>128423622</v>
       </c>
       <c r="B256" t="n">
-        <v>80181</v>
+        <v>88943</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>6463</v>
+        <v>510</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -26267,10 +26271,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>635454</v>
+        <v>634642</v>
       </c>
       <c r="R256" t="n">
-        <v>7087257</v>
+        <v>7087251</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26329,10 +26333,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128423622</v>
+        <v>128423625</v>
       </c>
       <c r="B257" t="n">
-        <v>88940</v>
+        <v>88943</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -26364,10 +26368,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>634642</v>
+        <v>634494</v>
       </c>
       <c r="R257" t="n">
-        <v>7087251</v>
+        <v>7087408</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -26426,10 +26430,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128423625</v>
+        <v>128423617</v>
       </c>
       <c r="B258" t="n">
-        <v>88940</v>
+        <v>91563</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -26437,23 +26441,19 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
-        </is>
-      </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
@@ -26461,10 +26461,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>634494</v>
+        <v>634507</v>
       </c>
       <c r="R258" t="n">
-        <v>7087408</v>
+        <v>7087328</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -26526,7 +26526,7 @@
         <v>128423626</v>
       </c>
       <c r="B259" t="n">
-        <v>88940</v>
+        <v>88943</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -26620,10 +26620,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>128423577</v>
+        <v>128423585</v>
       </c>
       <c r="B260" t="n">
-        <v>91504</v>
+        <v>92261</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -26631,21 +26631,21 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -26655,10 +26655,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>635153</v>
+        <v>634942</v>
       </c>
       <c r="R260" t="n">
-        <v>7087180</v>
+        <v>7087590</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -26717,41 +26717,49 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128423616</v>
+        <v>128492197</v>
       </c>
       <c r="B261" t="n">
-        <v>91560</v>
+        <v>95936</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H261" t="inlineStr"/>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
       <c r="I261" t="inlineStr"/>
+      <c r="J261" t="inlineStr"/>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
+      <c r="N261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>634993</v>
+        <v>635110</v>
       </c>
       <c r="R261" t="n">
-        <v>7087294</v>
+        <v>7087251</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26792,6 +26800,7 @@
       <c r="AE261" t="b">
         <v>0</v>
       </c>
+      <c r="AF261" t="inlineStr"/>
       <c r="AG261" t="b">
         <v>0</v>
       </c>
@@ -26810,32 +26819,32 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128423619</v>
+        <v>128423577</v>
       </c>
       <c r="B262" t="n">
-        <v>79041</v>
+        <v>91507</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -26845,10 +26854,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>635513</v>
+        <v>635153</v>
       </c>
       <c r="R262" t="n">
-        <v>7087316</v>
+        <v>7087180</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -26883,18 +26892,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC262" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD262" t="b">
         <v>0</v>
       </c>
       <c r="AE262" t="b">
         <v>0</v>
       </c>
-      <c r="AF262" t="inlineStr"/>
       <c r="AG262" t="b">
         <v>0</v>
       </c>
@@ -26913,34 +26916,30 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>128423594</v>
+        <v>128423616</v>
       </c>
       <c r="B263" t="n">
-        <v>80175</v>
+        <v>91563</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr"/>
       <c r="I263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
@@ -26948,10 +26947,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>634527</v>
+        <v>634993</v>
       </c>
       <c r="R263" t="n">
-        <v>7087301</v>
+        <v>7087294</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27010,10 +27009,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>128423620</v>
+        <v>128423619</v>
       </c>
       <c r="B264" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -27045,10 +27044,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>634756</v>
+        <v>635513</v>
       </c>
       <c r="R264" t="n">
-        <v>7087642</v>
+        <v>7087316</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27083,12 +27082,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD264" t="b">
         <v>0</v>
       </c>
       <c r="AE264" t="b">
         <v>0</v>
       </c>
+      <c r="AF264" t="inlineStr"/>
       <c r="AG264" t="b">
         <v>0</v>
       </c>
@@ -27107,10 +27112,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>128423585</v>
+        <v>128423594</v>
       </c>
       <c r="B265" t="n">
-        <v>92258</v>
+        <v>80177</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -27118,21 +27123,21 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -27142,10 +27147,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>634942</v>
+        <v>634527</v>
       </c>
       <c r="R265" t="n">
-        <v>7087590</v>
+        <v>7087301</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27204,49 +27209,45 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>128492197</v>
+        <v>128423620</v>
       </c>
       <c r="B266" t="n">
-        <v>95932</v>
+        <v>79043</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
-      <c r="J266" t="inlineStr"/>
-      <c r="K266" t="inlineStr"/>
-      <c r="L266" t="inlineStr"/>
-      <c r="N266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>635110</v>
+        <v>634756</v>
       </c>
       <c r="R266" t="n">
-        <v>7087251</v>
+        <v>7087642</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -27287,7 +27288,6 @@
       <c r="AE266" t="b">
         <v>0</v>
       </c>
-      <c r="AF266" t="inlineStr"/>
       <c r="AG266" t="b">
         <v>0</v>
       </c>
@@ -27309,7 +27309,7 @@
         <v>128423578</v>
       </c>
       <c r="B267" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>128423607</v>
       </c>
       <c r="B269" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>128423572</v>
       </c>
       <c r="B270" t="n">
-        <v>96952</v>
+        <v>96956</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -27699,45 +27699,49 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>128423576</v>
+        <v>128423603</v>
       </c>
       <c r="B271" t="n">
-        <v>91504</v>
+        <v>57727</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr"/>
+      <c r="M271" t="inlineStr"/>
+      <c r="N271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>634705</v>
+        <v>635240</v>
       </c>
       <c r="R271" t="n">
-        <v>7087668</v>
+        <v>7087224</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -27770,6 +27774,11 @@
       <c r="AA271" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -27796,10 +27805,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>128423603</v>
+        <v>128423614</v>
       </c>
       <c r="B272" t="n">
-        <v>57727</v>
+        <v>91557</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -27807,38 +27816,34 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="inlineStr"/>
-      <c r="N272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>635240</v>
+        <v>634673</v>
       </c>
       <c r="R272" t="n">
-        <v>7087224</v>
+        <v>7087631</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -27871,11 +27876,6 @@
       <c r="AA272" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC272" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -27902,32 +27902,32 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>128423614</v>
+        <v>128423576</v>
       </c>
       <c r="B273" t="n">
-        <v>91554</v>
+        <v>91507</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
@@ -27937,10 +27937,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>634673</v>
+        <v>634705</v>
       </c>
       <c r="R273" t="n">
-        <v>7087631</v>
+        <v>7087668</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -28002,7 +28002,7 @@
         <v>128423598</v>
       </c>
       <c r="B274" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -28096,32 +28096,32 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>128423599</v>
+        <v>128423592</v>
       </c>
       <c r="B275" t="n">
-        <v>91993</v>
+        <v>80177</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>1209</v>
+        <v>6462</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -28131,10 +28131,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>635464</v>
+        <v>635454</v>
       </c>
       <c r="R275" t="n">
-        <v>7087275</v>
+        <v>7087257</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -28193,32 +28193,32 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>128423592</v>
+        <v>128423599</v>
       </c>
       <c r="B276" t="n">
-        <v>80175</v>
+        <v>91996</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>6462</v>
+        <v>1209</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -28228,10 +28228,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>635454</v>
+        <v>635464</v>
       </c>
       <c r="R276" t="n">
-        <v>7087257</v>
+        <v>7087275</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -28293,7 +28293,7 @@
         <v>128423604</v>
       </c>
       <c r="B277" t="n">
-        <v>95932</v>
+        <v>95936</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -28484,10 +28484,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>128423590</v>
+        <v>128423588</v>
       </c>
       <c r="B279" t="n">
-        <v>92814</v>
+        <v>57887</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -28495,21 +28495,21 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>4361</v>
+        <v>103021</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
@@ -28519,10 +28519,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>635182</v>
+        <v>634560</v>
       </c>
       <c r="R279" t="n">
-        <v>7087227</v>
+        <v>7087311</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -28581,10 +28581,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>128423588</v>
+        <v>128423590</v>
       </c>
       <c r="B280" t="n">
-        <v>57887</v>
+        <v>92817</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -28592,21 +28592,21 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -28616,10 +28616,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>634560</v>
+        <v>635182</v>
       </c>
       <c r="R280" t="n">
-        <v>7087311</v>
+        <v>7087227</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -28681,7 +28681,7 @@
         <v>128423580</v>
       </c>
       <c r="B281" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -28778,7 +28778,7 @@
         <v>128423579</v>
       </c>
       <c r="B282" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -28875,7 +28875,7 @@
         <v>128423595</v>
       </c>
       <c r="B283" t="n">
-        <v>80175</v>
+        <v>80177</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -28969,32 +28969,32 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>128423601</v>
+        <v>128423574</v>
       </c>
       <c r="B284" t="n">
-        <v>91838</v>
+        <v>91507</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -29004,10 +29004,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>634475</v>
+        <v>634571</v>
       </c>
       <c r="R284" t="n">
-        <v>7087365</v>
+        <v>7087253</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -29066,32 +29066,32 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>128423574</v>
+        <v>128423601</v>
       </c>
       <c r="B285" t="n">
-        <v>91504</v>
+        <v>91841</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -29101,10 +29101,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>634571</v>
+        <v>634475</v>
       </c>
       <c r="R285" t="n">
-        <v>7087253</v>
+        <v>7087365</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -29166,7 +29166,7 @@
         <v>128423613</v>
       </c>
       <c r="B286" t="n">
-        <v>91554</v>
+        <v>91557</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>

--- a/artfynd/A 30047-2025 artfynd.xlsx
+++ b/artfynd/A 30047-2025 artfynd.xlsx
@@ -26620,32 +26620,32 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>128423585</v>
+        <v>128423619</v>
       </c>
       <c r="B260" t="n">
-        <v>92261</v>
+        <v>79043</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -26655,10 +26655,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>634942</v>
+        <v>635513</v>
       </c>
       <c r="R260" t="n">
-        <v>7087590</v>
+        <v>7087316</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -26693,12 +26693,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC260" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD260" t="b">
         <v>0</v>
       </c>
       <c r="AE260" t="b">
         <v>0</v>
       </c>
+      <c r="AF260" t="inlineStr"/>
       <c r="AG260" t="b">
         <v>0</v>
       </c>
@@ -26717,10 +26723,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128492197</v>
+        <v>128423594</v>
       </c>
       <c r="B261" t="n">
-        <v>95936</v>
+        <v>80177</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -26728,38 +26734,34 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>2809</v>
+        <v>6462</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
-      <c r="J261" t="inlineStr"/>
-      <c r="K261" t="inlineStr"/>
-      <c r="L261" t="inlineStr"/>
-      <c r="N261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>635110</v>
+        <v>634527</v>
       </c>
       <c r="R261" t="n">
-        <v>7087251</v>
+        <v>7087301</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26800,7 +26802,6 @@
       <c r="AE261" t="b">
         <v>0</v>
       </c>
-      <c r="AF261" t="inlineStr"/>
       <c r="AG261" t="b">
         <v>0</v>
       </c>
@@ -26819,32 +26820,32 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128423577</v>
+        <v>128423620</v>
       </c>
       <c r="B262" t="n">
-        <v>91507</v>
+        <v>79043</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -26854,10 +26855,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>635153</v>
+        <v>634756</v>
       </c>
       <c r="R262" t="n">
-        <v>7087180</v>
+        <v>7087642</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -26916,30 +26917,34 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>128423616</v>
+        <v>128423577</v>
       </c>
       <c r="B263" t="n">
-        <v>91563</v>
+        <v>91507</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H263" t="inlineStr"/>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
       <c r="I263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
@@ -26947,10 +26952,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>634993</v>
+        <v>635153</v>
       </c>
       <c r="R263" t="n">
-        <v>7087294</v>
+        <v>7087180</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27009,10 +27014,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>128423619</v>
+        <v>128423616</v>
       </c>
       <c r="B264" t="n">
-        <v>79043</v>
+        <v>91563</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -27020,23 +27025,19 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr"/>
       <c r="I264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
@@ -27044,10 +27045,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>635513</v>
+        <v>634993</v>
       </c>
       <c r="R264" t="n">
-        <v>7087316</v>
+        <v>7087294</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27082,18 +27083,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC264" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD264" t="b">
         <v>0</v>
       </c>
       <c r="AE264" t="b">
         <v>0</v>
       </c>
-      <c r="AF264" t="inlineStr"/>
       <c r="AG264" t="b">
         <v>0</v>
       </c>
@@ -27112,10 +27107,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>128423594</v>
+        <v>128423585</v>
       </c>
       <c r="B265" t="n">
-        <v>80177</v>
+        <v>92261</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -27123,21 +27118,21 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -27147,10 +27142,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>634527</v>
+        <v>634942</v>
       </c>
       <c r="R265" t="n">
-        <v>7087301</v>
+        <v>7087590</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27209,45 +27204,49 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>128423620</v>
+        <v>128492197</v>
       </c>
       <c r="B266" t="n">
-        <v>79043</v>
+        <v>95936</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
+      <c r="J266" t="inlineStr"/>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr"/>
+      <c r="N266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>634756</v>
+        <v>635110</v>
       </c>
       <c r="R266" t="n">
-        <v>7087642</v>
+        <v>7087251</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -27288,6 +27287,7 @@
       <c r="AE266" t="b">
         <v>0</v>
       </c>
+      <c r="AF266" t="inlineStr"/>
       <c r="AG266" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 30047-2025 artfynd.xlsx
+++ b/artfynd/A 30047-2025 artfynd.xlsx
@@ -24400,7 +24400,7 @@
         <v>128651017</v>
       </c>
       <c r="B237" t="n">
-        <v>97051</v>
+        <v>97053</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>128651018</v>
       </c>
       <c r="B238" t="n">
-        <v>95948</v>
+        <v>95950</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24594,7 +24594,7 @@
         <v>128423582</v>
       </c>
       <c r="B239" t="n">
-        <v>91838</v>
+        <v>91840</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         <v>128423605</v>
       </c>
       <c r="B240" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -24788,7 +24788,7 @@
         <v>128423608</v>
       </c>
       <c r="B241" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>128423623</v>
       </c>
       <c r="B242" t="n">
-        <v>88943</v>
+        <v>88945</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>128423573</v>
       </c>
       <c r="B243" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -25076,32 +25076,32 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>128423621</v>
+        <v>128423591</v>
       </c>
       <c r="B244" t="n">
-        <v>82877</v>
+        <v>80178</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -25111,10 +25111,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>634525</v>
+        <v>635451</v>
       </c>
       <c r="R244" t="n">
-        <v>7087295</v>
+        <v>7087225</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25173,32 +25173,32 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>128423591</v>
+        <v>128423597</v>
       </c>
       <c r="B245" t="n">
-        <v>80177</v>
+        <v>57724</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -25208,10 +25208,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>635451</v>
+        <v>634913</v>
       </c>
       <c r="R245" t="n">
-        <v>7087225</v>
+        <v>7087585</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25270,10 +25270,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>128423597</v>
+        <v>128423621</v>
       </c>
       <c r="B246" t="n">
-        <v>57724</v>
+        <v>82878</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -25281,21 +25281,21 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -25305,10 +25305,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>634913</v>
+        <v>634525</v>
       </c>
       <c r="R246" t="n">
-        <v>7087585</v>
+        <v>7087295</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25467,7 +25467,7 @@
         <v>128423618</v>
       </c>
       <c r="B248" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -25560,7 +25560,7 @@
         <v>128423575</v>
       </c>
       <c r="B249" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>128423606</v>
       </c>
       <c r="B250" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -25751,10 +25751,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>128423624</v>
+        <v>128423615</v>
       </c>
       <c r="B251" t="n">
-        <v>88943</v>
+        <v>91559</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -25762,21 +25762,21 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>510</v>
+        <v>1204</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -25786,10 +25786,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>634461</v>
+        <v>634897</v>
       </c>
       <c r="R251" t="n">
-        <v>7087363</v>
+        <v>7087591</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -25848,10 +25848,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>128423615</v>
+        <v>128423624</v>
       </c>
       <c r="B252" t="n">
-        <v>91557</v>
+        <v>88945</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -25859,21 +25859,21 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>1204</v>
+        <v>510</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -25883,10 +25883,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>634897</v>
+        <v>634461</v>
       </c>
       <c r="R252" t="n">
-        <v>7087591</v>
+        <v>7087363</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -25948,7 +25948,7 @@
         <v>128423628</v>
       </c>
       <c r="B253" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>128423593</v>
       </c>
       <c r="B254" t="n">
-        <v>80177</v>
+        <v>80178</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         <v>128423629</v>
       </c>
       <c r="B255" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -26239,7 +26239,7 @@
         <v>128423622</v>
       </c>
       <c r="B256" t="n">
-        <v>88943</v>
+        <v>88945</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -26336,7 +26336,7 @@
         <v>128423625</v>
       </c>
       <c r="B257" t="n">
-        <v>88943</v>
+        <v>88945</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>128423617</v>
       </c>
       <c r="B258" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>128423626</v>
       </c>
       <c r="B259" t="n">
-        <v>88943</v>
+        <v>88945</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -26620,32 +26620,32 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>128423619</v>
+        <v>128423585</v>
       </c>
       <c r="B260" t="n">
-        <v>79043</v>
+        <v>92263</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -26655,10 +26655,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>635513</v>
+        <v>634942</v>
       </c>
       <c r="R260" t="n">
-        <v>7087316</v>
+        <v>7087590</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -26693,18 +26693,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC260" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD260" t="b">
         <v>0</v>
       </c>
       <c r="AE260" t="b">
         <v>0</v>
       </c>
-      <c r="AF260" t="inlineStr"/>
       <c r="AG260" t="b">
         <v>0</v>
       </c>
@@ -26723,32 +26717,32 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128423594</v>
+        <v>128423619</v>
       </c>
       <c r="B261" t="n">
-        <v>80177</v>
+        <v>79044</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -26758,10 +26752,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>634527</v>
+        <v>635513</v>
       </c>
       <c r="R261" t="n">
-        <v>7087301</v>
+        <v>7087316</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26796,12 +26790,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD261" t="b">
         <v>0</v>
       </c>
       <c r="AE261" t="b">
         <v>0</v>
       </c>
+      <c r="AF261" t="inlineStr"/>
       <c r="AG261" t="b">
         <v>0</v>
       </c>
@@ -26823,7 +26823,7 @@
         <v>128423620</v>
       </c>
       <c r="B262" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -26917,10 +26917,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>128423577</v>
+        <v>128423594</v>
       </c>
       <c r="B263" t="n">
-        <v>91507</v>
+        <v>80178</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -26928,21 +26928,21 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -26952,10 +26952,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>635153</v>
+        <v>634527</v>
       </c>
       <c r="R263" t="n">
-        <v>7087180</v>
+        <v>7087301</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27014,30 +27014,34 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>128423616</v>
+        <v>128423577</v>
       </c>
       <c r="B264" t="n">
-        <v>91563</v>
+        <v>91509</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H264" t="inlineStr"/>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
       <c r="I264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
@@ -27045,10 +27049,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>634993</v>
+        <v>635153</v>
       </c>
       <c r="R264" t="n">
-        <v>7087294</v>
+        <v>7087180</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27107,34 +27111,30 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>128423585</v>
+        <v>128423616</v>
       </c>
       <c r="B265" t="n">
-        <v>92261</v>
+        <v>91565</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr"/>
       <c r="I265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
@@ -27142,10 +27142,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>634942</v>
+        <v>634993</v>
       </c>
       <c r="R265" t="n">
-        <v>7087590</v>
+        <v>7087294</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27207,7 +27207,7 @@
         <v>128492197</v>
       </c>
       <c r="B266" t="n">
-        <v>95936</v>
+        <v>95938</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -27306,32 +27306,32 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>128423578</v>
+        <v>128423602</v>
       </c>
       <c r="B267" t="n">
-        <v>91507</v>
+        <v>57727</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -27341,7 +27341,7 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>635327</v>
+        <v>635210</v>
       </c>
       <c r="R267" t="n">
         <v>7087158</v>
@@ -27377,6 +27377,11 @@
       <c r="AA267" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC267" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -27403,10 +27408,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>128423602</v>
+        <v>128423607</v>
       </c>
       <c r="B268" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -27414,21 +27419,21 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -27438,10 +27443,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>635210</v>
+        <v>635459</v>
       </c>
       <c r="R268" t="n">
-        <v>7087158</v>
+        <v>7087231</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -27474,11 +27479,6 @@
       <c r="AA268" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC268" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -27505,32 +27505,32 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>128423607</v>
+        <v>128423578</v>
       </c>
       <c r="B269" t="n">
-        <v>80148</v>
+        <v>91509</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -27540,10 +27540,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>635459</v>
+        <v>635327</v>
       </c>
       <c r="R269" t="n">
-        <v>7087231</v>
+        <v>7087158</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -27605,7 +27605,7 @@
         <v>128423572</v>
       </c>
       <c r="B270" t="n">
-        <v>96956</v>
+        <v>96958</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -27699,10 +27699,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>128423603</v>
+        <v>128423614</v>
       </c>
       <c r="B271" t="n">
-        <v>57727</v>
+        <v>91559</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -27710,38 +27710,34 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
-      <c r="K271" t="inlineStr"/>
-      <c r="L271" t="inlineStr"/>
-      <c r="M271" t="inlineStr"/>
-      <c r="N271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>635240</v>
+        <v>634673</v>
       </c>
       <c r="R271" t="n">
-        <v>7087224</v>
+        <v>7087631</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -27774,11 +27770,6 @@
       <c r="AA271" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC271" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -27805,32 +27796,32 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>128423614</v>
+        <v>128423576</v>
       </c>
       <c r="B272" t="n">
-        <v>91557</v>
+        <v>91509</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
@@ -27840,10 +27831,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>634673</v>
+        <v>634705</v>
       </c>
       <c r="R272" t="n">
-        <v>7087631</v>
+        <v>7087668</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -27902,45 +27893,49 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>128423576</v>
+        <v>128423603</v>
       </c>
       <c r="B273" t="n">
-        <v>91507</v>
+        <v>57727</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr"/>
+      <c r="N273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>634705</v>
+        <v>635240</v>
       </c>
       <c r="R273" t="n">
-        <v>7087668</v>
+        <v>7087224</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -27973,6 +27968,11 @@
       <c r="AA273" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -27999,32 +27999,32 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>128423598</v>
+        <v>128423592</v>
       </c>
       <c r="B274" t="n">
-        <v>80149</v>
+        <v>80178</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -28034,10 +28034,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>635632</v>
+        <v>635454</v>
       </c>
       <c r="R274" t="n">
-        <v>7087270</v>
+        <v>7087257</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28096,32 +28096,32 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>128423592</v>
+        <v>128423599</v>
       </c>
       <c r="B275" t="n">
-        <v>80177</v>
+        <v>91998</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>6462</v>
+        <v>1209</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -28131,10 +28131,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>635454</v>
+        <v>635464</v>
       </c>
       <c r="R275" t="n">
-        <v>7087257</v>
+        <v>7087275</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -28193,32 +28193,32 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>128423599</v>
+        <v>128423598</v>
       </c>
       <c r="B276" t="n">
-        <v>91996</v>
+        <v>80150</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>1209</v>
+        <v>2081</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -28228,10 +28228,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>635464</v>
+        <v>635632</v>
       </c>
       <c r="R276" t="n">
-        <v>7087275</v>
+        <v>7087270</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -28293,7 +28293,7 @@
         <v>128423604</v>
       </c>
       <c r="B277" t="n">
-        <v>95936</v>
+        <v>95938</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -28387,10 +28387,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>128423596</v>
+        <v>128423590</v>
       </c>
       <c r="B278" t="n">
-        <v>57724</v>
+        <v>92819</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -28398,21 +28398,21 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>100049</v>
+        <v>4361</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
@@ -28422,10 +28422,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>634648</v>
+        <v>635182</v>
       </c>
       <c r="R278" t="n">
-        <v>7087590</v>
+        <v>7087227</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -28484,10 +28484,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>128423588</v>
+        <v>128423596</v>
       </c>
       <c r="B279" t="n">
-        <v>57887</v>
+        <v>57724</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -28495,21 +28495,21 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
@@ -28519,10 +28519,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>634560</v>
+        <v>634648</v>
       </c>
       <c r="R279" t="n">
-        <v>7087311</v>
+        <v>7087590</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -28581,10 +28581,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>128423590</v>
+        <v>128423588</v>
       </c>
       <c r="B280" t="n">
-        <v>92817</v>
+        <v>57887</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -28592,21 +28592,21 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>4361</v>
+        <v>103021</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -28616,10 +28616,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>635182</v>
+        <v>634560</v>
       </c>
       <c r="R280" t="n">
-        <v>7087227</v>
+        <v>7087311</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -28681,7 +28681,7 @@
         <v>128423580</v>
       </c>
       <c r="B281" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -28778,7 +28778,7 @@
         <v>128423579</v>
       </c>
       <c r="B282" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -28875,7 +28875,7 @@
         <v>128423595</v>
       </c>
       <c r="B283" t="n">
-        <v>80177</v>
+        <v>80178</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -28969,32 +28969,32 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>128423574</v>
+        <v>128423601</v>
       </c>
       <c r="B284" t="n">
-        <v>91507</v>
+        <v>91843</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -29004,10 +29004,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>634571</v>
+        <v>634475</v>
       </c>
       <c r="R284" t="n">
-        <v>7087253</v>
+        <v>7087365</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -29066,32 +29066,32 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>128423601</v>
+        <v>128423574</v>
       </c>
       <c r="B285" t="n">
-        <v>91841</v>
+        <v>91509</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -29101,10 +29101,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>634475</v>
+        <v>634571</v>
       </c>
       <c r="R285" t="n">
-        <v>7087365</v>
+        <v>7087253</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -29166,7 +29166,7 @@
         <v>128423613</v>
       </c>
       <c r="B286" t="n">
-        <v>91557</v>
+        <v>91559</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>

--- a/artfynd/A 30047-2025 artfynd.xlsx
+++ b/artfynd/A 30047-2025 artfynd.xlsx
@@ -24400,7 +24400,7 @@
         <v>128651017</v>
       </c>
       <c r="B237" t="n">
-        <v>97053</v>
+        <v>97057</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>128651018</v>
       </c>
       <c r="B238" t="n">
-        <v>95950</v>
+        <v>95954</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24591,10 +24591,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>128423582</v>
+        <v>128423605</v>
       </c>
       <c r="B239" t="n">
-        <v>91840</v>
+        <v>80149</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -24602,21 +24602,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>73</v>
+        <v>6458</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -24626,10 +24626,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>635466</v>
+        <v>635331</v>
       </c>
       <c r="R239" t="n">
-        <v>7087277</v>
+        <v>7087194</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24688,7 +24688,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>128423605</v>
+        <v>128423608</v>
       </c>
       <c r="B240" t="n">
         <v>80149</v>
@@ -24723,10 +24723,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>635331</v>
+        <v>635603</v>
       </c>
       <c r="R240" t="n">
-        <v>7087194</v>
+        <v>7087226</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24785,10 +24785,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>128423608</v>
+        <v>128423582</v>
       </c>
       <c r="B241" t="n">
-        <v>80149</v>
+        <v>91844</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24796,21 +24796,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6458</v>
+        <v>73</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -24820,10 +24820,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>635603</v>
+        <v>635466</v>
       </c>
       <c r="R241" t="n">
-        <v>7087226</v>
+        <v>7087277</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -24882,32 +24882,32 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>128423623</v>
+        <v>128423573</v>
       </c>
       <c r="B242" t="n">
-        <v>88945</v>
+        <v>91513</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -24917,10 +24917,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>634583</v>
+        <v>634599</v>
       </c>
       <c r="R242" t="n">
-        <v>7087261</v>
+        <v>7087225</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24979,32 +24979,32 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>128423573</v>
+        <v>128423623</v>
       </c>
       <c r="B243" t="n">
-        <v>91509</v>
+        <v>88949</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -25014,10 +25014,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>634599</v>
+        <v>634583</v>
       </c>
       <c r="R243" t="n">
-        <v>7087225</v>
+        <v>7087261</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25076,32 +25076,32 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>128423591</v>
+        <v>128423621</v>
       </c>
       <c r="B244" t="n">
-        <v>80178</v>
+        <v>82878</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -25111,10 +25111,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>635451</v>
+        <v>634525</v>
       </c>
       <c r="R244" t="n">
-        <v>7087225</v>
+        <v>7087295</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25270,32 +25270,32 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>128423621</v>
+        <v>128423591</v>
       </c>
       <c r="B246" t="n">
-        <v>82878</v>
+        <v>80178</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -25305,10 +25305,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>634525</v>
+        <v>635451</v>
       </c>
       <c r="R246" t="n">
-        <v>7087295</v>
+        <v>7087225</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25464,10 +25464,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>128423618</v>
+        <v>128423606</v>
       </c>
       <c r="B248" t="n">
-        <v>91565</v>
+        <v>80149</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -25475,19 +25475,23 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H248" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
@@ -25495,10 +25499,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>634676</v>
+        <v>635122</v>
       </c>
       <c r="R248" t="n">
-        <v>7087616</v>
+        <v>7087242</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25557,34 +25561,30 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>128423575</v>
+        <v>128423618</v>
       </c>
       <c r="B249" t="n">
-        <v>91509</v>
+        <v>91569</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
@@ -25592,10 +25592,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>634574</v>
+        <v>634676</v>
       </c>
       <c r="R249" t="n">
-        <v>7087286</v>
+        <v>7087616</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25654,32 +25654,32 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>128423606</v>
+        <v>128423575</v>
       </c>
       <c r="B250" t="n">
-        <v>80149</v>
+        <v>91513</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -25689,10 +25689,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>635122</v>
+        <v>634574</v>
       </c>
       <c r="R250" t="n">
-        <v>7087242</v>
+        <v>7087286</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -25751,32 +25751,32 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>128423615</v>
+        <v>128423628</v>
       </c>
       <c r="B251" t="n">
-        <v>91559</v>
+        <v>80184</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>1204</v>
+        <v>6463</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -25786,10 +25786,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>634897</v>
+        <v>635451</v>
       </c>
       <c r="R251" t="n">
-        <v>7087591</v>
+        <v>7087225</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -25851,7 +25851,7 @@
         <v>128423624</v>
       </c>
       <c r="B252" t="n">
-        <v>88945</v>
+        <v>88949</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -25945,32 +25945,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>128423628</v>
+        <v>128423615</v>
       </c>
       <c r="B253" t="n">
-        <v>80184</v>
+        <v>91563</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>6463</v>
+        <v>1204</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -25980,10 +25980,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>635451</v>
+        <v>634897</v>
       </c>
       <c r="R253" t="n">
-        <v>7087225</v>
+        <v>7087591</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26042,34 +26042,30 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128423593</v>
+        <v>128423617</v>
       </c>
       <c r="B254" t="n">
-        <v>80178</v>
+        <v>91569</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr"/>
       <c r="I254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
@@ -26077,10 +26073,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>635471</v>
+        <v>634507</v>
       </c>
       <c r="R254" t="n">
-        <v>7087281</v>
+        <v>7087328</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26139,32 +26135,32 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>128423629</v>
+        <v>128423622</v>
       </c>
       <c r="B255" t="n">
-        <v>80184</v>
+        <v>88949</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>6463</v>
+        <v>510</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -26174,10 +26170,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>635454</v>
+        <v>634642</v>
       </c>
       <c r="R255" t="n">
-        <v>7087257</v>
+        <v>7087251</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26236,10 +26232,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>128423622</v>
+        <v>128423625</v>
       </c>
       <c r="B256" t="n">
-        <v>88945</v>
+        <v>88949</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -26271,10 +26267,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>634642</v>
+        <v>634494</v>
       </c>
       <c r="R256" t="n">
-        <v>7087251</v>
+        <v>7087408</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26333,32 +26329,32 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128423625</v>
+        <v>128423593</v>
       </c>
       <c r="B257" t="n">
-        <v>88945</v>
+        <v>80178</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>510</v>
+        <v>6462</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -26368,10 +26364,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>634494</v>
+        <v>635471</v>
       </c>
       <c r="R257" t="n">
-        <v>7087408</v>
+        <v>7087281</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -26430,30 +26426,34 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128423617</v>
+        <v>128423629</v>
       </c>
       <c r="B258" t="n">
-        <v>91565</v>
+        <v>80184</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H258" t="inlineStr"/>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
@@ -26461,10 +26461,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>634507</v>
+        <v>635454</v>
       </c>
       <c r="R258" t="n">
-        <v>7087328</v>
+        <v>7087257</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -26526,7 +26526,7 @@
         <v>128423626</v>
       </c>
       <c r="B259" t="n">
-        <v>88945</v>
+        <v>88949</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -26623,7 +26623,7 @@
         <v>128423585</v>
       </c>
       <c r="B260" t="n">
-        <v>92263</v>
+        <v>92267</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -26717,32 +26717,32 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128423619</v>
+        <v>128423577</v>
       </c>
       <c r="B261" t="n">
-        <v>79044</v>
+        <v>91513</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -26752,10 +26752,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>635513</v>
+        <v>635153</v>
       </c>
       <c r="R261" t="n">
-        <v>7087316</v>
+        <v>7087180</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26790,18 +26790,12 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC261" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD261" t="b">
         <v>0</v>
       </c>
       <c r="AE261" t="b">
         <v>0</v>
       </c>
-      <c r="AF261" t="inlineStr"/>
       <c r="AG261" t="b">
         <v>0</v>
       </c>
@@ -26820,10 +26814,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128423620</v>
+        <v>128423616</v>
       </c>
       <c r="B262" t="n">
-        <v>79044</v>
+        <v>91569</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -26831,23 +26825,19 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr"/>
       <c r="I262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
@@ -26855,10 +26845,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>634756</v>
+        <v>634993</v>
       </c>
       <c r="R262" t="n">
-        <v>7087642</v>
+        <v>7087294</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -26917,32 +26907,32 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>128423594</v>
+        <v>128423619</v>
       </c>
       <c r="B263" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -26952,10 +26942,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>634527</v>
+        <v>635513</v>
       </c>
       <c r="R263" t="n">
-        <v>7087301</v>
+        <v>7087316</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -26990,12 +26980,18 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="AC263" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD263" t="b">
         <v>0</v>
       </c>
       <c r="AE263" t="b">
         <v>0</v>
       </c>
+      <c r="AF263" t="inlineStr"/>
       <c r="AG263" t="b">
         <v>0</v>
       </c>
@@ -27014,32 +27010,32 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>128423577</v>
+        <v>128423620</v>
       </c>
       <c r="B264" t="n">
-        <v>91509</v>
+        <v>79044</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -27049,10 +27045,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>635153</v>
+        <v>634756</v>
       </c>
       <c r="R264" t="n">
-        <v>7087180</v>
+        <v>7087642</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27111,30 +27107,34 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>128423616</v>
+        <v>128423594</v>
       </c>
       <c r="B265" t="n">
-        <v>91565</v>
+        <v>80178</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H265" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
@@ -27142,10 +27142,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>634993</v>
+        <v>634527</v>
       </c>
       <c r="R265" t="n">
-        <v>7087294</v>
+        <v>7087301</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27207,7 +27207,7 @@
         <v>128492197</v>
       </c>
       <c r="B266" t="n">
-        <v>95938</v>
+        <v>95942</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -27306,10 +27306,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>128423602</v>
+        <v>128423607</v>
       </c>
       <c r="B267" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -27317,21 +27317,21 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -27341,10 +27341,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>635210</v>
+        <v>635459</v>
       </c>
       <c r="R267" t="n">
-        <v>7087158</v>
+        <v>7087231</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -27377,11 +27377,6 @@
       <c r="AA267" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC267" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -27408,32 +27403,32 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>128423607</v>
+        <v>128423578</v>
       </c>
       <c r="B268" t="n">
-        <v>80149</v>
+        <v>91513</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -27443,10 +27438,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>635459</v>
+        <v>635327</v>
       </c>
       <c r="R268" t="n">
-        <v>7087231</v>
+        <v>7087158</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -27505,32 +27500,32 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>128423578</v>
+        <v>128423602</v>
       </c>
       <c r="B269" t="n">
-        <v>91509</v>
+        <v>57727</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -27540,7 +27535,7 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>635327</v>
+        <v>635210</v>
       </c>
       <c r="R269" t="n">
         <v>7087158</v>
@@ -27576,6 +27571,11 @@
       <c r="AA269" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -27605,7 +27605,7 @@
         <v>128423572</v>
       </c>
       <c r="B270" t="n">
-        <v>96958</v>
+        <v>96962</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -27699,32 +27699,32 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>128423614</v>
+        <v>128423576</v>
       </c>
       <c r="B271" t="n">
-        <v>91559</v>
+        <v>91513</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
@@ -27734,10 +27734,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>634673</v>
+        <v>634705</v>
       </c>
       <c r="R271" t="n">
-        <v>7087631</v>
+        <v>7087668</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -27796,32 +27796,32 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>128423576</v>
+        <v>128423614</v>
       </c>
       <c r="B272" t="n">
-        <v>91509</v>
+        <v>91563</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
@@ -27831,10 +27831,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>634705</v>
+        <v>634673</v>
       </c>
       <c r="R272" t="n">
-        <v>7087668</v>
+        <v>7087631</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -28096,32 +28096,32 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>128423599</v>
+        <v>128423598</v>
       </c>
       <c r="B275" t="n">
-        <v>91998</v>
+        <v>80150</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>1209</v>
+        <v>2081</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -28131,10 +28131,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>635464</v>
+        <v>635632</v>
       </c>
       <c r="R275" t="n">
-        <v>7087275</v>
+        <v>7087270</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -28193,32 +28193,32 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>128423598</v>
+        <v>128423599</v>
       </c>
       <c r="B276" t="n">
-        <v>80150</v>
+        <v>92002</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>2081</v>
+        <v>1209</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -28228,10 +28228,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>635632</v>
+        <v>635464</v>
       </c>
       <c r="R276" t="n">
-        <v>7087270</v>
+        <v>7087275</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -28293,7 +28293,7 @@
         <v>128423604</v>
       </c>
       <c r="B277" t="n">
-        <v>95938</v>
+        <v>95942</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -28390,7 +28390,7 @@
         <v>128423590</v>
       </c>
       <c r="B278" t="n">
-        <v>92819</v>
+        <v>92823</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -28681,7 +28681,7 @@
         <v>128423580</v>
       </c>
       <c r="B281" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -28778,7 +28778,7 @@
         <v>128423579</v>
       </c>
       <c r="B282" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>128423601</v>
       </c>
       <c r="B284" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>128423574</v>
       </c>
       <c r="B285" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
         <v>128423613</v>
       </c>
       <c r="B286" t="n">
-        <v>91559</v>
+        <v>91563</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>

--- a/artfynd/A 30047-2025 artfynd.xlsx
+++ b/artfynd/A 30047-2025 artfynd.xlsx
@@ -24400,7 +24400,7 @@
         <v>128651017</v>
       </c>
       <c r="B237" t="n">
-        <v>97057</v>
+        <v>97065</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>128651018</v>
       </c>
       <c r="B238" t="n">
-        <v>95954</v>
+        <v>95962</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24591,10 +24591,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>128423605</v>
+        <v>128423582</v>
       </c>
       <c r="B239" t="n">
-        <v>80149</v>
+        <v>91845</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -24602,21 +24602,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>6458</v>
+        <v>73</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -24626,10 +24626,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>635331</v>
+        <v>635466</v>
       </c>
       <c r="R239" t="n">
-        <v>7087194</v>
+        <v>7087277</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24688,7 +24688,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>128423608</v>
+        <v>128423605</v>
       </c>
       <c r="B240" t="n">
         <v>80149</v>
@@ -24723,10 +24723,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>635603</v>
+        <v>635331</v>
       </c>
       <c r="R240" t="n">
-        <v>7087226</v>
+        <v>7087194</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24785,10 +24785,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>128423582</v>
+        <v>128423608</v>
       </c>
       <c r="B241" t="n">
-        <v>91844</v>
+        <v>80149</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24796,21 +24796,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>73</v>
+        <v>6458</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -24820,10 +24820,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>635466</v>
+        <v>635603</v>
       </c>
       <c r="R241" t="n">
-        <v>7087277</v>
+        <v>7087226</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -24882,32 +24882,32 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>128423573</v>
+        <v>128423623</v>
       </c>
       <c r="B242" t="n">
-        <v>91513</v>
+        <v>88950</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -24917,10 +24917,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>634599</v>
+        <v>634583</v>
       </c>
       <c r="R242" t="n">
-        <v>7087225</v>
+        <v>7087261</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24979,32 +24979,32 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>128423623</v>
+        <v>128423573</v>
       </c>
       <c r="B243" t="n">
-        <v>88949</v>
+        <v>91514</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -25014,10 +25014,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>634583</v>
+        <v>634599</v>
       </c>
       <c r="R243" t="n">
-        <v>7087261</v>
+        <v>7087225</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25173,32 +25173,32 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>128423597</v>
+        <v>128423591</v>
       </c>
       <c r="B245" t="n">
-        <v>57724</v>
+        <v>80178</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -25208,10 +25208,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>634913</v>
+        <v>635451</v>
       </c>
       <c r="R245" t="n">
-        <v>7087585</v>
+        <v>7087225</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25270,32 +25270,32 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>128423591</v>
+        <v>128423597</v>
       </c>
       <c r="B246" t="n">
-        <v>80178</v>
+        <v>57724</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -25305,10 +25305,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>635451</v>
+        <v>634913</v>
       </c>
       <c r="R246" t="n">
-        <v>7087225</v>
+        <v>7087585</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25464,10 +25464,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>128423606</v>
+        <v>128423618</v>
       </c>
       <c r="B248" t="n">
-        <v>80149</v>
+        <v>91570</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -25475,23 +25475,19 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr"/>
       <c r="I248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
@@ -25499,10 +25495,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>635122</v>
+        <v>634676</v>
       </c>
       <c r="R248" t="n">
-        <v>7087242</v>
+        <v>7087616</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25561,30 +25557,34 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>128423618</v>
+        <v>128423575</v>
       </c>
       <c r="B249" t="n">
-        <v>91569</v>
+        <v>91514</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr"/>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
       <c r="I249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
@@ -25592,10 +25592,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>634676</v>
+        <v>634574</v>
       </c>
       <c r="R249" t="n">
-        <v>7087616</v>
+        <v>7087286</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25654,32 +25654,32 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>128423575</v>
+        <v>128423606</v>
       </c>
       <c r="B250" t="n">
-        <v>91513</v>
+        <v>80149</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -25689,10 +25689,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>634574</v>
+        <v>635122</v>
       </c>
       <c r="R250" t="n">
-        <v>7087286</v>
+        <v>7087242</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -25751,32 +25751,32 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>128423628</v>
+        <v>128423624</v>
       </c>
       <c r="B251" t="n">
-        <v>80184</v>
+        <v>88950</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>6463</v>
+        <v>510</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -25786,10 +25786,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>635451</v>
+        <v>634461</v>
       </c>
       <c r="R251" t="n">
-        <v>7087225</v>
+        <v>7087363</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -25848,10 +25848,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>128423624</v>
+        <v>128423615</v>
       </c>
       <c r="B252" t="n">
-        <v>88949</v>
+        <v>91564</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -25859,21 +25859,21 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>510</v>
+        <v>1204</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -25883,10 +25883,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>634461</v>
+        <v>634897</v>
       </c>
       <c r="R252" t="n">
-        <v>7087363</v>
+        <v>7087591</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -25945,32 +25945,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>128423615</v>
+        <v>128423628</v>
       </c>
       <c r="B253" t="n">
-        <v>91563</v>
+        <v>80184</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>1204</v>
+        <v>6463</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -25980,10 +25980,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>634897</v>
+        <v>635451</v>
       </c>
       <c r="R253" t="n">
-        <v>7087591</v>
+        <v>7087225</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26042,10 +26042,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128423617</v>
+        <v>128423625</v>
       </c>
       <c r="B254" t="n">
-        <v>91569</v>
+        <v>88950</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -26053,19 +26053,23 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H254" t="inlineStr"/>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
       <c r="I254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
@@ -26073,10 +26077,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>634507</v>
+        <v>634494</v>
       </c>
       <c r="R254" t="n">
-        <v>7087328</v>
+        <v>7087408</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26135,10 +26139,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>128423622</v>
+        <v>128423617</v>
       </c>
       <c r="B255" t="n">
-        <v>88949</v>
+        <v>91570</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -26146,23 +26150,19 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
-        </is>
-      </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr"/>
       <c r="I255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
@@ -26170,10 +26170,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>634642</v>
+        <v>634507</v>
       </c>
       <c r="R255" t="n">
-        <v>7087251</v>
+        <v>7087328</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26232,10 +26232,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>128423625</v>
+        <v>128423622</v>
       </c>
       <c r="B256" t="n">
-        <v>88949</v>
+        <v>88950</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -26267,10 +26267,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>634494</v>
+        <v>634642</v>
       </c>
       <c r="R256" t="n">
-        <v>7087408</v>
+        <v>7087251</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26526,7 +26526,7 @@
         <v>128423626</v>
       </c>
       <c r="B259" t="n">
-        <v>88949</v>
+        <v>88950</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -26623,7 +26623,7 @@
         <v>128423585</v>
       </c>
       <c r="B260" t="n">
-        <v>92267</v>
+        <v>92268</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>128423577</v>
       </c>
       <c r="B261" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -26814,30 +26814,34 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128423616</v>
+        <v>128423594</v>
       </c>
       <c r="B262" t="n">
-        <v>91569</v>
+        <v>80178</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H262" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
@@ -26845,10 +26849,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>634993</v>
+        <v>634527</v>
       </c>
       <c r="R262" t="n">
-        <v>7087294</v>
+        <v>7087301</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27107,34 +27111,30 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>128423594</v>
+        <v>128423616</v>
       </c>
       <c r="B265" t="n">
-        <v>80178</v>
+        <v>91570</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr"/>
       <c r="I265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
@@ -27142,10 +27142,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>634527</v>
+        <v>634993</v>
       </c>
       <c r="R265" t="n">
-        <v>7087301</v>
+        <v>7087294</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27207,7 +27207,7 @@
         <v>128492197</v>
       </c>
       <c r="B266" t="n">
-        <v>95942</v>
+        <v>95950</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -27306,10 +27306,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>128423607</v>
+        <v>128423602</v>
       </c>
       <c r="B267" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -27317,21 +27317,21 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -27341,10 +27341,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>635459</v>
+        <v>635210</v>
       </c>
       <c r="R267" t="n">
-        <v>7087231</v>
+        <v>7087158</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -27377,6 +27377,11 @@
       <c r="AA267" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC267" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -27406,7 +27411,7 @@
         <v>128423578</v>
       </c>
       <c r="B268" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -27500,10 +27505,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>128423602</v>
+        <v>128423607</v>
       </c>
       <c r="B269" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -27511,21 +27516,21 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -27535,10 +27540,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>635210</v>
+        <v>635459</v>
       </c>
       <c r="R269" t="n">
-        <v>7087158</v>
+        <v>7087231</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -27571,11 +27576,6 @@
       <c r="AA269" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC269" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -27605,7 +27605,7 @@
         <v>128423572</v>
       </c>
       <c r="B270" t="n">
-        <v>96962</v>
+        <v>96970</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -27702,7 +27702,7 @@
         <v>128423576</v>
       </c>
       <c r="B271" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -27796,10 +27796,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>128423614</v>
+        <v>128423603</v>
       </c>
       <c r="B272" t="n">
-        <v>91563</v>
+        <v>57727</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -27807,34 +27807,38 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="inlineStr"/>
+      <c r="N272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>634673</v>
+        <v>635240</v>
       </c>
       <c r="R272" t="n">
-        <v>7087631</v>
+        <v>7087224</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -27867,6 +27871,11 @@
       <c r="AA272" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC272" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -27893,10 +27902,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>128423603</v>
+        <v>128423614</v>
       </c>
       <c r="B273" t="n">
-        <v>57727</v>
+        <v>91564</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -27904,38 +27913,34 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="inlineStr"/>
-      <c r="N273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>635240</v>
+        <v>634673</v>
       </c>
       <c r="R273" t="n">
-        <v>7087224</v>
+        <v>7087631</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -27968,11 +27973,6 @@
       <c r="AA273" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC273" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -27999,32 +27999,32 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>128423592</v>
+        <v>128423599</v>
       </c>
       <c r="B274" t="n">
-        <v>80178</v>
+        <v>92003</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>6462</v>
+        <v>1209</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -28034,10 +28034,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>635454</v>
+        <v>635464</v>
       </c>
       <c r="R274" t="n">
-        <v>7087257</v>
+        <v>7087275</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28096,32 +28096,32 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>128423598</v>
+        <v>128423592</v>
       </c>
       <c r="B275" t="n">
-        <v>80150</v>
+        <v>80178</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -28131,10 +28131,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>635632</v>
+        <v>635454</v>
       </c>
       <c r="R275" t="n">
-        <v>7087270</v>
+        <v>7087257</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -28193,32 +28193,32 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>128423599</v>
+        <v>128423598</v>
       </c>
       <c r="B276" t="n">
-        <v>92002</v>
+        <v>80150</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>1209</v>
+        <v>2081</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -28228,10 +28228,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>635464</v>
+        <v>635632</v>
       </c>
       <c r="R276" t="n">
-        <v>7087275</v>
+        <v>7087270</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -28293,7 +28293,7 @@
         <v>128423604</v>
       </c>
       <c r="B277" t="n">
-        <v>95942</v>
+        <v>95950</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -28390,7 +28390,7 @@
         <v>128423590</v>
       </c>
       <c r="B278" t="n">
-        <v>92823</v>
+        <v>92824</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -28681,7 +28681,7 @@
         <v>128423580</v>
       </c>
       <c r="B281" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -28778,7 +28778,7 @@
         <v>128423579</v>
       </c>
       <c r="B282" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -28969,32 +28969,32 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>128423601</v>
+        <v>128423574</v>
       </c>
       <c r="B284" t="n">
-        <v>91847</v>
+        <v>91514</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -29004,10 +29004,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>634475</v>
+        <v>634571</v>
       </c>
       <c r="R284" t="n">
-        <v>7087365</v>
+        <v>7087253</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -29066,32 +29066,32 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>128423574</v>
+        <v>128423601</v>
       </c>
       <c r="B285" t="n">
-        <v>91513</v>
+        <v>91848</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -29101,10 +29101,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>634571</v>
+        <v>634475</v>
       </c>
       <c r="R285" t="n">
-        <v>7087253</v>
+        <v>7087365</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -29166,7 +29166,7 @@
         <v>128423613</v>
       </c>
       <c r="B286" t="n">
-        <v>91563</v>
+        <v>91564</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>

--- a/artfynd/A 30047-2025 artfynd.xlsx
+++ b/artfynd/A 30047-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY280"/>
+  <dimension ref="A1:AZ280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423088</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423572</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119258737</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423582</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423112</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423087</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428594</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428595</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428596</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1646,6 +1696,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113161648</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1743,6 +1798,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113161653</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1840,6 +1900,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253475</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1937,6 +2002,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253481</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2034,6 +2104,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253484</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2131,6 +2206,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253486</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2232,6 +2312,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119258743</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2333,6 +2418,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119258763</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2434,6 +2524,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119258764</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2541,6 +2636,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128411777</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2638,6 +2738,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423190</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2735,6 +2840,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423191</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2832,6 +2942,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423192</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2929,6 +3044,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423193</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3026,6 +3146,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423622</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3123,6 +3248,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423623</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3220,6 +3350,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423624</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3317,6 +3452,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423625</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3414,6 +3554,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423626</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3511,6 +3656,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428589</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3608,6 +3758,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428590</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3709,6 +3864,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119258745</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3816,6 +3976,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128412855</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3913,6 +4078,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423600</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4010,6 +4180,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423601</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4107,6 +4282,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253458</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4204,6 +4384,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253485</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4305,6 +4490,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119258742</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4402,6 +4592,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423096</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4499,6 +4694,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423097</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4596,6 +4796,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423098</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4693,6 +4898,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428532</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4790,6 +5000,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117862166</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4897,6 +5112,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128409243</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4994,6 +5214,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423147</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5091,6 +5316,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423148</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5188,6 +5418,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423149</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5285,6 +5520,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423613</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5382,6 +5622,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423614</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5479,6 +5724,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423615</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5576,6 +5826,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428568</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5673,6 +5928,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423111</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5770,6 +6030,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423599</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5867,6 +6132,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253452</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5964,6 +6234,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253482</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6065,6 +6340,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119258760</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6166,6 +6446,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119258761</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6263,6 +6548,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423621</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6360,6 +6650,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428581</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6457,6 +6752,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428582</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6554,6 +6854,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428583</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6651,6 +6956,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428584</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6748,6 +7058,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428585</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6845,6 +7160,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128651017</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6942,6 +7262,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423113</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7039,6 +7364,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423598</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7136,6 +7466,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428554</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7233,6 +7568,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423604</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7335,6 +7675,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128492197</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7437,6 +7782,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128492196</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7534,6 +7884,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113161649</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7631,6 +7986,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423099</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7728,6 +8088,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423584</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7825,6 +8190,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423585</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7922,6 +8292,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428533</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8019,6 +8394,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423590</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8116,6 +8496,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253454</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8213,6 +8598,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253461</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8310,6 +8700,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253463</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8407,6 +8802,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253464</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8504,6 +8904,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253468</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8601,6 +9006,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253471</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8698,6 +9108,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253473</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8795,6 +9210,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253474</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8896,6 +9316,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119258732</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8997,6 +9422,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119258733</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9094,6 +9524,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113161654</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9191,6 +9626,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253465</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9288,6 +9728,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253469</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9385,6 +9830,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253476</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9482,6 +9932,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253479</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9579,6 +10034,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253483</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9676,6 +10136,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253488</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9783,6 +10248,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128409160</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9890,6 +10360,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128411934</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9987,6 +10462,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423089</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10084,6 +10564,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423090</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10181,6 +10666,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423091</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10278,6 +10768,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423092</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10375,6 +10870,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423093</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10472,6 +10972,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423094</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10569,6 +11074,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423573</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10666,6 +11176,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423574</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10763,6 +11278,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423575</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10860,6 +11380,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423576</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10957,6 +11482,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423577</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11054,6 +11584,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423578</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11151,6 +11686,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423579</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11248,6 +11788,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423580</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11345,6 +11890,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428529</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11442,6 +11992,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428530</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11539,6 +12094,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428531</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11636,6 +12196,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113161652</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11733,6 +12298,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253459</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11830,6 +12400,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253467</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11927,6 +12502,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253477</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12039,6 +12619,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128404271</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12151,6 +12736,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128404427</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12263,6 +12853,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128405478</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12370,6 +12965,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128407951</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12477,6 +13077,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128410776</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12574,6 +13179,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423154</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12671,6 +13281,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423155</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12768,6 +13383,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423156</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12865,6 +13485,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423157</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12962,6 +13587,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423158</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13059,6 +13689,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423159</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13156,6 +13791,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423160</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13253,6 +13893,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423161</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13350,6 +13995,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423162</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13447,6 +14097,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423163</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13544,6 +14199,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423165</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13641,6 +14301,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423166</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13738,6 +14403,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423167</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13835,6 +14505,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423168</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -13932,6 +14607,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423170</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14029,6 +14709,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423171</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14126,6 +14811,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423172</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14223,6 +14913,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423173</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14320,6 +15015,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423174</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14417,6 +15117,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423175</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14514,6 +15219,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423176</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14611,6 +15321,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423177</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14708,6 +15423,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423178</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -14805,6 +15525,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423179</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -14902,6 +15627,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423180</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -14999,6 +15729,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423181</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15096,6 +15831,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423183</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15193,6 +15933,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423184</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15290,6 +16035,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423185</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15387,6 +16137,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423186</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15484,6 +16239,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423187</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15581,6 +16341,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423188</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -15678,6 +16443,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423189</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -15781,6 +16551,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423619</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -15878,6 +16653,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423620</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -15975,6 +16755,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428571</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16072,6 +16857,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428572</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16169,6 +16959,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428573</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16266,6 +17061,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428574</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16363,6 +17163,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428575</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16460,6 +17265,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428577</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16557,6 +17367,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428578</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -16654,6 +17469,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428579</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -16751,6 +17571,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428580</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -16848,6 +17673,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423126</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -16945,6 +17775,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423127</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17042,6 +17877,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428557</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17139,6 +17979,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428567</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17236,6 +18081,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113161650</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17333,6 +18183,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113161659</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -17436,6 +18291,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428564</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -17533,6 +18393,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113161662</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -17630,6 +18495,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113161663</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -17727,6 +18597,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253462</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -17828,6 +18703,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119258747</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -17935,6 +18815,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128405308</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -18042,6 +18927,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128406204</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -18154,6 +19044,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423130</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -18251,6 +19146,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423131</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -18348,6 +19248,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423132</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -18445,6 +19350,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423133</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -18542,6 +19452,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423134</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -18639,6 +19554,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423135</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -18736,6 +19656,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423136</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -18833,6 +19758,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423137</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -18930,6 +19860,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423605</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -19027,6 +19962,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423606</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -19124,6 +20064,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423607</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -19221,6 +20166,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423608</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -19318,6 +20268,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428558</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -19415,6 +20370,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428559</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -19512,6 +20472,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423128</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -19609,6 +20574,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423129</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -19710,6 +20680,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119258736</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -19811,6 +20786,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119258740</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -19912,6 +20892,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119258741</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -20019,6 +21004,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128408809</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -20126,6 +21116,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128409643</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -20223,6 +21218,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423104</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -20320,6 +21320,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423105</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -20417,6 +21422,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423106</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -20514,6 +21524,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423107</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -20611,6 +21626,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423108</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -20708,6 +21728,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423109</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -20805,6 +21830,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423110</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -20902,6 +21932,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423591</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -20999,6 +22034,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423592</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -21096,6 +22136,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423593</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -21193,6 +22238,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423594</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -21290,6 +22340,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423595</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -21387,6 +22442,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428544</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -21484,6 +22544,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428545</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -21581,6 +22646,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428546</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -21678,6 +22748,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428547</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -21775,6 +22850,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428549</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -21872,6 +22952,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253453</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -21969,6 +23054,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423194</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -22066,6 +23156,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423195</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -22163,6 +23258,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423628</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -22260,6 +23360,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423629</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -22357,6 +23462,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428592</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -22454,6 +23564,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428593</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -22551,6 +23666,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423138</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -22648,6 +23768,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423139</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -22745,6 +23870,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423140</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -22842,6 +23972,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423141</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -22939,6 +24074,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423142</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -23036,6 +24176,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428561</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -23133,6 +24278,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428562</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -23235,6 +24385,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253466</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -23350,6 +24505,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128412839</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -23447,6 +24607,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423596</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -23544,6 +24709,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423597</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -23649,6 +24819,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428550</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -23754,6 +24929,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428551</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -23859,6 +25039,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428552</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -23969,6 +25154,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428553</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -24071,6 +25261,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113161657</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -24173,6 +25368,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113161661</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -24293,6 +25493,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128411527</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -24413,6 +25618,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128413141</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -24515,6 +25725,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423085</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -24617,6 +25832,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423114</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -24719,6 +25939,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423115</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -24821,6 +26046,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423116</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -24938,6 +26168,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423117</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -25055,6 +26290,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423118</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -25157,6 +26397,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423119</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -25263,6 +26508,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423120</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -25365,6 +26615,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423121</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -25467,6 +26722,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423198</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -25573,6 +26833,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423199</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -25675,6 +26940,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423200</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -25777,6 +27047,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423602</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -25883,6 +27158,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423603</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -25993,6 +27273,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428534</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -26103,6 +27388,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428535</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -26213,6 +27503,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428536</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -26323,6 +27618,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428537</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -26433,6 +27733,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428556</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -26540,6 +27845,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128409304</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -26637,6 +27947,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423586</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -26746,6 +28061,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253478</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -26855,6 +28175,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119258746</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -26952,6 +28277,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423612</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -27061,6 +28391,11 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428565</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -27158,6 +28493,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428566</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -27260,6 +28600,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113161656</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -27375,6 +28720,11 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128411794</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -27472,6 +28822,11 @@
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423101</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -27569,6 +28924,11 @@
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423588</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -27670,6 +29030,11 @@
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428540</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -27767,6 +29132,11 @@
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428541</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -27864,6 +29234,11 @@
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428542</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -27961,6 +29336,11 @@
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428543</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -28082,6 +29462,11 @@
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128409844</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -28179,6 +29564,11 @@
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428563</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -28276,6 +29666,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423122</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -28377,8 +29772,294 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119258754</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27